--- a/plantillas/excel_base.xlsx
+++ b/plantillas/excel_base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\estudiante\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD95B73-FC1D-4BA5-97CB-7F0EB48FAFC2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CBA6895-9165-443A-9925-ACD627348C03}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" tabRatio="570" xr2:uid="{73D17D42-2032-4221-9DBF-D2EB2D99B5D8}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="86">
   <si>
     <t>MODIFICACIÓN EN ASIGNATURAS DE LA MALLA CURRICULAR</t>
   </si>
@@ -92,43 +92,7 @@
     <t>AA</t>
   </si>
   <si>
-    <t>COD10000</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>SE ELIMINA POR REDISTRIBUCIÓN DE CONTENIDOS RELEVANTES EN OTRAS ASIGNATURAS. NO SE ALTERA EL PERFIL DE EGRESO.</t>
-  </si>
-  <si>
-    <t>COD10001</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>COD10002</t>
-  </si>
-  <si>
-    <t>Z</t>
-  </si>
-  <si>
-    <t>COD10003</t>
-  </si>
-  <si>
     <t>A</t>
-  </si>
-  <si>
-    <t>COD10004</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>COD10005</t>
-  </si>
-  <si>
-    <t>C</t>
   </si>
   <si>
     <t>MALLA CURRICULAR PROPUESTA</t>
@@ -459,7 +423,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -605,42 +569,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -689,57 +622,96 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -797,74 +769,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1327,1090 +1233,228 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ACDF5BE-B64F-40C3-9167-0581D119B289}">
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.42578125" style="76" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" style="76" customWidth="1"/>
-    <col min="4" max="4" width="14" style="76" customWidth="1"/>
-    <col min="5" max="5" width="3.42578125" style="75" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" style="76" customWidth="1"/>
-    <col min="7" max="7" width="4.28515625" style="82" customWidth="1"/>
-    <col min="8" max="8" width="18.5703125" style="82" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22" style="82" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.28515625" style="76" customWidth="1"/>
-    <col min="11" max="11" width="5.85546875" style="82" customWidth="1"/>
-    <col min="12" max="12" width="18.5703125" style="82" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22" style="82" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="47.7109375" style="76" customWidth="1"/>
-    <col min="15" max="256" width="11.42578125" style="76" customWidth="1"/>
-    <col min="257" max="16384" width="9.140625" style="76"/>
+    <col min="1" max="2" width="11.42578125" style="27" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" style="27" customWidth="1"/>
+    <col min="4" max="4" width="14" style="27" customWidth="1"/>
+    <col min="5" max="5" width="3.42578125" style="26" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" style="27" customWidth="1"/>
+    <col min="7" max="7" width="4.28515625" style="31" customWidth="1"/>
+    <col min="8" max="8" width="18.5703125" style="31" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22" style="31" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.28515625" style="27" customWidth="1"/>
+    <col min="11" max="11" width="5.85546875" style="31" customWidth="1"/>
+    <col min="12" max="12" width="18.5703125" style="31" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22" style="31" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="47.7109375" style="27" customWidth="1"/>
+    <col min="15" max="256" width="11.42578125" style="73" customWidth="1"/>
+    <col min="257" max="16384" width="9.140625" style="73"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
+      <c r="A1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
     </row>
     <row r="2" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
+      <c r="A2" s="38"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
     </row>
     <row r="3" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="69" t="s">
+      <c r="B3" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="69" t="s">
+      <c r="C3" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="70" t="s">
+      <c r="D3" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="70"/>
-      <c r="K3" s="70"/>
-      <c r="L3" s="70"/>
-      <c r="M3" s="70"/>
-      <c r="N3" s="70"/>
-    </row>
-    <row r="4" spans="1:14" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="36"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="36"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="60" t="s">
+      <c r="B4" s="32"/>
+      <c r="C4" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="77" t="s">
+      <c r="D4" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="74" t="s">
+      <c r="E4" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="78" t="s">
+      <c r="F4" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="78"/>
-      <c r="H4" s="79" t="s">
+      <c r="G4" s="34"/>
+      <c r="H4" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="79" t="s">
+      <c r="I4" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="78" t="s">
+      <c r="J4" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="78"/>
-      <c r="L4" s="79" t="s">
+      <c r="K4" s="34"/>
+      <c r="L4" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="79" t="s">
+      <c r="M4" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="N4" s="79" t="s">
+      <c r="N4" s="29" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="80" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="25"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="77" t="s">
+    <row r="5" spans="1:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="32"/>
+      <c r="B5" s="32"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="74"/>
-      <c r="F5" s="81" t="s">
+      <c r="E5" s="25"/>
+      <c r="F5" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G5" s="23">
         <v>3</v>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="32">
         <f>(G5+G6+G7)*16</f>
         <v>144</v>
       </c>
-      <c r="I5" s="61">
+      <c r="I5" s="37">
         <f>H5/48</f>
         <v>3</v>
       </c>
-      <c r="J5" s="81" t="s">
+      <c r="J5" s="30" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="23">
         <v>4</v>
       </c>
-      <c r="L5" s="25">
+      <c r="L5" s="32">
         <f>(K5+K6+K7)*16</f>
         <v>144</v>
       </c>
-      <c r="M5" s="61">
+      <c r="M5" s="37">
         <f>L5/48</f>
         <v>3</v>
       </c>
-      <c r="N5" s="62" t="s">
+      <c r="N5" s="35" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="25"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="77" t="s">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="32"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="74"/>
-      <c r="F6" s="81" t="s">
+      <c r="E6" s="25"/>
+      <c r="F6" s="30" t="s">
         <v>18</v>
       </c>
       <c r="G6" s="23">
         <v>2</v>
       </c>
-      <c r="H6" s="25"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="81" t="s">
+      <c r="H6" s="32"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="30" t="s">
         <v>18</v>
       </c>
       <c r="K6" s="23">
         <v>1</v>
       </c>
-      <c r="L6" s="25"/>
-      <c r="M6" s="61"/>
-      <c r="N6" s="62"/>
-    </row>
-    <row r="7" spans="1:14" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="25"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="60"/>
-      <c r="D7" s="77" t="s">
+      <c r="L6" s="32"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="35"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="32"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="74"/>
-      <c r="F7" s="81" t="s">
+      <c r="E7" s="25"/>
+      <c r="F7" s="30" t="s">
         <v>20</v>
       </c>
       <c r="G7" s="23">
         <v>4</v>
       </c>
-      <c r="H7" s="25"/>
-      <c r="I7" s="61"/>
-      <c r="J7" s="81" t="s">
+      <c r="H7" s="32"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="30" t="s">
         <v>20</v>
       </c>
       <c r="K7" s="23">
         <v>4</v>
       </c>
-      <c r="L7" s="25"/>
-      <c r="M7" s="61"/>
-      <c r="N7" s="62"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="71"/>
-      <c r="B8" s="72"/>
-      <c r="C8" s="72"/>
-      <c r="D8" s="72"/>
-      <c r="E8" s="72"/>
-      <c r="F8" s="72"/>
-      <c r="G8" s="72"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="72"/>
-      <c r="J8" s="72"/>
-      <c r="K8" s="72"/>
-      <c r="L8" s="72"/>
-      <c r="M8" s="72"/>
-      <c r="N8" s="73"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="25"/>
-      <c r="C9" s="60" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="77" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="74"/>
-      <c r="F9" s="78" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="78"/>
-      <c r="H9" s="79" t="s">
-        <v>10</v>
-      </c>
-      <c r="I9" s="79" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="78" t="s">
-        <v>12</v>
-      </c>
-      <c r="K9" s="78"/>
-      <c r="L9" s="79" t="s">
-        <v>10</v>
-      </c>
-      <c r="M9" s="79" t="s">
-        <v>11</v>
-      </c>
-      <c r="N9" s="79" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="60"/>
-      <c r="D10" s="77" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="74" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="81" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="23">
-        <v>2</v>
-      </c>
-      <c r="H10" s="25">
-        <f>(G10+G11+G12)*16</f>
-        <v>96</v>
-      </c>
-      <c r="I10" s="61">
-        <f>H10/48</f>
-        <v>2</v>
-      </c>
-      <c r="J10" s="81" t="s">
-        <v>15</v>
-      </c>
-      <c r="K10" s="23">
-        <v>0</v>
-      </c>
-      <c r="L10" s="25">
-        <f>(K10+K11+K12)*16</f>
-        <v>0</v>
-      </c>
-      <c r="M10" s="61">
-        <f>L10/48</f>
-        <v>0</v>
-      </c>
-      <c r="N10" s="62" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="25"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="60"/>
-      <c r="D11" s="77" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="74"/>
-      <c r="F11" s="81" t="s">
-        <v>18</v>
-      </c>
-      <c r="G11" s="23">
-        <v>2</v>
-      </c>
-      <c r="H11" s="25"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="81" t="s">
-        <v>18</v>
-      </c>
-      <c r="K11" s="23">
-        <v>0</v>
-      </c>
-      <c r="L11" s="25"/>
-      <c r="M11" s="61"/>
-      <c r="N11" s="62"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="25"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="60"/>
-      <c r="D12" s="77" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="74"/>
-      <c r="F12" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="G12" s="23">
-        <v>2</v>
-      </c>
-      <c r="H12" s="25"/>
-      <c r="I12" s="61"/>
-      <c r="J12" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="K12" s="23">
-        <v>0</v>
-      </c>
-      <c r="L12" s="25"/>
-      <c r="M12" s="61"/>
-      <c r="N12" s="62"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="63"/>
-      <c r="B13" s="64"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="64"/>
-      <c r="K13" s="64"/>
-      <c r="L13" s="64"/>
-      <c r="M13" s="64"/>
-      <c r="N13" s="65"/>
-    </row>
-    <row r="14" spans="1:14" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="25"/>
-      <c r="C14" s="60" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="77" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="74"/>
-      <c r="F14" s="78" t="s">
-        <v>9</v>
-      </c>
-      <c r="G14" s="78"/>
-      <c r="H14" s="79" t="s">
-        <v>10</v>
-      </c>
-      <c r="I14" s="79" t="s">
-        <v>11</v>
-      </c>
-      <c r="J14" s="78" t="s">
-        <v>12</v>
-      </c>
-      <c r="K14" s="78"/>
-      <c r="L14" s="79" t="s">
-        <v>10</v>
-      </c>
-      <c r="M14" s="79" t="s">
-        <v>11</v>
-      </c>
-      <c r="N14" s="79" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="25"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="77" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="74"/>
-      <c r="F15" s="81" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" s="23"/>
-      <c r="H15" s="25">
-        <f>(G15+G16+G17)*16</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="61">
-        <f>H15/48</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="81" t="s">
-        <v>15</v>
-      </c>
-      <c r="K15" s="23"/>
-      <c r="L15" s="25">
-        <f>(K15+K16+K17)*16</f>
-        <v>0</v>
-      </c>
-      <c r="M15" s="61">
-        <f>L15/48</f>
-        <v>0</v>
-      </c>
-      <c r="N15" s="62"/>
-    </row>
-    <row r="16" spans="1:14" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="25"/>
-      <c r="B16" s="25"/>
-      <c r="C16" s="60"/>
-      <c r="D16" s="77" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="74"/>
-      <c r="F16" s="81" t="s">
-        <v>18</v>
-      </c>
-      <c r="G16" s="23"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="61"/>
-      <c r="J16" s="81" t="s">
-        <v>18</v>
-      </c>
-      <c r="K16" s="23"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="61"/>
-      <c r="N16" s="62"/>
-    </row>
-    <row r="17" spans="1:14" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="25"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="60"/>
-      <c r="D17" s="77" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" s="74"/>
-      <c r="F17" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="23"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="61"/>
-      <c r="J17" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="K17" s="23"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="61"/>
-      <c r="N17" s="62"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="66"/>
-      <c r="B18" s="67"/>
-      <c r="C18" s="67"/>
-      <c r="D18" s="67"/>
-      <c r="E18" s="67"/>
-      <c r="F18" s="67"/>
-      <c r="G18" s="67"/>
-      <c r="H18" s="67"/>
-      <c r="I18" s="67"/>
-      <c r="J18" s="67"/>
-      <c r="K18" s="67"/>
-      <c r="L18" s="67"/>
-      <c r="M18" s="67"/>
-      <c r="N18" s="68"/>
-    </row>
-    <row r="19" spans="1:14" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="25"/>
-      <c r="C19" s="60" t="s">
-        <v>27</v>
-      </c>
-      <c r="D19" s="77" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="74"/>
-      <c r="F19" s="78" t="s">
-        <v>9</v>
-      </c>
-      <c r="G19" s="78"/>
-      <c r="H19" s="79" t="s">
-        <v>10</v>
-      </c>
-      <c r="I19" s="79" t="s">
-        <v>11</v>
-      </c>
-      <c r="J19" s="78" t="s">
-        <v>12</v>
-      </c>
-      <c r="K19" s="78"/>
-      <c r="L19" s="79" t="s">
-        <v>10</v>
-      </c>
-      <c r="M19" s="79" t="s">
-        <v>11</v>
-      </c>
-      <c r="N19" s="79" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="25"/>
-      <c r="B20" s="25"/>
-      <c r="C20" s="60"/>
-      <c r="D20" s="77" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="74"/>
-      <c r="F20" s="81" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20" s="23"/>
-      <c r="H20" s="25">
-        <f>(G20+G21+G22)*16</f>
-        <v>0</v>
-      </c>
-      <c r="I20" s="61">
-        <f>H20/48</f>
-        <v>0</v>
-      </c>
-      <c r="J20" s="81" t="s">
-        <v>15</v>
-      </c>
-      <c r="K20" s="23"/>
-      <c r="L20" s="25">
-        <f>(K20+K21+K22)*16</f>
-        <v>0</v>
-      </c>
-      <c r="M20" s="61">
-        <f>L20/48</f>
-        <v>0</v>
-      </c>
-      <c r="N20" s="62"/>
-    </row>
-    <row r="21" spans="1:14" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="25"/>
-      <c r="B21" s="25"/>
-      <c r="C21" s="60"/>
-      <c r="D21" s="77" t="s">
-        <v>17</v>
-      </c>
-      <c r="E21" s="74"/>
-      <c r="F21" s="81" t="s">
-        <v>18</v>
-      </c>
-      <c r="G21" s="23"/>
-      <c r="H21" s="25"/>
-      <c r="I21" s="61"/>
-      <c r="J21" s="81" t="s">
-        <v>18</v>
-      </c>
-      <c r="K21" s="23"/>
-      <c r="L21" s="25"/>
-      <c r="M21" s="61"/>
-      <c r="N21" s="62"/>
-    </row>
-    <row r="22" spans="1:14" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="25"/>
-      <c r="B22" s="25"/>
-      <c r="C22" s="60"/>
-      <c r="D22" s="77" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" s="74"/>
-      <c r="F22" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" s="23"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="61"/>
-      <c r="J22" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="K22" s="23"/>
-      <c r="L22" s="25"/>
-      <c r="M22" s="61"/>
-      <c r="N22" s="62"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="66"/>
-      <c r="B23" s="67"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="67"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="67"/>
-      <c r="J23" s="67"/>
-      <c r="K23" s="67"/>
-      <c r="L23" s="67"/>
-      <c r="M23" s="67"/>
-      <c r="N23" s="68"/>
-    </row>
-    <row r="24" spans="1:14" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24" s="25"/>
-      <c r="C24" s="60" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24" s="77" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="74"/>
-      <c r="F24" s="78" t="s">
-        <v>9</v>
-      </c>
-      <c r="G24" s="78"/>
-      <c r="H24" s="79" t="s">
-        <v>10</v>
-      </c>
-      <c r="I24" s="79" t="s">
-        <v>11</v>
-      </c>
-      <c r="J24" s="78" t="s">
-        <v>12</v>
-      </c>
-      <c r="K24" s="78"/>
-      <c r="L24" s="79" t="s">
-        <v>10</v>
-      </c>
-      <c r="M24" s="79" t="s">
-        <v>11</v>
-      </c>
-      <c r="N24" s="79" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="25"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="60"/>
-      <c r="D25" s="77" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="74"/>
-      <c r="F25" s="81" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25" s="23"/>
-      <c r="H25" s="25">
-        <f>(G25+G26+G27)*16</f>
-        <v>0</v>
-      </c>
-      <c r="I25" s="61">
-        <f>H25/48</f>
-        <v>0</v>
-      </c>
-      <c r="J25" s="81" t="s">
-        <v>15</v>
-      </c>
-      <c r="K25" s="23"/>
-      <c r="L25" s="25">
-        <f>(K25+K26+K27)*16</f>
-        <v>0</v>
-      </c>
-      <c r="M25" s="61">
-        <f>L25/48</f>
-        <v>0</v>
-      </c>
-      <c r="N25" s="62"/>
-    </row>
-    <row r="26" spans="1:14" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="25"/>
-      <c r="B26" s="25"/>
-      <c r="C26" s="60"/>
-      <c r="D26" s="77" t="s">
-        <v>17</v>
-      </c>
-      <c r="E26" s="74"/>
-      <c r="F26" s="81" t="s">
-        <v>18</v>
-      </c>
-      <c r="G26" s="23"/>
-      <c r="H26" s="25"/>
-      <c r="I26" s="61"/>
-      <c r="J26" s="81" t="s">
-        <v>18</v>
-      </c>
-      <c r="K26" s="23"/>
-      <c r="L26" s="25"/>
-      <c r="M26" s="61"/>
-      <c r="N26" s="62"/>
-    </row>
-    <row r="27" spans="1:14" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="25"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="60"/>
-      <c r="D27" s="77" t="s">
-        <v>19</v>
-      </c>
-      <c r="E27" s="74"/>
-      <c r="F27" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="G27" s="23"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="61"/>
-      <c r="J27" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="K27" s="23"/>
-      <c r="L27" s="25"/>
-      <c r="M27" s="61"/>
-      <c r="N27" s="62"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="66"/>
-      <c r="B28" s="67"/>
-      <c r="C28" s="67"/>
-      <c r="D28" s="67"/>
-      <c r="E28" s="67"/>
-      <c r="F28" s="67"/>
-      <c r="G28" s="67"/>
-      <c r="H28" s="67"/>
-      <c r="I28" s="67"/>
-      <c r="J28" s="67"/>
-      <c r="K28" s="67"/>
-      <c r="L28" s="67"/>
-      <c r="M28" s="67"/>
-      <c r="N28" s="68"/>
-    </row>
-    <row r="29" spans="1:14" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29" s="25"/>
-      <c r="C29" s="60" t="s">
-        <v>31</v>
-      </c>
-      <c r="D29" s="77" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="74"/>
-      <c r="F29" s="78" t="s">
-        <v>9</v>
-      </c>
-      <c r="G29" s="78"/>
-      <c r="H29" s="79" t="s">
-        <v>10</v>
-      </c>
-      <c r="I29" s="79" t="s">
-        <v>11</v>
-      </c>
-      <c r="J29" s="78" t="s">
-        <v>12</v>
-      </c>
-      <c r="K29" s="78"/>
-      <c r="L29" s="79" t="s">
-        <v>10</v>
-      </c>
-      <c r="M29" s="79" t="s">
-        <v>11</v>
-      </c>
-      <c r="N29" s="79" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="25"/>
-      <c r="B30" s="25"/>
-      <c r="C30" s="60"/>
-      <c r="D30" s="77" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="74"/>
-      <c r="F30" s="81" t="s">
-        <v>15</v>
-      </c>
-      <c r="G30" s="23"/>
-      <c r="H30" s="25">
-        <f>(G30+G31+G32)*16</f>
-        <v>0</v>
-      </c>
-      <c r="I30" s="61">
-        <f>H30/48</f>
-        <v>0</v>
-      </c>
-      <c r="J30" s="81" t="s">
-        <v>15</v>
-      </c>
-      <c r="K30" s="23"/>
-      <c r="L30" s="25">
-        <f>(K30+K31+K32)*16</f>
-        <v>0</v>
-      </c>
-      <c r="M30" s="61">
-        <f>L30/48</f>
-        <v>0</v>
-      </c>
-      <c r="N30" s="62"/>
-    </row>
-    <row r="31" spans="1:14" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="25"/>
-      <c r="B31" s="25"/>
-      <c r="C31" s="60"/>
-      <c r="D31" s="77" t="s">
-        <v>17</v>
-      </c>
-      <c r="E31" s="74"/>
-      <c r="F31" s="81" t="s">
-        <v>18</v>
-      </c>
-      <c r="G31" s="23"/>
-      <c r="H31" s="25"/>
-      <c r="I31" s="61"/>
-      <c r="J31" s="81" t="s">
-        <v>18</v>
-      </c>
-      <c r="K31" s="23"/>
-      <c r="L31" s="25"/>
-      <c r="M31" s="61"/>
-      <c r="N31" s="62"/>
-    </row>
-    <row r="32" spans="1:14" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="25"/>
-      <c r="B32" s="25"/>
-      <c r="C32" s="60"/>
-      <c r="D32" s="77" t="s">
-        <v>19</v>
-      </c>
-      <c r="E32" s="74"/>
-      <c r="F32" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="G32" s="23"/>
-      <c r="H32" s="25"/>
-      <c r="I32" s="61"/>
-      <c r="J32" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="K32" s="23"/>
-      <c r="L32" s="25"/>
-      <c r="M32" s="61"/>
-      <c r="N32" s="62"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="66"/>
-      <c r="B33" s="67"/>
-      <c r="C33" s="67"/>
-      <c r="D33" s="67"/>
-      <c r="E33" s="67"/>
-      <c r="F33" s="67"/>
-      <c r="G33" s="67"/>
-      <c r="H33" s="67"/>
-      <c r="I33" s="67"/>
-      <c r="J33" s="67"/>
-      <c r="K33" s="67"/>
-      <c r="L33" s="67"/>
-      <c r="M33" s="67"/>
-      <c r="N33" s="68"/>
-    </row>
-    <row r="34" spans="1:14" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" s="25"/>
-      <c r="C34" s="60" t="s">
-        <v>33</v>
-      </c>
-      <c r="D34" s="77" t="s">
-        <v>7</v>
-      </c>
-      <c r="E34" s="74"/>
-      <c r="F34" s="78" t="s">
-        <v>9</v>
-      </c>
-      <c r="G34" s="78"/>
-      <c r="H34" s="79" t="s">
-        <v>10</v>
-      </c>
-      <c r="I34" s="79" t="s">
-        <v>11</v>
-      </c>
-      <c r="J34" s="78" t="s">
-        <v>12</v>
-      </c>
-      <c r="K34" s="78"/>
-      <c r="L34" s="79" t="s">
-        <v>10</v>
-      </c>
-      <c r="M34" s="79" t="s">
-        <v>11</v>
-      </c>
-      <c r="N34" s="79" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="25"/>
-      <c r="B35" s="25"/>
-      <c r="C35" s="60"/>
-      <c r="D35" s="77" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" s="74"/>
-      <c r="F35" s="81" t="s">
-        <v>15</v>
-      </c>
-      <c r="G35" s="23"/>
-      <c r="H35" s="25">
-        <f>(G35+G36+G37)*16</f>
-        <v>0</v>
-      </c>
-      <c r="I35" s="61">
-        <f>H35/48</f>
-        <v>0</v>
-      </c>
-      <c r="J35" s="81" t="s">
-        <v>15</v>
-      </c>
-      <c r="K35" s="23"/>
-      <c r="L35" s="25">
-        <f>(K35+K36+K37)*16</f>
-        <v>0</v>
-      </c>
-      <c r="M35" s="61">
-        <f>L35/48</f>
-        <v>0</v>
-      </c>
-      <c r="N35" s="62"/>
-    </row>
-    <row r="36" spans="1:14" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="25"/>
-      <c r="B36" s="25"/>
-      <c r="C36" s="60"/>
-      <c r="D36" s="77" t="s">
-        <v>17</v>
-      </c>
-      <c r="E36" s="74"/>
-      <c r="F36" s="81" t="s">
-        <v>18</v>
-      </c>
-      <c r="G36" s="23"/>
-      <c r="H36" s="25"/>
-      <c r="I36" s="61"/>
-      <c r="J36" s="81" t="s">
-        <v>18</v>
-      </c>
-      <c r="K36" s="23"/>
-      <c r="L36" s="25"/>
-      <c r="M36" s="61"/>
-      <c r="N36" s="62"/>
-    </row>
-    <row r="37" spans="1:14" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="25"/>
-      <c r="B37" s="25"/>
-      <c r="C37" s="60"/>
-      <c r="D37" s="77" t="s">
-        <v>19</v>
-      </c>
-      <c r="E37" s="74"/>
-      <c r="F37" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="G37" s="23"/>
-      <c r="H37" s="25"/>
-      <c r="I37" s="61"/>
-      <c r="J37" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="K37" s="23"/>
-      <c r="L37" s="25"/>
-      <c r="M37" s="61"/>
-      <c r="N37" s="62"/>
+      <c r="L7" s="32"/>
+      <c r="M7" s="37"/>
+      <c r="N7" s="35"/>
     </row>
   </sheetData>
-  <mergeCells count="78">
-    <mergeCell ref="A24:A27"/>
-    <mergeCell ref="A29:A32"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="A8:N8"/>
-    <mergeCell ref="A13:N13"/>
-    <mergeCell ref="A18:N18"/>
-    <mergeCell ref="A23:N23"/>
-    <mergeCell ref="A28:N28"/>
-    <mergeCell ref="A33:N33"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="B24:B27"/>
-    <mergeCell ref="B29:B32"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="C34:C37"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="N35:N37"/>
+  <mergeCells count="12">
+    <mergeCell ref="L5:L7"/>
+    <mergeCell ref="M5:M7"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="A1:N2"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="C4:C7"/>
     <mergeCell ref="D3:N3"/>
-    <mergeCell ref="C29:C32"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="N30:N32"/>
-    <mergeCell ref="H25:H27"/>
-    <mergeCell ref="I25:I27"/>
-    <mergeCell ref="H30:H32"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="N10:N12"/>
-    <mergeCell ref="C14:C17"/>
     <mergeCell ref="N5:N7"/>
     <mergeCell ref="H5:H7"/>
     <mergeCell ref="I5:I7"/>
-    <mergeCell ref="A1:N2"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="C19:C22"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="N15:N17"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="N20:N22"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="H35:H37"/>
-    <mergeCell ref="C24:C27"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="N25:N27"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="I35:I37"/>
-    <mergeCell ref="L35:L37"/>
-    <mergeCell ref="M35:M37"/>
-    <mergeCell ref="L5:L7"/>
-    <mergeCell ref="M5:M7"/>
-    <mergeCell ref="L10:L12"/>
-    <mergeCell ref="M10:M12"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H10:H12"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="I10:I12"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="I15:I17"/>
-    <mergeCell ref="H20:H22"/>
-    <mergeCell ref="I20:I22"/>
-    <mergeCell ref="I30:I32"/>
-    <mergeCell ref="L15:L17"/>
-    <mergeCell ref="M15:M17"/>
-    <mergeCell ref="L20:L22"/>
-    <mergeCell ref="M20:M22"/>
-    <mergeCell ref="M30:M32"/>
-    <mergeCell ref="L25:L27"/>
-    <mergeCell ref="M25:M27"/>
-    <mergeCell ref="L30:L32"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2505,264 +1549,264 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="26"/>
-      <c r="Z1" s="26"/>
-      <c r="AA1" s="26"/>
-      <c r="AB1" s="26"/>
-      <c r="AC1" s="26"/>
-      <c r="AD1" s="26"/>
-      <c r="AE1" s="26"/>
-      <c r="AF1" s="26"/>
-      <c r="AG1" s="26"/>
-      <c r="AH1" s="26"/>
-      <c r="AI1" s="26"/>
-      <c r="AJ1" s="26"/>
-      <c r="AK1" s="26"/>
-      <c r="AL1" s="26"/>
-      <c r="AM1" s="26"/>
-      <c r="AN1" s="26"/>
-      <c r="AO1" s="26"/>
-      <c r="AP1" s="26"/>
-      <c r="AQ1" s="26"/>
-      <c r="AR1" s="26"/>
-      <c r="AS1" s="26"/>
-      <c r="AT1" s="26"/>
-      <c r="AU1" s="26"/>
-      <c r="AV1" s="26"/>
-      <c r="AW1" s="26"/>
-      <c r="AX1" s="26"/>
-      <c r="AY1" s="26"/>
-      <c r="AZ1" s="26"/>
-      <c r="BA1" s="26"/>
-      <c r="BB1" s="26"/>
-      <c r="BC1" s="26"/>
-      <c r="BD1" s="26"/>
-      <c r="BE1" s="26"/>
-      <c r="BF1" s="26"/>
-      <c r="BG1" s="26"/>
-      <c r="BH1" s="26"/>
-      <c r="BI1" s="26"/>
-      <c r="BJ1" s="26"/>
-      <c r="BK1" s="26"/>
-      <c r="BL1" s="26"/>
-      <c r="BM1" s="26"/>
-      <c r="BN1" s="26"/>
-      <c r="BO1" s="26"/>
-      <c r="BP1" s="26"/>
-      <c r="BQ1" s="26"/>
-      <c r="BR1" s="26"/>
-      <c r="BS1" s="26"/>
-      <c r="BT1" s="26"/>
-      <c r="BU1" s="26"/>
-      <c r="BV1" s="26"/>
-      <c r="BW1" s="26"/>
-      <c r="BX1" s="26"/>
-      <c r="BY1" s="26"/>
-      <c r="BZ1" s="26"/>
-      <c r="CA1" s="26"/>
-      <c r="CB1" s="26"/>
-      <c r="CC1" s="26"/>
-      <c r="CD1" s="26"/>
-      <c r="CE1" s="26"/>
-      <c r="CF1" s="26"/>
+      <c r="A1" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
+      <c r="S1" s="53"/>
+      <c r="T1" s="53"/>
+      <c r="U1" s="53"/>
+      <c r="V1" s="53"/>
+      <c r="W1" s="53"/>
+      <c r="X1" s="53"/>
+      <c r="Y1" s="53"/>
+      <c r="Z1" s="53"/>
+      <c r="AA1" s="53"/>
+      <c r="AB1" s="53"/>
+      <c r="AC1" s="53"/>
+      <c r="AD1" s="53"/>
+      <c r="AE1" s="53"/>
+      <c r="AF1" s="53"/>
+      <c r="AG1" s="53"/>
+      <c r="AH1" s="53"/>
+      <c r="AI1" s="53"/>
+      <c r="AJ1" s="53"/>
+      <c r="AK1" s="53"/>
+      <c r="AL1" s="53"/>
+      <c r="AM1" s="53"/>
+      <c r="AN1" s="53"/>
+      <c r="AO1" s="53"/>
+      <c r="AP1" s="53"/>
+      <c r="AQ1" s="53"/>
+      <c r="AR1" s="53"/>
+      <c r="AS1" s="53"/>
+      <c r="AT1" s="53"/>
+      <c r="AU1" s="53"/>
+      <c r="AV1" s="53"/>
+      <c r="AW1" s="53"/>
+      <c r="AX1" s="53"/>
+      <c r="AY1" s="53"/>
+      <c r="AZ1" s="53"/>
+      <c r="BA1" s="53"/>
+      <c r="BB1" s="53"/>
+      <c r="BC1" s="53"/>
+      <c r="BD1" s="53"/>
+      <c r="BE1" s="53"/>
+      <c r="BF1" s="53"/>
+      <c r="BG1" s="53"/>
+      <c r="BH1" s="53"/>
+      <c r="BI1" s="53"/>
+      <c r="BJ1" s="53"/>
+      <c r="BK1" s="53"/>
+      <c r="BL1" s="53"/>
+      <c r="BM1" s="53"/>
+      <c r="BN1" s="53"/>
+      <c r="BO1" s="53"/>
+      <c r="BP1" s="53"/>
+      <c r="BQ1" s="53"/>
+      <c r="BR1" s="53"/>
+      <c r="BS1" s="53"/>
+      <c r="BT1" s="53"/>
+      <c r="BU1" s="53"/>
+      <c r="BV1" s="53"/>
+      <c r="BW1" s="53"/>
+      <c r="BX1" s="53"/>
+      <c r="BY1" s="53"/>
+      <c r="BZ1" s="53"/>
+      <c r="CA1" s="53"/>
+      <c r="CB1" s="53"/>
+      <c r="CC1" s="53"/>
+      <c r="CD1" s="53"/>
+      <c r="CE1" s="53"/>
+      <c r="CF1" s="53"/>
     </row>
     <row r="2" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="26"/>
-      <c r="V2" s="26"/>
-      <c r="W2" s="26"/>
-      <c r="X2" s="26"/>
-      <c r="Y2" s="26"/>
-      <c r="Z2" s="26"/>
-      <c r="AA2" s="26"/>
-      <c r="AB2" s="26"/>
-      <c r="AC2" s="26"/>
-      <c r="AD2" s="26"/>
-      <c r="AE2" s="26"/>
-      <c r="AF2" s="26"/>
-      <c r="AG2" s="26"/>
-      <c r="AH2" s="26"/>
-      <c r="AI2" s="26"/>
-      <c r="AJ2" s="26"/>
-      <c r="AK2" s="26"/>
-      <c r="AL2" s="26"/>
-      <c r="AM2" s="26"/>
-      <c r="AN2" s="26"/>
-      <c r="AO2" s="26"/>
-      <c r="AP2" s="26"/>
-      <c r="AQ2" s="26"/>
-      <c r="AR2" s="26"/>
-      <c r="AS2" s="26"/>
-      <c r="AT2" s="26"/>
-      <c r="AU2" s="26"/>
-      <c r="AV2" s="26"/>
-      <c r="AW2" s="26"/>
-      <c r="AX2" s="26"/>
-      <c r="AY2" s="26"/>
-      <c r="AZ2" s="26"/>
-      <c r="BA2" s="26"/>
-      <c r="BB2" s="26"/>
-      <c r="BC2" s="26"/>
-      <c r="BD2" s="26"/>
-      <c r="BE2" s="26"/>
-      <c r="BF2" s="26"/>
-      <c r="BG2" s="26"/>
-      <c r="BH2" s="26"/>
-      <c r="BI2" s="26"/>
-      <c r="BJ2" s="26"/>
-      <c r="BK2" s="26"/>
-      <c r="BL2" s="26"/>
-      <c r="BM2" s="26"/>
-      <c r="BN2" s="26"/>
-      <c r="BO2" s="26"/>
-      <c r="BP2" s="26"/>
-      <c r="BQ2" s="26"/>
-      <c r="BR2" s="26"/>
-      <c r="BS2" s="26"/>
-      <c r="BT2" s="26"/>
-      <c r="BU2" s="26"/>
-      <c r="BV2" s="26"/>
-      <c r="BW2" s="26"/>
-      <c r="BX2" s="26"/>
-      <c r="BY2" s="26"/>
-      <c r="BZ2" s="26"/>
-      <c r="CA2" s="26"/>
-      <c r="CB2" s="26"/>
-      <c r="CC2" s="26"/>
-      <c r="CD2" s="26"/>
-      <c r="CE2" s="26"/>
-      <c r="CF2" s="26"/>
+      <c r="A2" s="53"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+      <c r="Q2" s="53"/>
+      <c r="R2" s="53"/>
+      <c r="S2" s="53"/>
+      <c r="T2" s="53"/>
+      <c r="U2" s="53"/>
+      <c r="V2" s="53"/>
+      <c r="W2" s="53"/>
+      <c r="X2" s="53"/>
+      <c r="Y2" s="53"/>
+      <c r="Z2" s="53"/>
+      <c r="AA2" s="53"/>
+      <c r="AB2" s="53"/>
+      <c r="AC2" s="53"/>
+      <c r="AD2" s="53"/>
+      <c r="AE2" s="53"/>
+      <c r="AF2" s="53"/>
+      <c r="AG2" s="53"/>
+      <c r="AH2" s="53"/>
+      <c r="AI2" s="53"/>
+      <c r="AJ2" s="53"/>
+      <c r="AK2" s="53"/>
+      <c r="AL2" s="53"/>
+      <c r="AM2" s="53"/>
+      <c r="AN2" s="53"/>
+      <c r="AO2" s="53"/>
+      <c r="AP2" s="53"/>
+      <c r="AQ2" s="53"/>
+      <c r="AR2" s="53"/>
+      <c r="AS2" s="53"/>
+      <c r="AT2" s="53"/>
+      <c r="AU2" s="53"/>
+      <c r="AV2" s="53"/>
+      <c r="AW2" s="53"/>
+      <c r="AX2" s="53"/>
+      <c r="AY2" s="53"/>
+      <c r="AZ2" s="53"/>
+      <c r="BA2" s="53"/>
+      <c r="BB2" s="53"/>
+      <c r="BC2" s="53"/>
+      <c r="BD2" s="53"/>
+      <c r="BE2" s="53"/>
+      <c r="BF2" s="53"/>
+      <c r="BG2" s="53"/>
+      <c r="BH2" s="53"/>
+      <c r="BI2" s="53"/>
+      <c r="BJ2" s="53"/>
+      <c r="BK2" s="53"/>
+      <c r="BL2" s="53"/>
+      <c r="BM2" s="53"/>
+      <c r="BN2" s="53"/>
+      <c r="BO2" s="53"/>
+      <c r="BP2" s="53"/>
+      <c r="BQ2" s="53"/>
+      <c r="BR2" s="53"/>
+      <c r="BS2" s="53"/>
+      <c r="BT2" s="53"/>
+      <c r="BU2" s="53"/>
+      <c r="BV2" s="53"/>
+      <c r="BW2" s="53"/>
+      <c r="BX2" s="53"/>
+      <c r="BY2" s="53"/>
+      <c r="BZ2" s="53"/>
+      <c r="CA2" s="53"/>
+      <c r="CB2" s="53"/>
+      <c r="CC2" s="53"/>
+      <c r="CD2" s="53"/>
+      <c r="CE2" s="53"/>
+      <c r="CF2" s="53"/>
     </row>
     <row r="3" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
-      <c r="Q3" s="26"/>
-      <c r="R3" s="26"/>
-      <c r="S3" s="26"/>
-      <c r="T3" s="26"/>
-      <c r="U3" s="26"/>
-      <c r="V3" s="26"/>
-      <c r="W3" s="26"/>
-      <c r="X3" s="26"/>
-      <c r="Y3" s="26"/>
-      <c r="Z3" s="26"/>
-      <c r="AA3" s="26"/>
-      <c r="AB3" s="26"/>
-      <c r="AC3" s="26"/>
-      <c r="AD3" s="26"/>
-      <c r="AE3" s="26"/>
-      <c r="AF3" s="26"/>
-      <c r="AG3" s="26"/>
-      <c r="AH3" s="26"/>
-      <c r="AI3" s="26"/>
-      <c r="AJ3" s="26"/>
-      <c r="AK3" s="26"/>
-      <c r="AL3" s="26"/>
-      <c r="AM3" s="26"/>
-      <c r="AN3" s="26"/>
-      <c r="AO3" s="26"/>
-      <c r="AP3" s="26"/>
-      <c r="AQ3" s="26"/>
-      <c r="AR3" s="26"/>
-      <c r="AS3" s="26"/>
-      <c r="AT3" s="26"/>
-      <c r="AU3" s="26"/>
-      <c r="AV3" s="26"/>
-      <c r="AW3" s="26"/>
-      <c r="AX3" s="26"/>
-      <c r="AY3" s="26"/>
-      <c r="AZ3" s="26"/>
-      <c r="BA3" s="26"/>
-      <c r="BB3" s="26"/>
-      <c r="BC3" s="26"/>
-      <c r="BD3" s="26"/>
-      <c r="BE3" s="26"/>
-      <c r="BF3" s="26"/>
-      <c r="BG3" s="26"/>
-      <c r="BH3" s="26"/>
-      <c r="BI3" s="26"/>
-      <c r="BJ3" s="26"/>
-      <c r="BK3" s="26"/>
-      <c r="BL3" s="26"/>
-      <c r="BM3" s="26"/>
-      <c r="BN3" s="26"/>
-      <c r="BO3" s="26"/>
-      <c r="BP3" s="26"/>
-      <c r="BQ3" s="26"/>
-      <c r="BR3" s="26"/>
-      <c r="BS3" s="26"/>
-      <c r="BT3" s="26"/>
-      <c r="BU3" s="26"/>
-      <c r="BV3" s="26"/>
-      <c r="BW3" s="26"/>
-      <c r="BX3" s="26"/>
-      <c r="BY3" s="26"/>
-      <c r="BZ3" s="26"/>
-      <c r="CA3" s="26"/>
-      <c r="CB3" s="26"/>
-      <c r="CC3" s="26"/>
-      <c r="CD3" s="26"/>
-      <c r="CE3" s="26"/>
-      <c r="CF3" s="26"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="53"/>
+      <c r="N3" s="53"/>
+      <c r="O3" s="53"/>
+      <c r="P3" s="53"/>
+      <c r="Q3" s="53"/>
+      <c r="R3" s="53"/>
+      <c r="S3" s="53"/>
+      <c r="T3" s="53"/>
+      <c r="U3" s="53"/>
+      <c r="V3" s="53"/>
+      <c r="W3" s="53"/>
+      <c r="X3" s="53"/>
+      <c r="Y3" s="53"/>
+      <c r="Z3" s="53"/>
+      <c r="AA3" s="53"/>
+      <c r="AB3" s="53"/>
+      <c r="AC3" s="53"/>
+      <c r="AD3" s="53"/>
+      <c r="AE3" s="53"/>
+      <c r="AF3" s="53"/>
+      <c r="AG3" s="53"/>
+      <c r="AH3" s="53"/>
+      <c r="AI3" s="53"/>
+      <c r="AJ3" s="53"/>
+      <c r="AK3" s="53"/>
+      <c r="AL3" s="53"/>
+      <c r="AM3" s="53"/>
+      <c r="AN3" s="53"/>
+      <c r="AO3" s="53"/>
+      <c r="AP3" s="53"/>
+      <c r="AQ3" s="53"/>
+      <c r="AR3" s="53"/>
+      <c r="AS3" s="53"/>
+      <c r="AT3" s="53"/>
+      <c r="AU3" s="53"/>
+      <c r="AV3" s="53"/>
+      <c r="AW3" s="53"/>
+      <c r="AX3" s="53"/>
+      <c r="AY3" s="53"/>
+      <c r="AZ3" s="53"/>
+      <c r="BA3" s="53"/>
+      <c r="BB3" s="53"/>
+      <c r="BC3" s="53"/>
+      <c r="BD3" s="53"/>
+      <c r="BE3" s="53"/>
+      <c r="BF3" s="53"/>
+      <c r="BG3" s="53"/>
+      <c r="BH3" s="53"/>
+      <c r="BI3" s="53"/>
+      <c r="BJ3" s="53"/>
+      <c r="BK3" s="53"/>
+      <c r="BL3" s="53"/>
+      <c r="BM3" s="53"/>
+      <c r="BN3" s="53"/>
+      <c r="BO3" s="53"/>
+      <c r="BP3" s="53"/>
+      <c r="BQ3" s="53"/>
+      <c r="BR3" s="53"/>
+      <c r="BS3" s="53"/>
+      <c r="BT3" s="53"/>
+      <c r="BU3" s="53"/>
+      <c r="BV3" s="53"/>
+      <c r="BW3" s="53"/>
+      <c r="BX3" s="53"/>
+      <c r="BY3" s="53"/>
+      <c r="BZ3" s="53"/>
+      <c r="CA3" s="53"/>
+      <c r="CB3" s="53"/>
+      <c r="CC3" s="53"/>
+      <c r="CD3" s="53"/>
+      <c r="CE3" s="53"/>
+      <c r="CF3" s="53"/>
     </row>
     <row r="5" spans="1:84" x14ac:dyDescent="0.25">
       <c r="G5" s="1"/>
@@ -2821,306 +1865,306 @@
       <c r="BW5" s="1"/>
     </row>
     <row r="6" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="32" t="s">
-        <v>92</v>
-      </c>
-      <c r="B6" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="29"/>
-      <c r="G6" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="30"/>
-      <c r="L6" s="30"/>
+      <c r="A6" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="41"/>
+      <c r="G6" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
+      <c r="J6" s="46"/>
+      <c r="K6" s="46"/>
+      <c r="L6" s="46"/>
       <c r="M6" s="1"/>
-      <c r="P6" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q6" s="30"/>
-      <c r="R6" s="30"/>
-      <c r="S6" s="30"/>
-      <c r="T6" s="30"/>
-      <c r="U6" s="30"/>
-      <c r="Y6" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z6" s="30"/>
-      <c r="AA6" s="30"/>
-      <c r="AB6" s="30"/>
-      <c r="AC6" s="30"/>
-      <c r="AD6" s="30"/>
+      <c r="P6" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q6" s="46"/>
+      <c r="R6" s="46"/>
+      <c r="S6" s="46"/>
+      <c r="T6" s="46"/>
+      <c r="U6" s="46"/>
+      <c r="Y6" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z6" s="46"/>
+      <c r="AA6" s="46"/>
+      <c r="AB6" s="46"/>
+      <c r="AC6" s="46"/>
+      <c r="AD6" s="46"/>
       <c r="AE6" s="1"/>
-      <c r="AH6" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI6" s="30"/>
-      <c r="AJ6" s="30"/>
-      <c r="AK6" s="30"/>
-      <c r="AL6" s="30"/>
-      <c r="AM6" s="30"/>
+      <c r="AH6" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI6" s="46"/>
+      <c r="AJ6" s="46"/>
+      <c r="AK6" s="46"/>
+      <c r="AL6" s="46"/>
+      <c r="AM6" s="46"/>
       <c r="AN6" s="1"/>
-      <c r="AQ6" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR6" s="30"/>
-      <c r="AS6" s="30"/>
-      <c r="AT6" s="30"/>
-      <c r="AU6" s="30"/>
-      <c r="AV6" s="30"/>
+      <c r="AQ6" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="AR6" s="46"/>
+      <c r="AS6" s="46"/>
+      <c r="AT6" s="46"/>
+      <c r="AU6" s="46"/>
+      <c r="AV6" s="46"/>
       <c r="AW6" s="1"/>
-      <c r="AZ6" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA6" s="30"/>
-      <c r="BB6" s="30"/>
-      <c r="BC6" s="30"/>
-      <c r="BD6" s="30"/>
-      <c r="BE6" s="30"/>
-      <c r="BI6" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="BJ6" s="30"/>
-      <c r="BK6" s="30"/>
-      <c r="BL6" s="30"/>
-      <c r="BM6" s="30"/>
-      <c r="BN6" s="30"/>
-      <c r="BR6" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="BS6" s="30"/>
-      <c r="BT6" s="30"/>
-      <c r="BU6" s="30"/>
-      <c r="BV6" s="30"/>
-      <c r="BW6" s="30"/>
+      <c r="AZ6" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="BA6" s="46"/>
+      <c r="BB6" s="46"/>
+      <c r="BC6" s="46"/>
+      <c r="BD6" s="46"/>
+      <c r="BE6" s="46"/>
+      <c r="BI6" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="BJ6" s="46"/>
+      <c r="BK6" s="46"/>
+      <c r="BL6" s="46"/>
+      <c r="BM6" s="46"/>
+      <c r="BN6" s="46"/>
+      <c r="BR6" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="BS6" s="46"/>
+      <c r="BT6" s="46"/>
+      <c r="BU6" s="46"/>
+      <c r="BV6" s="46"/>
+      <c r="BW6" s="46"/>
     </row>
     <row r="7" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A7" s="33"/>
+      <c r="A7" s="51"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
       <c r="G7" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="H7" s="4">
         <v>3</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="J7" s="4">
         <v>2</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L7" s="4">
         <v>4</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="N7">
         <f>(H7+J7+L7)/3</f>
         <v>3</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="Q7" s="4">
         <v>3</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="S7" s="4">
         <v>2</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="U7" s="4">
         <v>4</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="W7">
         <f>(Q7+S7+U7)/3</f>
         <v>3</v>
       </c>
       <c r="Y7" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="Z7" s="4">
         <v>3</v>
       </c>
       <c r="AA7" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AB7" s="4">
         <v>0</v>
       </c>
       <c r="AC7" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="AD7" s="4">
         <v>6</v>
       </c>
       <c r="AE7" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AF7">
         <f>(Z7+AB7+AD7)/3</f>
         <v>3</v>
       </c>
       <c r="AH7" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="AI7" s="4">
         <v>3</v>
       </c>
       <c r="AJ7" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AK7" s="4">
         <v>1</v>
       </c>
       <c r="AL7" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="AM7" s="4">
         <v>5</v>
       </c>
       <c r="AN7" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AO7">
         <f>(AI7+AK7+AM7)/3</f>
         <v>3</v>
       </c>
       <c r="AQ7" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="AR7" s="4">
         <v>1</v>
       </c>
       <c r="AS7" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AT7" s="4">
         <v>1</v>
       </c>
       <c r="AU7" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="AV7" s="4">
         <v>1</v>
       </c>
       <c r="AW7" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AX7">
         <f>(AR7+AT7+AV7)/3</f>
         <v>1</v>
       </c>
       <c r="AZ7" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BA7" s="4">
         <v>2</v>
       </c>
       <c r="BB7" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BC7" s="4">
         <v>2</v>
       </c>
       <c r="BD7" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BE7" s="4">
         <v>2</v>
       </c>
       <c r="BF7" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BG7">
         <f>(BA7+BC7+BE7)/3</f>
         <v>2</v>
       </c>
       <c r="BI7" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BJ7" s="4">
         <v>2</v>
       </c>
       <c r="BK7" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BL7" s="4">
         <v>2</v>
       </c>
       <c r="BM7" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BN7" s="4">
         <v>2</v>
       </c>
       <c r="BO7" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BP7">
         <f>(BJ7+BL7+BN7)/3</f>
         <v>2</v>
       </c>
       <c r="BR7" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BS7" s="4">
         <v>0</v>
       </c>
       <c r="BT7" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BU7" s="4">
         <v>0</v>
       </c>
       <c r="BV7" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BW7" s="4">
         <v>0</v>
       </c>
       <c r="BX7" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BY7">
         <f>(BS7+BU7+BW7)/3</f>
         <v>0</v>
       </c>
       <c r="CA7" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="CB7" s="4">
         <f>H7+Q7+Z7+AI7+AR7+BA7+BJ7+BS7</f>
         <v>17</v>
       </c>
       <c r="CC7" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="CD7" s="4">
         <f>J7+S7+AB7+AK7+AT7+BC7+BL7+BU7</f>
         <v>10</v>
       </c>
       <c r="CE7" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="CF7" s="4">
         <f>L7+U7+AD7+AM7+AV7+BE7+BN7+BW7</f>
@@ -3128,284 +2172,284 @@
       </c>
     </row>
     <row r="8" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A8" s="33"/>
-      <c r="CA8" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="CB8" s="31"/>
-      <c r="CC8" s="31"/>
-      <c r="CD8" s="31"/>
-      <c r="CE8" s="31"/>
+      <c r="A8" s="51"/>
+      <c r="CA8" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="CB8" s="48"/>
+      <c r="CC8" s="48"/>
+      <c r="CD8" s="48"/>
+      <c r="CE8" s="48"/>
       <c r="CF8" s="3">
         <f>(CB7+CD7+CF7)*16</f>
         <v>816</v>
       </c>
     </row>
     <row r="9" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A9" s="33"/>
-      <c r="CA9" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="CB9" s="28"/>
-      <c r="CC9" s="28"/>
-      <c r="CD9" s="28"/>
-      <c r="CE9" s="29"/>
+      <c r="A9" s="51"/>
+      <c r="CA9" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="CB9" s="40"/>
+      <c r="CC9" s="40"/>
+      <c r="CD9" s="40"/>
+      <c r="CE9" s="41"/>
       <c r="CF9" s="3">
         <f>CF8/48</f>
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="33"/>
-      <c r="B10" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="29"/>
-      <c r="G10" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="30"/>
-      <c r="K10" s="30"/>
-      <c r="L10" s="30"/>
+      <c r="A10" s="51"/>
+      <c r="B10" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="41"/>
+      <c r="G10" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46"/>
+      <c r="J10" s="46"/>
+      <c r="K10" s="46"/>
+      <c r="L10" s="46"/>
       <c r="M10" s="1"/>
-      <c r="P10" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q10" s="30"/>
-      <c r="R10" s="30"/>
-      <c r="S10" s="30"/>
-      <c r="T10" s="30"/>
-      <c r="U10" s="30"/>
-      <c r="Y10" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z10" s="30"/>
-      <c r="AA10" s="30"/>
-      <c r="AB10" s="30"/>
-      <c r="AC10" s="30"/>
-      <c r="AD10" s="30"/>
+      <c r="P10" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q10" s="46"/>
+      <c r="R10" s="46"/>
+      <c r="S10" s="46"/>
+      <c r="T10" s="46"/>
+      <c r="U10" s="46"/>
+      <c r="Y10" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z10" s="46"/>
+      <c r="AA10" s="46"/>
+      <c r="AB10" s="46"/>
+      <c r="AC10" s="46"/>
+      <c r="AD10" s="46"/>
       <c r="AE10" s="1"/>
-      <c r="AH10" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI10" s="30"/>
-      <c r="AJ10" s="30"/>
-      <c r="AK10" s="30"/>
-      <c r="AL10" s="30"/>
-      <c r="AM10" s="30"/>
+      <c r="AH10" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI10" s="46"/>
+      <c r="AJ10" s="46"/>
+      <c r="AK10" s="46"/>
+      <c r="AL10" s="46"/>
+      <c r="AM10" s="46"/>
       <c r="AN10" s="1"/>
-      <c r="AQ10" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR10" s="30"/>
-      <c r="AS10" s="30"/>
-      <c r="AT10" s="30"/>
-      <c r="AU10" s="30"/>
-      <c r="AV10" s="30"/>
+      <c r="AQ10" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="AR10" s="46"/>
+      <c r="AS10" s="46"/>
+      <c r="AT10" s="46"/>
+      <c r="AU10" s="46"/>
+      <c r="AV10" s="46"/>
       <c r="AW10" s="1"/>
-      <c r="AZ10" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA10" s="30"/>
-      <c r="BB10" s="30"/>
-      <c r="BC10" s="30"/>
-      <c r="BD10" s="30"/>
-      <c r="BE10" s="30"/>
-      <c r="BI10" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="BJ10" s="30"/>
-      <c r="BK10" s="30"/>
-      <c r="BL10" s="30"/>
-      <c r="BM10" s="30"/>
-      <c r="BN10" s="30"/>
-      <c r="BR10" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="BS10" s="30"/>
-      <c r="BT10" s="30"/>
-      <c r="BU10" s="30"/>
-      <c r="BV10" s="30"/>
-      <c r="BW10" s="30"/>
+      <c r="AZ10" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="BA10" s="46"/>
+      <c r="BB10" s="46"/>
+      <c r="BC10" s="46"/>
+      <c r="BD10" s="46"/>
+      <c r="BE10" s="46"/>
+      <c r="BI10" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="BJ10" s="46"/>
+      <c r="BK10" s="46"/>
+      <c r="BL10" s="46"/>
+      <c r="BM10" s="46"/>
+      <c r="BN10" s="46"/>
+      <c r="BR10" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="BS10" s="46"/>
+      <c r="BT10" s="46"/>
+      <c r="BU10" s="46"/>
+      <c r="BV10" s="46"/>
+      <c r="BW10" s="46"/>
     </row>
     <row r="11" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A11" s="33"/>
+      <c r="A11" s="51"/>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
       <c r="E11" s="15"/>
       <c r="G11" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="3" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="3" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L11" s="4"/>
       <c r="M11" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="N11">
         <f>(H11+J11+L11)/3</f>
         <v>0</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="Q11" s="4"/>
       <c r="R11" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="S11" s="4"/>
       <c r="T11" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="U11" s="4"/>
       <c r="V11" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="W11">
         <f>(Q11+S11+U11)/3</f>
         <v>0</v>
       </c>
       <c r="Y11" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="Z11" s="4"/>
       <c r="AA11" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AB11" s="4"/>
       <c r="AC11" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="AD11" s="4"/>
       <c r="AE11" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AF11">
         <f>(Z11+AB11+AD11)/3</f>
         <v>0</v>
       </c>
       <c r="AH11" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="AI11" s="4"/>
       <c r="AJ11" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AK11" s="4"/>
       <c r="AL11" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="AM11" s="4"/>
       <c r="AN11" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AO11">
         <f>(AI11+AK11+AM11)/3</f>
         <v>0</v>
       </c>
       <c r="AQ11" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="AR11" s="4"/>
       <c r="AS11" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AT11" s="4"/>
       <c r="AU11" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="AV11" s="4"/>
       <c r="AW11" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AX11">
         <f>(AR11+AT11+AV11)/3</f>
         <v>0</v>
       </c>
       <c r="AZ11" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BA11" s="4"/>
       <c r="BB11" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BC11" s="4"/>
       <c r="BD11" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BE11" s="4"/>
       <c r="BF11" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BG11">
         <f>(BA11+BC11+BE11)/3</f>
         <v>0</v>
       </c>
       <c r="BI11" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BJ11" s="4"/>
       <c r="BK11" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BL11" s="4"/>
       <c r="BM11" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BN11" s="4"/>
       <c r="BO11" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BP11">
         <f>(BJ11+BL11+BN11)/3</f>
         <v>0</v>
       </c>
       <c r="BR11" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BS11" s="4"/>
       <c r="BT11" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BU11" s="4"/>
       <c r="BV11" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BW11" s="4"/>
       <c r="BX11" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BY11">
         <f>(BS11+BU11+BW11)/3</f>
         <v>0</v>
       </c>
       <c r="CA11" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="CB11" s="4">
         <f>H11+Q11+Z11+AI11+AR11+BA11+BJ11+BS11</f>
         <v>0</v>
       </c>
       <c r="CC11" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="CD11" s="4">
         <f>J11+S11+AB11+AK11+AT11+BC11+BL11+BU11</f>
         <v>0</v>
       </c>
       <c r="CE11" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="CF11" s="4">
         <f>L11+U11+AD11+AM11+AV11+BE11+BN11+BW11</f>
@@ -3413,284 +2457,284 @@
       </c>
     </row>
     <row r="12" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A12" s="33"/>
-      <c r="CA12" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="CB12" s="31"/>
-      <c r="CC12" s="31"/>
-      <c r="CD12" s="31"/>
-      <c r="CE12" s="31"/>
+      <c r="A12" s="51"/>
+      <c r="CA12" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="CB12" s="48"/>
+      <c r="CC12" s="48"/>
+      <c r="CD12" s="48"/>
+      <c r="CE12" s="48"/>
       <c r="CF12" s="3">
         <f>(CB11+CD11+CF11)*16</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A13" s="34"/>
-      <c r="CA13" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="CB13" s="28"/>
-      <c r="CC13" s="28"/>
-      <c r="CD13" s="28"/>
-      <c r="CE13" s="29"/>
+      <c r="A13" s="52"/>
+      <c r="CA13" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="CB13" s="40"/>
+      <c r="CC13" s="40"/>
+      <c r="CD13" s="40"/>
+      <c r="CE13" s="41"/>
       <c r="CF13" s="3">
         <f>CF12/48</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="32" t="s">
-        <v>93</v>
-      </c>
-      <c r="B14" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="29"/>
-      <c r="G14" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
-      <c r="K14" s="30"/>
-      <c r="L14" s="30"/>
+      <c r="A14" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="41"/>
+      <c r="G14" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="46"/>
       <c r="M14" s="1"/>
-      <c r="P14" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q14" s="30"/>
-      <c r="R14" s="30"/>
-      <c r="S14" s="30"/>
-      <c r="T14" s="30"/>
-      <c r="U14" s="30"/>
-      <c r="Y14" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z14" s="30"/>
-      <c r="AA14" s="30"/>
-      <c r="AB14" s="30"/>
-      <c r="AC14" s="30"/>
-      <c r="AD14" s="30"/>
+      <c r="P14" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q14" s="46"/>
+      <c r="R14" s="46"/>
+      <c r="S14" s="46"/>
+      <c r="T14" s="46"/>
+      <c r="U14" s="46"/>
+      <c r="Y14" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z14" s="46"/>
+      <c r="AA14" s="46"/>
+      <c r="AB14" s="46"/>
+      <c r="AC14" s="46"/>
+      <c r="AD14" s="46"/>
       <c r="AE14" s="1"/>
-      <c r="AH14" s="30"/>
-      <c r="AI14" s="30"/>
-      <c r="AJ14" s="30"/>
-      <c r="AK14" s="30"/>
-      <c r="AL14" s="30"/>
-      <c r="AM14" s="30"/>
+      <c r="AH14" s="46"/>
+      <c r="AI14" s="46"/>
+      <c r="AJ14" s="46"/>
+      <c r="AK14" s="46"/>
+      <c r="AL14" s="46"/>
+      <c r="AM14" s="46"/>
       <c r="AN14" s="1"/>
-      <c r="AQ14" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR14" s="30"/>
-      <c r="AS14" s="30"/>
-      <c r="AT14" s="30"/>
-      <c r="AU14" s="30"/>
-      <c r="AV14" s="30"/>
+      <c r="AQ14" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="AR14" s="46"/>
+      <c r="AS14" s="46"/>
+      <c r="AT14" s="46"/>
+      <c r="AU14" s="46"/>
+      <c r="AV14" s="46"/>
       <c r="AW14" s="1"/>
-      <c r="AZ14" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA14" s="30"/>
-      <c r="BB14" s="30"/>
-      <c r="BC14" s="30"/>
-      <c r="BD14" s="30"/>
-      <c r="BE14" s="30"/>
-      <c r="BI14" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="BJ14" s="30"/>
-      <c r="BK14" s="30"/>
-      <c r="BL14" s="30"/>
-      <c r="BM14" s="30"/>
-      <c r="BN14" s="30"/>
-      <c r="BR14" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="BS14" s="30"/>
-      <c r="BT14" s="30"/>
-      <c r="BU14" s="30"/>
-      <c r="BV14" s="30"/>
-      <c r="BW14" s="30"/>
+      <c r="AZ14" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="BA14" s="46"/>
+      <c r="BB14" s="46"/>
+      <c r="BC14" s="46"/>
+      <c r="BD14" s="46"/>
+      <c r="BE14" s="46"/>
+      <c r="BI14" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="BJ14" s="46"/>
+      <c r="BK14" s="46"/>
+      <c r="BL14" s="46"/>
+      <c r="BM14" s="46"/>
+      <c r="BN14" s="46"/>
+      <c r="BR14" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="BS14" s="46"/>
+      <c r="BT14" s="46"/>
+      <c r="BU14" s="46"/>
+      <c r="BV14" s="46"/>
+      <c r="BW14" s="46"/>
     </row>
     <row r="15" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A15" s="33"/>
+      <c r="A15" s="51"/>
       <c r="B15" s="15"/>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
       <c r="G15" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="3" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="J15" s="4"/>
       <c r="K15" s="3" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L15" s="4"/>
       <c r="M15" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="N15">
         <f>(H15+J15+L15)/3</f>
         <v>0</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="Q15" s="4"/>
       <c r="R15" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="S15" s="4"/>
       <c r="T15" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="U15" s="4"/>
       <c r="V15" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="W15">
         <f>(Q15+S15+U15)/3</f>
         <v>0</v>
       </c>
       <c r="Y15" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="Z15" s="4"/>
       <c r="AA15" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AB15" s="4"/>
       <c r="AC15" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="AD15" s="4"/>
       <c r="AE15" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AF15">
         <f>(Z15+AB15+AD15)/3</f>
         <v>0</v>
       </c>
       <c r="AH15" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="AI15" s="4"/>
       <c r="AJ15" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AK15" s="4"/>
       <c r="AL15" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="AM15" s="4"/>
       <c r="AN15" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AO15">
         <f>(AI15+AK15+AM15)/3</f>
         <v>0</v>
       </c>
       <c r="AQ15" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="AR15" s="4"/>
       <c r="AS15" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AT15" s="4"/>
       <c r="AU15" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="AV15" s="4"/>
       <c r="AW15" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AX15">
         <f>(AR15+AT15+AV15)/3</f>
         <v>0</v>
       </c>
       <c r="AZ15" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BA15" s="4"/>
       <c r="BB15" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BC15" s="4"/>
       <c r="BD15" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BE15" s="4"/>
       <c r="BF15" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BG15">
         <f>(BA15+BC15+BE15)/3</f>
         <v>0</v>
       </c>
       <c r="BI15" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BJ15" s="4"/>
       <c r="BK15" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BL15" s="4"/>
       <c r="BM15" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BN15" s="4"/>
       <c r="BO15" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BP15">
         <f>(BJ15+BL15+BN15)/3</f>
         <v>0</v>
       </c>
       <c r="BR15" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BS15" s="4"/>
       <c r="BT15" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BU15" s="4"/>
       <c r="BV15" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BW15" s="4"/>
       <c r="BX15" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BY15">
         <f>(BS15+BU15+BW15)/3</f>
         <v>0</v>
       </c>
       <c r="CA15" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="CB15" s="4">
         <f>H15+Q15+Z15+AI15+AR15+BA15+BJ15+BS15</f>
         <v>0</v>
       </c>
       <c r="CC15" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="CD15" s="4">
         <f>J15+S15+AB15+AK15+AT15+BC15+BL15+BU15</f>
         <v>0</v>
       </c>
       <c r="CE15" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="CF15" s="4">
         <f>L15+U15+AD15+AM15+AV15+BE15+BN15+BW15</f>
@@ -3698,282 +2742,282 @@
       </c>
     </row>
     <row r="16" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A16" s="33"/>
-      <c r="CA16" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="CB16" s="31"/>
-      <c r="CC16" s="31"/>
-      <c r="CD16" s="31"/>
-      <c r="CE16" s="31"/>
+      <c r="A16" s="51"/>
+      <c r="CA16" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="CB16" s="48"/>
+      <c r="CC16" s="48"/>
+      <c r="CD16" s="48"/>
+      <c r="CE16" s="48"/>
       <c r="CF16" s="3">
         <f>(CB15+CD15+CF15)*16</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A17" s="33"/>
-      <c r="CA17" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="CB17" s="28"/>
-      <c r="CC17" s="28"/>
-      <c r="CD17" s="28"/>
-      <c r="CE17" s="29"/>
+      <c r="A17" s="51"/>
+      <c r="CA17" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="CB17" s="40"/>
+      <c r="CC17" s="40"/>
+      <c r="CD17" s="40"/>
+      <c r="CE17" s="41"/>
       <c r="CF17" s="3">
         <f>CF16/48</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="33"/>
-      <c r="B18" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="29"/>
-      <c r="G18" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="30"/>
-      <c r="L18" s="30"/>
+      <c r="A18" s="51"/>
+      <c r="B18" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="41"/>
+      <c r="G18" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18" s="46"/>
+      <c r="I18" s="46"/>
+      <c r="J18" s="46"/>
+      <c r="K18" s="46"/>
+      <c r="L18" s="46"/>
       <c r="M18" s="1"/>
-      <c r="P18" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q18" s="30"/>
-      <c r="R18" s="30"/>
-      <c r="S18" s="30"/>
-      <c r="T18" s="30"/>
-      <c r="U18" s="30"/>
-      <c r="Y18" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z18" s="30"/>
-      <c r="AA18" s="30"/>
-      <c r="AB18" s="30"/>
-      <c r="AC18" s="30"/>
-      <c r="AD18" s="30"/>
+      <c r="P18" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q18" s="46"/>
+      <c r="R18" s="46"/>
+      <c r="S18" s="46"/>
+      <c r="T18" s="46"/>
+      <c r="U18" s="46"/>
+      <c r="Y18" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z18" s="46"/>
+      <c r="AA18" s="46"/>
+      <c r="AB18" s="46"/>
+      <c r="AC18" s="46"/>
+      <c r="AD18" s="46"/>
       <c r="AE18" s="1"/>
-      <c r="AH18" s="30"/>
-      <c r="AI18" s="30"/>
-      <c r="AJ18" s="30"/>
-      <c r="AK18" s="30"/>
-      <c r="AL18" s="30"/>
-      <c r="AM18" s="30"/>
+      <c r="AH18" s="46"/>
+      <c r="AI18" s="46"/>
+      <c r="AJ18" s="46"/>
+      <c r="AK18" s="46"/>
+      <c r="AL18" s="46"/>
+      <c r="AM18" s="46"/>
       <c r="AN18" s="1"/>
-      <c r="AQ18" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR18" s="30"/>
-      <c r="AS18" s="30"/>
-      <c r="AT18" s="30"/>
-      <c r="AU18" s="30"/>
-      <c r="AV18" s="30"/>
+      <c r="AQ18" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="AR18" s="46"/>
+      <c r="AS18" s="46"/>
+      <c r="AT18" s="46"/>
+      <c r="AU18" s="46"/>
+      <c r="AV18" s="46"/>
       <c r="AW18" s="1"/>
-      <c r="AZ18" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA18" s="30"/>
-      <c r="BB18" s="30"/>
-      <c r="BC18" s="30"/>
-      <c r="BD18" s="30"/>
-      <c r="BE18" s="30"/>
-      <c r="BI18" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="BJ18" s="30"/>
-      <c r="BK18" s="30"/>
-      <c r="BL18" s="30"/>
-      <c r="BM18" s="30"/>
-      <c r="BN18" s="30"/>
-      <c r="BR18" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="BS18" s="30"/>
-      <c r="BT18" s="30"/>
-      <c r="BU18" s="30"/>
-      <c r="BV18" s="30"/>
-      <c r="BW18" s="30"/>
+      <c r="AZ18" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="BA18" s="46"/>
+      <c r="BB18" s="46"/>
+      <c r="BC18" s="46"/>
+      <c r="BD18" s="46"/>
+      <c r="BE18" s="46"/>
+      <c r="BI18" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="BJ18" s="46"/>
+      <c r="BK18" s="46"/>
+      <c r="BL18" s="46"/>
+      <c r="BM18" s="46"/>
+      <c r="BN18" s="46"/>
+      <c r="BR18" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="BS18" s="46"/>
+      <c r="BT18" s="46"/>
+      <c r="BU18" s="46"/>
+      <c r="BV18" s="46"/>
+      <c r="BW18" s="46"/>
     </row>
     <row r="19" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A19" s="33"/>
+      <c r="A19" s="51"/>
       <c r="B19" s="15"/>
       <c r="C19" s="15"/>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
       <c r="G19" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="3" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="J19" s="4"/>
       <c r="K19" s="3" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L19" s="4"/>
       <c r="M19" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="N19">
         <f>(H19+J19+L19)/3</f>
         <v>0</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="Q19" s="4"/>
       <c r="R19" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="S19" s="4"/>
       <c r="T19" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="U19" s="4"/>
       <c r="V19" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="W19">
         <f>(Q19+S19+U19)/3</f>
         <v>0</v>
       </c>
       <c r="Y19" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="Z19" s="4"/>
       <c r="AA19" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AB19" s="4"/>
       <c r="AC19" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="AD19" s="4"/>
       <c r="AE19" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AF19">
         <f>(Z19+AB19+AD19)/3</f>
         <v>0</v>
       </c>
       <c r="AH19" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="AI19" s="4"/>
       <c r="AJ19" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AK19" s="4"/>
       <c r="AL19" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="AM19" s="4"/>
       <c r="AN19" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AO19">
         <f>(AI19+AK19+AM19)/3</f>
         <v>0</v>
       </c>
       <c r="AQ19" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="AR19" s="4"/>
       <c r="AS19" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AT19" s="4"/>
       <c r="AU19" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="AV19" s="4"/>
       <c r="AW19" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AX19">
         <f>(AR19+AT19+AV19)/3</f>
         <v>0</v>
       </c>
       <c r="AZ19" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BA19" s="4"/>
       <c r="BB19" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BC19" s="4"/>
       <c r="BD19" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BE19" s="4"/>
       <c r="BF19" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BG19">
         <f>(BA19+BC19+BE19)/3</f>
         <v>0</v>
       </c>
       <c r="BI19" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BJ19" s="4"/>
       <c r="BK19" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BL19" s="4"/>
       <c r="BM19" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BN19" s="4"/>
       <c r="BO19" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BP19">
         <f>(BJ19+BL19+BN19)/3</f>
         <v>0</v>
       </c>
       <c r="BR19" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BS19" s="4"/>
       <c r="BT19" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BU19" s="4"/>
       <c r="BV19" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BW19" s="4"/>
       <c r="BX19" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BY19">
         <f>(BS19+BU19+BW19)/3</f>
         <v>0</v>
       </c>
       <c r="CA19" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="CB19" s="4">
         <f>H19+Q19+Z19+AI19+AR19+BA19+BJ19+BS19</f>
         <v>0</v>
       </c>
       <c r="CC19" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="CD19" s="4">
         <f>J19+S19+AB19+AK19+AT19+BC19+BL19+BU19</f>
         <v>0</v>
       </c>
       <c r="CE19" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="CF19" s="4">
         <f>L19+U19+AD19+AM19+AV19+BE19+BN19+BW19</f>
@@ -3981,284 +3025,284 @@
       </c>
     </row>
     <row r="20" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A20" s="33"/>
-      <c r="CA20" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="CB20" s="31"/>
-      <c r="CC20" s="31"/>
-      <c r="CD20" s="31"/>
-      <c r="CE20" s="31"/>
+      <c r="A20" s="51"/>
+      <c r="CA20" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="CB20" s="48"/>
+      <c r="CC20" s="48"/>
+      <c r="CD20" s="48"/>
+      <c r="CE20" s="48"/>
       <c r="CF20" s="3">
         <f>(CB19+CD19+CF19)*16</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A21" s="34"/>
-      <c r="CA21" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="CB21" s="28"/>
-      <c r="CC21" s="28"/>
-      <c r="CD21" s="28"/>
-      <c r="CE21" s="29"/>
+      <c r="A21" s="52"/>
+      <c r="CA21" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="CB21" s="40"/>
+      <c r="CC21" s="40"/>
+      <c r="CD21" s="40"/>
+      <c r="CE21" s="41"/>
       <c r="CF21" s="3">
         <f>CF20/48</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="32" t="s">
-        <v>94</v>
-      </c>
-      <c r="B22" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="29"/>
-      <c r="G22" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="H22" s="30"/>
-      <c r="I22" s="30"/>
-      <c r="J22" s="30"/>
-      <c r="K22" s="30"/>
-      <c r="L22" s="30"/>
+      <c r="A22" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="B22" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="40"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="41"/>
+      <c r="G22" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="H22" s="46"/>
+      <c r="I22" s="46"/>
+      <c r="J22" s="46"/>
+      <c r="K22" s="46"/>
+      <c r="L22" s="46"/>
       <c r="M22" s="1"/>
-      <c r="P22" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q22" s="30"/>
-      <c r="R22" s="30"/>
-      <c r="S22" s="30"/>
-      <c r="T22" s="30"/>
-      <c r="U22" s="30"/>
-      <c r="Y22" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z22" s="30"/>
-      <c r="AA22" s="30"/>
-      <c r="AB22" s="30"/>
-      <c r="AC22" s="30"/>
-      <c r="AD22" s="30"/>
+      <c r="P22" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q22" s="46"/>
+      <c r="R22" s="46"/>
+      <c r="S22" s="46"/>
+      <c r="T22" s="46"/>
+      <c r="U22" s="46"/>
+      <c r="Y22" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z22" s="46"/>
+      <c r="AA22" s="46"/>
+      <c r="AB22" s="46"/>
+      <c r="AC22" s="46"/>
+      <c r="AD22" s="46"/>
       <c r="AE22" s="1"/>
-      <c r="AH22" s="30"/>
-      <c r="AI22" s="30"/>
-      <c r="AJ22" s="30"/>
-      <c r="AK22" s="30"/>
-      <c r="AL22" s="30"/>
-      <c r="AM22" s="30"/>
+      <c r="AH22" s="46"/>
+      <c r="AI22" s="46"/>
+      <c r="AJ22" s="46"/>
+      <c r="AK22" s="46"/>
+      <c r="AL22" s="46"/>
+      <c r="AM22" s="46"/>
       <c r="AN22" s="1"/>
-      <c r="AQ22" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR22" s="30"/>
-      <c r="AS22" s="30"/>
-      <c r="AT22" s="30"/>
-      <c r="AU22" s="30"/>
-      <c r="AV22" s="30"/>
+      <c r="AQ22" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="AR22" s="46"/>
+      <c r="AS22" s="46"/>
+      <c r="AT22" s="46"/>
+      <c r="AU22" s="46"/>
+      <c r="AV22" s="46"/>
       <c r="AW22" s="1"/>
-      <c r="AZ22" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA22" s="30"/>
-      <c r="BB22" s="30"/>
-      <c r="BC22" s="30"/>
-      <c r="BD22" s="30"/>
-      <c r="BE22" s="30"/>
-      <c r="BI22" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="BJ22" s="30"/>
-      <c r="BK22" s="30"/>
-      <c r="BL22" s="30"/>
-      <c r="BM22" s="30"/>
-      <c r="BN22" s="30"/>
-      <c r="BR22" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="BS22" s="30"/>
-      <c r="BT22" s="30"/>
-      <c r="BU22" s="30"/>
-      <c r="BV22" s="30"/>
-      <c r="BW22" s="30"/>
+      <c r="AZ22" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="BA22" s="46"/>
+      <c r="BB22" s="46"/>
+      <c r="BC22" s="46"/>
+      <c r="BD22" s="46"/>
+      <c r="BE22" s="46"/>
+      <c r="BI22" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="BJ22" s="46"/>
+      <c r="BK22" s="46"/>
+      <c r="BL22" s="46"/>
+      <c r="BM22" s="46"/>
+      <c r="BN22" s="46"/>
+      <c r="BR22" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="BS22" s="46"/>
+      <c r="BT22" s="46"/>
+      <c r="BU22" s="46"/>
+      <c r="BV22" s="46"/>
+      <c r="BW22" s="46"/>
     </row>
     <row r="23" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A23" s="33"/>
+      <c r="A23" s="51"/>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
       <c r="E23" s="15"/>
       <c r="G23" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="H23" s="4"/>
       <c r="I23" s="3" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="J23" s="4"/>
       <c r="K23" s="3" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L23" s="4"/>
       <c r="M23" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="N23">
         <f>(H23+J23+L23)/3</f>
         <v>0</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="Q23" s="4"/>
       <c r="R23" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="S23" s="4"/>
       <c r="T23" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="U23" s="4"/>
       <c r="V23" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="W23">
         <f>(Q23+S23+U23)/3</f>
         <v>0</v>
       </c>
       <c r="Y23" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="Z23" s="4"/>
       <c r="AA23" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AB23" s="4"/>
       <c r="AC23" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="AD23" s="4"/>
       <c r="AE23" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AF23">
         <f>(Z23+AB23+AD23)/3</f>
         <v>0</v>
       </c>
       <c r="AH23" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="AI23" s="4"/>
       <c r="AJ23" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AK23" s="4"/>
       <c r="AL23" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="AM23" s="4"/>
       <c r="AN23" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AO23">
         <f>(AI23+AK23+AM23)/3</f>
         <v>0</v>
       </c>
       <c r="AQ23" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="AR23" s="4"/>
       <c r="AS23" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AT23" s="4"/>
       <c r="AU23" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="AV23" s="4"/>
       <c r="AW23" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AX23">
         <f>(AR23+AT23+AV23)/3</f>
         <v>0</v>
       </c>
       <c r="AZ23" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BA23" s="4"/>
       <c r="BB23" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BC23" s="4"/>
       <c r="BD23" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BE23" s="4"/>
       <c r="BF23" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BG23">
         <f>(BA23+BC23+BE23)/3</f>
         <v>0</v>
       </c>
       <c r="BI23" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BJ23" s="4"/>
       <c r="BK23" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BL23" s="4"/>
       <c r="BM23" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BN23" s="4"/>
       <c r="BO23" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BP23">
         <f>(BJ23+BL23+BN23)/3</f>
         <v>0</v>
       </c>
       <c r="BR23" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BS23" s="4"/>
       <c r="BT23" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BU23" s="4"/>
       <c r="BV23" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BW23" s="4"/>
       <c r="BX23" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BY23">
         <f>(BS23+BU23+BW23)/3</f>
         <v>0</v>
       </c>
       <c r="CA23" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="CB23" s="4">
         <f>H23+Q23+Z23+AI23+AR23+BA23+BJ23+BS23</f>
         <v>0</v>
       </c>
       <c r="CC23" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="CD23" s="4">
         <f>J23+S23+AB23+AK23+AT23+BC23+BL23+BU23</f>
         <v>0</v>
       </c>
       <c r="CE23" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="CF23" s="4">
         <f>L23+U23+AD23+AM23+AV23+BE23+BN23+BW23</f>
@@ -4266,282 +3310,282 @@
       </c>
     </row>
     <row r="24" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A24" s="33"/>
-      <c r="CA24" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="CB24" s="31"/>
-      <c r="CC24" s="31"/>
-      <c r="CD24" s="31"/>
-      <c r="CE24" s="31"/>
+      <c r="A24" s="51"/>
+      <c r="CA24" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="CB24" s="48"/>
+      <c r="CC24" s="48"/>
+      <c r="CD24" s="48"/>
+      <c r="CE24" s="48"/>
       <c r="CF24" s="3">
         <f>(CB23+CD23+CF23)*16</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A25" s="33"/>
-      <c r="CA25" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="CB25" s="28"/>
-      <c r="CC25" s="28"/>
-      <c r="CD25" s="28"/>
-      <c r="CE25" s="29"/>
+      <c r="A25" s="51"/>
+      <c r="CA25" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="CB25" s="40"/>
+      <c r="CC25" s="40"/>
+      <c r="CD25" s="40"/>
+      <c r="CE25" s="41"/>
       <c r="CF25" s="3">
         <f>CF24/48</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="33"/>
-      <c r="B26" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="29"/>
-      <c r="G26" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="30"/>
-      <c r="K26" s="30"/>
-      <c r="L26" s="30"/>
+      <c r="A26" s="51"/>
+      <c r="B26" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="41"/>
+      <c r="G26" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="H26" s="46"/>
+      <c r="I26" s="46"/>
+      <c r="J26" s="46"/>
+      <c r="K26" s="46"/>
+      <c r="L26" s="46"/>
       <c r="M26" s="1"/>
-      <c r="P26" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q26" s="30"/>
-      <c r="R26" s="30"/>
-      <c r="S26" s="30"/>
-      <c r="T26" s="30"/>
-      <c r="U26" s="30"/>
-      <c r="Y26" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z26" s="30"/>
-      <c r="AA26" s="30"/>
-      <c r="AB26" s="30"/>
-      <c r="AC26" s="30"/>
-      <c r="AD26" s="30"/>
+      <c r="P26" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q26" s="46"/>
+      <c r="R26" s="46"/>
+      <c r="S26" s="46"/>
+      <c r="T26" s="46"/>
+      <c r="U26" s="46"/>
+      <c r="Y26" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z26" s="46"/>
+      <c r="AA26" s="46"/>
+      <c r="AB26" s="46"/>
+      <c r="AC26" s="46"/>
+      <c r="AD26" s="46"/>
       <c r="AE26" s="1"/>
-      <c r="AH26" s="30"/>
-      <c r="AI26" s="30"/>
-      <c r="AJ26" s="30"/>
-      <c r="AK26" s="30"/>
-      <c r="AL26" s="30"/>
-      <c r="AM26" s="30"/>
+      <c r="AH26" s="46"/>
+      <c r="AI26" s="46"/>
+      <c r="AJ26" s="46"/>
+      <c r="AK26" s="46"/>
+      <c r="AL26" s="46"/>
+      <c r="AM26" s="46"/>
       <c r="AN26" s="1"/>
-      <c r="AQ26" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR26" s="30"/>
-      <c r="AS26" s="30"/>
-      <c r="AT26" s="30"/>
-      <c r="AU26" s="30"/>
-      <c r="AV26" s="30"/>
+      <c r="AQ26" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="AR26" s="46"/>
+      <c r="AS26" s="46"/>
+      <c r="AT26" s="46"/>
+      <c r="AU26" s="46"/>
+      <c r="AV26" s="46"/>
       <c r="AW26" s="1"/>
-      <c r="AZ26" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA26" s="30"/>
-      <c r="BB26" s="30"/>
-      <c r="BC26" s="30"/>
-      <c r="BD26" s="30"/>
-      <c r="BE26" s="30"/>
-      <c r="BI26" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="BJ26" s="30"/>
-      <c r="BK26" s="30"/>
-      <c r="BL26" s="30"/>
-      <c r="BM26" s="30"/>
-      <c r="BN26" s="30"/>
-      <c r="BR26" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="BS26" s="30"/>
-      <c r="BT26" s="30"/>
-      <c r="BU26" s="30"/>
-      <c r="BV26" s="30"/>
-      <c r="BW26" s="30"/>
+      <c r="AZ26" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="BA26" s="46"/>
+      <c r="BB26" s="46"/>
+      <c r="BC26" s="46"/>
+      <c r="BD26" s="46"/>
+      <c r="BE26" s="46"/>
+      <c r="BI26" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="BJ26" s="46"/>
+      <c r="BK26" s="46"/>
+      <c r="BL26" s="46"/>
+      <c r="BM26" s="46"/>
+      <c r="BN26" s="46"/>
+      <c r="BR26" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="BS26" s="46"/>
+      <c r="BT26" s="46"/>
+      <c r="BU26" s="46"/>
+      <c r="BV26" s="46"/>
+      <c r="BW26" s="46"/>
     </row>
     <row r="27" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A27" s="33"/>
+      <c r="A27" s="51"/>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
       <c r="D27" s="15"/>
       <c r="E27" s="15"/>
       <c r="G27" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="H27" s="4"/>
       <c r="I27" s="3" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="J27" s="4"/>
       <c r="K27" s="3" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L27" s="4"/>
       <c r="M27" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="N27">
         <f>(H27+J27+L27)/3</f>
         <v>0</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="Q27" s="4"/>
       <c r="R27" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="S27" s="4"/>
       <c r="T27" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="U27" s="4"/>
       <c r="V27" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="W27">
         <f>(Q27+S27+U27)/3</f>
         <v>0</v>
       </c>
       <c r="Y27" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="Z27" s="4"/>
       <c r="AA27" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AB27" s="4"/>
       <c r="AC27" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="AD27" s="4"/>
       <c r="AE27" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AF27">
         <f>(Z27+AB27+AD27)/3</f>
         <v>0</v>
       </c>
       <c r="AH27" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="AI27" s="4"/>
       <c r="AJ27" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AK27" s="4"/>
       <c r="AL27" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="AM27" s="4"/>
       <c r="AN27" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AO27">
         <f>(AI27+AK27+AM27)/3</f>
         <v>0</v>
       </c>
       <c r="AQ27" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="AR27" s="4"/>
       <c r="AS27" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AT27" s="4"/>
       <c r="AU27" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="AV27" s="4"/>
       <c r="AW27" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AX27">
         <f>(AR27+AT27+AV27)/3</f>
         <v>0</v>
       </c>
       <c r="AZ27" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BA27" s="4"/>
       <c r="BB27" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BC27" s="4"/>
       <c r="BD27" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BE27" s="4"/>
       <c r="BF27" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BG27">
         <f>(BA27+BC27+BE27)/3</f>
         <v>0</v>
       </c>
       <c r="BI27" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BJ27" s="4"/>
       <c r="BK27" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BL27" s="4"/>
       <c r="BM27" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BN27" s="4"/>
       <c r="BO27" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BP27">
         <f>(BJ27+BL27+BN27)/3</f>
         <v>0</v>
       </c>
       <c r="BR27" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BS27" s="4"/>
       <c r="BT27" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BU27" s="4"/>
       <c r="BV27" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BW27" s="4"/>
       <c r="BX27" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BY27">
         <f>(BS27+BU27+BW27)/3</f>
         <v>0</v>
       </c>
       <c r="CA27" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="CB27" s="4">
         <f>H27+Q27+Z27+AI27+AR27+BA27+BJ27+BS27</f>
         <v>0</v>
       </c>
       <c r="CC27" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="CD27" s="4">
         <f>J27+S27+AB27+AK27+AT27+BC27+BL27+BU27</f>
         <v>0</v>
       </c>
       <c r="CE27" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="CF27" s="4">
         <f>L27+U27+AD27+AM27+AV27+BE27+BN27+BW27</f>
@@ -4549,284 +3593,284 @@
       </c>
     </row>
     <row r="28" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A28" s="33"/>
-      <c r="CA28" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="CB28" s="31"/>
-      <c r="CC28" s="31"/>
-      <c r="CD28" s="31"/>
-      <c r="CE28" s="31"/>
+      <c r="A28" s="51"/>
+      <c r="CA28" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="CB28" s="48"/>
+      <c r="CC28" s="48"/>
+      <c r="CD28" s="48"/>
+      <c r="CE28" s="48"/>
       <c r="CF28" s="3">
         <f>(CB27+CD27+CF27)*16</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A29" s="34"/>
-      <c r="CA29" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="CB29" s="28"/>
-      <c r="CC29" s="28"/>
-      <c r="CD29" s="28"/>
-      <c r="CE29" s="29"/>
+      <c r="A29" s="52"/>
+      <c r="CA29" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="CB29" s="40"/>
+      <c r="CC29" s="40"/>
+      <c r="CD29" s="40"/>
+      <c r="CE29" s="41"/>
       <c r="CF29" s="3">
         <f>CF28/48</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="40" t="s">
-        <v>95</v>
-      </c>
-      <c r="B30" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="29"/>
-      <c r="G30" s="30" t="s">
+      <c r="A30" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="B30" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="H30" s="30"/>
-      <c r="I30" s="30"/>
-      <c r="J30" s="30"/>
-      <c r="K30" s="30"/>
-      <c r="L30" s="30"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="41"/>
+      <c r="G30" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="H30" s="46"/>
+      <c r="I30" s="46"/>
+      <c r="J30" s="46"/>
+      <c r="K30" s="46"/>
+      <c r="L30" s="46"/>
       <c r="M30" s="1"/>
-      <c r="P30" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q30" s="30"/>
-      <c r="R30" s="30"/>
-      <c r="S30" s="30"/>
-      <c r="T30" s="30"/>
-      <c r="U30" s="30"/>
-      <c r="Y30" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z30" s="30"/>
-      <c r="AA30" s="30"/>
-      <c r="AB30" s="30"/>
-      <c r="AC30" s="30"/>
-      <c r="AD30" s="30"/>
+      <c r="P30" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q30" s="46"/>
+      <c r="R30" s="46"/>
+      <c r="S30" s="46"/>
+      <c r="T30" s="46"/>
+      <c r="U30" s="46"/>
+      <c r="Y30" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z30" s="46"/>
+      <c r="AA30" s="46"/>
+      <c r="AB30" s="46"/>
+      <c r="AC30" s="46"/>
+      <c r="AD30" s="46"/>
       <c r="AE30" s="1"/>
-      <c r="AH30" s="30"/>
-      <c r="AI30" s="30"/>
-      <c r="AJ30" s="30"/>
-      <c r="AK30" s="30"/>
-      <c r="AL30" s="30"/>
-      <c r="AM30" s="30"/>
+      <c r="AH30" s="46"/>
+      <c r="AI30" s="46"/>
+      <c r="AJ30" s="46"/>
+      <c r="AK30" s="46"/>
+      <c r="AL30" s="46"/>
+      <c r="AM30" s="46"/>
       <c r="AN30" s="1"/>
-      <c r="AQ30" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR30" s="30"/>
-      <c r="AS30" s="30"/>
-      <c r="AT30" s="30"/>
-      <c r="AU30" s="30"/>
-      <c r="AV30" s="30"/>
+      <c r="AQ30" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="AR30" s="46"/>
+      <c r="AS30" s="46"/>
+      <c r="AT30" s="46"/>
+      <c r="AU30" s="46"/>
+      <c r="AV30" s="46"/>
       <c r="AW30" s="1"/>
-      <c r="AZ30" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA30" s="30"/>
-      <c r="BB30" s="30"/>
-      <c r="BC30" s="30"/>
-      <c r="BD30" s="30"/>
-      <c r="BE30" s="30"/>
-      <c r="BI30" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="BJ30" s="30"/>
-      <c r="BK30" s="30"/>
-      <c r="BL30" s="30"/>
-      <c r="BM30" s="30"/>
-      <c r="BN30" s="30"/>
-      <c r="BR30" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="BS30" s="30"/>
-      <c r="BT30" s="30"/>
-      <c r="BU30" s="30"/>
-      <c r="BV30" s="30"/>
-      <c r="BW30" s="30"/>
+      <c r="AZ30" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="BA30" s="46"/>
+      <c r="BB30" s="46"/>
+      <c r="BC30" s="46"/>
+      <c r="BD30" s="46"/>
+      <c r="BE30" s="46"/>
+      <c r="BI30" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="BJ30" s="46"/>
+      <c r="BK30" s="46"/>
+      <c r="BL30" s="46"/>
+      <c r="BM30" s="46"/>
+      <c r="BN30" s="46"/>
+      <c r="BR30" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="BS30" s="46"/>
+      <c r="BT30" s="46"/>
+      <c r="BU30" s="46"/>
+      <c r="BV30" s="46"/>
+      <c r="BW30" s="46"/>
     </row>
     <row r="31" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A31" s="40"/>
+      <c r="A31" s="42"/>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
       <c r="D31" s="15"/>
       <c r="E31" s="15"/>
       <c r="G31" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="H31" s="4"/>
       <c r="I31" s="3" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="J31" s="4"/>
       <c r="K31" s="3" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L31" s="4"/>
       <c r="M31" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="N31">
         <f>(H31+J31+L31)/3</f>
         <v>0</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="Q31" s="4"/>
       <c r="R31" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="S31" s="4"/>
       <c r="T31" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="U31" s="4"/>
       <c r="V31" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="W31">
         <f>(Q31+S31+U31)/3</f>
         <v>0</v>
       </c>
       <c r="Y31" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="Z31" s="4"/>
       <c r="AA31" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AB31" s="4"/>
       <c r="AC31" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="AD31" s="4"/>
       <c r="AE31" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AF31">
         <f>(Z31+AB31+AD31)/3</f>
         <v>0</v>
       </c>
       <c r="AH31" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="AI31" s="4"/>
       <c r="AJ31" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AK31" s="4"/>
       <c r="AL31" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="AM31" s="4"/>
       <c r="AN31" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AO31">
         <f>(AI31+AK31+AM31)/3</f>
         <v>0</v>
       </c>
       <c r="AQ31" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="AR31" s="4"/>
       <c r="AS31" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AT31" s="4"/>
       <c r="AU31" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="AV31" s="4"/>
       <c r="AW31" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AX31">
         <f>(AR31+AT31+AV31)/3</f>
         <v>0</v>
       </c>
       <c r="AZ31" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BA31" s="4"/>
       <c r="BB31" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BC31" s="4"/>
       <c r="BD31" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BE31" s="4"/>
       <c r="BF31" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BG31">
         <f>(BA31+BC31+BE31)/3</f>
         <v>0</v>
       </c>
       <c r="BI31" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BJ31" s="4"/>
       <c r="BK31" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BL31" s="4"/>
       <c r="BM31" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BN31" s="4"/>
       <c r="BO31" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BP31">
         <f>(BJ31+BL31+BN31)/3</f>
         <v>0</v>
       </c>
       <c r="BR31" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BS31" s="4"/>
       <c r="BT31" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BU31" s="4"/>
       <c r="BV31" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BW31" s="4"/>
       <c r="BX31" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BY31">
         <f>(BS31+BU31+BW31)/3</f>
         <v>0</v>
       </c>
       <c r="CA31" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="CB31" s="4">
         <f>H31+Q31+Z31+AI31+AR31+BA31+BJ31+BS31</f>
         <v>0</v>
       </c>
       <c r="CC31" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="CD31" s="4">
         <f>J31+S31+AB31+AK31+AT31+BC31+BL31+BU31</f>
         <v>0</v>
       </c>
       <c r="CE31" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="CF31" s="4">
         <f>L31+U31+AD31+AM31+AV31+BE31+BN31+BW31</f>
@@ -4834,282 +3878,282 @@
       </c>
     </row>
     <row r="32" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A32" s="40"/>
-      <c r="CA32" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="CB32" s="31"/>
-      <c r="CC32" s="31"/>
-      <c r="CD32" s="31"/>
-      <c r="CE32" s="31"/>
+      <c r="A32" s="42"/>
+      <c r="CA32" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="CB32" s="48"/>
+      <c r="CC32" s="48"/>
+      <c r="CD32" s="48"/>
+      <c r="CE32" s="48"/>
       <c r="CF32" s="3">
         <f>(CB31+CD31+CF31)*16</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A33" s="40"/>
-      <c r="CA33" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="CB33" s="28"/>
-      <c r="CC33" s="28"/>
-      <c r="CD33" s="28"/>
-      <c r="CE33" s="29"/>
+      <c r="A33" s="42"/>
+      <c r="CA33" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="CB33" s="40"/>
+      <c r="CC33" s="40"/>
+      <c r="CD33" s="40"/>
+      <c r="CE33" s="41"/>
       <c r="CF33" s="3">
         <f>CF32/48</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="40"/>
-      <c r="B34" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="29"/>
-      <c r="G34" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="H34" s="30"/>
-      <c r="I34" s="30"/>
-      <c r="J34" s="30"/>
-      <c r="K34" s="30"/>
-      <c r="L34" s="30"/>
+      <c r="A34" s="42"/>
+      <c r="B34" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="41"/>
+      <c r="G34" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="H34" s="46"/>
+      <c r="I34" s="46"/>
+      <c r="J34" s="46"/>
+      <c r="K34" s="46"/>
+      <c r="L34" s="46"/>
       <c r="M34" s="1"/>
-      <c r="P34" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q34" s="30"/>
-      <c r="R34" s="30"/>
-      <c r="S34" s="30"/>
-      <c r="T34" s="30"/>
-      <c r="U34" s="30"/>
-      <c r="Y34" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z34" s="30"/>
-      <c r="AA34" s="30"/>
-      <c r="AB34" s="30"/>
-      <c r="AC34" s="30"/>
-      <c r="AD34" s="30"/>
+      <c r="P34" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q34" s="46"/>
+      <c r="R34" s="46"/>
+      <c r="S34" s="46"/>
+      <c r="T34" s="46"/>
+      <c r="U34" s="46"/>
+      <c r="Y34" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z34" s="46"/>
+      <c r="AA34" s="46"/>
+      <c r="AB34" s="46"/>
+      <c r="AC34" s="46"/>
+      <c r="AD34" s="46"/>
       <c r="AE34" s="1"/>
-      <c r="AH34" s="30"/>
-      <c r="AI34" s="30"/>
-      <c r="AJ34" s="30"/>
-      <c r="AK34" s="30"/>
-      <c r="AL34" s="30"/>
-      <c r="AM34" s="30"/>
+      <c r="AH34" s="46"/>
+      <c r="AI34" s="46"/>
+      <c r="AJ34" s="46"/>
+      <c r="AK34" s="46"/>
+      <c r="AL34" s="46"/>
+      <c r="AM34" s="46"/>
       <c r="AN34" s="1"/>
-      <c r="AQ34" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR34" s="30"/>
-      <c r="AS34" s="30"/>
-      <c r="AT34" s="30"/>
-      <c r="AU34" s="30"/>
-      <c r="AV34" s="30"/>
+      <c r="AQ34" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="AR34" s="46"/>
+      <c r="AS34" s="46"/>
+      <c r="AT34" s="46"/>
+      <c r="AU34" s="46"/>
+      <c r="AV34" s="46"/>
       <c r="AW34" s="1"/>
-      <c r="AZ34" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA34" s="30"/>
-      <c r="BB34" s="30"/>
-      <c r="BC34" s="30"/>
-      <c r="BD34" s="30"/>
-      <c r="BE34" s="30"/>
-      <c r="BI34" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="BJ34" s="30"/>
-      <c r="BK34" s="30"/>
-      <c r="BL34" s="30"/>
-      <c r="BM34" s="30"/>
-      <c r="BN34" s="30"/>
-      <c r="BR34" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="BS34" s="30"/>
-      <c r="BT34" s="30"/>
-      <c r="BU34" s="30"/>
-      <c r="BV34" s="30"/>
-      <c r="BW34" s="30"/>
+      <c r="AZ34" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="BA34" s="46"/>
+      <c r="BB34" s="46"/>
+      <c r="BC34" s="46"/>
+      <c r="BD34" s="46"/>
+      <c r="BE34" s="46"/>
+      <c r="BI34" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="BJ34" s="46"/>
+      <c r="BK34" s="46"/>
+      <c r="BL34" s="46"/>
+      <c r="BM34" s="46"/>
+      <c r="BN34" s="46"/>
+      <c r="BR34" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="BS34" s="46"/>
+      <c r="BT34" s="46"/>
+      <c r="BU34" s="46"/>
+      <c r="BV34" s="46"/>
+      <c r="BW34" s="46"/>
     </row>
     <row r="35" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A35" s="40"/>
+      <c r="A35" s="42"/>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
       <c r="D35" s="15"/>
       <c r="E35" s="15"/>
       <c r="G35" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="H35" s="4"/>
       <c r="I35" s="3" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="J35" s="4"/>
       <c r="K35" s="3" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L35" s="4"/>
       <c r="M35" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="N35">
         <f>(H35+J35+L35)/3</f>
         <v>0</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="Q35" s="4"/>
       <c r="R35" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="S35" s="4"/>
       <c r="T35" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="U35" s="4"/>
       <c r="V35" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="W35">
         <f>(Q35+S35+U35)/3</f>
         <v>0</v>
       </c>
       <c r="Y35" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="Z35" s="4"/>
       <c r="AA35" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AB35" s="4"/>
       <c r="AC35" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="AD35" s="4"/>
       <c r="AE35" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AF35">
         <f>(Z35+AB35+AD35)/3</f>
         <v>0</v>
       </c>
       <c r="AH35" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="AI35" s="4"/>
       <c r="AJ35" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AK35" s="4"/>
       <c r="AL35" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="AM35" s="4"/>
       <c r="AN35" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AO35">
         <f>(AI35+AK35+AM35)/3</f>
         <v>0</v>
       </c>
       <c r="AQ35" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="AR35" s="4"/>
       <c r="AS35" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AT35" s="4"/>
       <c r="AU35" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="AV35" s="4"/>
       <c r="AW35" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AX35">
         <f>(AR35+AT35+AV35)/3</f>
         <v>0</v>
       </c>
       <c r="AZ35" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BA35" s="4"/>
       <c r="BB35" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BC35" s="4"/>
       <c r="BD35" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BE35" s="4"/>
       <c r="BF35" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BG35">
         <f>(BA35+BC35+BE35)/3</f>
         <v>0</v>
       </c>
       <c r="BI35" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BJ35" s="4"/>
       <c r="BK35" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BL35" s="4"/>
       <c r="BM35" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BN35" s="4"/>
       <c r="BO35" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BP35">
         <f>(BJ35+BL35+BN35)/3</f>
         <v>0</v>
       </c>
       <c r="BR35" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BS35" s="4"/>
       <c r="BT35" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BU35" s="4"/>
       <c r="BV35" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BW35" s="4"/>
       <c r="BX35" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BY35">
         <f>(BS35+BU35+BW35)/3</f>
         <v>0</v>
       </c>
       <c r="CA35" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="CB35" s="4">
         <f>H35+Q35+Z35+AI35+AR35+BA35+BJ35+BS35</f>
         <v>0</v>
       </c>
       <c r="CC35" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="CD35" s="4">
         <f>J35+S35+AB35+AK35+AT35+BC35+BL35+BU35</f>
         <v>0</v>
       </c>
       <c r="CE35" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="CF35" s="4">
         <f>L35+U35+AD35+AM35+AV35+BE35+BN35+BW35</f>
@@ -5117,284 +4161,284 @@
       </c>
     </row>
     <row r="36" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A36" s="40"/>
-      <c r="CA36" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="CB36" s="31"/>
-      <c r="CC36" s="31"/>
-      <c r="CD36" s="31"/>
-      <c r="CE36" s="31"/>
+      <c r="A36" s="42"/>
+      <c r="CA36" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="CB36" s="48"/>
+      <c r="CC36" s="48"/>
+      <c r="CD36" s="48"/>
+      <c r="CE36" s="48"/>
       <c r="CF36" s="3">
         <f>(CB35+CD35+CF35)*16</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A37" s="40"/>
-      <c r="CA37" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="CB37" s="28"/>
-      <c r="CC37" s="28"/>
-      <c r="CD37" s="28"/>
-      <c r="CE37" s="29"/>
+      <c r="A37" s="42"/>
+      <c r="CA37" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="CB37" s="40"/>
+      <c r="CC37" s="40"/>
+      <c r="CD37" s="40"/>
+      <c r="CE37" s="41"/>
       <c r="CF37" s="3">
         <f>CF36/48</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="B38" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="29"/>
-      <c r="G38" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="H38" s="38"/>
-      <c r="I38" s="38"/>
-      <c r="J38" s="38"/>
-      <c r="K38" s="38"/>
-      <c r="L38" s="39"/>
+      <c r="A38" s="42" t="s">
+        <v>84</v>
+      </c>
+      <c r="B38" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" s="40"/>
+      <c r="D38" s="40"/>
+      <c r="E38" s="41"/>
+      <c r="G38" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="H38" s="44"/>
+      <c r="I38" s="44"/>
+      <c r="J38" s="44"/>
+      <c r="K38" s="44"/>
+      <c r="L38" s="45"/>
       <c r="M38" s="1"/>
-      <c r="P38" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q38" s="38"/>
-      <c r="R38" s="38"/>
-      <c r="S38" s="38"/>
-      <c r="T38" s="38"/>
-      <c r="U38" s="39"/>
-      <c r="Y38" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z38" s="38"/>
-      <c r="AA38" s="38"/>
-      <c r="AB38" s="38"/>
-      <c r="AC38" s="38"/>
-      <c r="AD38" s="39"/>
+      <c r="P38" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q38" s="44"/>
+      <c r="R38" s="44"/>
+      <c r="S38" s="44"/>
+      <c r="T38" s="44"/>
+      <c r="U38" s="45"/>
+      <c r="Y38" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z38" s="44"/>
+      <c r="AA38" s="44"/>
+      <c r="AB38" s="44"/>
+      <c r="AC38" s="44"/>
+      <c r="AD38" s="45"/>
       <c r="AE38" s="1"/>
-      <c r="AH38" s="37"/>
-      <c r="AI38" s="38"/>
-      <c r="AJ38" s="38"/>
-      <c r="AK38" s="38"/>
-      <c r="AL38" s="38"/>
-      <c r="AM38" s="39"/>
+      <c r="AH38" s="43"/>
+      <c r="AI38" s="44"/>
+      <c r="AJ38" s="44"/>
+      <c r="AK38" s="44"/>
+      <c r="AL38" s="44"/>
+      <c r="AM38" s="45"/>
       <c r="AN38" s="1"/>
-      <c r="AQ38" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR38" s="38"/>
-      <c r="AS38" s="38"/>
-      <c r="AT38" s="38"/>
-      <c r="AU38" s="38"/>
-      <c r="AV38" s="39"/>
+      <c r="AQ38" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="AR38" s="44"/>
+      <c r="AS38" s="44"/>
+      <c r="AT38" s="44"/>
+      <c r="AU38" s="44"/>
+      <c r="AV38" s="45"/>
       <c r="AW38" s="1"/>
-      <c r="AZ38" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA38" s="38"/>
-      <c r="BB38" s="38"/>
-      <c r="BC38" s="38"/>
-      <c r="BD38" s="38"/>
-      <c r="BE38" s="39"/>
-      <c r="BI38" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="BJ38" s="38"/>
-      <c r="BK38" s="38"/>
-      <c r="BL38" s="38"/>
-      <c r="BM38" s="38"/>
-      <c r="BN38" s="39"/>
-      <c r="BR38" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="BS38" s="38"/>
-      <c r="BT38" s="38"/>
-      <c r="BU38" s="38"/>
-      <c r="BV38" s="38"/>
-      <c r="BW38" s="39"/>
+      <c r="AZ38" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="BA38" s="44"/>
+      <c r="BB38" s="44"/>
+      <c r="BC38" s="44"/>
+      <c r="BD38" s="44"/>
+      <c r="BE38" s="45"/>
+      <c r="BI38" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="BJ38" s="44"/>
+      <c r="BK38" s="44"/>
+      <c r="BL38" s="44"/>
+      <c r="BM38" s="44"/>
+      <c r="BN38" s="45"/>
+      <c r="BR38" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="BS38" s="44"/>
+      <c r="BT38" s="44"/>
+      <c r="BU38" s="44"/>
+      <c r="BV38" s="44"/>
+      <c r="BW38" s="45"/>
     </row>
     <row r="39" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A39" s="40"/>
+      <c r="A39" s="42"/>
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
       <c r="D39" s="15"/>
       <c r="E39" s="15"/>
       <c r="G39" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="H39" s="4"/>
       <c r="I39" s="3" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="J39" s="4"/>
       <c r="K39" s="3" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L39" s="4"/>
       <c r="M39" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="N39">
         <f>(H39+J39+L39)/3</f>
         <v>0</v>
       </c>
       <c r="P39" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="Q39" s="4"/>
       <c r="R39" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="S39" s="4"/>
       <c r="T39" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="U39" s="4"/>
       <c r="V39" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="W39">
         <f>(Q39+S39+U39)/3</f>
         <v>0</v>
       </c>
       <c r="Y39" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="Z39" s="4"/>
       <c r="AA39" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AB39" s="4"/>
       <c r="AC39" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="AD39" s="4"/>
       <c r="AE39" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AF39">
         <f>(Z39+AB39+AD39)/3</f>
         <v>0</v>
       </c>
       <c r="AH39" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="AI39" s="4"/>
       <c r="AJ39" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AK39" s="4"/>
       <c r="AL39" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="AM39" s="4"/>
       <c r="AN39" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AO39">
         <f>(AI39+AK39+AM39)/3</f>
         <v>0</v>
       </c>
       <c r="AQ39" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="AR39" s="4"/>
       <c r="AS39" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AT39" s="4"/>
       <c r="AU39" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="AV39" s="4"/>
       <c r="AW39" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AX39">
         <f>(AR39+AT39+AV39)/3</f>
         <v>0</v>
       </c>
       <c r="AZ39" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BA39" s="4"/>
       <c r="BB39" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BC39" s="4"/>
       <c r="BD39" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BE39" s="4"/>
       <c r="BF39" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BG39">
         <f>(BA39+BC39+BE39)/3</f>
         <v>0</v>
       </c>
       <c r="BI39" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BJ39" s="4"/>
       <c r="BK39" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BL39" s="4"/>
       <c r="BM39" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BN39" s="4"/>
       <c r="BO39" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BP39">
         <f>(BJ39+BL39+BN39)/3</f>
         <v>0</v>
       </c>
       <c r="BR39" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BS39" s="4"/>
       <c r="BT39" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BU39" s="4"/>
       <c r="BV39" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BW39" s="4"/>
       <c r="BX39" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BY39">
         <f>(BS39+BU39+BW39)/3</f>
         <v>0</v>
       </c>
       <c r="CA39" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="CB39" s="4">
         <f>H39+Q39+Z39+AI39+AR39+BA39+BJ39+BS39</f>
         <v>0</v>
       </c>
       <c r="CC39" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="CD39" s="4">
         <f>J39+S39+AB39+AK39+AT39+BC39+BL39+BU39</f>
         <v>0</v>
       </c>
       <c r="CE39" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="CF39" s="4">
         <f>L39+U39+AD39+AM39+AV39+BE39+BN39+BW39</f>
@@ -5402,28 +4446,28 @@
       </c>
     </row>
     <row r="40" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A40" s="40"/>
-      <c r="CA40" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="CB40" s="28"/>
-      <c r="CC40" s="28"/>
-      <c r="CD40" s="28"/>
-      <c r="CE40" s="29"/>
+      <c r="A40" s="42"/>
+      <c r="CA40" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="CB40" s="40"/>
+      <c r="CC40" s="40"/>
+      <c r="CD40" s="40"/>
+      <c r="CE40" s="41"/>
       <c r="CF40" s="3">
         <f>(CB39+CD39+CF39)*16</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A41" s="40"/>
-      <c r="CA41" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="CB41" s="28"/>
-      <c r="CC41" s="28"/>
-      <c r="CD41" s="28"/>
-      <c r="CE41" s="29"/>
+      <c r="A41" s="42"/>
+      <c r="CA41" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="CB41" s="40"/>
+      <c r="CC41" s="40"/>
+      <c r="CD41" s="40"/>
+      <c r="CE41" s="41"/>
       <c r="CF41" s="3">
         <f>CF40/48</f>
         <v>0</v>
@@ -5431,28 +4475,28 @@
     </row>
     <row r="43" spans="1:84" x14ac:dyDescent="0.25">
       <c r="G43" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H43" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="I43" s="35"/>
-      <c r="J43" s="35"/>
-      <c r="K43" s="35"/>
-      <c r="L43" s="35"/>
-      <c r="M43" s="35"/>
-      <c r="N43" s="35"/>
-      <c r="O43" s="35"/>
-      <c r="P43" s="35"/>
-      <c r="Q43" s="35"/>
-      <c r="R43" s="35"/>
+        <v>21</v>
+      </c>
+      <c r="H43" s="49" t="s">
+        <v>38</v>
+      </c>
+      <c r="I43" s="49"/>
+      <c r="J43" s="49"/>
+      <c r="K43" s="49"/>
+      <c r="L43" s="49"/>
+      <c r="M43" s="49"/>
+      <c r="N43" s="49"/>
+      <c r="O43" s="49"/>
+      <c r="P43" s="49"/>
+      <c r="Q43" s="49"/>
+      <c r="R43" s="49"/>
     </row>
     <row r="44" spans="1:84" x14ac:dyDescent="0.25">
       <c r="G44" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="I44" s="11"/>
       <c r="J44" s="11"/>
@@ -5470,7 +4514,7 @@
         <v>18</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="I45" s="11"/>
       <c r="J45" s="11"/>
@@ -5488,7 +4532,7 @@
         <v>20</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="I46" s="11"/>
       <c r="J46" s="11"/>
@@ -5500,26 +4544,26 @@
       <c r="P46" s="11"/>
       <c r="Q46" s="11"/>
       <c r="R46" s="11"/>
-      <c r="CA46" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="CB46" s="36"/>
-      <c r="CC46" s="36"/>
-      <c r="CD46" s="36"/>
-      <c r="CE46" s="36"/>
+      <c r="CA46" s="47" t="s">
+        <v>42</v>
+      </c>
+      <c r="CB46" s="47"/>
+      <c r="CC46" s="47"/>
+      <c r="CD46" s="47"/>
+      <c r="CE46" s="47"/>
       <c r="CF46">
         <f>CB19+CB23+CB27+CB31+CB35+CB15+CB11+CB7+CB39</f>
         <v>17</v>
       </c>
     </row>
     <row r="47" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="CA47" s="36" t="s">
-        <v>55</v>
-      </c>
-      <c r="CB47" s="36"/>
-      <c r="CC47" s="36"/>
-      <c r="CD47" s="36"/>
-      <c r="CE47" s="36"/>
+      <c r="CA47" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="CB47" s="47"/>
+      <c r="CC47" s="47"/>
+      <c r="CD47" s="47"/>
+      <c r="CE47" s="47"/>
       <c r="CF47">
         <f>CD19+CD23+CD27+CD31+CD35+CD15+CD11+CD7+CD39</f>
         <v>10</v>
@@ -5527,15 +4571,15 @@
     </row>
     <row r="48" spans="1:84" x14ac:dyDescent="0.25">
       <c r="H48" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="CA48" s="36" t="s">
-        <v>57</v>
-      </c>
-      <c r="CB48" s="36"/>
-      <c r="CC48" s="36"/>
-      <c r="CD48" s="36"/>
-      <c r="CE48" s="36"/>
+        <v>44</v>
+      </c>
+      <c r="CA48" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="CB48" s="47"/>
+      <c r="CC48" s="47"/>
+      <c r="CD48" s="47"/>
+      <c r="CE48" s="47"/>
       <c r="CF48">
         <f>CF19+CF23+CF27+CF31+CF35+CF15+CF11+CF7+CF39</f>
         <v>24</v>
@@ -5544,49 +4588,49 @@
     <row r="49" spans="7:84" x14ac:dyDescent="0.25">
       <c r="G49" s="16"/>
       <c r="H49" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="CA49" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="CB49" s="36"/>
-      <c r="CC49" s="36"/>
-      <c r="CD49" s="36"/>
-      <c r="CE49" s="36"/>
+        <v>46</v>
+      </c>
+      <c r="CA49" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="CB49" s="47"/>
+      <c r="CC49" s="47"/>
+      <c r="CD49" s="47"/>
+      <c r="CE49" s="47"/>
     </row>
     <row r="50" spans="7:84" x14ac:dyDescent="0.25">
       <c r="G50" s="17"/>
       <c r="H50" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="CA50" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="CB50" s="36"/>
-      <c r="CC50" s="36"/>
-      <c r="CD50" s="36"/>
-      <c r="CE50" s="36"/>
+        <v>48</v>
+      </c>
+      <c r="CA50" s="47" t="s">
+        <v>49</v>
+      </c>
+      <c r="CB50" s="47"/>
+      <c r="CC50" s="47"/>
+      <c r="CD50" s="47"/>
+      <c r="CE50" s="47"/>
     </row>
     <row r="51" spans="7:84" x14ac:dyDescent="0.25">
       <c r="G51" s="18"/>
       <c r="H51" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="CA51" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="CB51" s="36"/>
-      <c r="CC51" s="36"/>
-      <c r="CD51" s="36"/>
-      <c r="CE51" s="36"/>
+        <v>50</v>
+      </c>
+      <c r="CA51" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="CB51" s="47"/>
+      <c r="CC51" s="47"/>
+      <c r="CD51" s="47"/>
+      <c r="CE51" s="47"/>
     </row>
     <row r="52" spans="7:84" x14ac:dyDescent="0.25">
       <c r="G52" s="19"/>
       <c r="H52" s="11" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="CA52" s="5" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="CB52" s="5"/>
       <c r="CC52" s="5"/>
@@ -5600,10 +4644,10 @@
     <row r="53" spans="7:84" x14ac:dyDescent="0.25">
       <c r="G53" s="20"/>
       <c r="H53" s="11" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="CA53" s="5" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="CB53" s="5"/>
       <c r="CC53" s="5"/>
@@ -5617,72 +4661,79 @@
     <row r="54" spans="7:84" x14ac:dyDescent="0.25">
       <c r="G54" s="21"/>
       <c r="H54" s="11" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
     </row>
     <row r="55" spans="7:84" x14ac:dyDescent="0.25">
       <c r="G55" s="22"/>
       <c r="H55" s="11" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="56" spans="7:84" x14ac:dyDescent="0.25">
       <c r="G56" s="22"/>
       <c r="H56" s="11" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
     </row>
     <row r="57" spans="7:84" x14ac:dyDescent="0.25">
       <c r="X57" s="2" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="AK57" s="2" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="AL57" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="112">
-    <mergeCell ref="CA21:CE21"/>
-    <mergeCell ref="A30:A37"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="G38:L38"/>
-    <mergeCell ref="P38:U38"/>
-    <mergeCell ref="Y38:AD38"/>
-    <mergeCell ref="AH38:AM38"/>
-    <mergeCell ref="BR18:BW18"/>
-    <mergeCell ref="BR22:BW22"/>
-    <mergeCell ref="BR26:BW26"/>
-    <mergeCell ref="BR30:BW30"/>
-    <mergeCell ref="BR34:BW34"/>
-    <mergeCell ref="BI18:BN18"/>
-    <mergeCell ref="BI22:BN22"/>
-    <mergeCell ref="BI26:BN26"/>
-    <mergeCell ref="BI30:BN30"/>
-    <mergeCell ref="BI34:BN34"/>
-    <mergeCell ref="CA50:CE50"/>
-    <mergeCell ref="CA51:CE51"/>
-    <mergeCell ref="Y26:AD26"/>
-    <mergeCell ref="AH26:AM26"/>
-    <mergeCell ref="AQ26:AV26"/>
-    <mergeCell ref="CA32:CE32"/>
-    <mergeCell ref="CA33:CE33"/>
-    <mergeCell ref="AZ26:BE26"/>
-    <mergeCell ref="CA48:CE48"/>
-    <mergeCell ref="CA28:CE28"/>
-    <mergeCell ref="CA29:CE29"/>
-    <mergeCell ref="AQ30:AV30"/>
-    <mergeCell ref="AZ30:BE30"/>
-    <mergeCell ref="CA49:CE49"/>
-    <mergeCell ref="CA36:CE36"/>
-    <mergeCell ref="CA37:CE37"/>
-    <mergeCell ref="Y30:AD30"/>
-    <mergeCell ref="AH30:AM30"/>
-    <mergeCell ref="CA40:CE40"/>
-    <mergeCell ref="CA41:CE41"/>
+    <mergeCell ref="A1:CF3"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="AZ6:BE6"/>
+    <mergeCell ref="AH14:AM14"/>
+    <mergeCell ref="AQ14:AV14"/>
+    <mergeCell ref="BI6:BN6"/>
+    <mergeCell ref="BI10:BN10"/>
+    <mergeCell ref="BI14:BN14"/>
+    <mergeCell ref="BR6:BW6"/>
+    <mergeCell ref="BR10:BW10"/>
+    <mergeCell ref="BR14:BW14"/>
+    <mergeCell ref="Y6:AD6"/>
+    <mergeCell ref="AH6:AM6"/>
+    <mergeCell ref="AQ6:AV6"/>
+    <mergeCell ref="CA8:CE8"/>
+    <mergeCell ref="A6:A13"/>
+    <mergeCell ref="A14:A21"/>
+    <mergeCell ref="G6:L6"/>
+    <mergeCell ref="P6:U6"/>
+    <mergeCell ref="G14:L14"/>
+    <mergeCell ref="P14:U14"/>
+    <mergeCell ref="Y14:AD14"/>
+    <mergeCell ref="CA9:CE9"/>
+    <mergeCell ref="CA12:CE12"/>
+    <mergeCell ref="CA13:CE13"/>
+    <mergeCell ref="CA16:CE16"/>
+    <mergeCell ref="CA17:CE17"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="AZ22:BE22"/>
+    <mergeCell ref="AZ10:BE10"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="CA20:CE20"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="G10:L10"/>
+    <mergeCell ref="P10:U10"/>
+    <mergeCell ref="Y10:AD10"/>
+    <mergeCell ref="AH10:AM10"/>
+    <mergeCell ref="AQ10:AV10"/>
+    <mergeCell ref="AZ14:BE14"/>
+    <mergeCell ref="G18:L18"/>
+    <mergeCell ref="P18:U18"/>
+    <mergeCell ref="Y18:AD18"/>
+    <mergeCell ref="AH18:AM18"/>
+    <mergeCell ref="AQ18:AV18"/>
+    <mergeCell ref="AZ18:BE18"/>
     <mergeCell ref="H43:R43"/>
     <mergeCell ref="CA46:CE46"/>
     <mergeCell ref="CA47:CE47"/>
@@ -5707,54 +4758,47 @@
     <mergeCell ref="AH34:AM34"/>
     <mergeCell ref="G30:L30"/>
     <mergeCell ref="P30:U30"/>
+    <mergeCell ref="CA50:CE50"/>
+    <mergeCell ref="CA51:CE51"/>
+    <mergeCell ref="Y26:AD26"/>
+    <mergeCell ref="AH26:AM26"/>
+    <mergeCell ref="AQ26:AV26"/>
+    <mergeCell ref="CA32:CE32"/>
+    <mergeCell ref="CA33:CE33"/>
+    <mergeCell ref="AZ26:BE26"/>
+    <mergeCell ref="CA48:CE48"/>
+    <mergeCell ref="CA28:CE28"/>
+    <mergeCell ref="CA29:CE29"/>
+    <mergeCell ref="AQ30:AV30"/>
+    <mergeCell ref="AZ30:BE30"/>
+    <mergeCell ref="CA49:CE49"/>
+    <mergeCell ref="CA36:CE36"/>
+    <mergeCell ref="CA37:CE37"/>
+    <mergeCell ref="Y30:AD30"/>
+    <mergeCell ref="AH30:AM30"/>
+    <mergeCell ref="CA40:CE40"/>
+    <mergeCell ref="CA41:CE41"/>
+    <mergeCell ref="BR18:BW18"/>
+    <mergeCell ref="BR22:BW22"/>
+    <mergeCell ref="BR26:BW26"/>
+    <mergeCell ref="BR30:BW30"/>
+    <mergeCell ref="BR34:BW34"/>
+    <mergeCell ref="BI18:BN18"/>
+    <mergeCell ref="BI22:BN22"/>
+    <mergeCell ref="BI26:BN26"/>
+    <mergeCell ref="BI30:BN30"/>
+    <mergeCell ref="BI34:BN34"/>
+    <mergeCell ref="CA21:CE21"/>
+    <mergeCell ref="A30:A37"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="G38:L38"/>
+    <mergeCell ref="P38:U38"/>
+    <mergeCell ref="Y38:AD38"/>
+    <mergeCell ref="AH38:AM38"/>
     <mergeCell ref="A22:A29"/>
-    <mergeCell ref="CA9:CE9"/>
-    <mergeCell ref="CA12:CE12"/>
-    <mergeCell ref="CA13:CE13"/>
-    <mergeCell ref="CA16:CE16"/>
-    <mergeCell ref="CA17:CE17"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="AZ22:BE22"/>
-    <mergeCell ref="AZ10:BE10"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="CA20:CE20"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="G10:L10"/>
-    <mergeCell ref="P10:U10"/>
-    <mergeCell ref="Y10:AD10"/>
-    <mergeCell ref="AH10:AM10"/>
-    <mergeCell ref="AQ10:AV10"/>
-    <mergeCell ref="AZ14:BE14"/>
-    <mergeCell ref="G18:L18"/>
-    <mergeCell ref="P18:U18"/>
-    <mergeCell ref="Y18:AD18"/>
-    <mergeCell ref="AH18:AM18"/>
-    <mergeCell ref="AQ18:AV18"/>
-    <mergeCell ref="AZ18:BE18"/>
-    <mergeCell ref="A1:CF3"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="AZ6:BE6"/>
-    <mergeCell ref="AH14:AM14"/>
-    <mergeCell ref="AQ14:AV14"/>
-    <mergeCell ref="BI6:BN6"/>
-    <mergeCell ref="BI10:BN10"/>
-    <mergeCell ref="BI14:BN14"/>
-    <mergeCell ref="BR6:BW6"/>
-    <mergeCell ref="BR10:BW10"/>
-    <mergeCell ref="BR14:BW14"/>
-    <mergeCell ref="Y6:AD6"/>
-    <mergeCell ref="AH6:AM6"/>
-    <mergeCell ref="AQ6:AV6"/>
-    <mergeCell ref="CA8:CE8"/>
-    <mergeCell ref="A6:A13"/>
-    <mergeCell ref="A14:A21"/>
-    <mergeCell ref="G6:L6"/>
-    <mergeCell ref="P6:U6"/>
-    <mergeCell ref="G14:L14"/>
-    <mergeCell ref="P14:U14"/>
-    <mergeCell ref="Y14:AD14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5775,178 +4819,178 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
+      <c r="A1" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
+      <c r="S1" s="53"/>
+      <c r="T1" s="53"/>
+      <c r="U1" s="53"/>
+      <c r="V1" s="53"/>
+      <c r="W1" s="53"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="26"/>
-      <c r="V2" s="26"/>
-      <c r="W2" s="26"/>
+      <c r="A2" s="53"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+      <c r="Q2" s="53"/>
+      <c r="R2" s="53"/>
+      <c r="S2" s="53"/>
+      <c r="T2" s="53"/>
+      <c r="U2" s="53"/>
+      <c r="V2" s="53"/>
+      <c r="W2" s="53"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
-        <v>74</v>
-      </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
-      <c r="N3" s="42"/>
-      <c r="O3" s="42"/>
-      <c r="P3" s="42"/>
-      <c r="Q3" s="42"/>
-      <c r="R3" s="42"/>
-      <c r="S3" s="42"/>
-      <c r="T3" s="42"/>
-      <c r="U3" s="42"/>
-      <c r="V3" s="42"/>
-      <c r="W3" s="42"/>
+      <c r="A3" s="54" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="55"/>
+      <c r="L3" s="55"/>
+      <c r="M3" s="55"/>
+      <c r="N3" s="55"/>
+      <c r="O3" s="55"/>
+      <c r="P3" s="55"/>
+      <c r="Q3" s="55"/>
+      <c r="R3" s="55"/>
+      <c r="S3" s="55"/>
+      <c r="T3" s="55"/>
+      <c r="U3" s="55"/>
+      <c r="V3" s="55"/>
+      <c r="W3" s="55"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="59" t="s">
-        <v>75</v>
-      </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="43"/>
-      <c r="M4" s="43"/>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="43"/>
-      <c r="T4" s="43"/>
-      <c r="U4" s="43"/>
-      <c r="V4" s="43"/>
-      <c r="W4" s="43"/>
+      <c r="A4" s="72" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
+      <c r="L4" s="56"/>
+      <c r="M4" s="56"/>
+      <c r="N4" s="56"/>
+      <c r="O4" s="56"/>
+      <c r="P4" s="56"/>
+      <c r="Q4" s="56"/>
+      <c r="R4" s="56"/>
+      <c r="S4" s="56"/>
+      <c r="T4" s="56"/>
+      <c r="U4" s="56"/>
+      <c r="V4" s="56"/>
+      <c r="W4" s="56"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="48" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="A5" s="61" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="61"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
       <c r="K5" s="6"/>
-      <c r="L5" s="49" t="s">
-        <v>77</v>
-      </c>
-      <c r="M5" s="49"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="44" t="s">
-        <v>78</v>
-      </c>
-      <c r="V5" s="45"/>
-      <c r="W5" s="45"/>
+      <c r="L5" s="62" t="s">
+        <v>65</v>
+      </c>
+      <c r="M5" s="62"/>
+      <c r="N5" s="62"/>
+      <c r="O5" s="62"/>
+      <c r="P5" s="62"/>
+      <c r="Q5" s="62"/>
+      <c r="R5" s="62"/>
+      <c r="S5" s="62"/>
+      <c r="T5" s="62"/>
+      <c r="U5" s="57" t="s">
+        <v>66</v>
+      </c>
+      <c r="V5" s="58"/>
+      <c r="W5" s="58"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="50"/>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="53" t="s">
-        <v>79</v>
-      </c>
-      <c r="F6" s="53"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="55" t="s">
-        <v>80</v>
-      </c>
-      <c r="I6" s="53"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="57"/>
-      <c r="M6" s="57"/>
-      <c r="N6" s="58"/>
-      <c r="O6" s="49" t="s">
-        <v>79</v>
-      </c>
-      <c r="P6" s="49"/>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="56" t="s">
-        <v>80</v>
-      </c>
-      <c r="S6" s="57"/>
-      <c r="T6" s="58"/>
-      <c r="U6" s="46"/>
-      <c r="V6" s="47"/>
-      <c r="W6" s="47"/>
+      <c r="A6" s="63"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="66" t="s">
+        <v>67</v>
+      </c>
+      <c r="F6" s="66"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="68" t="s">
+        <v>68</v>
+      </c>
+      <c r="I6" s="66"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="69"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="70"/>
+      <c r="N6" s="71"/>
+      <c r="O6" s="62" t="s">
+        <v>67</v>
+      </c>
+      <c r="P6" s="62"/>
+      <c r="Q6" s="62"/>
+      <c r="R6" s="69" t="s">
+        <v>68</v>
+      </c>
+      <c r="S6" s="70"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="59"/>
+      <c r="V6" s="60"/>
+      <c r="W6" s="60"/>
     </row>
     <row r="7" spans="1:26" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>2</v>
@@ -5958,25 +5002,25 @@
         <v>3</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>2</v>
@@ -5988,31 +5032,31 @@
         <v>3</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="Q7" s="9" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="R7" s="9" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="S7" s="9" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="U7" s="10" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="V7" s="10" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="W7" s="10" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
@@ -6663,7 +5707,7 @@
     </row>
     <row r="33" spans="8:20" x14ac:dyDescent="0.25">
       <c r="H33" s="2" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I33">
         <f>SUM(I8:I32)</f>
@@ -6674,7 +5718,7 @@
         <v>0</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="S33">
         <f>SUM(S8:S32)</f>
@@ -6708,15 +5752,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101000D056AFC88326C4799448B54C880494B" ma:contentTypeVersion="0" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="4e1e4b56ebf0b63f67924dd21a513bd2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="26ff3a126252e742cc2543983a566b0e">
     <xsd:element name="properties">
@@ -6830,15 +5865,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C29C807D-6D16-46D1-BB9C-632513C228B6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0D9287C-CE41-4A48-B358-97A71E5FD6DC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6852,4 +5888,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C29C807D-6D16-46D1-BB9C-632513C228B6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/plantillas/excel_base.xlsx
+++ b/plantillas/excel_base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\estudiante\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44199D1C-2700-4F5B-B0C0-4B4CBD61BBED}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B06081CA-CE96-46CA-A714-62E27A8504F1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" tabRatio="570" xr2:uid="{73D17D42-2032-4221-9DBF-D2EB2D99B5D8}"/>
   </bookViews>
@@ -1065,6 +1065,81 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1083,26 +1158,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1110,76 +1179,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1682,79 +1682,79 @@
       <c r="E1" s="11"/>
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
-      <c r="H1" s="71" t="s">
+      <c r="H1" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="I1" s="71"/>
-      <c r="J1" s="71"/>
-      <c r="K1" s="71"/>
-      <c r="L1" s="71"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="71"/>
-      <c r="O1" s="71"/>
-      <c r="P1" s="71"/>
-      <c r="Q1" s="71"/>
-      <c r="R1" s="71"/>
-      <c r="S1" s="71"/>
-      <c r="T1" s="71"/>
-      <c r="U1" s="71"/>
-      <c r="V1" s="71"/>
-      <c r="W1" s="71"/>
-      <c r="X1" s="71"/>
-      <c r="Y1" s="71"/>
-      <c r="Z1" s="71"/>
-      <c r="AA1" s="71"/>
-      <c r="AB1" s="71"/>
-      <c r="AC1" s="71"/>
-      <c r="AD1" s="71"/>
-      <c r="AE1" s="71"/>
-      <c r="AF1" s="71"/>
-      <c r="AG1" s="71"/>
-      <c r="AH1" s="71"/>
-      <c r="AI1" s="71"/>
-      <c r="AJ1" s="71"/>
-      <c r="AK1" s="71"/>
-      <c r="AL1" s="71"/>
-      <c r="AM1" s="71"/>
-      <c r="AN1" s="71"/>
-      <c r="AO1" s="71"/>
-      <c r="AP1" s="71"/>
-      <c r="AQ1" s="71"/>
-      <c r="AR1" s="71"/>
-      <c r="AS1" s="71"/>
-      <c r="AT1" s="71"/>
-      <c r="AU1" s="71"/>
-      <c r="AV1" s="71"/>
-      <c r="AW1" s="71"/>
-      <c r="AX1" s="71"/>
-      <c r="AY1" s="71"/>
-      <c r="AZ1" s="71"/>
-      <c r="BA1" s="71"/>
-      <c r="BB1" s="71"/>
-      <c r="BC1" s="71"/>
-      <c r="BD1" s="71"/>
-      <c r="BE1" s="71"/>
-      <c r="BF1" s="71"/>
-      <c r="BG1" s="71"/>
-      <c r="BH1" s="71"/>
-      <c r="BI1" s="71"/>
-      <c r="BJ1" s="71"/>
-      <c r="BK1" s="71"/>
-      <c r="BL1" s="71"/>
-      <c r="BM1" s="71"/>
-      <c r="BN1" s="71"/>
-      <c r="BO1" s="71"/>
-      <c r="BP1" s="71"/>
-      <c r="BQ1" s="71"/>
-      <c r="BR1" s="71"/>
-      <c r="BS1" s="71"/>
-      <c r="BT1" s="71"/>
-      <c r="BU1" s="71"/>
-      <c r="BV1" s="71"/>
-      <c r="BW1" s="71"/>
-      <c r="BX1" s="71"/>
-      <c r="BY1" s="71"/>
-      <c r="BZ1" s="71"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+      <c r="T1" s="41"/>
+      <c r="U1" s="41"/>
+      <c r="V1" s="41"/>
+      <c r="W1" s="41"/>
+      <c r="X1" s="41"/>
+      <c r="Y1" s="41"/>
+      <c r="Z1" s="41"/>
+      <c r="AA1" s="41"/>
+      <c r="AB1" s="41"/>
+      <c r="AC1" s="41"/>
+      <c r="AD1" s="41"/>
+      <c r="AE1" s="41"/>
+      <c r="AF1" s="41"/>
+      <c r="AG1" s="41"/>
+      <c r="AH1" s="41"/>
+      <c r="AI1" s="41"/>
+      <c r="AJ1" s="41"/>
+      <c r="AK1" s="41"/>
+      <c r="AL1" s="41"/>
+      <c r="AM1" s="41"/>
+      <c r="AN1" s="41"/>
+      <c r="AO1" s="41"/>
+      <c r="AP1" s="41"/>
+      <c r="AQ1" s="41"/>
+      <c r="AR1" s="41"/>
+      <c r="AS1" s="41"/>
+      <c r="AT1" s="41"/>
+      <c r="AU1" s="41"/>
+      <c r="AV1" s="41"/>
+      <c r="AW1" s="41"/>
+      <c r="AX1" s="41"/>
+      <c r="AY1" s="41"/>
+      <c r="AZ1" s="41"/>
+      <c r="BA1" s="41"/>
+      <c r="BB1" s="41"/>
+      <c r="BC1" s="41"/>
+      <c r="BD1" s="41"/>
+      <c r="BE1" s="41"/>
+      <c r="BF1" s="41"/>
+      <c r="BG1" s="41"/>
+      <c r="BH1" s="41"/>
+      <c r="BI1" s="41"/>
+      <c r="BJ1" s="41"/>
+      <c r="BK1" s="41"/>
+      <c r="BL1" s="41"/>
+      <c r="BM1" s="41"/>
+      <c r="BN1" s="41"/>
+      <c r="BO1" s="41"/>
+      <c r="BP1" s="41"/>
+      <c r="BQ1" s="41"/>
+      <c r="BR1" s="41"/>
+      <c r="BS1" s="41"/>
+      <c r="BT1" s="41"/>
+      <c r="BU1" s="41"/>
+      <c r="BV1" s="41"/>
+      <c r="BW1" s="41"/>
+      <c r="BX1" s="41"/>
+      <c r="BY1" s="41"/>
+      <c r="BZ1" s="41"/>
       <c r="CA1" s="11"/>
       <c r="CB1" s="11"/>
       <c r="CC1" s="11"/>
@@ -1769,77 +1769,77 @@
       <c r="E2" s="11"/>
       <c r="F2" s="11"/>
       <c r="G2" s="11"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71"/>
-      <c r="N2" s="71"/>
-      <c r="O2" s="71"/>
-      <c r="P2" s="71"/>
-      <c r="Q2" s="71"/>
-      <c r="R2" s="71"/>
-      <c r="S2" s="71"/>
-      <c r="T2" s="71"/>
-      <c r="U2" s="71"/>
-      <c r="V2" s="71"/>
-      <c r="W2" s="71"/>
-      <c r="X2" s="71"/>
-      <c r="Y2" s="71"/>
-      <c r="Z2" s="71"/>
-      <c r="AA2" s="71"/>
-      <c r="AB2" s="71"/>
-      <c r="AC2" s="71"/>
-      <c r="AD2" s="71"/>
-      <c r="AE2" s="71"/>
-      <c r="AF2" s="71"/>
-      <c r="AG2" s="71"/>
-      <c r="AH2" s="71"/>
-      <c r="AI2" s="71"/>
-      <c r="AJ2" s="71"/>
-      <c r="AK2" s="71"/>
-      <c r="AL2" s="71"/>
-      <c r="AM2" s="71"/>
-      <c r="AN2" s="71"/>
-      <c r="AO2" s="71"/>
-      <c r="AP2" s="71"/>
-      <c r="AQ2" s="71"/>
-      <c r="AR2" s="71"/>
-      <c r="AS2" s="71"/>
-      <c r="AT2" s="71"/>
-      <c r="AU2" s="71"/>
-      <c r="AV2" s="71"/>
-      <c r="AW2" s="71"/>
-      <c r="AX2" s="71"/>
-      <c r="AY2" s="71"/>
-      <c r="AZ2" s="71"/>
-      <c r="BA2" s="71"/>
-      <c r="BB2" s="71"/>
-      <c r="BC2" s="71"/>
-      <c r="BD2" s="71"/>
-      <c r="BE2" s="71"/>
-      <c r="BF2" s="71"/>
-      <c r="BG2" s="71"/>
-      <c r="BH2" s="71"/>
-      <c r="BI2" s="71"/>
-      <c r="BJ2" s="71"/>
-      <c r="BK2" s="71"/>
-      <c r="BL2" s="71"/>
-      <c r="BM2" s="71"/>
-      <c r="BN2" s="71"/>
-      <c r="BO2" s="71"/>
-      <c r="BP2" s="71"/>
-      <c r="BQ2" s="71"/>
-      <c r="BR2" s="71"/>
-      <c r="BS2" s="71"/>
-      <c r="BT2" s="71"/>
-      <c r="BU2" s="71"/>
-      <c r="BV2" s="71"/>
-      <c r="BW2" s="71"/>
-      <c r="BX2" s="71"/>
-      <c r="BY2" s="71"/>
-      <c r="BZ2" s="71"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="41"/>
+      <c r="Q2" s="41"/>
+      <c r="R2" s="41"/>
+      <c r="S2" s="41"/>
+      <c r="T2" s="41"/>
+      <c r="U2" s="41"/>
+      <c r="V2" s="41"/>
+      <c r="W2" s="41"/>
+      <c r="X2" s="41"/>
+      <c r="Y2" s="41"/>
+      <c r="Z2" s="41"/>
+      <c r="AA2" s="41"/>
+      <c r="AB2" s="41"/>
+      <c r="AC2" s="41"/>
+      <c r="AD2" s="41"/>
+      <c r="AE2" s="41"/>
+      <c r="AF2" s="41"/>
+      <c r="AG2" s="41"/>
+      <c r="AH2" s="41"/>
+      <c r="AI2" s="41"/>
+      <c r="AJ2" s="41"/>
+      <c r="AK2" s="41"/>
+      <c r="AL2" s="41"/>
+      <c r="AM2" s="41"/>
+      <c r="AN2" s="41"/>
+      <c r="AO2" s="41"/>
+      <c r="AP2" s="41"/>
+      <c r="AQ2" s="41"/>
+      <c r="AR2" s="41"/>
+      <c r="AS2" s="41"/>
+      <c r="AT2" s="41"/>
+      <c r="AU2" s="41"/>
+      <c r="AV2" s="41"/>
+      <c r="AW2" s="41"/>
+      <c r="AX2" s="41"/>
+      <c r="AY2" s="41"/>
+      <c r="AZ2" s="41"/>
+      <c r="BA2" s="41"/>
+      <c r="BB2" s="41"/>
+      <c r="BC2" s="41"/>
+      <c r="BD2" s="41"/>
+      <c r="BE2" s="41"/>
+      <c r="BF2" s="41"/>
+      <c r="BG2" s="41"/>
+      <c r="BH2" s="41"/>
+      <c r="BI2" s="41"/>
+      <c r="BJ2" s="41"/>
+      <c r="BK2" s="41"/>
+      <c r="BL2" s="41"/>
+      <c r="BM2" s="41"/>
+      <c r="BN2" s="41"/>
+      <c r="BO2" s="41"/>
+      <c r="BP2" s="41"/>
+      <c r="BQ2" s="41"/>
+      <c r="BR2" s="41"/>
+      <c r="BS2" s="41"/>
+      <c r="BT2" s="41"/>
+      <c r="BU2" s="41"/>
+      <c r="BV2" s="41"/>
+      <c r="BW2" s="41"/>
+      <c r="BX2" s="41"/>
+      <c r="BY2" s="41"/>
+      <c r="BZ2" s="41"/>
       <c r="CA2" s="11"/>
       <c r="CB2" s="11"/>
       <c r="CC2" s="11"/>
@@ -1854,77 +1854,77 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="71"/>
-      <c r="K3" s="71"/>
-      <c r="L3" s="71"/>
-      <c r="M3" s="71"/>
-      <c r="N3" s="71"/>
-      <c r="O3" s="71"/>
-      <c r="P3" s="71"/>
-      <c r="Q3" s="71"/>
-      <c r="R3" s="71"/>
-      <c r="S3" s="71"/>
-      <c r="T3" s="71"/>
-      <c r="U3" s="71"/>
-      <c r="V3" s="71"/>
-      <c r="W3" s="71"/>
-      <c r="X3" s="71"/>
-      <c r="Y3" s="71"/>
-      <c r="Z3" s="71"/>
-      <c r="AA3" s="71"/>
-      <c r="AB3" s="71"/>
-      <c r="AC3" s="71"/>
-      <c r="AD3" s="71"/>
-      <c r="AE3" s="71"/>
-      <c r="AF3" s="71"/>
-      <c r="AG3" s="71"/>
-      <c r="AH3" s="71"/>
-      <c r="AI3" s="71"/>
-      <c r="AJ3" s="71"/>
-      <c r="AK3" s="71"/>
-      <c r="AL3" s="71"/>
-      <c r="AM3" s="71"/>
-      <c r="AN3" s="71"/>
-      <c r="AO3" s="71"/>
-      <c r="AP3" s="71"/>
-      <c r="AQ3" s="71"/>
-      <c r="AR3" s="71"/>
-      <c r="AS3" s="71"/>
-      <c r="AT3" s="71"/>
-      <c r="AU3" s="71"/>
-      <c r="AV3" s="71"/>
-      <c r="AW3" s="71"/>
-      <c r="AX3" s="71"/>
-      <c r="AY3" s="71"/>
-      <c r="AZ3" s="71"/>
-      <c r="BA3" s="71"/>
-      <c r="BB3" s="71"/>
-      <c r="BC3" s="71"/>
-      <c r="BD3" s="71"/>
-      <c r="BE3" s="71"/>
-      <c r="BF3" s="71"/>
-      <c r="BG3" s="71"/>
-      <c r="BH3" s="71"/>
-      <c r="BI3" s="71"/>
-      <c r="BJ3" s="71"/>
-      <c r="BK3" s="71"/>
-      <c r="BL3" s="71"/>
-      <c r="BM3" s="71"/>
-      <c r="BN3" s="71"/>
-      <c r="BO3" s="71"/>
-      <c r="BP3" s="71"/>
-      <c r="BQ3" s="71"/>
-      <c r="BR3" s="71"/>
-      <c r="BS3" s="71"/>
-      <c r="BT3" s="71"/>
-      <c r="BU3" s="71"/>
-      <c r="BV3" s="71"/>
-      <c r="BW3" s="71"/>
-      <c r="BX3" s="71"/>
-      <c r="BY3" s="71"/>
-      <c r="BZ3" s="71"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="41"/>
+      <c r="R3" s="41"/>
+      <c r="S3" s="41"/>
+      <c r="T3" s="41"/>
+      <c r="U3" s="41"/>
+      <c r="V3" s="41"/>
+      <c r="W3" s="41"/>
+      <c r="X3" s="41"/>
+      <c r="Y3" s="41"/>
+      <c r="Z3" s="41"/>
+      <c r="AA3" s="41"/>
+      <c r="AB3" s="41"/>
+      <c r="AC3" s="41"/>
+      <c r="AD3" s="41"/>
+      <c r="AE3" s="41"/>
+      <c r="AF3" s="41"/>
+      <c r="AG3" s="41"/>
+      <c r="AH3" s="41"/>
+      <c r="AI3" s="41"/>
+      <c r="AJ3" s="41"/>
+      <c r="AK3" s="41"/>
+      <c r="AL3" s="41"/>
+      <c r="AM3" s="41"/>
+      <c r="AN3" s="41"/>
+      <c r="AO3" s="41"/>
+      <c r="AP3" s="41"/>
+      <c r="AQ3" s="41"/>
+      <c r="AR3" s="41"/>
+      <c r="AS3" s="41"/>
+      <c r="AT3" s="41"/>
+      <c r="AU3" s="41"/>
+      <c r="AV3" s="41"/>
+      <c r="AW3" s="41"/>
+      <c r="AX3" s="41"/>
+      <c r="AY3" s="41"/>
+      <c r="AZ3" s="41"/>
+      <c r="BA3" s="41"/>
+      <c r="BB3" s="41"/>
+      <c r="BC3" s="41"/>
+      <c r="BD3" s="41"/>
+      <c r="BE3" s="41"/>
+      <c r="BF3" s="41"/>
+      <c r="BG3" s="41"/>
+      <c r="BH3" s="41"/>
+      <c r="BI3" s="41"/>
+      <c r="BJ3" s="41"/>
+      <c r="BK3" s="41"/>
+      <c r="BL3" s="41"/>
+      <c r="BM3" s="41"/>
+      <c r="BN3" s="41"/>
+      <c r="BO3" s="41"/>
+      <c r="BP3" s="41"/>
+      <c r="BQ3" s="41"/>
+      <c r="BR3" s="41"/>
+      <c r="BS3" s="41"/>
+      <c r="BT3" s="41"/>
+      <c r="BU3" s="41"/>
+      <c r="BV3" s="41"/>
+      <c r="BW3" s="41"/>
+      <c r="BX3" s="41"/>
+      <c r="BY3" s="41"/>
+      <c r="BZ3" s="41"/>
       <c r="CA3" s="11"/>
       <c r="CB3" s="11"/>
       <c r="CC3" s="11"/>
@@ -1939,77 +1939,77 @@
       <c r="E4" s="12"/>
       <c r="F4" s="12"/>
       <c r="G4" s="12"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="71"/>
-      <c r="K4" s="71"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="71"/>
-      <c r="N4" s="71"/>
-      <c r="O4" s="71"/>
-      <c r="P4" s="71"/>
-      <c r="Q4" s="71"/>
-      <c r="R4" s="71"/>
-      <c r="S4" s="71"/>
-      <c r="T4" s="71"/>
-      <c r="U4" s="71"/>
-      <c r="V4" s="71"/>
-      <c r="W4" s="71"/>
-      <c r="X4" s="71"/>
-      <c r="Y4" s="71"/>
-      <c r="Z4" s="71"/>
-      <c r="AA4" s="71"/>
-      <c r="AB4" s="71"/>
-      <c r="AC4" s="71"/>
-      <c r="AD4" s="71"/>
-      <c r="AE4" s="71"/>
-      <c r="AF4" s="71"/>
-      <c r="AG4" s="71"/>
-      <c r="AH4" s="71"/>
-      <c r="AI4" s="71"/>
-      <c r="AJ4" s="71"/>
-      <c r="AK4" s="71"/>
-      <c r="AL4" s="71"/>
-      <c r="AM4" s="71"/>
-      <c r="AN4" s="71"/>
-      <c r="AO4" s="71"/>
-      <c r="AP4" s="71"/>
-      <c r="AQ4" s="71"/>
-      <c r="AR4" s="71"/>
-      <c r="AS4" s="71"/>
-      <c r="AT4" s="71"/>
-      <c r="AU4" s="71"/>
-      <c r="AV4" s="71"/>
-      <c r="AW4" s="71"/>
-      <c r="AX4" s="71"/>
-      <c r="AY4" s="71"/>
-      <c r="AZ4" s="71"/>
-      <c r="BA4" s="71"/>
-      <c r="BB4" s="71"/>
-      <c r="BC4" s="71"/>
-      <c r="BD4" s="71"/>
-      <c r="BE4" s="71"/>
-      <c r="BF4" s="71"/>
-      <c r="BG4" s="71"/>
-      <c r="BH4" s="71"/>
-      <c r="BI4" s="71"/>
-      <c r="BJ4" s="71"/>
-      <c r="BK4" s="71"/>
-      <c r="BL4" s="71"/>
-      <c r="BM4" s="71"/>
-      <c r="BN4" s="71"/>
-      <c r="BO4" s="71"/>
-      <c r="BP4" s="71"/>
-      <c r="BQ4" s="71"/>
-      <c r="BR4" s="71"/>
-      <c r="BS4" s="71"/>
-      <c r="BT4" s="71"/>
-      <c r="BU4" s="71"/>
-      <c r="BV4" s="71"/>
-      <c r="BW4" s="71"/>
-      <c r="BX4" s="71"/>
-      <c r="BY4" s="71"/>
-      <c r="BZ4" s="71"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="41"/>
+      <c r="P4" s="41"/>
+      <c r="Q4" s="41"/>
+      <c r="R4" s="41"/>
+      <c r="S4" s="41"/>
+      <c r="T4" s="41"/>
+      <c r="U4" s="41"/>
+      <c r="V4" s="41"/>
+      <c r="W4" s="41"/>
+      <c r="X4" s="41"/>
+      <c r="Y4" s="41"/>
+      <c r="Z4" s="41"/>
+      <c r="AA4" s="41"/>
+      <c r="AB4" s="41"/>
+      <c r="AC4" s="41"/>
+      <c r="AD4" s="41"/>
+      <c r="AE4" s="41"/>
+      <c r="AF4" s="41"/>
+      <c r="AG4" s="41"/>
+      <c r="AH4" s="41"/>
+      <c r="AI4" s="41"/>
+      <c r="AJ4" s="41"/>
+      <c r="AK4" s="41"/>
+      <c r="AL4" s="41"/>
+      <c r="AM4" s="41"/>
+      <c r="AN4" s="41"/>
+      <c r="AO4" s="41"/>
+      <c r="AP4" s="41"/>
+      <c r="AQ4" s="41"/>
+      <c r="AR4" s="41"/>
+      <c r="AS4" s="41"/>
+      <c r="AT4" s="41"/>
+      <c r="AU4" s="41"/>
+      <c r="AV4" s="41"/>
+      <c r="AW4" s="41"/>
+      <c r="AX4" s="41"/>
+      <c r="AY4" s="41"/>
+      <c r="AZ4" s="41"/>
+      <c r="BA4" s="41"/>
+      <c r="BB4" s="41"/>
+      <c r="BC4" s="41"/>
+      <c r="BD4" s="41"/>
+      <c r="BE4" s="41"/>
+      <c r="BF4" s="41"/>
+      <c r="BG4" s="41"/>
+      <c r="BH4" s="41"/>
+      <c r="BI4" s="41"/>
+      <c r="BJ4" s="41"/>
+      <c r="BK4" s="41"/>
+      <c r="BL4" s="41"/>
+      <c r="BM4" s="41"/>
+      <c r="BN4" s="41"/>
+      <c r="BO4" s="41"/>
+      <c r="BP4" s="41"/>
+      <c r="BQ4" s="41"/>
+      <c r="BR4" s="41"/>
+      <c r="BS4" s="41"/>
+      <c r="BT4" s="41"/>
+      <c r="BU4" s="41"/>
+      <c r="BV4" s="41"/>
+      <c r="BW4" s="41"/>
+      <c r="BX4" s="41"/>
+      <c r="BY4" s="41"/>
+      <c r="BZ4" s="41"/>
       <c r="CA4" s="12"/>
       <c r="CB4" s="12"/>
       <c r="CC4" s="12"/>
@@ -2104,142 +2104,142 @@
       <c r="CG5" s="12"/>
     </row>
     <row r="6" spans="3:85" x14ac:dyDescent="0.25">
-      <c r="I6" s="72" t="s">
+      <c r="I6" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="J6" s="73"/>
-      <c r="K6" s="73"/>
-      <c r="L6" s="73"/>
-      <c r="M6" s="73"/>
-      <c r="N6" s="74"/>
-      <c r="R6" s="72" t="s">
+      <c r="J6" s="43"/>
+      <c r="K6" s="43"/>
+      <c r="L6" s="43"/>
+      <c r="M6" s="43"/>
+      <c r="N6" s="44"/>
+      <c r="R6" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="S6" s="73"/>
-      <c r="T6" s="73"/>
-      <c r="U6" s="73"/>
-      <c r="V6" s="73"/>
-      <c r="W6" s="74"/>
-      <c r="AA6" s="72" t="s">
+      <c r="S6" s="43"/>
+      <c r="T6" s="43"/>
+      <c r="U6" s="43"/>
+      <c r="V6" s="43"/>
+      <c r="W6" s="44"/>
+      <c r="AA6" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="AB6" s="73"/>
-      <c r="AC6" s="73"/>
-      <c r="AD6" s="73"/>
-      <c r="AE6" s="73"/>
-      <c r="AF6" s="74"/>
-      <c r="AJ6" s="72" t="s">
+      <c r="AB6" s="43"/>
+      <c r="AC6" s="43"/>
+      <c r="AD6" s="43"/>
+      <c r="AE6" s="43"/>
+      <c r="AF6" s="44"/>
+      <c r="AJ6" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="AK6" s="73"/>
-      <c r="AL6" s="73"/>
-      <c r="AM6" s="73"/>
-      <c r="AN6" s="73"/>
-      <c r="AO6" s="74"/>
-      <c r="AS6" s="72" t="s">
+      <c r="AK6" s="43"/>
+      <c r="AL6" s="43"/>
+      <c r="AM6" s="43"/>
+      <c r="AN6" s="43"/>
+      <c r="AO6" s="44"/>
+      <c r="AS6" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="AT6" s="73"/>
-      <c r="AU6" s="73"/>
-      <c r="AV6" s="73"/>
-      <c r="AW6" s="73"/>
-      <c r="AX6" s="74"/>
-      <c r="BB6" s="72" t="s">
+      <c r="AT6" s="43"/>
+      <c r="AU6" s="43"/>
+      <c r="AV6" s="43"/>
+      <c r="AW6" s="43"/>
+      <c r="AX6" s="44"/>
+      <c r="BB6" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="BC6" s="73"/>
-      <c r="BD6" s="73"/>
-      <c r="BE6" s="73"/>
-      <c r="BF6" s="73"/>
-      <c r="BG6" s="74"/>
-      <c r="BK6" s="72" t="s">
+      <c r="BC6" s="43"/>
+      <c r="BD6" s="43"/>
+      <c r="BE6" s="43"/>
+      <c r="BF6" s="43"/>
+      <c r="BG6" s="44"/>
+      <c r="BK6" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="BL6" s="73"/>
-      <c r="BM6" s="73"/>
-      <c r="BN6" s="73"/>
-      <c r="BO6" s="73"/>
-      <c r="BP6" s="74"/>
-      <c r="BT6" s="72" t="s">
+      <c r="BL6" s="43"/>
+      <c r="BM6" s="43"/>
+      <c r="BN6" s="43"/>
+      <c r="BO6" s="43"/>
+      <c r="BP6" s="44"/>
+      <c r="BT6" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="BU6" s="73"/>
-      <c r="BV6" s="73"/>
-      <c r="BW6" s="73"/>
-      <c r="BX6" s="73"/>
-      <c r="BY6" s="74"/>
+      <c r="BU6" s="43"/>
+      <c r="BV6" s="43"/>
+      <c r="BW6" s="43"/>
+      <c r="BX6" s="43"/>
+      <c r="BY6" s="44"/>
     </row>
     <row r="7" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H7" s="23"/>
-      <c r="I7" s="75"/>
-      <c r="J7" s="76"/>
-      <c r="K7" s="76"/>
-      <c r="L7" s="76"/>
-      <c r="M7" s="76"/>
-      <c r="N7" s="77"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="46"/>
+      <c r="K7" s="46"/>
+      <c r="L7" s="46"/>
+      <c r="M7" s="46"/>
+      <c r="N7" s="47"/>
       <c r="O7" s="23"/>
       <c r="P7" s="23"/>
       <c r="Q7" s="23"/>
-      <c r="R7" s="75"/>
-      <c r="S7" s="76"/>
-      <c r="T7" s="76"/>
-      <c r="U7" s="76"/>
-      <c r="V7" s="76"/>
-      <c r="W7" s="77"/>
+      <c r="R7" s="45"/>
+      <c r="S7" s="46"/>
+      <c r="T7" s="46"/>
+      <c r="U7" s="46"/>
+      <c r="V7" s="46"/>
+      <c r="W7" s="47"/>
       <c r="X7" s="23"/>
       <c r="Y7" s="23"/>
       <c r="Z7" s="23"/>
-      <c r="AA7" s="75"/>
-      <c r="AB7" s="76"/>
-      <c r="AC7" s="76"/>
-      <c r="AD7" s="76"/>
-      <c r="AE7" s="76"/>
-      <c r="AF7" s="77"/>
+      <c r="AA7" s="45"/>
+      <c r="AB7" s="46"/>
+      <c r="AC7" s="46"/>
+      <c r="AD7" s="46"/>
+      <c r="AE7" s="46"/>
+      <c r="AF7" s="47"/>
       <c r="AG7" s="23"/>
       <c r="AH7" s="23"/>
       <c r="AI7" s="23"/>
-      <c r="AJ7" s="75"/>
-      <c r="AK7" s="76"/>
-      <c r="AL7" s="76"/>
-      <c r="AM7" s="76"/>
-      <c r="AN7" s="76"/>
-      <c r="AO7" s="77"/>
+      <c r="AJ7" s="45"/>
+      <c r="AK7" s="46"/>
+      <c r="AL7" s="46"/>
+      <c r="AM7" s="46"/>
+      <c r="AN7" s="46"/>
+      <c r="AO7" s="47"/>
       <c r="AP7" s="23"/>
       <c r="AQ7" s="23"/>
       <c r="AR7" s="23"/>
-      <c r="AS7" s="75"/>
-      <c r="AT7" s="76"/>
-      <c r="AU7" s="76"/>
-      <c r="AV7" s="76"/>
-      <c r="AW7" s="76"/>
-      <c r="AX7" s="77"/>
+      <c r="AS7" s="45"/>
+      <c r="AT7" s="46"/>
+      <c r="AU7" s="46"/>
+      <c r="AV7" s="46"/>
+      <c r="AW7" s="46"/>
+      <c r="AX7" s="47"/>
       <c r="AY7" s="23"/>
       <c r="AZ7" s="23"/>
       <c r="BA7" s="23"/>
-      <c r="BB7" s="75"/>
-      <c r="BC7" s="76"/>
-      <c r="BD7" s="76"/>
-      <c r="BE7" s="76"/>
-      <c r="BF7" s="76"/>
-      <c r="BG7" s="77"/>
+      <c r="BB7" s="45"/>
+      <c r="BC7" s="46"/>
+      <c r="BD7" s="46"/>
+      <c r="BE7" s="46"/>
+      <c r="BF7" s="46"/>
+      <c r="BG7" s="47"/>
       <c r="BH7" s="23"/>
       <c r="BI7" s="23"/>
       <c r="BJ7" s="23"/>
-      <c r="BK7" s="75"/>
-      <c r="BL7" s="76"/>
-      <c r="BM7" s="76"/>
-      <c r="BN7" s="76"/>
-      <c r="BO7" s="76"/>
-      <c r="BP7" s="77"/>
+      <c r="BK7" s="45"/>
+      <c r="BL7" s="46"/>
+      <c r="BM7" s="46"/>
+      <c r="BN7" s="46"/>
+      <c r="BO7" s="46"/>
+      <c r="BP7" s="47"/>
       <c r="BQ7" s="23"/>
       <c r="BR7" s="23"/>
       <c r="BS7" s="23"/>
-      <c r="BT7" s="75"/>
-      <c r="BU7" s="76"/>
-      <c r="BV7" s="76"/>
-      <c r="BW7" s="76"/>
-      <c r="BX7" s="76"/>
-      <c r="BY7" s="77"/>
+      <c r="BT7" s="45"/>
+      <c r="BU7" s="46"/>
+      <c r="BV7" s="46"/>
+      <c r="BW7" s="46"/>
+      <c r="BX7" s="46"/>
+      <c r="BY7" s="47"/>
       <c r="BZ7" s="23"/>
       <c r="CA7" s="23"/>
     </row>
@@ -2281,154 +2281,154 @@
       <c r="BR8" s="23"/>
     </row>
     <row r="9" spans="3:85" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="51" t="s">
+      <c r="C9" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="40"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="40"/>
-      <c r="M9" s="40"/>
-      <c r="N9" s="40"/>
-      <c r="O9" s="41"/>
-      <c r="Q9" s="39"/>
-      <c r="R9" s="40"/>
-      <c r="S9" s="40"/>
-      <c r="T9" s="40"/>
-      <c r="U9" s="40"/>
-      <c r="V9" s="40"/>
-      <c r="W9" s="40"/>
-      <c r="X9" s="41"/>
-      <c r="Z9" s="39"/>
-      <c r="AA9" s="40"/>
-      <c r="AB9" s="40"/>
-      <c r="AC9" s="40"/>
-      <c r="AD9" s="40"/>
-      <c r="AE9" s="40"/>
-      <c r="AF9" s="40"/>
-      <c r="AG9" s="41"/>
-      <c r="AI9" s="39"/>
-      <c r="AJ9" s="40"/>
-      <c r="AK9" s="40"/>
-      <c r="AL9" s="40"/>
-      <c r="AM9" s="40"/>
-      <c r="AN9" s="40"/>
-      <c r="AO9" s="40"/>
-      <c r="AP9" s="41"/>
-      <c r="AR9" s="39"/>
-      <c r="AS9" s="40"/>
-      <c r="AT9" s="40"/>
-      <c r="AU9" s="40"/>
-      <c r="AV9" s="40"/>
-      <c r="AW9" s="40"/>
-      <c r="AX9" s="40"/>
-      <c r="AY9" s="41"/>
-      <c r="BA9" s="39"/>
-      <c r="BB9" s="40"/>
-      <c r="BC9" s="40"/>
-      <c r="BD9" s="40"/>
-      <c r="BE9" s="40"/>
-      <c r="BF9" s="40"/>
-      <c r="BG9" s="40"/>
-      <c r="BH9" s="41"/>
-      <c r="BJ9" s="45"/>
-      <c r="BK9" s="46"/>
-      <c r="BL9" s="46"/>
-      <c r="BM9" s="46"/>
-      <c r="BN9" s="46"/>
-      <c r="BO9" s="46"/>
-      <c r="BP9" s="46"/>
-      <c r="BQ9" s="47"/>
-      <c r="BS9" s="45"/>
-      <c r="BT9" s="46"/>
-      <c r="BU9" s="46"/>
-      <c r="BV9" s="46"/>
-      <c r="BW9" s="46"/>
-      <c r="BX9" s="46"/>
-      <c r="BY9" s="46"/>
-      <c r="BZ9" s="47"/>
-      <c r="CB9" s="59" t="s">
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="65"/>
+      <c r="J9" s="65"/>
+      <c r="K9" s="65"/>
+      <c r="L9" s="65"/>
+      <c r="M9" s="65"/>
+      <c r="N9" s="65"/>
+      <c r="O9" s="66"/>
+      <c r="Q9" s="64"/>
+      <c r="R9" s="65"/>
+      <c r="S9" s="65"/>
+      <c r="T9" s="65"/>
+      <c r="U9" s="65"/>
+      <c r="V9" s="65"/>
+      <c r="W9" s="65"/>
+      <c r="X9" s="66"/>
+      <c r="Z9" s="64"/>
+      <c r="AA9" s="65"/>
+      <c r="AB9" s="65"/>
+      <c r="AC9" s="65"/>
+      <c r="AD9" s="65"/>
+      <c r="AE9" s="65"/>
+      <c r="AF9" s="65"/>
+      <c r="AG9" s="66"/>
+      <c r="AI9" s="64"/>
+      <c r="AJ9" s="65"/>
+      <c r="AK9" s="65"/>
+      <c r="AL9" s="65"/>
+      <c r="AM9" s="65"/>
+      <c r="AN9" s="65"/>
+      <c r="AO9" s="65"/>
+      <c r="AP9" s="66"/>
+      <c r="AR9" s="64"/>
+      <c r="AS9" s="65"/>
+      <c r="AT9" s="65"/>
+      <c r="AU9" s="65"/>
+      <c r="AV9" s="65"/>
+      <c r="AW9" s="65"/>
+      <c r="AX9" s="65"/>
+      <c r="AY9" s="66"/>
+      <c r="BA9" s="64"/>
+      <c r="BB9" s="65"/>
+      <c r="BC9" s="65"/>
+      <c r="BD9" s="65"/>
+      <c r="BE9" s="65"/>
+      <c r="BF9" s="65"/>
+      <c r="BG9" s="65"/>
+      <c r="BH9" s="66"/>
+      <c r="BJ9" s="48"/>
+      <c r="BK9" s="49"/>
+      <c r="BL9" s="49"/>
+      <c r="BM9" s="49"/>
+      <c r="BN9" s="49"/>
+      <c r="BO9" s="49"/>
+      <c r="BP9" s="49"/>
+      <c r="BQ9" s="50"/>
+      <c r="BS9" s="48"/>
+      <c r="BT9" s="49"/>
+      <c r="BU9" s="49"/>
+      <c r="BV9" s="49"/>
+      <c r="BW9" s="49"/>
+      <c r="BX9" s="49"/>
+      <c r="BY9" s="49"/>
+      <c r="BZ9" s="50"/>
+      <c r="CB9" s="72" t="s">
         <v>49</v>
       </c>
-      <c r="CC9" s="60"/>
-      <c r="CD9" s="60"/>
-      <c r="CE9" s="60"/>
-      <c r="CF9" s="60"/>
-      <c r="CG9" s="61"/>
+      <c r="CC9" s="73"/>
+      <c r="CD9" s="73"/>
+      <c r="CE9" s="73"/>
+      <c r="CF9" s="73"/>
+      <c r="CG9" s="74"/>
     </row>
     <row r="10" spans="3:85" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="43"/>
-      <c r="J10" s="43"/>
-      <c r="K10" s="43"/>
-      <c r="L10" s="43"/>
-      <c r="M10" s="43"/>
-      <c r="N10" s="43"/>
-      <c r="O10" s="44"/>
-      <c r="Q10" s="42"/>
-      <c r="R10" s="43"/>
-      <c r="S10" s="43"/>
-      <c r="T10" s="43"/>
-      <c r="U10" s="43"/>
-      <c r="V10" s="43"/>
-      <c r="W10" s="43"/>
-      <c r="X10" s="44"/>
-      <c r="Z10" s="42"/>
-      <c r="AA10" s="43"/>
-      <c r="AB10" s="43"/>
-      <c r="AC10" s="43"/>
-      <c r="AD10" s="43"/>
-      <c r="AE10" s="43"/>
-      <c r="AF10" s="43"/>
-      <c r="AG10" s="44"/>
-      <c r="AI10" s="42"/>
-      <c r="AJ10" s="43"/>
-      <c r="AK10" s="43"/>
-      <c r="AL10" s="43"/>
-      <c r="AM10" s="43"/>
-      <c r="AN10" s="43"/>
-      <c r="AO10" s="43"/>
-      <c r="AP10" s="44"/>
-      <c r="AR10" s="42"/>
-      <c r="AS10" s="43"/>
-      <c r="AT10" s="43"/>
-      <c r="AU10" s="43"/>
-      <c r="AV10" s="43"/>
-      <c r="AW10" s="43"/>
-      <c r="AX10" s="43"/>
-      <c r="AY10" s="44"/>
-      <c r="BA10" s="42"/>
-      <c r="BB10" s="43"/>
-      <c r="BC10" s="43"/>
-      <c r="BD10" s="43"/>
-      <c r="BE10" s="43"/>
-      <c r="BF10" s="43"/>
-      <c r="BG10" s="43"/>
-      <c r="BH10" s="44"/>
-      <c r="BJ10" s="48"/>
-      <c r="BK10" s="49"/>
-      <c r="BL10" s="49"/>
-      <c r="BM10" s="49"/>
-      <c r="BN10" s="49"/>
-      <c r="BO10" s="49"/>
-      <c r="BP10" s="49"/>
-      <c r="BQ10" s="50"/>
-      <c r="BS10" s="48"/>
-      <c r="BT10" s="49"/>
-      <c r="BU10" s="49"/>
-      <c r="BV10" s="49"/>
-      <c r="BW10" s="49"/>
-      <c r="BX10" s="49"/>
-      <c r="BY10" s="49"/>
-      <c r="BZ10" s="50"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
+      <c r="F10" s="58"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="68"/>
+      <c r="J10" s="68"/>
+      <c r="K10" s="68"/>
+      <c r="L10" s="68"/>
+      <c r="M10" s="68"/>
+      <c r="N10" s="68"/>
+      <c r="O10" s="69"/>
+      <c r="Q10" s="67"/>
+      <c r="R10" s="68"/>
+      <c r="S10" s="68"/>
+      <c r="T10" s="68"/>
+      <c r="U10" s="68"/>
+      <c r="V10" s="68"/>
+      <c r="W10" s="68"/>
+      <c r="X10" s="69"/>
+      <c r="Z10" s="67"/>
+      <c r="AA10" s="68"/>
+      <c r="AB10" s="68"/>
+      <c r="AC10" s="68"/>
+      <c r="AD10" s="68"/>
+      <c r="AE10" s="68"/>
+      <c r="AF10" s="68"/>
+      <c r="AG10" s="69"/>
+      <c r="AI10" s="67"/>
+      <c r="AJ10" s="68"/>
+      <c r="AK10" s="68"/>
+      <c r="AL10" s="68"/>
+      <c r="AM10" s="68"/>
+      <c r="AN10" s="68"/>
+      <c r="AO10" s="68"/>
+      <c r="AP10" s="69"/>
+      <c r="AR10" s="67"/>
+      <c r="AS10" s="68"/>
+      <c r="AT10" s="68"/>
+      <c r="AU10" s="68"/>
+      <c r="AV10" s="68"/>
+      <c r="AW10" s="68"/>
+      <c r="AX10" s="68"/>
+      <c r="AY10" s="69"/>
+      <c r="BA10" s="67"/>
+      <c r="BB10" s="68"/>
+      <c r="BC10" s="68"/>
+      <c r="BD10" s="68"/>
+      <c r="BE10" s="68"/>
+      <c r="BF10" s="68"/>
+      <c r="BG10" s="68"/>
+      <c r="BH10" s="69"/>
+      <c r="BJ10" s="51"/>
+      <c r="BK10" s="52"/>
+      <c r="BL10" s="52"/>
+      <c r="BM10" s="52"/>
+      <c r="BN10" s="52"/>
+      <c r="BO10" s="52"/>
+      <c r="BP10" s="52"/>
+      <c r="BQ10" s="53"/>
+      <c r="BS10" s="51"/>
+      <c r="BT10" s="52"/>
+      <c r="BU10" s="52"/>
+      <c r="BV10" s="52"/>
+      <c r="BW10" s="52"/>
+      <c r="BX10" s="52"/>
+      <c r="BY10" s="52"/>
+      <c r="BZ10" s="53"/>
       <c r="CB10" s="16" t="s">
         <v>18</v>
       </c>
@@ -2604,17 +2604,17 @@
         <f>SUM(BT11+BV11+BX11)*16</f>
         <v>0</v>
       </c>
-      <c r="CB11" s="56" t="s">
+      <c r="CB11" s="77" t="s">
         <v>40</v>
       </c>
-      <c r="CC11" s="51"/>
-      <c r="CD11" s="51"/>
-      <c r="CE11" s="51">
+      <c r="CC11" s="58"/>
+      <c r="CD11" s="58"/>
+      <c r="CE11" s="58">
         <f ca="1">CE12*3*16</f>
         <v>0</v>
       </c>
-      <c r="CF11" s="51"/>
-      <c r="CG11" s="52"/>
+      <c r="CF11" s="58"/>
+      <c r="CG11" s="75"/>
     </row>
     <row r="12" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="N12" s="28" t="s">
@@ -2673,168 +2673,168 @@
         <f>(BT11+BV11+BX11)/3</f>
         <v>0</v>
       </c>
-      <c r="CB12" s="53" t="s">
+      <c r="CB12" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="CC12" s="54"/>
-      <c r="CD12" s="54"/>
-      <c r="CE12" s="54">
+      <c r="CC12" s="56"/>
+      <c r="CD12" s="56"/>
+      <c r="CE12" s="56">
         <f ca="1">SUM(IF(MOD(COLUMN(O12:OFFSET(CE12,0,-1)) - COLUMN(O12), 9) = 0, O12:OFFSET(CE12,0,-1), 0))</f>
         <v>0</v>
       </c>
-      <c r="CF12" s="54"/>
-      <c r="CG12" s="55"/>
+      <c r="CF12" s="56"/>
+      <c r="CG12" s="57"/>
     </row>
     <row r="13" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="3:85" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="51" t="s">
+      <c r="C14" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="40"/>
-      <c r="M14" s="40"/>
-      <c r="N14" s="40"/>
-      <c r="O14" s="41"/>
-      <c r="Q14" s="39"/>
-      <c r="R14" s="40"/>
-      <c r="S14" s="40"/>
-      <c r="T14" s="40"/>
-      <c r="U14" s="40"/>
-      <c r="V14" s="40"/>
-      <c r="W14" s="40"/>
-      <c r="X14" s="41"/>
-      <c r="Z14" s="39"/>
-      <c r="AA14" s="40"/>
-      <c r="AB14" s="40"/>
-      <c r="AC14" s="40"/>
-      <c r="AD14" s="40"/>
-      <c r="AE14" s="40"/>
-      <c r="AF14" s="40"/>
-      <c r="AG14" s="41"/>
-      <c r="AI14" s="39"/>
-      <c r="AJ14" s="40"/>
-      <c r="AK14" s="40"/>
-      <c r="AL14" s="40"/>
-      <c r="AM14" s="40"/>
-      <c r="AN14" s="40"/>
-      <c r="AO14" s="40"/>
-      <c r="AP14" s="41"/>
-      <c r="AR14" s="39"/>
-      <c r="AS14" s="40"/>
-      <c r="AT14" s="40"/>
-      <c r="AU14" s="40"/>
-      <c r="AV14" s="40"/>
-      <c r="AW14" s="40"/>
-      <c r="AX14" s="40"/>
-      <c r="AY14" s="41"/>
-      <c r="BA14" s="39"/>
-      <c r="BB14" s="40"/>
-      <c r="BC14" s="40"/>
-      <c r="BD14" s="40"/>
-      <c r="BE14" s="40"/>
-      <c r="BF14" s="40"/>
-      <c r="BG14" s="40"/>
-      <c r="BH14" s="41"/>
-      <c r="BJ14" s="45"/>
-      <c r="BK14" s="46"/>
-      <c r="BL14" s="46"/>
-      <c r="BM14" s="46"/>
-      <c r="BN14" s="46"/>
-      <c r="BO14" s="46"/>
-      <c r="BP14" s="46"/>
-      <c r="BQ14" s="47"/>
-      <c r="BS14" s="45"/>
-      <c r="BT14" s="46"/>
-      <c r="BU14" s="46"/>
-      <c r="BV14" s="46"/>
-      <c r="BW14" s="46"/>
-      <c r="BX14" s="46"/>
-      <c r="BY14" s="46"/>
-      <c r="BZ14" s="47"/>
-      <c r="CB14" s="62" t="s">
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="58"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="65"/>
+      <c r="K14" s="65"/>
+      <c r="L14" s="65"/>
+      <c r="M14" s="65"/>
+      <c r="N14" s="65"/>
+      <c r="O14" s="66"/>
+      <c r="Q14" s="64"/>
+      <c r="R14" s="65"/>
+      <c r="S14" s="65"/>
+      <c r="T14" s="65"/>
+      <c r="U14" s="65"/>
+      <c r="V14" s="65"/>
+      <c r="W14" s="65"/>
+      <c r="X14" s="66"/>
+      <c r="Z14" s="64"/>
+      <c r="AA14" s="65"/>
+      <c r="AB14" s="65"/>
+      <c r="AC14" s="65"/>
+      <c r="AD14" s="65"/>
+      <c r="AE14" s="65"/>
+      <c r="AF14" s="65"/>
+      <c r="AG14" s="66"/>
+      <c r="AI14" s="64"/>
+      <c r="AJ14" s="65"/>
+      <c r="AK14" s="65"/>
+      <c r="AL14" s="65"/>
+      <c r="AM14" s="65"/>
+      <c r="AN14" s="65"/>
+      <c r="AO14" s="65"/>
+      <c r="AP14" s="66"/>
+      <c r="AR14" s="64"/>
+      <c r="AS14" s="65"/>
+      <c r="AT14" s="65"/>
+      <c r="AU14" s="65"/>
+      <c r="AV14" s="65"/>
+      <c r="AW14" s="65"/>
+      <c r="AX14" s="65"/>
+      <c r="AY14" s="66"/>
+      <c r="BA14" s="64"/>
+      <c r="BB14" s="65"/>
+      <c r="BC14" s="65"/>
+      <c r="BD14" s="65"/>
+      <c r="BE14" s="65"/>
+      <c r="BF14" s="65"/>
+      <c r="BG14" s="65"/>
+      <c r="BH14" s="66"/>
+      <c r="BJ14" s="48"/>
+      <c r="BK14" s="49"/>
+      <c r="BL14" s="49"/>
+      <c r="BM14" s="49"/>
+      <c r="BN14" s="49"/>
+      <c r="BO14" s="49"/>
+      <c r="BP14" s="49"/>
+      <c r="BQ14" s="50"/>
+      <c r="BS14" s="48"/>
+      <c r="BT14" s="49"/>
+      <c r="BU14" s="49"/>
+      <c r="BV14" s="49"/>
+      <c r="BW14" s="49"/>
+      <c r="BX14" s="49"/>
+      <c r="BY14" s="49"/>
+      <c r="BZ14" s="50"/>
+      <c r="CB14" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="CC14" s="63"/>
-      <c r="CD14" s="63"/>
-      <c r="CE14" s="63"/>
-      <c r="CF14" s="63"/>
-      <c r="CG14" s="64"/>
+      <c r="CC14" s="62"/>
+      <c r="CD14" s="62"/>
+      <c r="CE14" s="62"/>
+      <c r="CF14" s="62"/>
+      <c r="CG14" s="63"/>
     </row>
     <row r="15" spans="3:85" x14ac:dyDescent="0.25">
-      <c r="C15" s="51"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="43"/>
-      <c r="M15" s="43"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="44"/>
-      <c r="Q15" s="42"/>
-      <c r="R15" s="43"/>
-      <c r="S15" s="43"/>
-      <c r="T15" s="43"/>
-      <c r="U15" s="43"/>
-      <c r="V15" s="43"/>
-      <c r="W15" s="43"/>
-      <c r="X15" s="44"/>
-      <c r="Z15" s="42"/>
-      <c r="AA15" s="43"/>
-      <c r="AB15" s="43"/>
-      <c r="AC15" s="43"/>
-      <c r="AD15" s="43"/>
-      <c r="AE15" s="43"/>
-      <c r="AF15" s="43"/>
-      <c r="AG15" s="44"/>
-      <c r="AI15" s="42"/>
-      <c r="AJ15" s="43"/>
-      <c r="AK15" s="43"/>
-      <c r="AL15" s="43"/>
-      <c r="AM15" s="43"/>
-      <c r="AN15" s="43"/>
-      <c r="AO15" s="43"/>
-      <c r="AP15" s="44"/>
-      <c r="AR15" s="42"/>
-      <c r="AS15" s="43"/>
-      <c r="AT15" s="43"/>
-      <c r="AU15" s="43"/>
-      <c r="AV15" s="43"/>
-      <c r="AW15" s="43"/>
-      <c r="AX15" s="43"/>
-      <c r="AY15" s="44"/>
-      <c r="BA15" s="42"/>
-      <c r="BB15" s="43"/>
-      <c r="BC15" s="43"/>
-      <c r="BD15" s="43"/>
-      <c r="BE15" s="43"/>
-      <c r="BF15" s="43"/>
-      <c r="BG15" s="43"/>
-      <c r="BH15" s="44"/>
-      <c r="BJ15" s="48"/>
-      <c r="BK15" s="49"/>
-      <c r="BL15" s="49"/>
-      <c r="BM15" s="49"/>
-      <c r="BN15" s="49"/>
-      <c r="BO15" s="49"/>
-      <c r="BP15" s="49"/>
-      <c r="BQ15" s="50"/>
-      <c r="BS15" s="48"/>
-      <c r="BT15" s="49"/>
-      <c r="BU15" s="49"/>
-      <c r="BV15" s="49"/>
-      <c r="BW15" s="49"/>
-      <c r="BX15" s="49"/>
-      <c r="BY15" s="49"/>
-      <c r="BZ15" s="50"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="68"/>
+      <c r="J15" s="68"/>
+      <c r="K15" s="68"/>
+      <c r="L15" s="68"/>
+      <c r="M15" s="68"/>
+      <c r="N15" s="68"/>
+      <c r="O15" s="69"/>
+      <c r="Q15" s="67"/>
+      <c r="R15" s="68"/>
+      <c r="S15" s="68"/>
+      <c r="T15" s="68"/>
+      <c r="U15" s="68"/>
+      <c r="V15" s="68"/>
+      <c r="W15" s="68"/>
+      <c r="X15" s="69"/>
+      <c r="Z15" s="67"/>
+      <c r="AA15" s="68"/>
+      <c r="AB15" s="68"/>
+      <c r="AC15" s="68"/>
+      <c r="AD15" s="68"/>
+      <c r="AE15" s="68"/>
+      <c r="AF15" s="68"/>
+      <c r="AG15" s="69"/>
+      <c r="AI15" s="67"/>
+      <c r="AJ15" s="68"/>
+      <c r="AK15" s="68"/>
+      <c r="AL15" s="68"/>
+      <c r="AM15" s="68"/>
+      <c r="AN15" s="68"/>
+      <c r="AO15" s="68"/>
+      <c r="AP15" s="69"/>
+      <c r="AR15" s="67"/>
+      <c r="AS15" s="68"/>
+      <c r="AT15" s="68"/>
+      <c r="AU15" s="68"/>
+      <c r="AV15" s="68"/>
+      <c r="AW15" s="68"/>
+      <c r="AX15" s="68"/>
+      <c r="AY15" s="69"/>
+      <c r="BA15" s="67"/>
+      <c r="BB15" s="68"/>
+      <c r="BC15" s="68"/>
+      <c r="BD15" s="68"/>
+      <c r="BE15" s="68"/>
+      <c r="BF15" s="68"/>
+      <c r="BG15" s="68"/>
+      <c r="BH15" s="69"/>
+      <c r="BJ15" s="51"/>
+      <c r="BK15" s="52"/>
+      <c r="BL15" s="52"/>
+      <c r="BM15" s="52"/>
+      <c r="BN15" s="52"/>
+      <c r="BO15" s="52"/>
+      <c r="BP15" s="52"/>
+      <c r="BQ15" s="53"/>
+      <c r="BS15" s="51"/>
+      <c r="BT15" s="52"/>
+      <c r="BU15" s="52"/>
+      <c r="BV15" s="52"/>
+      <c r="BW15" s="52"/>
+      <c r="BX15" s="52"/>
+      <c r="BY15" s="52"/>
+      <c r="BZ15" s="53"/>
       <c r="CB15" s="16" t="s">
         <v>18</v>
       </c>
@@ -3010,17 +3010,17 @@
         <f>SUM(BT16+BV16+BX16)*16</f>
         <v>0</v>
       </c>
-      <c r="CB16" s="65" t="s">
+      <c r="CB16" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="CC16" s="51"/>
-      <c r="CD16" s="51"/>
-      <c r="CE16" s="51">
+      <c r="CC16" s="58"/>
+      <c r="CD16" s="58"/>
+      <c r="CE16" s="58">
         <f ca="1">CE17*3*16</f>
         <v>0</v>
       </c>
-      <c r="CF16" s="51"/>
-      <c r="CG16" s="68"/>
+      <c r="CF16" s="58"/>
+      <c r="CG16" s="59"/>
     </row>
     <row r="17" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="N17" s="28" t="s">
@@ -3079,168 +3079,168 @@
         <f>(BT16+BV16+BX16)/3</f>
         <v>0</v>
       </c>
-      <c r="CB17" s="66" t="s">
+      <c r="CB17" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="CC17" s="67"/>
-      <c r="CD17" s="67"/>
-      <c r="CE17" s="54">
+      <c r="CC17" s="55"/>
+      <c r="CD17" s="55"/>
+      <c r="CE17" s="56">
         <f ca="1">SUM(IF(MOD(COLUMN(O17:OFFSET(CE17,0,-1)) - COLUMN(O17), 9) = 0, O17:OFFSET(CE17,0,-1), 0))</f>
         <v>0</v>
       </c>
-      <c r="CF17" s="54"/>
-      <c r="CG17" s="55"/>
+      <c r="CF17" s="56"/>
+      <c r="CG17" s="57"/>
     </row>
     <row r="18" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="3:85" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="51" t="s">
+      <c r="C19" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="40"/>
-      <c r="K19" s="40"/>
-      <c r="L19" s="40"/>
-      <c r="M19" s="40"/>
-      <c r="N19" s="40"/>
-      <c r="O19" s="41"/>
-      <c r="Q19" s="39"/>
-      <c r="R19" s="40"/>
-      <c r="S19" s="40"/>
-      <c r="T19" s="40"/>
-      <c r="U19" s="40"/>
-      <c r="V19" s="40"/>
-      <c r="W19" s="40"/>
-      <c r="X19" s="41"/>
-      <c r="Z19" s="39"/>
-      <c r="AA19" s="40"/>
-      <c r="AB19" s="40"/>
-      <c r="AC19" s="40"/>
-      <c r="AD19" s="40"/>
-      <c r="AE19" s="40"/>
-      <c r="AF19" s="40"/>
-      <c r="AG19" s="41"/>
-      <c r="AI19" s="39"/>
-      <c r="AJ19" s="40"/>
-      <c r="AK19" s="40"/>
-      <c r="AL19" s="40"/>
-      <c r="AM19" s="40"/>
-      <c r="AN19" s="40"/>
-      <c r="AO19" s="40"/>
-      <c r="AP19" s="41"/>
-      <c r="AR19" s="39"/>
-      <c r="AS19" s="40"/>
-      <c r="AT19" s="40"/>
-      <c r="AU19" s="40"/>
-      <c r="AV19" s="40"/>
-      <c r="AW19" s="40"/>
-      <c r="AX19" s="40"/>
-      <c r="AY19" s="41"/>
-      <c r="BA19" s="39"/>
-      <c r="BB19" s="40"/>
-      <c r="BC19" s="40"/>
-      <c r="BD19" s="40"/>
-      <c r="BE19" s="40"/>
-      <c r="BF19" s="40"/>
-      <c r="BG19" s="40"/>
-      <c r="BH19" s="41"/>
-      <c r="BJ19" s="45"/>
-      <c r="BK19" s="46"/>
-      <c r="BL19" s="46"/>
-      <c r="BM19" s="46"/>
-      <c r="BN19" s="46"/>
-      <c r="BO19" s="46"/>
-      <c r="BP19" s="46"/>
-      <c r="BQ19" s="47"/>
-      <c r="BS19" s="45"/>
-      <c r="BT19" s="46"/>
-      <c r="BU19" s="46"/>
-      <c r="BV19" s="46"/>
-      <c r="BW19" s="46"/>
-      <c r="BX19" s="46"/>
-      <c r="BY19" s="46"/>
-      <c r="BZ19" s="47"/>
-      <c r="CB19" s="62" t="s">
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="58"/>
+      <c r="H19" s="64"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="65"/>
+      <c r="K19" s="65"/>
+      <c r="L19" s="65"/>
+      <c r="M19" s="65"/>
+      <c r="N19" s="65"/>
+      <c r="O19" s="66"/>
+      <c r="Q19" s="64"/>
+      <c r="R19" s="65"/>
+      <c r="S19" s="65"/>
+      <c r="T19" s="65"/>
+      <c r="U19" s="65"/>
+      <c r="V19" s="65"/>
+      <c r="W19" s="65"/>
+      <c r="X19" s="66"/>
+      <c r="Z19" s="64"/>
+      <c r="AA19" s="65"/>
+      <c r="AB19" s="65"/>
+      <c r="AC19" s="65"/>
+      <c r="AD19" s="65"/>
+      <c r="AE19" s="65"/>
+      <c r="AF19" s="65"/>
+      <c r="AG19" s="66"/>
+      <c r="AI19" s="64"/>
+      <c r="AJ19" s="65"/>
+      <c r="AK19" s="65"/>
+      <c r="AL19" s="65"/>
+      <c r="AM19" s="65"/>
+      <c r="AN19" s="65"/>
+      <c r="AO19" s="65"/>
+      <c r="AP19" s="66"/>
+      <c r="AR19" s="64"/>
+      <c r="AS19" s="65"/>
+      <c r="AT19" s="65"/>
+      <c r="AU19" s="65"/>
+      <c r="AV19" s="65"/>
+      <c r="AW19" s="65"/>
+      <c r="AX19" s="65"/>
+      <c r="AY19" s="66"/>
+      <c r="BA19" s="64"/>
+      <c r="BB19" s="65"/>
+      <c r="BC19" s="65"/>
+      <c r="BD19" s="65"/>
+      <c r="BE19" s="65"/>
+      <c r="BF19" s="65"/>
+      <c r="BG19" s="65"/>
+      <c r="BH19" s="66"/>
+      <c r="BJ19" s="48"/>
+      <c r="BK19" s="49"/>
+      <c r="BL19" s="49"/>
+      <c r="BM19" s="49"/>
+      <c r="BN19" s="49"/>
+      <c r="BO19" s="49"/>
+      <c r="BP19" s="49"/>
+      <c r="BQ19" s="50"/>
+      <c r="BS19" s="48"/>
+      <c r="BT19" s="49"/>
+      <c r="BU19" s="49"/>
+      <c r="BV19" s="49"/>
+      <c r="BW19" s="49"/>
+      <c r="BX19" s="49"/>
+      <c r="BY19" s="49"/>
+      <c r="BZ19" s="50"/>
+      <c r="CB19" s="61" t="s">
         <v>53</v>
       </c>
-      <c r="CC19" s="63"/>
-      <c r="CD19" s="63"/>
-      <c r="CE19" s="63"/>
-      <c r="CF19" s="63"/>
-      <c r="CG19" s="64"/>
+      <c r="CC19" s="62"/>
+      <c r="CD19" s="62"/>
+      <c r="CE19" s="62"/>
+      <c r="CF19" s="62"/>
+      <c r="CG19" s="63"/>
     </row>
     <row r="20" spans="3:85" x14ac:dyDescent="0.25">
-      <c r="C20" s="51"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="51"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="43"/>
-      <c r="J20" s="43"/>
-      <c r="K20" s="43"/>
-      <c r="L20" s="43"/>
-      <c r="M20" s="43"/>
-      <c r="N20" s="43"/>
-      <c r="O20" s="44"/>
-      <c r="Q20" s="42"/>
-      <c r="R20" s="43"/>
-      <c r="S20" s="43"/>
-      <c r="T20" s="43"/>
-      <c r="U20" s="43"/>
-      <c r="V20" s="43"/>
-      <c r="W20" s="43"/>
-      <c r="X20" s="44"/>
-      <c r="Z20" s="42"/>
-      <c r="AA20" s="43"/>
-      <c r="AB20" s="43"/>
-      <c r="AC20" s="43"/>
-      <c r="AD20" s="43"/>
-      <c r="AE20" s="43"/>
-      <c r="AF20" s="43"/>
-      <c r="AG20" s="44"/>
-      <c r="AI20" s="42"/>
-      <c r="AJ20" s="43"/>
-      <c r="AK20" s="43"/>
-      <c r="AL20" s="43"/>
-      <c r="AM20" s="43"/>
-      <c r="AN20" s="43"/>
-      <c r="AO20" s="43"/>
-      <c r="AP20" s="44"/>
-      <c r="AR20" s="42"/>
-      <c r="AS20" s="43"/>
-      <c r="AT20" s="43"/>
-      <c r="AU20" s="43"/>
-      <c r="AV20" s="43"/>
-      <c r="AW20" s="43"/>
-      <c r="AX20" s="43"/>
-      <c r="AY20" s="44"/>
-      <c r="BA20" s="42"/>
-      <c r="BB20" s="43"/>
-      <c r="BC20" s="43"/>
-      <c r="BD20" s="43"/>
-      <c r="BE20" s="43"/>
-      <c r="BF20" s="43"/>
-      <c r="BG20" s="43"/>
-      <c r="BH20" s="44"/>
-      <c r="BJ20" s="48"/>
-      <c r="BK20" s="49"/>
-      <c r="BL20" s="49"/>
-      <c r="BM20" s="49"/>
-      <c r="BN20" s="49"/>
-      <c r="BO20" s="49"/>
-      <c r="BP20" s="49"/>
-      <c r="BQ20" s="50"/>
-      <c r="BS20" s="48"/>
-      <c r="BT20" s="49"/>
-      <c r="BU20" s="49"/>
-      <c r="BV20" s="49"/>
-      <c r="BW20" s="49"/>
-      <c r="BX20" s="49"/>
-      <c r="BY20" s="49"/>
-      <c r="BZ20" s="50"/>
+      <c r="C20" s="58"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="58"/>
+      <c r="H20" s="67"/>
+      <c r="I20" s="68"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="68"/>
+      <c r="L20" s="68"/>
+      <c r="M20" s="68"/>
+      <c r="N20" s="68"/>
+      <c r="O20" s="69"/>
+      <c r="Q20" s="67"/>
+      <c r="R20" s="68"/>
+      <c r="S20" s="68"/>
+      <c r="T20" s="68"/>
+      <c r="U20" s="68"/>
+      <c r="V20" s="68"/>
+      <c r="W20" s="68"/>
+      <c r="X20" s="69"/>
+      <c r="Z20" s="67"/>
+      <c r="AA20" s="68"/>
+      <c r="AB20" s="68"/>
+      <c r="AC20" s="68"/>
+      <c r="AD20" s="68"/>
+      <c r="AE20" s="68"/>
+      <c r="AF20" s="68"/>
+      <c r="AG20" s="69"/>
+      <c r="AI20" s="67"/>
+      <c r="AJ20" s="68"/>
+      <c r="AK20" s="68"/>
+      <c r="AL20" s="68"/>
+      <c r="AM20" s="68"/>
+      <c r="AN20" s="68"/>
+      <c r="AO20" s="68"/>
+      <c r="AP20" s="69"/>
+      <c r="AR20" s="67"/>
+      <c r="AS20" s="68"/>
+      <c r="AT20" s="68"/>
+      <c r="AU20" s="68"/>
+      <c r="AV20" s="68"/>
+      <c r="AW20" s="68"/>
+      <c r="AX20" s="68"/>
+      <c r="AY20" s="69"/>
+      <c r="BA20" s="67"/>
+      <c r="BB20" s="68"/>
+      <c r="BC20" s="68"/>
+      <c r="BD20" s="68"/>
+      <c r="BE20" s="68"/>
+      <c r="BF20" s="68"/>
+      <c r="BG20" s="68"/>
+      <c r="BH20" s="69"/>
+      <c r="BJ20" s="51"/>
+      <c r="BK20" s="52"/>
+      <c r="BL20" s="52"/>
+      <c r="BM20" s="52"/>
+      <c r="BN20" s="52"/>
+      <c r="BO20" s="52"/>
+      <c r="BP20" s="52"/>
+      <c r="BQ20" s="53"/>
+      <c r="BS20" s="51"/>
+      <c r="BT20" s="52"/>
+      <c r="BU20" s="52"/>
+      <c r="BV20" s="52"/>
+      <c r="BW20" s="52"/>
+      <c r="BX20" s="52"/>
+      <c r="BY20" s="52"/>
+      <c r="BZ20" s="53"/>
       <c r="CB20" s="16" t="s">
         <v>18</v>
       </c>
@@ -3416,17 +3416,17 @@
         <f>SUM(BT21+BV21+BX21)*16</f>
         <v>0</v>
       </c>
-      <c r="CB21" s="65" t="s">
+      <c r="CB21" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="CC21" s="51"/>
-      <c r="CD21" s="51"/>
-      <c r="CE21" s="51">
+      <c r="CC21" s="58"/>
+      <c r="CD21" s="58"/>
+      <c r="CE21" s="58">
         <f ca="1">CE22*3*16</f>
         <v>0</v>
       </c>
-      <c r="CF21" s="51"/>
-      <c r="CG21" s="68"/>
+      <c r="CF21" s="58"/>
+      <c r="CG21" s="59"/>
     </row>
     <row r="22" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="N22" s="28" t="s">
@@ -3485,168 +3485,168 @@
         <f>(BT21+BV21+BX21)/3</f>
         <v>0</v>
       </c>
-      <c r="CB22" s="66" t="s">
+      <c r="CB22" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="CC22" s="67"/>
-      <c r="CD22" s="67"/>
-      <c r="CE22" s="54">
+      <c r="CC22" s="55"/>
+      <c r="CD22" s="55"/>
+      <c r="CE22" s="56">
         <f ca="1">SUM(IF(MOD(COLUMN(O22:OFFSET(CE22,0,-1)) - COLUMN(O22), 9) = 0, O22:OFFSET(CE22,0,-1), 0))</f>
         <v>0</v>
       </c>
-      <c r="CF22" s="54"/>
-      <c r="CG22" s="55"/>
+      <c r="CF22" s="56"/>
+      <c r="CG22" s="57"/>
     </row>
     <row r="23" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="3:85" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C24" s="51" t="s">
+      <c r="C24" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="51"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="40"/>
-      <c r="K24" s="40"/>
-      <c r="L24" s="40"/>
-      <c r="M24" s="40"/>
-      <c r="N24" s="40"/>
-      <c r="O24" s="41"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="40"/>
-      <c r="S24" s="40"/>
-      <c r="T24" s="40"/>
-      <c r="U24" s="40"/>
-      <c r="V24" s="40"/>
-      <c r="W24" s="40"/>
-      <c r="X24" s="41"/>
-      <c r="Z24" s="39"/>
-      <c r="AA24" s="40"/>
-      <c r="AB24" s="40"/>
-      <c r="AC24" s="40"/>
-      <c r="AD24" s="40"/>
-      <c r="AE24" s="40"/>
-      <c r="AF24" s="40"/>
-      <c r="AG24" s="41"/>
-      <c r="AI24" s="39"/>
-      <c r="AJ24" s="40"/>
-      <c r="AK24" s="40"/>
-      <c r="AL24" s="40"/>
-      <c r="AM24" s="40"/>
-      <c r="AN24" s="40"/>
-      <c r="AO24" s="40"/>
-      <c r="AP24" s="41"/>
-      <c r="AR24" s="39"/>
-      <c r="AS24" s="40"/>
-      <c r="AT24" s="40"/>
-      <c r="AU24" s="40"/>
-      <c r="AV24" s="40"/>
-      <c r="AW24" s="40"/>
-      <c r="AX24" s="40"/>
-      <c r="AY24" s="41"/>
-      <c r="BA24" s="39"/>
-      <c r="BB24" s="40"/>
-      <c r="BC24" s="40"/>
-      <c r="BD24" s="40"/>
-      <c r="BE24" s="40"/>
-      <c r="BF24" s="40"/>
-      <c r="BG24" s="40"/>
-      <c r="BH24" s="41"/>
-      <c r="BJ24" s="45"/>
-      <c r="BK24" s="46"/>
-      <c r="BL24" s="46"/>
-      <c r="BM24" s="46"/>
-      <c r="BN24" s="46"/>
-      <c r="BO24" s="46"/>
-      <c r="BP24" s="46"/>
-      <c r="BQ24" s="47"/>
-      <c r="BS24" s="45"/>
-      <c r="BT24" s="46"/>
-      <c r="BU24" s="46"/>
-      <c r="BV24" s="46"/>
-      <c r="BW24" s="46"/>
-      <c r="BX24" s="46"/>
-      <c r="BY24" s="46"/>
-      <c r="BZ24" s="47"/>
-      <c r="CB24" s="62" t="s">
+      <c r="D24" s="58"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="58"/>
+      <c r="H24" s="64"/>
+      <c r="I24" s="65"/>
+      <c r="J24" s="65"/>
+      <c r="K24" s="65"/>
+      <c r="L24" s="65"/>
+      <c r="M24" s="65"/>
+      <c r="N24" s="65"/>
+      <c r="O24" s="66"/>
+      <c r="Q24" s="64"/>
+      <c r="R24" s="65"/>
+      <c r="S24" s="65"/>
+      <c r="T24" s="65"/>
+      <c r="U24" s="65"/>
+      <c r="V24" s="65"/>
+      <c r="W24" s="65"/>
+      <c r="X24" s="66"/>
+      <c r="Z24" s="64"/>
+      <c r="AA24" s="65"/>
+      <c r="AB24" s="65"/>
+      <c r="AC24" s="65"/>
+      <c r="AD24" s="65"/>
+      <c r="AE24" s="65"/>
+      <c r="AF24" s="65"/>
+      <c r="AG24" s="66"/>
+      <c r="AI24" s="64"/>
+      <c r="AJ24" s="65"/>
+      <c r="AK24" s="65"/>
+      <c r="AL24" s="65"/>
+      <c r="AM24" s="65"/>
+      <c r="AN24" s="65"/>
+      <c r="AO24" s="65"/>
+      <c r="AP24" s="66"/>
+      <c r="AR24" s="64"/>
+      <c r="AS24" s="65"/>
+      <c r="AT24" s="65"/>
+      <c r="AU24" s="65"/>
+      <c r="AV24" s="65"/>
+      <c r="AW24" s="65"/>
+      <c r="AX24" s="65"/>
+      <c r="AY24" s="66"/>
+      <c r="BA24" s="64"/>
+      <c r="BB24" s="65"/>
+      <c r="BC24" s="65"/>
+      <c r="BD24" s="65"/>
+      <c r="BE24" s="65"/>
+      <c r="BF24" s="65"/>
+      <c r="BG24" s="65"/>
+      <c r="BH24" s="66"/>
+      <c r="BJ24" s="48"/>
+      <c r="BK24" s="49"/>
+      <c r="BL24" s="49"/>
+      <c r="BM24" s="49"/>
+      <c r="BN24" s="49"/>
+      <c r="BO24" s="49"/>
+      <c r="BP24" s="49"/>
+      <c r="BQ24" s="50"/>
+      <c r="BS24" s="48"/>
+      <c r="BT24" s="49"/>
+      <c r="BU24" s="49"/>
+      <c r="BV24" s="49"/>
+      <c r="BW24" s="49"/>
+      <c r="BX24" s="49"/>
+      <c r="BY24" s="49"/>
+      <c r="BZ24" s="50"/>
+      <c r="CB24" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="CC24" s="63"/>
-      <c r="CD24" s="63"/>
-      <c r="CE24" s="63"/>
-      <c r="CF24" s="63"/>
-      <c r="CG24" s="64"/>
+      <c r="CC24" s="62"/>
+      <c r="CD24" s="62"/>
+      <c r="CE24" s="62"/>
+      <c r="CF24" s="62"/>
+      <c r="CG24" s="63"/>
     </row>
     <row r="25" spans="3:85" x14ac:dyDescent="0.25">
-      <c r="C25" s="51"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="51"/>
-      <c r="H25" s="42"/>
-      <c r="I25" s="43"/>
-      <c r="J25" s="43"/>
-      <c r="K25" s="43"/>
-      <c r="L25" s="43"/>
-      <c r="M25" s="43"/>
-      <c r="N25" s="43"/>
-      <c r="O25" s="44"/>
-      <c r="Q25" s="42"/>
-      <c r="R25" s="43"/>
-      <c r="S25" s="43"/>
-      <c r="T25" s="43"/>
-      <c r="U25" s="43"/>
-      <c r="V25" s="43"/>
-      <c r="W25" s="43"/>
-      <c r="X25" s="44"/>
-      <c r="Z25" s="42"/>
-      <c r="AA25" s="43"/>
-      <c r="AB25" s="43"/>
-      <c r="AC25" s="43"/>
-      <c r="AD25" s="43"/>
-      <c r="AE25" s="43"/>
-      <c r="AF25" s="43"/>
-      <c r="AG25" s="44"/>
-      <c r="AI25" s="42"/>
-      <c r="AJ25" s="43"/>
-      <c r="AK25" s="43"/>
-      <c r="AL25" s="43"/>
-      <c r="AM25" s="43"/>
-      <c r="AN25" s="43"/>
-      <c r="AO25" s="43"/>
-      <c r="AP25" s="44"/>
-      <c r="AR25" s="42"/>
-      <c r="AS25" s="43"/>
-      <c r="AT25" s="43"/>
-      <c r="AU25" s="43"/>
-      <c r="AV25" s="43"/>
-      <c r="AW25" s="43"/>
-      <c r="AX25" s="43"/>
-      <c r="AY25" s="44"/>
-      <c r="BA25" s="42"/>
-      <c r="BB25" s="43"/>
-      <c r="BC25" s="43"/>
-      <c r="BD25" s="43"/>
-      <c r="BE25" s="43"/>
-      <c r="BF25" s="43"/>
-      <c r="BG25" s="43"/>
-      <c r="BH25" s="44"/>
-      <c r="BJ25" s="48"/>
-      <c r="BK25" s="49"/>
-      <c r="BL25" s="49"/>
-      <c r="BM25" s="49"/>
-      <c r="BN25" s="49"/>
-      <c r="BO25" s="49"/>
-      <c r="BP25" s="49"/>
-      <c r="BQ25" s="50"/>
-      <c r="BS25" s="48"/>
-      <c r="BT25" s="49"/>
-      <c r="BU25" s="49"/>
-      <c r="BV25" s="49"/>
-      <c r="BW25" s="49"/>
-      <c r="BX25" s="49"/>
-      <c r="BY25" s="49"/>
-      <c r="BZ25" s="50"/>
+      <c r="C25" s="58"/>
+      <c r="D25" s="58"/>
+      <c r="E25" s="58"/>
+      <c r="F25" s="58"/>
+      <c r="H25" s="67"/>
+      <c r="I25" s="68"/>
+      <c r="J25" s="68"/>
+      <c r="K25" s="68"/>
+      <c r="L25" s="68"/>
+      <c r="M25" s="68"/>
+      <c r="N25" s="68"/>
+      <c r="O25" s="69"/>
+      <c r="Q25" s="67"/>
+      <c r="R25" s="68"/>
+      <c r="S25" s="68"/>
+      <c r="T25" s="68"/>
+      <c r="U25" s="68"/>
+      <c r="V25" s="68"/>
+      <c r="W25" s="68"/>
+      <c r="X25" s="69"/>
+      <c r="Z25" s="67"/>
+      <c r="AA25" s="68"/>
+      <c r="AB25" s="68"/>
+      <c r="AC25" s="68"/>
+      <c r="AD25" s="68"/>
+      <c r="AE25" s="68"/>
+      <c r="AF25" s="68"/>
+      <c r="AG25" s="69"/>
+      <c r="AI25" s="67"/>
+      <c r="AJ25" s="68"/>
+      <c r="AK25" s="68"/>
+      <c r="AL25" s="68"/>
+      <c r="AM25" s="68"/>
+      <c r="AN25" s="68"/>
+      <c r="AO25" s="68"/>
+      <c r="AP25" s="69"/>
+      <c r="AR25" s="67"/>
+      <c r="AS25" s="68"/>
+      <c r="AT25" s="68"/>
+      <c r="AU25" s="68"/>
+      <c r="AV25" s="68"/>
+      <c r="AW25" s="68"/>
+      <c r="AX25" s="68"/>
+      <c r="AY25" s="69"/>
+      <c r="BA25" s="67"/>
+      <c r="BB25" s="68"/>
+      <c r="BC25" s="68"/>
+      <c r="BD25" s="68"/>
+      <c r="BE25" s="68"/>
+      <c r="BF25" s="68"/>
+      <c r="BG25" s="68"/>
+      <c r="BH25" s="69"/>
+      <c r="BJ25" s="51"/>
+      <c r="BK25" s="52"/>
+      <c r="BL25" s="52"/>
+      <c r="BM25" s="52"/>
+      <c r="BN25" s="52"/>
+      <c r="BO25" s="52"/>
+      <c r="BP25" s="52"/>
+      <c r="BQ25" s="53"/>
+      <c r="BS25" s="51"/>
+      <c r="BT25" s="52"/>
+      <c r="BU25" s="52"/>
+      <c r="BV25" s="52"/>
+      <c r="BW25" s="52"/>
+      <c r="BX25" s="52"/>
+      <c r="BY25" s="52"/>
+      <c r="BZ25" s="53"/>
       <c r="CB25" s="16" t="s">
         <v>18</v>
       </c>
@@ -3822,17 +3822,17 @@
         <f>SUM(BT26+BV26+BX26)*16</f>
         <v>0</v>
       </c>
-      <c r="CB26" s="65" t="s">
+      <c r="CB26" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="CC26" s="51"/>
-      <c r="CD26" s="51"/>
-      <c r="CE26" s="51">
+      <c r="CC26" s="58"/>
+      <c r="CD26" s="58"/>
+      <c r="CE26" s="58">
         <f ca="1">CE27*3*16</f>
         <v>0</v>
       </c>
-      <c r="CF26" s="51"/>
-      <c r="CG26" s="68"/>
+      <c r="CF26" s="58"/>
+      <c r="CG26" s="59"/>
     </row>
     <row r="27" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="N27" s="28" t="s">
@@ -3891,168 +3891,168 @@
         <f>(BT26+BV26+BX26)/3</f>
         <v>0</v>
       </c>
-      <c r="CB27" s="66" t="s">
+      <c r="CB27" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="CC27" s="67"/>
-      <c r="CD27" s="67"/>
-      <c r="CE27" s="54">
+      <c r="CC27" s="55"/>
+      <c r="CD27" s="55"/>
+      <c r="CE27" s="56">
         <f ca="1">SUM(IF(MOD(COLUMN(O27:OFFSET(CE27,0,-1)) - COLUMN(O27), 9) = 0, O27:OFFSET(CE27,0,-1), 0))</f>
         <v>0</v>
       </c>
-      <c r="CF27" s="54"/>
-      <c r="CG27" s="55"/>
+      <c r="CF27" s="56"/>
+      <c r="CG27" s="57"/>
     </row>
     <row r="28" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="3:85" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C29" s="51" t="s">
+      <c r="C29" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="51"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="40"/>
-      <c r="J29" s="40"/>
-      <c r="K29" s="40"/>
-      <c r="L29" s="40"/>
-      <c r="M29" s="40"/>
-      <c r="N29" s="40"/>
-      <c r="O29" s="41"/>
-      <c r="Q29" s="39"/>
-      <c r="R29" s="40"/>
-      <c r="S29" s="40"/>
-      <c r="T29" s="40"/>
-      <c r="U29" s="40"/>
-      <c r="V29" s="40"/>
-      <c r="W29" s="40"/>
-      <c r="X29" s="41"/>
-      <c r="Z29" s="39"/>
-      <c r="AA29" s="40"/>
-      <c r="AB29" s="40"/>
-      <c r="AC29" s="40"/>
-      <c r="AD29" s="40"/>
-      <c r="AE29" s="40"/>
-      <c r="AF29" s="40"/>
-      <c r="AG29" s="41"/>
-      <c r="AI29" s="39"/>
-      <c r="AJ29" s="40"/>
-      <c r="AK29" s="40"/>
-      <c r="AL29" s="40"/>
-      <c r="AM29" s="40"/>
-      <c r="AN29" s="40"/>
-      <c r="AO29" s="40"/>
-      <c r="AP29" s="41"/>
-      <c r="AR29" s="39"/>
-      <c r="AS29" s="40"/>
-      <c r="AT29" s="40"/>
-      <c r="AU29" s="40"/>
-      <c r="AV29" s="40"/>
-      <c r="AW29" s="40"/>
-      <c r="AX29" s="40"/>
-      <c r="AY29" s="41"/>
-      <c r="BA29" s="39"/>
-      <c r="BB29" s="40"/>
-      <c r="BC29" s="40"/>
-      <c r="BD29" s="40"/>
-      <c r="BE29" s="40"/>
-      <c r="BF29" s="40"/>
-      <c r="BG29" s="40"/>
-      <c r="BH29" s="41"/>
-      <c r="BJ29" s="45"/>
-      <c r="BK29" s="46"/>
-      <c r="BL29" s="46"/>
-      <c r="BM29" s="46"/>
-      <c r="BN29" s="46"/>
-      <c r="BO29" s="46"/>
-      <c r="BP29" s="46"/>
-      <c r="BQ29" s="47"/>
-      <c r="BS29" s="45"/>
-      <c r="BT29" s="46"/>
-      <c r="BU29" s="46"/>
-      <c r="BV29" s="46"/>
-      <c r="BW29" s="46"/>
-      <c r="BX29" s="46"/>
-      <c r="BY29" s="46"/>
-      <c r="BZ29" s="47"/>
-      <c r="CB29" s="62" t="s">
+      <c r="D29" s="58"/>
+      <c r="E29" s="58"/>
+      <c r="F29" s="58"/>
+      <c r="H29" s="64"/>
+      <c r="I29" s="65"/>
+      <c r="J29" s="65"/>
+      <c r="K29" s="65"/>
+      <c r="L29" s="65"/>
+      <c r="M29" s="65"/>
+      <c r="N29" s="65"/>
+      <c r="O29" s="66"/>
+      <c r="Q29" s="64"/>
+      <c r="R29" s="65"/>
+      <c r="S29" s="65"/>
+      <c r="T29" s="65"/>
+      <c r="U29" s="65"/>
+      <c r="V29" s="65"/>
+      <c r="W29" s="65"/>
+      <c r="X29" s="66"/>
+      <c r="Z29" s="64"/>
+      <c r="AA29" s="65"/>
+      <c r="AB29" s="65"/>
+      <c r="AC29" s="65"/>
+      <c r="AD29" s="65"/>
+      <c r="AE29" s="65"/>
+      <c r="AF29" s="65"/>
+      <c r="AG29" s="66"/>
+      <c r="AI29" s="64"/>
+      <c r="AJ29" s="65"/>
+      <c r="AK29" s="65"/>
+      <c r="AL29" s="65"/>
+      <c r="AM29" s="65"/>
+      <c r="AN29" s="65"/>
+      <c r="AO29" s="65"/>
+      <c r="AP29" s="66"/>
+      <c r="AR29" s="64"/>
+      <c r="AS29" s="65"/>
+      <c r="AT29" s="65"/>
+      <c r="AU29" s="65"/>
+      <c r="AV29" s="65"/>
+      <c r="AW29" s="65"/>
+      <c r="AX29" s="65"/>
+      <c r="AY29" s="66"/>
+      <c r="BA29" s="64"/>
+      <c r="BB29" s="65"/>
+      <c r="BC29" s="65"/>
+      <c r="BD29" s="65"/>
+      <c r="BE29" s="65"/>
+      <c r="BF29" s="65"/>
+      <c r="BG29" s="65"/>
+      <c r="BH29" s="66"/>
+      <c r="BJ29" s="48"/>
+      <c r="BK29" s="49"/>
+      <c r="BL29" s="49"/>
+      <c r="BM29" s="49"/>
+      <c r="BN29" s="49"/>
+      <c r="BO29" s="49"/>
+      <c r="BP29" s="49"/>
+      <c r="BQ29" s="50"/>
+      <c r="BS29" s="48"/>
+      <c r="BT29" s="49"/>
+      <c r="BU29" s="49"/>
+      <c r="BV29" s="49"/>
+      <c r="BW29" s="49"/>
+      <c r="BX29" s="49"/>
+      <c r="BY29" s="49"/>
+      <c r="BZ29" s="50"/>
+      <c r="CB29" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="CC29" s="63"/>
-      <c r="CD29" s="63"/>
-      <c r="CE29" s="63"/>
-      <c r="CF29" s="63"/>
-      <c r="CG29" s="64"/>
+      <c r="CC29" s="62"/>
+      <c r="CD29" s="62"/>
+      <c r="CE29" s="62"/>
+      <c r="CF29" s="62"/>
+      <c r="CG29" s="63"/>
     </row>
     <row r="30" spans="3:85" x14ac:dyDescent="0.25">
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="51"/>
-      <c r="H30" s="42"/>
-      <c r="I30" s="43"/>
-      <c r="J30" s="43"/>
-      <c r="K30" s="43"/>
-      <c r="L30" s="43"/>
-      <c r="M30" s="43"/>
-      <c r="N30" s="43"/>
-      <c r="O30" s="44"/>
-      <c r="Q30" s="42"/>
-      <c r="R30" s="43"/>
-      <c r="S30" s="43"/>
-      <c r="T30" s="43"/>
-      <c r="U30" s="43"/>
-      <c r="V30" s="43"/>
-      <c r="W30" s="43"/>
-      <c r="X30" s="44"/>
-      <c r="Z30" s="42"/>
-      <c r="AA30" s="43"/>
-      <c r="AB30" s="43"/>
-      <c r="AC30" s="43"/>
-      <c r="AD30" s="43"/>
-      <c r="AE30" s="43"/>
-      <c r="AF30" s="43"/>
-      <c r="AG30" s="44"/>
-      <c r="AI30" s="42"/>
-      <c r="AJ30" s="43"/>
-      <c r="AK30" s="43"/>
-      <c r="AL30" s="43"/>
-      <c r="AM30" s="43"/>
-      <c r="AN30" s="43"/>
-      <c r="AO30" s="43"/>
-      <c r="AP30" s="44"/>
-      <c r="AR30" s="42"/>
-      <c r="AS30" s="43"/>
-      <c r="AT30" s="43"/>
-      <c r="AU30" s="43"/>
-      <c r="AV30" s="43"/>
-      <c r="AW30" s="43"/>
-      <c r="AX30" s="43"/>
-      <c r="AY30" s="44"/>
-      <c r="BA30" s="42"/>
-      <c r="BB30" s="43"/>
-      <c r="BC30" s="43"/>
-      <c r="BD30" s="43"/>
-      <c r="BE30" s="43"/>
-      <c r="BF30" s="43"/>
-      <c r="BG30" s="43"/>
-      <c r="BH30" s="44"/>
-      <c r="BJ30" s="48"/>
-      <c r="BK30" s="49"/>
-      <c r="BL30" s="49"/>
-      <c r="BM30" s="49"/>
-      <c r="BN30" s="49"/>
-      <c r="BO30" s="49"/>
-      <c r="BP30" s="49"/>
-      <c r="BQ30" s="50"/>
-      <c r="BS30" s="48"/>
-      <c r="BT30" s="49"/>
-      <c r="BU30" s="49"/>
-      <c r="BV30" s="49"/>
-      <c r="BW30" s="49"/>
-      <c r="BX30" s="49"/>
-      <c r="BY30" s="49"/>
-      <c r="BZ30" s="50"/>
+      <c r="C30" s="58"/>
+      <c r="D30" s="58"/>
+      <c r="E30" s="58"/>
+      <c r="F30" s="58"/>
+      <c r="H30" s="67"/>
+      <c r="I30" s="68"/>
+      <c r="J30" s="68"/>
+      <c r="K30" s="68"/>
+      <c r="L30" s="68"/>
+      <c r="M30" s="68"/>
+      <c r="N30" s="68"/>
+      <c r="O30" s="69"/>
+      <c r="Q30" s="67"/>
+      <c r="R30" s="68"/>
+      <c r="S30" s="68"/>
+      <c r="T30" s="68"/>
+      <c r="U30" s="68"/>
+      <c r="V30" s="68"/>
+      <c r="W30" s="68"/>
+      <c r="X30" s="69"/>
+      <c r="Z30" s="67"/>
+      <c r="AA30" s="68"/>
+      <c r="AB30" s="68"/>
+      <c r="AC30" s="68"/>
+      <c r="AD30" s="68"/>
+      <c r="AE30" s="68"/>
+      <c r="AF30" s="68"/>
+      <c r="AG30" s="69"/>
+      <c r="AI30" s="67"/>
+      <c r="AJ30" s="68"/>
+      <c r="AK30" s="68"/>
+      <c r="AL30" s="68"/>
+      <c r="AM30" s="68"/>
+      <c r="AN30" s="68"/>
+      <c r="AO30" s="68"/>
+      <c r="AP30" s="69"/>
+      <c r="AR30" s="67"/>
+      <c r="AS30" s="68"/>
+      <c r="AT30" s="68"/>
+      <c r="AU30" s="68"/>
+      <c r="AV30" s="68"/>
+      <c r="AW30" s="68"/>
+      <c r="AX30" s="68"/>
+      <c r="AY30" s="69"/>
+      <c r="BA30" s="67"/>
+      <c r="BB30" s="68"/>
+      <c r="BC30" s="68"/>
+      <c r="BD30" s="68"/>
+      <c r="BE30" s="68"/>
+      <c r="BF30" s="68"/>
+      <c r="BG30" s="68"/>
+      <c r="BH30" s="69"/>
+      <c r="BJ30" s="51"/>
+      <c r="BK30" s="52"/>
+      <c r="BL30" s="52"/>
+      <c r="BM30" s="52"/>
+      <c r="BN30" s="52"/>
+      <c r="BO30" s="52"/>
+      <c r="BP30" s="52"/>
+      <c r="BQ30" s="53"/>
+      <c r="BS30" s="51"/>
+      <c r="BT30" s="52"/>
+      <c r="BU30" s="52"/>
+      <c r="BV30" s="52"/>
+      <c r="BW30" s="52"/>
+      <c r="BX30" s="52"/>
+      <c r="BY30" s="52"/>
+      <c r="BZ30" s="53"/>
       <c r="CB30" s="16" t="s">
         <v>18</v>
       </c>
@@ -4228,17 +4228,17 @@
         <f>SUM(BT31+BV31+BX31)*16</f>
         <v>0</v>
       </c>
-      <c r="CB31" s="65" t="s">
+      <c r="CB31" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="CC31" s="51"/>
-      <c r="CD31" s="51"/>
-      <c r="CE31" s="51">
+      <c r="CC31" s="58"/>
+      <c r="CD31" s="58"/>
+      <c r="CE31" s="58">
         <f ca="1">CE32*3*16</f>
         <v>0</v>
       </c>
-      <c r="CF31" s="51"/>
-      <c r="CG31" s="68"/>
+      <c r="CF31" s="58"/>
+      <c r="CG31" s="59"/>
     </row>
     <row r="32" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="N32" s="28" t="s">
@@ -4297,168 +4297,168 @@
         <f>(BT31+BV31+BX31)/3</f>
         <v>0</v>
       </c>
-      <c r="CB32" s="66" t="s">
+      <c r="CB32" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="CC32" s="67"/>
-      <c r="CD32" s="67"/>
-      <c r="CE32" s="54">
+      <c r="CC32" s="55"/>
+      <c r="CD32" s="55"/>
+      <c r="CE32" s="56">
         <f ca="1">SUM(IF(MOD(COLUMN(O32:OFFSET(CE32,0,-1)) - COLUMN(O32), 9) = 0, O32:OFFSET(CE32,0,-1), 0))</f>
         <v>0</v>
       </c>
-      <c r="CF32" s="54"/>
-      <c r="CG32" s="55"/>
+      <c r="CF32" s="56"/>
+      <c r="CG32" s="57"/>
     </row>
     <row r="33" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="34" spans="3:85" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C34" s="51" t="s">
+      <c r="C34" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="D34" s="51"/>
-      <c r="E34" s="51"/>
-      <c r="F34" s="51"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="40"/>
-      <c r="J34" s="40"/>
-      <c r="K34" s="40"/>
-      <c r="L34" s="40"/>
-      <c r="M34" s="40"/>
-      <c r="N34" s="40"/>
-      <c r="O34" s="41"/>
-      <c r="Q34" s="39"/>
-      <c r="R34" s="40"/>
-      <c r="S34" s="40"/>
-      <c r="T34" s="40"/>
-      <c r="U34" s="40"/>
-      <c r="V34" s="40"/>
-      <c r="W34" s="40"/>
-      <c r="X34" s="41"/>
-      <c r="Z34" s="39"/>
-      <c r="AA34" s="40"/>
-      <c r="AB34" s="40"/>
-      <c r="AC34" s="40"/>
-      <c r="AD34" s="40"/>
-      <c r="AE34" s="40"/>
-      <c r="AF34" s="40"/>
-      <c r="AG34" s="41"/>
-      <c r="AI34" s="39"/>
-      <c r="AJ34" s="40"/>
-      <c r="AK34" s="40"/>
-      <c r="AL34" s="40"/>
-      <c r="AM34" s="40"/>
-      <c r="AN34" s="40"/>
-      <c r="AO34" s="40"/>
-      <c r="AP34" s="41"/>
-      <c r="AR34" s="39"/>
-      <c r="AS34" s="40"/>
-      <c r="AT34" s="40"/>
-      <c r="AU34" s="40"/>
-      <c r="AV34" s="40"/>
-      <c r="AW34" s="40"/>
-      <c r="AX34" s="40"/>
-      <c r="AY34" s="41"/>
-      <c r="BA34" s="39"/>
-      <c r="BB34" s="40"/>
-      <c r="BC34" s="40"/>
-      <c r="BD34" s="40"/>
-      <c r="BE34" s="40"/>
-      <c r="BF34" s="40"/>
-      <c r="BG34" s="40"/>
-      <c r="BH34" s="41"/>
-      <c r="BJ34" s="45"/>
-      <c r="BK34" s="46"/>
-      <c r="BL34" s="46"/>
-      <c r="BM34" s="46"/>
-      <c r="BN34" s="46"/>
-      <c r="BO34" s="46"/>
-      <c r="BP34" s="46"/>
-      <c r="BQ34" s="47"/>
-      <c r="BS34" s="45"/>
-      <c r="BT34" s="46"/>
-      <c r="BU34" s="46"/>
-      <c r="BV34" s="46"/>
-      <c r="BW34" s="46"/>
-      <c r="BX34" s="46"/>
-      <c r="BY34" s="46"/>
-      <c r="BZ34" s="47"/>
-      <c r="CB34" s="62" t="s">
+      <c r="D34" s="58"/>
+      <c r="E34" s="58"/>
+      <c r="F34" s="58"/>
+      <c r="H34" s="64"/>
+      <c r="I34" s="65"/>
+      <c r="J34" s="65"/>
+      <c r="K34" s="65"/>
+      <c r="L34" s="65"/>
+      <c r="M34" s="65"/>
+      <c r="N34" s="65"/>
+      <c r="O34" s="66"/>
+      <c r="Q34" s="64"/>
+      <c r="R34" s="65"/>
+      <c r="S34" s="65"/>
+      <c r="T34" s="65"/>
+      <c r="U34" s="65"/>
+      <c r="V34" s="65"/>
+      <c r="W34" s="65"/>
+      <c r="X34" s="66"/>
+      <c r="Z34" s="64"/>
+      <c r="AA34" s="65"/>
+      <c r="AB34" s="65"/>
+      <c r="AC34" s="65"/>
+      <c r="AD34" s="65"/>
+      <c r="AE34" s="65"/>
+      <c r="AF34" s="65"/>
+      <c r="AG34" s="66"/>
+      <c r="AI34" s="64"/>
+      <c r="AJ34" s="65"/>
+      <c r="AK34" s="65"/>
+      <c r="AL34" s="65"/>
+      <c r="AM34" s="65"/>
+      <c r="AN34" s="65"/>
+      <c r="AO34" s="65"/>
+      <c r="AP34" s="66"/>
+      <c r="AR34" s="64"/>
+      <c r="AS34" s="65"/>
+      <c r="AT34" s="65"/>
+      <c r="AU34" s="65"/>
+      <c r="AV34" s="65"/>
+      <c r="AW34" s="65"/>
+      <c r="AX34" s="65"/>
+      <c r="AY34" s="66"/>
+      <c r="BA34" s="64"/>
+      <c r="BB34" s="65"/>
+      <c r="BC34" s="65"/>
+      <c r="BD34" s="65"/>
+      <c r="BE34" s="65"/>
+      <c r="BF34" s="65"/>
+      <c r="BG34" s="65"/>
+      <c r="BH34" s="66"/>
+      <c r="BJ34" s="48"/>
+      <c r="BK34" s="49"/>
+      <c r="BL34" s="49"/>
+      <c r="BM34" s="49"/>
+      <c r="BN34" s="49"/>
+      <c r="BO34" s="49"/>
+      <c r="BP34" s="49"/>
+      <c r="BQ34" s="50"/>
+      <c r="BS34" s="48"/>
+      <c r="BT34" s="49"/>
+      <c r="BU34" s="49"/>
+      <c r="BV34" s="49"/>
+      <c r="BW34" s="49"/>
+      <c r="BX34" s="49"/>
+      <c r="BY34" s="49"/>
+      <c r="BZ34" s="50"/>
+      <c r="CB34" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="CC34" s="63"/>
-      <c r="CD34" s="63"/>
-      <c r="CE34" s="63"/>
-      <c r="CF34" s="63"/>
-      <c r="CG34" s="64"/>
+      <c r="CC34" s="62"/>
+      <c r="CD34" s="62"/>
+      <c r="CE34" s="62"/>
+      <c r="CF34" s="62"/>
+      <c r="CG34" s="63"/>
     </row>
     <row r="35" spans="3:85" x14ac:dyDescent="0.25">
-      <c r="C35" s="51"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="51"/>
-      <c r="F35" s="51"/>
-      <c r="H35" s="42"/>
-      <c r="I35" s="43"/>
-      <c r="J35" s="43"/>
-      <c r="K35" s="43"/>
-      <c r="L35" s="43"/>
-      <c r="M35" s="43"/>
-      <c r="N35" s="43"/>
-      <c r="O35" s="44"/>
-      <c r="Q35" s="42"/>
-      <c r="R35" s="43"/>
-      <c r="S35" s="43"/>
-      <c r="T35" s="43"/>
-      <c r="U35" s="43"/>
-      <c r="V35" s="43"/>
-      <c r="W35" s="43"/>
-      <c r="X35" s="44"/>
-      <c r="Z35" s="42"/>
-      <c r="AA35" s="43"/>
-      <c r="AB35" s="43"/>
-      <c r="AC35" s="43"/>
-      <c r="AD35" s="43"/>
-      <c r="AE35" s="43"/>
-      <c r="AF35" s="43"/>
-      <c r="AG35" s="44"/>
-      <c r="AI35" s="42"/>
-      <c r="AJ35" s="43"/>
-      <c r="AK35" s="43"/>
-      <c r="AL35" s="43"/>
-      <c r="AM35" s="43"/>
-      <c r="AN35" s="43"/>
-      <c r="AO35" s="43"/>
-      <c r="AP35" s="44"/>
-      <c r="AR35" s="42"/>
-      <c r="AS35" s="43"/>
-      <c r="AT35" s="43"/>
-      <c r="AU35" s="43"/>
-      <c r="AV35" s="43"/>
-      <c r="AW35" s="43"/>
-      <c r="AX35" s="43"/>
-      <c r="AY35" s="44"/>
-      <c r="BA35" s="42"/>
-      <c r="BB35" s="43"/>
-      <c r="BC35" s="43"/>
-      <c r="BD35" s="43"/>
-      <c r="BE35" s="43"/>
-      <c r="BF35" s="43"/>
-      <c r="BG35" s="43"/>
-      <c r="BH35" s="44"/>
-      <c r="BJ35" s="48"/>
-      <c r="BK35" s="49"/>
-      <c r="BL35" s="49"/>
-      <c r="BM35" s="49"/>
-      <c r="BN35" s="49"/>
-      <c r="BO35" s="49"/>
-      <c r="BP35" s="49"/>
-      <c r="BQ35" s="50"/>
-      <c r="BS35" s="48"/>
-      <c r="BT35" s="49"/>
-      <c r="BU35" s="49"/>
-      <c r="BV35" s="49"/>
-      <c r="BW35" s="49"/>
-      <c r="BX35" s="49"/>
-      <c r="BY35" s="49"/>
-      <c r="BZ35" s="50"/>
+      <c r="C35" s="58"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="58"/>
+      <c r="H35" s="67"/>
+      <c r="I35" s="68"/>
+      <c r="J35" s="68"/>
+      <c r="K35" s="68"/>
+      <c r="L35" s="68"/>
+      <c r="M35" s="68"/>
+      <c r="N35" s="68"/>
+      <c r="O35" s="69"/>
+      <c r="Q35" s="67"/>
+      <c r="R35" s="68"/>
+      <c r="S35" s="68"/>
+      <c r="T35" s="68"/>
+      <c r="U35" s="68"/>
+      <c r="V35" s="68"/>
+      <c r="W35" s="68"/>
+      <c r="X35" s="69"/>
+      <c r="Z35" s="67"/>
+      <c r="AA35" s="68"/>
+      <c r="AB35" s="68"/>
+      <c r="AC35" s="68"/>
+      <c r="AD35" s="68"/>
+      <c r="AE35" s="68"/>
+      <c r="AF35" s="68"/>
+      <c r="AG35" s="69"/>
+      <c r="AI35" s="67"/>
+      <c r="AJ35" s="68"/>
+      <c r="AK35" s="68"/>
+      <c r="AL35" s="68"/>
+      <c r="AM35" s="68"/>
+      <c r="AN35" s="68"/>
+      <c r="AO35" s="68"/>
+      <c r="AP35" s="69"/>
+      <c r="AR35" s="67"/>
+      <c r="AS35" s="68"/>
+      <c r="AT35" s="68"/>
+      <c r="AU35" s="68"/>
+      <c r="AV35" s="68"/>
+      <c r="AW35" s="68"/>
+      <c r="AX35" s="68"/>
+      <c r="AY35" s="69"/>
+      <c r="BA35" s="67"/>
+      <c r="BB35" s="68"/>
+      <c r="BC35" s="68"/>
+      <c r="BD35" s="68"/>
+      <c r="BE35" s="68"/>
+      <c r="BF35" s="68"/>
+      <c r="BG35" s="68"/>
+      <c r="BH35" s="69"/>
+      <c r="BJ35" s="51"/>
+      <c r="BK35" s="52"/>
+      <c r="BL35" s="52"/>
+      <c r="BM35" s="52"/>
+      <c r="BN35" s="52"/>
+      <c r="BO35" s="52"/>
+      <c r="BP35" s="52"/>
+      <c r="BQ35" s="53"/>
+      <c r="BS35" s="51"/>
+      <c r="BT35" s="52"/>
+      <c r="BU35" s="52"/>
+      <c r="BV35" s="52"/>
+      <c r="BW35" s="52"/>
+      <c r="BX35" s="52"/>
+      <c r="BY35" s="52"/>
+      <c r="BZ35" s="53"/>
       <c r="CB35" s="16" t="s">
         <v>18</v>
       </c>
@@ -4634,17 +4634,17 @@
         <f>SUM(BT36+BV36+BX36)*16</f>
         <v>0</v>
       </c>
-      <c r="CB36" s="65" t="s">
+      <c r="CB36" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="CC36" s="51"/>
-      <c r="CD36" s="51"/>
-      <c r="CE36" s="51">
+      <c r="CC36" s="58"/>
+      <c r="CD36" s="58"/>
+      <c r="CE36" s="58">
         <f ca="1">CE37*3*16</f>
         <v>0</v>
       </c>
-      <c r="CF36" s="51"/>
-      <c r="CG36" s="68"/>
+      <c r="CF36" s="58"/>
+      <c r="CG36" s="59"/>
     </row>
     <row r="37" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="N37" s="28" t="s">
@@ -4703,168 +4703,168 @@
         <f>(BT36+BV36+BX36)/3</f>
         <v>0</v>
       </c>
-      <c r="CB37" s="66" t="s">
+      <c r="CB37" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="CC37" s="67"/>
-      <c r="CD37" s="67"/>
-      <c r="CE37" s="54">
+      <c r="CC37" s="55"/>
+      <c r="CD37" s="55"/>
+      <c r="CE37" s="56">
         <f ca="1">SUM(IF(MOD(COLUMN(O37:OFFSET(CE37,0,-1)) - COLUMN(O37), 9) = 0, O37:OFFSET(CE37,0,-1), 0))</f>
         <v>0</v>
       </c>
-      <c r="CF37" s="54"/>
-      <c r="CG37" s="55"/>
+      <c r="CF37" s="56"/>
+      <c r="CG37" s="57"/>
     </row>
     <row r="38" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="39" spans="3:85" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="51" t="s">
+      <c r="C39" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="D39" s="51"/>
-      <c r="E39" s="51"/>
-      <c r="F39" s="51"/>
-      <c r="H39" s="39"/>
-      <c r="I39" s="40"/>
-      <c r="J39" s="40"/>
-      <c r="K39" s="40"/>
-      <c r="L39" s="40"/>
-      <c r="M39" s="40"/>
-      <c r="N39" s="40"/>
-      <c r="O39" s="41"/>
-      <c r="Q39" s="39"/>
-      <c r="R39" s="40"/>
-      <c r="S39" s="40"/>
-      <c r="T39" s="40"/>
-      <c r="U39" s="40"/>
-      <c r="V39" s="40"/>
-      <c r="W39" s="40"/>
-      <c r="X39" s="41"/>
-      <c r="Z39" s="39"/>
-      <c r="AA39" s="40"/>
-      <c r="AB39" s="40"/>
-      <c r="AC39" s="40"/>
-      <c r="AD39" s="40"/>
-      <c r="AE39" s="40"/>
-      <c r="AF39" s="40"/>
-      <c r="AG39" s="41"/>
-      <c r="AI39" s="39"/>
-      <c r="AJ39" s="40"/>
-      <c r="AK39" s="40"/>
-      <c r="AL39" s="40"/>
-      <c r="AM39" s="40"/>
-      <c r="AN39" s="40"/>
-      <c r="AO39" s="40"/>
-      <c r="AP39" s="41"/>
-      <c r="AR39" s="39"/>
-      <c r="AS39" s="40"/>
-      <c r="AT39" s="40"/>
-      <c r="AU39" s="40"/>
-      <c r="AV39" s="40"/>
-      <c r="AW39" s="40"/>
-      <c r="AX39" s="40"/>
-      <c r="AY39" s="41"/>
-      <c r="BA39" s="39"/>
-      <c r="BB39" s="40"/>
-      <c r="BC39" s="40"/>
-      <c r="BD39" s="40"/>
-      <c r="BE39" s="40"/>
-      <c r="BF39" s="40"/>
-      <c r="BG39" s="40"/>
-      <c r="BH39" s="41"/>
-      <c r="BJ39" s="45"/>
-      <c r="BK39" s="46"/>
-      <c r="BL39" s="46"/>
-      <c r="BM39" s="46"/>
-      <c r="BN39" s="46"/>
-      <c r="BO39" s="46"/>
-      <c r="BP39" s="46"/>
-      <c r="BQ39" s="47"/>
-      <c r="BS39" s="45"/>
-      <c r="BT39" s="46"/>
-      <c r="BU39" s="46"/>
-      <c r="BV39" s="46"/>
-      <c r="BW39" s="46"/>
-      <c r="BX39" s="46"/>
-      <c r="BY39" s="46"/>
-      <c r="BZ39" s="47"/>
-      <c r="CB39" s="62" t="s">
+      <c r="D39" s="58"/>
+      <c r="E39" s="58"/>
+      <c r="F39" s="58"/>
+      <c r="H39" s="64"/>
+      <c r="I39" s="65"/>
+      <c r="J39" s="65"/>
+      <c r="K39" s="65"/>
+      <c r="L39" s="65"/>
+      <c r="M39" s="65"/>
+      <c r="N39" s="65"/>
+      <c r="O39" s="66"/>
+      <c r="Q39" s="64"/>
+      <c r="R39" s="65"/>
+      <c r="S39" s="65"/>
+      <c r="T39" s="65"/>
+      <c r="U39" s="65"/>
+      <c r="V39" s="65"/>
+      <c r="W39" s="65"/>
+      <c r="X39" s="66"/>
+      <c r="Z39" s="64"/>
+      <c r="AA39" s="65"/>
+      <c r="AB39" s="65"/>
+      <c r="AC39" s="65"/>
+      <c r="AD39" s="65"/>
+      <c r="AE39" s="65"/>
+      <c r="AF39" s="65"/>
+      <c r="AG39" s="66"/>
+      <c r="AI39" s="64"/>
+      <c r="AJ39" s="65"/>
+      <c r="AK39" s="65"/>
+      <c r="AL39" s="65"/>
+      <c r="AM39" s="65"/>
+      <c r="AN39" s="65"/>
+      <c r="AO39" s="65"/>
+      <c r="AP39" s="66"/>
+      <c r="AR39" s="64"/>
+      <c r="AS39" s="65"/>
+      <c r="AT39" s="65"/>
+      <c r="AU39" s="65"/>
+      <c r="AV39" s="65"/>
+      <c r="AW39" s="65"/>
+      <c r="AX39" s="65"/>
+      <c r="AY39" s="66"/>
+      <c r="BA39" s="64"/>
+      <c r="BB39" s="65"/>
+      <c r="BC39" s="65"/>
+      <c r="BD39" s="65"/>
+      <c r="BE39" s="65"/>
+      <c r="BF39" s="65"/>
+      <c r="BG39" s="65"/>
+      <c r="BH39" s="66"/>
+      <c r="BJ39" s="48"/>
+      <c r="BK39" s="49"/>
+      <c r="BL39" s="49"/>
+      <c r="BM39" s="49"/>
+      <c r="BN39" s="49"/>
+      <c r="BO39" s="49"/>
+      <c r="BP39" s="49"/>
+      <c r="BQ39" s="50"/>
+      <c r="BS39" s="48"/>
+      <c r="BT39" s="49"/>
+      <c r="BU39" s="49"/>
+      <c r="BV39" s="49"/>
+      <c r="BW39" s="49"/>
+      <c r="BX39" s="49"/>
+      <c r="BY39" s="49"/>
+      <c r="BZ39" s="50"/>
+      <c r="CB39" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="CC39" s="63"/>
-      <c r="CD39" s="63"/>
-      <c r="CE39" s="63"/>
-      <c r="CF39" s="63"/>
-      <c r="CG39" s="64"/>
+      <c r="CC39" s="62"/>
+      <c r="CD39" s="62"/>
+      <c r="CE39" s="62"/>
+      <c r="CF39" s="62"/>
+      <c r="CG39" s="63"/>
     </row>
     <row r="40" spans="3:85" x14ac:dyDescent="0.25">
-      <c r="C40" s="51"/>
-      <c r="D40" s="51"/>
-      <c r="E40" s="51"/>
-      <c r="F40" s="51"/>
-      <c r="H40" s="42"/>
-      <c r="I40" s="43"/>
-      <c r="J40" s="43"/>
-      <c r="K40" s="43"/>
-      <c r="L40" s="43"/>
-      <c r="M40" s="43"/>
-      <c r="N40" s="43"/>
-      <c r="O40" s="44"/>
-      <c r="Q40" s="42"/>
-      <c r="R40" s="43"/>
-      <c r="S40" s="43"/>
-      <c r="T40" s="43"/>
-      <c r="U40" s="43"/>
-      <c r="V40" s="43"/>
-      <c r="W40" s="43"/>
-      <c r="X40" s="44"/>
-      <c r="Z40" s="42"/>
-      <c r="AA40" s="43"/>
-      <c r="AB40" s="43"/>
-      <c r="AC40" s="43"/>
-      <c r="AD40" s="43"/>
-      <c r="AE40" s="43"/>
-      <c r="AF40" s="43"/>
-      <c r="AG40" s="44"/>
-      <c r="AI40" s="42"/>
-      <c r="AJ40" s="43"/>
-      <c r="AK40" s="43"/>
-      <c r="AL40" s="43"/>
-      <c r="AM40" s="43"/>
-      <c r="AN40" s="43"/>
-      <c r="AO40" s="43"/>
-      <c r="AP40" s="44"/>
-      <c r="AR40" s="42"/>
-      <c r="AS40" s="43"/>
-      <c r="AT40" s="43"/>
-      <c r="AU40" s="43"/>
-      <c r="AV40" s="43"/>
-      <c r="AW40" s="43"/>
-      <c r="AX40" s="43"/>
-      <c r="AY40" s="44"/>
-      <c r="BA40" s="42"/>
-      <c r="BB40" s="43"/>
-      <c r="BC40" s="43"/>
-      <c r="BD40" s="43"/>
-      <c r="BE40" s="43"/>
-      <c r="BF40" s="43"/>
-      <c r="BG40" s="43"/>
-      <c r="BH40" s="44"/>
-      <c r="BJ40" s="48"/>
-      <c r="BK40" s="49"/>
-      <c r="BL40" s="49"/>
-      <c r="BM40" s="49"/>
-      <c r="BN40" s="49"/>
-      <c r="BO40" s="49"/>
-      <c r="BP40" s="49"/>
-      <c r="BQ40" s="50"/>
-      <c r="BS40" s="48"/>
-      <c r="BT40" s="49"/>
-      <c r="BU40" s="49"/>
-      <c r="BV40" s="49"/>
-      <c r="BW40" s="49"/>
-      <c r="BX40" s="49"/>
-      <c r="BY40" s="49"/>
-      <c r="BZ40" s="50"/>
+      <c r="C40" s="58"/>
+      <c r="D40" s="58"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="58"/>
+      <c r="H40" s="67"/>
+      <c r="I40" s="68"/>
+      <c r="J40" s="68"/>
+      <c r="K40" s="68"/>
+      <c r="L40" s="68"/>
+      <c r="M40" s="68"/>
+      <c r="N40" s="68"/>
+      <c r="O40" s="69"/>
+      <c r="Q40" s="67"/>
+      <c r="R40" s="68"/>
+      <c r="S40" s="68"/>
+      <c r="T40" s="68"/>
+      <c r="U40" s="68"/>
+      <c r="V40" s="68"/>
+      <c r="W40" s="68"/>
+      <c r="X40" s="69"/>
+      <c r="Z40" s="67"/>
+      <c r="AA40" s="68"/>
+      <c r="AB40" s="68"/>
+      <c r="AC40" s="68"/>
+      <c r="AD40" s="68"/>
+      <c r="AE40" s="68"/>
+      <c r="AF40" s="68"/>
+      <c r="AG40" s="69"/>
+      <c r="AI40" s="67"/>
+      <c r="AJ40" s="68"/>
+      <c r="AK40" s="68"/>
+      <c r="AL40" s="68"/>
+      <c r="AM40" s="68"/>
+      <c r="AN40" s="68"/>
+      <c r="AO40" s="68"/>
+      <c r="AP40" s="69"/>
+      <c r="AR40" s="67"/>
+      <c r="AS40" s="68"/>
+      <c r="AT40" s="68"/>
+      <c r="AU40" s="68"/>
+      <c r="AV40" s="68"/>
+      <c r="AW40" s="68"/>
+      <c r="AX40" s="68"/>
+      <c r="AY40" s="69"/>
+      <c r="BA40" s="67"/>
+      <c r="BB40" s="68"/>
+      <c r="BC40" s="68"/>
+      <c r="BD40" s="68"/>
+      <c r="BE40" s="68"/>
+      <c r="BF40" s="68"/>
+      <c r="BG40" s="68"/>
+      <c r="BH40" s="69"/>
+      <c r="BJ40" s="51"/>
+      <c r="BK40" s="52"/>
+      <c r="BL40" s="52"/>
+      <c r="BM40" s="52"/>
+      <c r="BN40" s="52"/>
+      <c r="BO40" s="52"/>
+      <c r="BP40" s="52"/>
+      <c r="BQ40" s="53"/>
+      <c r="BS40" s="51"/>
+      <c r="BT40" s="52"/>
+      <c r="BU40" s="52"/>
+      <c r="BV40" s="52"/>
+      <c r="BW40" s="52"/>
+      <c r="BX40" s="52"/>
+      <c r="BY40" s="52"/>
+      <c r="BZ40" s="53"/>
       <c r="CB40" s="16" t="s">
         <v>18</v>
       </c>
@@ -5040,17 +5040,17 @@
         <f>SUM(BT41+BV41+BX41)*16</f>
         <v>0</v>
       </c>
-      <c r="CB41" s="65" t="s">
+      <c r="CB41" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="CC41" s="51"/>
-      <c r="CD41" s="51"/>
-      <c r="CE41" s="51">
+      <c r="CC41" s="58"/>
+      <c r="CD41" s="58"/>
+      <c r="CE41" s="58">
         <f ca="1">CE42*3*16</f>
         <v>0</v>
       </c>
-      <c r="CF41" s="51"/>
-      <c r="CG41" s="68"/>
+      <c r="CF41" s="58"/>
+      <c r="CG41" s="59"/>
     </row>
     <row r="42" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="N42" s="28" t="s">
@@ -5109,168 +5109,168 @@
         <f>(BT41+BV41+BX41)/3</f>
         <v>0</v>
       </c>
-      <c r="CB42" s="66" t="s">
+      <c r="CB42" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="CC42" s="67"/>
-      <c r="CD42" s="67"/>
-      <c r="CE42" s="54">
+      <c r="CC42" s="55"/>
+      <c r="CD42" s="55"/>
+      <c r="CE42" s="56">
         <f ca="1">SUM(IF(MOD(COLUMN(O42:OFFSET(CE42,0,-1)) - COLUMN(O42), 9) = 0, O42:OFFSET(CE42,0,-1), 0))</f>
         <v>0</v>
       </c>
-      <c r="CF42" s="54"/>
-      <c r="CG42" s="55"/>
+      <c r="CF42" s="56"/>
+      <c r="CG42" s="57"/>
     </row>
     <row r="43" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="44" spans="3:85" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="51" t="s">
+      <c r="C44" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="D44" s="51"/>
-      <c r="E44" s="51"/>
-      <c r="F44" s="51"/>
-      <c r="H44" s="39"/>
-      <c r="I44" s="40"/>
-      <c r="J44" s="40"/>
-      <c r="K44" s="40"/>
-      <c r="L44" s="40"/>
-      <c r="M44" s="40"/>
-      <c r="N44" s="40"/>
-      <c r="O44" s="41"/>
-      <c r="Q44" s="39"/>
-      <c r="R44" s="40"/>
-      <c r="S44" s="40"/>
-      <c r="T44" s="40"/>
-      <c r="U44" s="40"/>
-      <c r="V44" s="40"/>
-      <c r="W44" s="40"/>
-      <c r="X44" s="41"/>
-      <c r="Z44" s="39"/>
-      <c r="AA44" s="40"/>
-      <c r="AB44" s="40"/>
-      <c r="AC44" s="40"/>
-      <c r="AD44" s="40"/>
-      <c r="AE44" s="40"/>
-      <c r="AF44" s="40"/>
-      <c r="AG44" s="41"/>
-      <c r="AI44" s="39"/>
-      <c r="AJ44" s="40"/>
-      <c r="AK44" s="40"/>
-      <c r="AL44" s="40"/>
-      <c r="AM44" s="40"/>
-      <c r="AN44" s="40"/>
-      <c r="AO44" s="40"/>
-      <c r="AP44" s="41"/>
-      <c r="AR44" s="39"/>
-      <c r="AS44" s="40"/>
-      <c r="AT44" s="40"/>
-      <c r="AU44" s="40"/>
-      <c r="AV44" s="40"/>
-      <c r="AW44" s="40"/>
-      <c r="AX44" s="40"/>
-      <c r="AY44" s="41"/>
-      <c r="BA44" s="39"/>
-      <c r="BB44" s="40"/>
-      <c r="BC44" s="40"/>
-      <c r="BD44" s="40"/>
-      <c r="BE44" s="40"/>
-      <c r="BF44" s="40"/>
-      <c r="BG44" s="40"/>
-      <c r="BH44" s="41"/>
-      <c r="BJ44" s="45"/>
-      <c r="BK44" s="46"/>
-      <c r="BL44" s="46"/>
-      <c r="BM44" s="46"/>
-      <c r="BN44" s="46"/>
-      <c r="BO44" s="46"/>
-      <c r="BP44" s="46"/>
-      <c r="BQ44" s="47"/>
-      <c r="BS44" s="45"/>
-      <c r="BT44" s="46"/>
-      <c r="BU44" s="46"/>
-      <c r="BV44" s="46"/>
-      <c r="BW44" s="46"/>
-      <c r="BX44" s="46"/>
-      <c r="BY44" s="46"/>
-      <c r="BZ44" s="47"/>
-      <c r="CB44" s="62" t="s">
+      <c r="D44" s="58"/>
+      <c r="E44" s="58"/>
+      <c r="F44" s="58"/>
+      <c r="H44" s="64"/>
+      <c r="I44" s="65"/>
+      <c r="J44" s="65"/>
+      <c r="K44" s="65"/>
+      <c r="L44" s="65"/>
+      <c r="M44" s="65"/>
+      <c r="N44" s="65"/>
+      <c r="O44" s="66"/>
+      <c r="Q44" s="64"/>
+      <c r="R44" s="65"/>
+      <c r="S44" s="65"/>
+      <c r="T44" s="65"/>
+      <c r="U44" s="65"/>
+      <c r="V44" s="65"/>
+      <c r="W44" s="65"/>
+      <c r="X44" s="66"/>
+      <c r="Z44" s="64"/>
+      <c r="AA44" s="65"/>
+      <c r="AB44" s="65"/>
+      <c r="AC44" s="65"/>
+      <c r="AD44" s="65"/>
+      <c r="AE44" s="65"/>
+      <c r="AF44" s="65"/>
+      <c r="AG44" s="66"/>
+      <c r="AI44" s="64"/>
+      <c r="AJ44" s="65"/>
+      <c r="AK44" s="65"/>
+      <c r="AL44" s="65"/>
+      <c r="AM44" s="65"/>
+      <c r="AN44" s="65"/>
+      <c r="AO44" s="65"/>
+      <c r="AP44" s="66"/>
+      <c r="AR44" s="64"/>
+      <c r="AS44" s="65"/>
+      <c r="AT44" s="65"/>
+      <c r="AU44" s="65"/>
+      <c r="AV44" s="65"/>
+      <c r="AW44" s="65"/>
+      <c r="AX44" s="65"/>
+      <c r="AY44" s="66"/>
+      <c r="BA44" s="64"/>
+      <c r="BB44" s="65"/>
+      <c r="BC44" s="65"/>
+      <c r="BD44" s="65"/>
+      <c r="BE44" s="65"/>
+      <c r="BF44" s="65"/>
+      <c r="BG44" s="65"/>
+      <c r="BH44" s="66"/>
+      <c r="BJ44" s="48"/>
+      <c r="BK44" s="49"/>
+      <c r="BL44" s="49"/>
+      <c r="BM44" s="49"/>
+      <c r="BN44" s="49"/>
+      <c r="BO44" s="49"/>
+      <c r="BP44" s="49"/>
+      <c r="BQ44" s="50"/>
+      <c r="BS44" s="48"/>
+      <c r="BT44" s="49"/>
+      <c r="BU44" s="49"/>
+      <c r="BV44" s="49"/>
+      <c r="BW44" s="49"/>
+      <c r="BX44" s="49"/>
+      <c r="BY44" s="49"/>
+      <c r="BZ44" s="50"/>
+      <c r="CB44" s="61" t="s">
         <v>58</v>
       </c>
-      <c r="CC44" s="63"/>
-      <c r="CD44" s="63"/>
-      <c r="CE44" s="63"/>
-      <c r="CF44" s="63"/>
-      <c r="CG44" s="64"/>
+      <c r="CC44" s="62"/>
+      <c r="CD44" s="62"/>
+      <c r="CE44" s="62"/>
+      <c r="CF44" s="62"/>
+      <c r="CG44" s="63"/>
     </row>
     <row r="45" spans="3:85" x14ac:dyDescent="0.25">
-      <c r="C45" s="51"/>
-      <c r="D45" s="51"/>
-      <c r="E45" s="51"/>
-      <c r="F45" s="51"/>
-      <c r="H45" s="42"/>
-      <c r="I45" s="43"/>
-      <c r="J45" s="43"/>
-      <c r="K45" s="43"/>
-      <c r="L45" s="43"/>
-      <c r="M45" s="43"/>
-      <c r="N45" s="43"/>
-      <c r="O45" s="44"/>
-      <c r="Q45" s="42"/>
-      <c r="R45" s="43"/>
-      <c r="S45" s="43"/>
-      <c r="T45" s="43"/>
-      <c r="U45" s="43"/>
-      <c r="V45" s="43"/>
-      <c r="W45" s="43"/>
-      <c r="X45" s="44"/>
-      <c r="Z45" s="42"/>
-      <c r="AA45" s="43"/>
-      <c r="AB45" s="43"/>
-      <c r="AC45" s="43"/>
-      <c r="AD45" s="43"/>
-      <c r="AE45" s="43"/>
-      <c r="AF45" s="43"/>
-      <c r="AG45" s="44"/>
-      <c r="AI45" s="42"/>
-      <c r="AJ45" s="43"/>
-      <c r="AK45" s="43"/>
-      <c r="AL45" s="43"/>
-      <c r="AM45" s="43"/>
-      <c r="AN45" s="43"/>
-      <c r="AO45" s="43"/>
-      <c r="AP45" s="44"/>
-      <c r="AR45" s="42"/>
-      <c r="AS45" s="43"/>
-      <c r="AT45" s="43"/>
-      <c r="AU45" s="43"/>
-      <c r="AV45" s="43"/>
-      <c r="AW45" s="43"/>
-      <c r="AX45" s="43"/>
-      <c r="AY45" s="44"/>
-      <c r="BA45" s="42"/>
-      <c r="BB45" s="43"/>
-      <c r="BC45" s="43"/>
-      <c r="BD45" s="43"/>
-      <c r="BE45" s="43"/>
-      <c r="BF45" s="43"/>
-      <c r="BG45" s="43"/>
-      <c r="BH45" s="44"/>
-      <c r="BJ45" s="48"/>
-      <c r="BK45" s="49"/>
-      <c r="BL45" s="49"/>
-      <c r="BM45" s="49"/>
-      <c r="BN45" s="49"/>
-      <c r="BO45" s="49"/>
-      <c r="BP45" s="49"/>
-      <c r="BQ45" s="50"/>
-      <c r="BS45" s="48"/>
-      <c r="BT45" s="49"/>
-      <c r="BU45" s="49"/>
-      <c r="BV45" s="49"/>
-      <c r="BW45" s="49"/>
-      <c r="BX45" s="49"/>
-      <c r="BY45" s="49"/>
-      <c r="BZ45" s="50"/>
+      <c r="C45" s="58"/>
+      <c r="D45" s="58"/>
+      <c r="E45" s="58"/>
+      <c r="F45" s="58"/>
+      <c r="H45" s="67"/>
+      <c r="I45" s="68"/>
+      <c r="J45" s="68"/>
+      <c r="K45" s="68"/>
+      <c r="L45" s="68"/>
+      <c r="M45" s="68"/>
+      <c r="N45" s="68"/>
+      <c r="O45" s="69"/>
+      <c r="Q45" s="67"/>
+      <c r="R45" s="68"/>
+      <c r="S45" s="68"/>
+      <c r="T45" s="68"/>
+      <c r="U45" s="68"/>
+      <c r="V45" s="68"/>
+      <c r="W45" s="68"/>
+      <c r="X45" s="69"/>
+      <c r="Z45" s="67"/>
+      <c r="AA45" s="68"/>
+      <c r="AB45" s="68"/>
+      <c r="AC45" s="68"/>
+      <c r="AD45" s="68"/>
+      <c r="AE45" s="68"/>
+      <c r="AF45" s="68"/>
+      <c r="AG45" s="69"/>
+      <c r="AI45" s="67"/>
+      <c r="AJ45" s="68"/>
+      <c r="AK45" s="68"/>
+      <c r="AL45" s="68"/>
+      <c r="AM45" s="68"/>
+      <c r="AN45" s="68"/>
+      <c r="AO45" s="68"/>
+      <c r="AP45" s="69"/>
+      <c r="AR45" s="67"/>
+      <c r="AS45" s="68"/>
+      <c r="AT45" s="68"/>
+      <c r="AU45" s="68"/>
+      <c r="AV45" s="68"/>
+      <c r="AW45" s="68"/>
+      <c r="AX45" s="68"/>
+      <c r="AY45" s="69"/>
+      <c r="BA45" s="67"/>
+      <c r="BB45" s="68"/>
+      <c r="BC45" s="68"/>
+      <c r="BD45" s="68"/>
+      <c r="BE45" s="68"/>
+      <c r="BF45" s="68"/>
+      <c r="BG45" s="68"/>
+      <c r="BH45" s="69"/>
+      <c r="BJ45" s="51"/>
+      <c r="BK45" s="52"/>
+      <c r="BL45" s="52"/>
+      <c r="BM45" s="52"/>
+      <c r="BN45" s="52"/>
+      <c r="BO45" s="52"/>
+      <c r="BP45" s="52"/>
+      <c r="BQ45" s="53"/>
+      <c r="BS45" s="51"/>
+      <c r="BT45" s="52"/>
+      <c r="BU45" s="52"/>
+      <c r="BV45" s="52"/>
+      <c r="BW45" s="52"/>
+      <c r="BX45" s="52"/>
+      <c r="BY45" s="52"/>
+      <c r="BZ45" s="53"/>
       <c r="CB45" s="16" t="s">
         <v>18</v>
       </c>
@@ -5446,17 +5446,17 @@
         <f>SUM(BT46+BV46+BX46)*16</f>
         <v>0</v>
       </c>
-      <c r="CB46" s="65" t="s">
+      <c r="CB46" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="CC46" s="51"/>
-      <c r="CD46" s="51"/>
-      <c r="CE46" s="51">
+      <c r="CC46" s="58"/>
+      <c r="CD46" s="58"/>
+      <c r="CE46" s="58">
         <f ca="1">CE47*3*16</f>
         <v>0</v>
       </c>
-      <c r="CF46" s="51"/>
-      <c r="CG46" s="68"/>
+      <c r="CF46" s="58"/>
+      <c r="CG46" s="59"/>
     </row>
     <row r="47" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="N47" s="28" t="s">
@@ -5515,17 +5515,17 @@
         <f>(BT46+BV46+BX46)/3</f>
         <v>0</v>
       </c>
-      <c r="CB47" s="66" t="s">
+      <c r="CB47" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="CC47" s="67"/>
-      <c r="CD47" s="67"/>
-      <c r="CE47" s="54">
+      <c r="CC47" s="55"/>
+      <c r="CD47" s="55"/>
+      <c r="CE47" s="56">
         <f ca="1">SUM(IF(MOD(COLUMN(O47:OFFSET(CE47,0,-1)) - COLUMN(O47), 9) = 0, O47:OFFSET(CE47,0,-1), 0))</f>
         <v>0</v>
       </c>
-      <c r="CF47" s="54"/>
-      <c r="CG47" s="55"/>
+      <c r="CF47" s="56"/>
+      <c r="CG47" s="57"/>
     </row>
     <row r="48" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="CB48" s="18"/>
@@ -5536,154 +5536,154 @@
       <c r="CG48" s="18"/>
     </row>
     <row r="49" spans="3:119" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C49" s="51" t="s">
+      <c r="C49" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="D49" s="51"/>
-      <c r="E49" s="51"/>
-      <c r="F49" s="51"/>
-      <c r="H49" s="39"/>
-      <c r="I49" s="40"/>
-      <c r="J49" s="40"/>
-      <c r="K49" s="40"/>
-      <c r="L49" s="40"/>
-      <c r="M49" s="40"/>
-      <c r="N49" s="40"/>
-      <c r="O49" s="41"/>
-      <c r="Q49" s="39"/>
-      <c r="R49" s="40"/>
-      <c r="S49" s="40"/>
-      <c r="T49" s="40"/>
-      <c r="U49" s="40"/>
-      <c r="V49" s="40"/>
-      <c r="W49" s="40"/>
-      <c r="X49" s="41"/>
-      <c r="Z49" s="39"/>
-      <c r="AA49" s="40"/>
-      <c r="AB49" s="40"/>
-      <c r="AC49" s="40"/>
-      <c r="AD49" s="40"/>
-      <c r="AE49" s="40"/>
-      <c r="AF49" s="40"/>
-      <c r="AG49" s="41"/>
-      <c r="AI49" s="39"/>
-      <c r="AJ49" s="40"/>
-      <c r="AK49" s="40"/>
-      <c r="AL49" s="40"/>
-      <c r="AM49" s="40"/>
-      <c r="AN49" s="40"/>
-      <c r="AO49" s="40"/>
-      <c r="AP49" s="41"/>
-      <c r="AR49" s="39"/>
-      <c r="AS49" s="40"/>
-      <c r="AT49" s="40"/>
-      <c r="AU49" s="40"/>
-      <c r="AV49" s="40"/>
-      <c r="AW49" s="40"/>
-      <c r="AX49" s="40"/>
-      <c r="AY49" s="41"/>
-      <c r="BA49" s="39"/>
-      <c r="BB49" s="40"/>
-      <c r="BC49" s="40"/>
-      <c r="BD49" s="40"/>
-      <c r="BE49" s="40"/>
-      <c r="BF49" s="40"/>
-      <c r="BG49" s="40"/>
-      <c r="BH49" s="41"/>
-      <c r="BJ49" s="45"/>
-      <c r="BK49" s="46"/>
-      <c r="BL49" s="46"/>
-      <c r="BM49" s="46"/>
-      <c r="BN49" s="46"/>
-      <c r="BO49" s="46"/>
-      <c r="BP49" s="46"/>
-      <c r="BQ49" s="47"/>
-      <c r="BS49" s="45"/>
-      <c r="BT49" s="46"/>
-      <c r="BU49" s="46"/>
-      <c r="BV49" s="46"/>
-      <c r="BW49" s="46"/>
-      <c r="BX49" s="46"/>
-      <c r="BY49" s="46"/>
-      <c r="BZ49" s="47"/>
-      <c r="CB49" s="62" t="s">
+      <c r="D49" s="58"/>
+      <c r="E49" s="58"/>
+      <c r="F49" s="58"/>
+      <c r="H49" s="64"/>
+      <c r="I49" s="65"/>
+      <c r="J49" s="65"/>
+      <c r="K49" s="65"/>
+      <c r="L49" s="65"/>
+      <c r="M49" s="65"/>
+      <c r="N49" s="65"/>
+      <c r="O49" s="66"/>
+      <c r="Q49" s="64"/>
+      <c r="R49" s="65"/>
+      <c r="S49" s="65"/>
+      <c r="T49" s="65"/>
+      <c r="U49" s="65"/>
+      <c r="V49" s="65"/>
+      <c r="W49" s="65"/>
+      <c r="X49" s="66"/>
+      <c r="Z49" s="64"/>
+      <c r="AA49" s="65"/>
+      <c r="AB49" s="65"/>
+      <c r="AC49" s="65"/>
+      <c r="AD49" s="65"/>
+      <c r="AE49" s="65"/>
+      <c r="AF49" s="65"/>
+      <c r="AG49" s="66"/>
+      <c r="AI49" s="64"/>
+      <c r="AJ49" s="65"/>
+      <c r="AK49" s="65"/>
+      <c r="AL49" s="65"/>
+      <c r="AM49" s="65"/>
+      <c r="AN49" s="65"/>
+      <c r="AO49" s="65"/>
+      <c r="AP49" s="66"/>
+      <c r="AR49" s="64"/>
+      <c r="AS49" s="65"/>
+      <c r="AT49" s="65"/>
+      <c r="AU49" s="65"/>
+      <c r="AV49" s="65"/>
+      <c r="AW49" s="65"/>
+      <c r="AX49" s="65"/>
+      <c r="AY49" s="66"/>
+      <c r="BA49" s="64"/>
+      <c r="BB49" s="65"/>
+      <c r="BC49" s="65"/>
+      <c r="BD49" s="65"/>
+      <c r="BE49" s="65"/>
+      <c r="BF49" s="65"/>
+      <c r="BG49" s="65"/>
+      <c r="BH49" s="66"/>
+      <c r="BJ49" s="48"/>
+      <c r="BK49" s="49"/>
+      <c r="BL49" s="49"/>
+      <c r="BM49" s="49"/>
+      <c r="BN49" s="49"/>
+      <c r="BO49" s="49"/>
+      <c r="BP49" s="49"/>
+      <c r="BQ49" s="50"/>
+      <c r="BS49" s="48"/>
+      <c r="BT49" s="49"/>
+      <c r="BU49" s="49"/>
+      <c r="BV49" s="49"/>
+      <c r="BW49" s="49"/>
+      <c r="BX49" s="49"/>
+      <c r="BY49" s="49"/>
+      <c r="BZ49" s="50"/>
+      <c r="CB49" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="CC49" s="63"/>
-      <c r="CD49" s="63"/>
-      <c r="CE49" s="63"/>
-      <c r="CF49" s="63"/>
-      <c r="CG49" s="64"/>
+      <c r="CC49" s="62"/>
+      <c r="CD49" s="62"/>
+      <c r="CE49" s="62"/>
+      <c r="CF49" s="62"/>
+      <c r="CG49" s="63"/>
     </row>
     <row r="50" spans="3:119" x14ac:dyDescent="0.25">
-      <c r="C50" s="51"/>
-      <c r="D50" s="51"/>
-      <c r="E50" s="51"/>
-      <c r="F50" s="51"/>
-      <c r="H50" s="42"/>
-      <c r="I50" s="43"/>
-      <c r="J50" s="43"/>
-      <c r="K50" s="43"/>
-      <c r="L50" s="43"/>
-      <c r="M50" s="43"/>
-      <c r="N50" s="43"/>
-      <c r="O50" s="44"/>
-      <c r="Q50" s="42"/>
-      <c r="R50" s="43"/>
-      <c r="S50" s="43"/>
-      <c r="T50" s="43"/>
-      <c r="U50" s="43"/>
-      <c r="V50" s="43"/>
-      <c r="W50" s="43"/>
-      <c r="X50" s="44"/>
-      <c r="Z50" s="42"/>
-      <c r="AA50" s="43"/>
-      <c r="AB50" s="43"/>
-      <c r="AC50" s="43"/>
-      <c r="AD50" s="43"/>
-      <c r="AE50" s="43"/>
-      <c r="AF50" s="43"/>
-      <c r="AG50" s="44"/>
-      <c r="AI50" s="42"/>
-      <c r="AJ50" s="43"/>
-      <c r="AK50" s="43"/>
-      <c r="AL50" s="43"/>
-      <c r="AM50" s="43"/>
-      <c r="AN50" s="43"/>
-      <c r="AO50" s="43"/>
-      <c r="AP50" s="44"/>
-      <c r="AR50" s="42"/>
-      <c r="AS50" s="43"/>
-      <c r="AT50" s="43"/>
-      <c r="AU50" s="43"/>
-      <c r="AV50" s="43"/>
-      <c r="AW50" s="43"/>
-      <c r="AX50" s="43"/>
-      <c r="AY50" s="44"/>
-      <c r="BA50" s="42"/>
-      <c r="BB50" s="43"/>
-      <c r="BC50" s="43"/>
-      <c r="BD50" s="43"/>
-      <c r="BE50" s="43"/>
-      <c r="BF50" s="43"/>
-      <c r="BG50" s="43"/>
-      <c r="BH50" s="44"/>
-      <c r="BJ50" s="48"/>
-      <c r="BK50" s="49"/>
-      <c r="BL50" s="49"/>
-      <c r="BM50" s="49"/>
-      <c r="BN50" s="49"/>
-      <c r="BO50" s="49"/>
-      <c r="BP50" s="49"/>
-      <c r="BQ50" s="50"/>
-      <c r="BS50" s="48"/>
-      <c r="BT50" s="49"/>
-      <c r="BU50" s="49"/>
-      <c r="BV50" s="49"/>
-      <c r="BW50" s="49"/>
-      <c r="BX50" s="49"/>
-      <c r="BY50" s="49"/>
-      <c r="BZ50" s="50"/>
+      <c r="C50" s="58"/>
+      <c r="D50" s="58"/>
+      <c r="E50" s="58"/>
+      <c r="F50" s="58"/>
+      <c r="H50" s="67"/>
+      <c r="I50" s="68"/>
+      <c r="J50" s="68"/>
+      <c r="K50" s="68"/>
+      <c r="L50" s="68"/>
+      <c r="M50" s="68"/>
+      <c r="N50" s="68"/>
+      <c r="O50" s="69"/>
+      <c r="Q50" s="67"/>
+      <c r="R50" s="68"/>
+      <c r="S50" s="68"/>
+      <c r="T50" s="68"/>
+      <c r="U50" s="68"/>
+      <c r="V50" s="68"/>
+      <c r="W50" s="68"/>
+      <c r="X50" s="69"/>
+      <c r="Z50" s="67"/>
+      <c r="AA50" s="68"/>
+      <c r="AB50" s="68"/>
+      <c r="AC50" s="68"/>
+      <c r="AD50" s="68"/>
+      <c r="AE50" s="68"/>
+      <c r="AF50" s="68"/>
+      <c r="AG50" s="69"/>
+      <c r="AI50" s="67"/>
+      <c r="AJ50" s="68"/>
+      <c r="AK50" s="68"/>
+      <c r="AL50" s="68"/>
+      <c r="AM50" s="68"/>
+      <c r="AN50" s="68"/>
+      <c r="AO50" s="68"/>
+      <c r="AP50" s="69"/>
+      <c r="AR50" s="67"/>
+      <c r="AS50" s="68"/>
+      <c r="AT50" s="68"/>
+      <c r="AU50" s="68"/>
+      <c r="AV50" s="68"/>
+      <c r="AW50" s="68"/>
+      <c r="AX50" s="68"/>
+      <c r="AY50" s="69"/>
+      <c r="BA50" s="67"/>
+      <c r="BB50" s="68"/>
+      <c r="BC50" s="68"/>
+      <c r="BD50" s="68"/>
+      <c r="BE50" s="68"/>
+      <c r="BF50" s="68"/>
+      <c r="BG50" s="68"/>
+      <c r="BH50" s="69"/>
+      <c r="BJ50" s="51"/>
+      <c r="BK50" s="52"/>
+      <c r="BL50" s="52"/>
+      <c r="BM50" s="52"/>
+      <c r="BN50" s="52"/>
+      <c r="BO50" s="52"/>
+      <c r="BP50" s="52"/>
+      <c r="BQ50" s="53"/>
+      <c r="BS50" s="51"/>
+      <c r="BT50" s="52"/>
+      <c r="BU50" s="52"/>
+      <c r="BV50" s="52"/>
+      <c r="BW50" s="52"/>
+      <c r="BX50" s="52"/>
+      <c r="BY50" s="52"/>
+      <c r="BZ50" s="53"/>
       <c r="CB50" s="16" t="s">
         <v>18</v>
       </c>
@@ -5859,17 +5859,17 @@
         <f>SUM(BT51+BV51+BX51)*16</f>
         <v>0</v>
       </c>
-      <c r="CB51" s="65" t="s">
+      <c r="CB51" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="CC51" s="51"/>
-      <c r="CD51" s="51"/>
-      <c r="CE51" s="51">
+      <c r="CC51" s="58"/>
+      <c r="CD51" s="58"/>
+      <c r="CE51" s="58">
         <f ca="1">CE52*3*16</f>
         <v>0</v>
       </c>
-      <c r="CF51" s="51"/>
-      <c r="CG51" s="68"/>
+      <c r="CF51" s="58"/>
+      <c r="CG51" s="59"/>
       <c r="CN51" s="18"/>
       <c r="CW51" s="18"/>
       <c r="DF51" s="18"/>
@@ -5932,17 +5932,17 @@
         <f>(BT51+BV51+BX51)/3</f>
         <v>0</v>
       </c>
-      <c r="CB52" s="66" t="s">
+      <c r="CB52" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="CC52" s="67"/>
-      <c r="CD52" s="67"/>
-      <c r="CE52" s="54">
+      <c r="CC52" s="55"/>
+      <c r="CD52" s="55"/>
+      <c r="CE52" s="56">
         <f ca="1">SUM(IF(MOD(COLUMN(O52:OFFSET(CE52,0,-1)) - COLUMN(O52), 9) = 0, O52:OFFSET(CE52,0,-1), 0))</f>
         <v>0</v>
       </c>
-      <c r="CF52" s="54"/>
-      <c r="CG52" s="55"/>
+      <c r="CF52" s="56"/>
+      <c r="CG52" s="57"/>
     </row>
     <row r="53" spans="3:119" x14ac:dyDescent="0.25">
       <c r="CB53" s="19"/>
@@ -6043,13 +6043,13 @@
       <c r="BP56" s="29"/>
       <c r="BQ56" s="29"/>
       <c r="BR56" s="29"/>
-      <c r="CB56" s="57" t="s">
+      <c r="CB56" s="70" t="s">
         <v>32</v>
       </c>
-      <c r="CC56" s="58"/>
-      <c r="CD56" s="58"/>
-      <c r="CE56" s="58"/>
-      <c r="CF56" s="58"/>
+      <c r="CC56" s="71"/>
+      <c r="CD56" s="71"/>
+      <c r="CE56" s="71"/>
+      <c r="CF56" s="71"/>
       <c r="CG56" s="20">
         <f ca="1">(CC25+CC30+CC35+CC40+CC45+CC20+CC15+CC10+CC50)</f>
         <v>0</v>
@@ -6197,13 +6197,13 @@
       <c r="BA63" s="18"/>
       <c r="BJ63" s="18"/>
       <c r="BK63" s="29"/>
-      <c r="CB63" s="69" t="s">
+      <c r="CB63" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="CC63" s="70"/>
-      <c r="CD63" s="70"/>
-      <c r="CE63" s="70"/>
-      <c r="CF63" s="70"/>
+      <c r="CC63" s="40"/>
+      <c r="CD63" s="40"/>
+      <c r="CE63" s="40"/>
+      <c r="CF63" s="40"/>
       <c r="CG63" s="22">
         <f ca="1">CG62/(3*16)</f>
         <v>12</v>
@@ -6254,28 +6254,101 @@
     </row>
   </sheetData>
   <mergeCells count="143">
-    <mergeCell ref="CB62:CF62"/>
-    <mergeCell ref="CB63:CF63"/>
-    <mergeCell ref="H1:BZ4"/>
-    <mergeCell ref="I6:N7"/>
-    <mergeCell ref="R6:W7"/>
-    <mergeCell ref="AA6:AF7"/>
-    <mergeCell ref="AJ6:AO7"/>
-    <mergeCell ref="AS6:AX7"/>
-    <mergeCell ref="BB6:BG7"/>
-    <mergeCell ref="BS49:BZ50"/>
-    <mergeCell ref="BS9:BZ10"/>
-    <mergeCell ref="BS14:BZ15"/>
-    <mergeCell ref="BS19:BZ20"/>
-    <mergeCell ref="BS24:BZ25"/>
-    <mergeCell ref="BS29:BZ30"/>
-    <mergeCell ref="BK6:BP7"/>
-    <mergeCell ref="BT6:BY7"/>
-    <mergeCell ref="CB52:CD52"/>
-    <mergeCell ref="CE52:CG52"/>
-    <mergeCell ref="CE46:CG46"/>
-    <mergeCell ref="CE47:CG47"/>
-    <mergeCell ref="CB51:CD51"/>
+    <mergeCell ref="CB57:CF57"/>
+    <mergeCell ref="CB58:CF58"/>
+    <mergeCell ref="CB59:CF59"/>
+    <mergeCell ref="CB60:CF60"/>
+    <mergeCell ref="CB61:CF61"/>
+    <mergeCell ref="BA29:BH30"/>
+    <mergeCell ref="H24:O25"/>
+    <mergeCell ref="BJ19:BQ20"/>
+    <mergeCell ref="CE11:CG11"/>
+    <mergeCell ref="CB12:CD12"/>
+    <mergeCell ref="CE12:CG12"/>
+    <mergeCell ref="CB11:CD11"/>
+    <mergeCell ref="H19:O20"/>
+    <mergeCell ref="Q19:X20"/>
+    <mergeCell ref="Z19:AG20"/>
+    <mergeCell ref="AI19:AP20"/>
+    <mergeCell ref="AR19:AY20"/>
+    <mergeCell ref="H14:O15"/>
+    <mergeCell ref="H34:O35"/>
+    <mergeCell ref="Q34:X35"/>
+    <mergeCell ref="Z34:AG35"/>
+    <mergeCell ref="AI34:AP35"/>
+    <mergeCell ref="BA9:BH10"/>
+    <mergeCell ref="AR9:AY10"/>
+    <mergeCell ref="AI9:AP10"/>
+    <mergeCell ref="Z9:AG10"/>
+    <mergeCell ref="Q9:X10"/>
+    <mergeCell ref="Q24:X25"/>
+    <mergeCell ref="CB56:CF56"/>
+    <mergeCell ref="CB9:CG9"/>
+    <mergeCell ref="C14:F15"/>
+    <mergeCell ref="Q14:X15"/>
+    <mergeCell ref="Z14:AG15"/>
+    <mergeCell ref="AI14:AP15"/>
+    <mergeCell ref="AR14:AY15"/>
+    <mergeCell ref="BA14:BH15"/>
+    <mergeCell ref="BJ14:BQ15"/>
+    <mergeCell ref="BA19:BH20"/>
+    <mergeCell ref="BJ9:BQ10"/>
+    <mergeCell ref="H9:O10"/>
+    <mergeCell ref="C9:F10"/>
+    <mergeCell ref="CB14:CG14"/>
+    <mergeCell ref="CB16:CD16"/>
+    <mergeCell ref="CB17:CD17"/>
+    <mergeCell ref="CE16:CG16"/>
+    <mergeCell ref="CE17:CG17"/>
+    <mergeCell ref="AR34:AY35"/>
+    <mergeCell ref="BA34:BH35"/>
+    <mergeCell ref="BJ34:BQ35"/>
+    <mergeCell ref="Z24:AG25"/>
+    <mergeCell ref="AI24:AP25"/>
+    <mergeCell ref="AR24:AY25"/>
+    <mergeCell ref="BA24:BH25"/>
+    <mergeCell ref="H29:O30"/>
+    <mergeCell ref="Q29:X30"/>
+    <mergeCell ref="Z29:AG30"/>
+    <mergeCell ref="AI29:AP30"/>
+    <mergeCell ref="AR29:AY30"/>
+    <mergeCell ref="BJ24:BQ25"/>
+    <mergeCell ref="CE22:CG22"/>
+    <mergeCell ref="CB24:CG24"/>
+    <mergeCell ref="CB26:CD26"/>
+    <mergeCell ref="H49:O50"/>
+    <mergeCell ref="Q49:X50"/>
+    <mergeCell ref="Z49:AG50"/>
+    <mergeCell ref="AI49:AP50"/>
+    <mergeCell ref="AR49:AY50"/>
+    <mergeCell ref="BA49:BH50"/>
+    <mergeCell ref="BJ39:BQ40"/>
+    <mergeCell ref="H44:O45"/>
+    <mergeCell ref="Q44:X45"/>
+    <mergeCell ref="Z44:AG45"/>
+    <mergeCell ref="AI44:AP45"/>
+    <mergeCell ref="AR44:AY45"/>
+    <mergeCell ref="BA44:BH45"/>
+    <mergeCell ref="BJ44:BQ45"/>
+    <mergeCell ref="H39:O40"/>
+    <mergeCell ref="Q39:X40"/>
+    <mergeCell ref="Z39:AG40"/>
+    <mergeCell ref="AI39:AP40"/>
+    <mergeCell ref="AR39:AY40"/>
+    <mergeCell ref="BA39:BH40"/>
+    <mergeCell ref="BJ29:BQ30"/>
+    <mergeCell ref="CB41:CD41"/>
+    <mergeCell ref="CE41:CG41"/>
+    <mergeCell ref="CB42:CD42"/>
+    <mergeCell ref="CE42:CG42"/>
+    <mergeCell ref="CB44:CG44"/>
+    <mergeCell ref="CB32:CD32"/>
+    <mergeCell ref="CE32:CG32"/>
+    <mergeCell ref="CB34:CG34"/>
+    <mergeCell ref="CB36:CD36"/>
+    <mergeCell ref="CE36:CG36"/>
+    <mergeCell ref="CB37:CD37"/>
+    <mergeCell ref="CE37:CG37"/>
     <mergeCell ref="C19:F20"/>
     <mergeCell ref="C24:F25"/>
     <mergeCell ref="C29:F30"/>
@@ -6300,103 +6373,30 @@
     <mergeCell ref="CB21:CD21"/>
     <mergeCell ref="CE21:CG21"/>
     <mergeCell ref="CB22:CD22"/>
+    <mergeCell ref="CB62:CF62"/>
+    <mergeCell ref="CB63:CF63"/>
+    <mergeCell ref="H1:BZ4"/>
+    <mergeCell ref="I6:N7"/>
+    <mergeCell ref="R6:W7"/>
+    <mergeCell ref="AA6:AF7"/>
+    <mergeCell ref="AJ6:AO7"/>
+    <mergeCell ref="AS6:AX7"/>
+    <mergeCell ref="BB6:BG7"/>
+    <mergeCell ref="BS49:BZ50"/>
+    <mergeCell ref="BS9:BZ10"/>
+    <mergeCell ref="BS14:BZ15"/>
+    <mergeCell ref="BS19:BZ20"/>
+    <mergeCell ref="BS24:BZ25"/>
+    <mergeCell ref="BS29:BZ30"/>
+    <mergeCell ref="BK6:BP7"/>
+    <mergeCell ref="BT6:BY7"/>
+    <mergeCell ref="CB52:CD52"/>
+    <mergeCell ref="CE52:CG52"/>
+    <mergeCell ref="CE46:CG46"/>
+    <mergeCell ref="CE47:CG47"/>
+    <mergeCell ref="CB51:CD51"/>
     <mergeCell ref="CE51:CG51"/>
     <mergeCell ref="CB39:CG39"/>
-    <mergeCell ref="CB41:CD41"/>
-    <mergeCell ref="CE41:CG41"/>
-    <mergeCell ref="CB42:CD42"/>
-    <mergeCell ref="CE42:CG42"/>
-    <mergeCell ref="CB44:CG44"/>
-    <mergeCell ref="CB32:CD32"/>
-    <mergeCell ref="CE32:CG32"/>
-    <mergeCell ref="CB34:CG34"/>
-    <mergeCell ref="CB36:CD36"/>
-    <mergeCell ref="CE36:CG36"/>
-    <mergeCell ref="CB37:CD37"/>
-    <mergeCell ref="CE37:CG37"/>
-    <mergeCell ref="CE22:CG22"/>
-    <mergeCell ref="CB24:CG24"/>
-    <mergeCell ref="CB26:CD26"/>
-    <mergeCell ref="H49:O50"/>
-    <mergeCell ref="Q49:X50"/>
-    <mergeCell ref="Z49:AG50"/>
-    <mergeCell ref="AI49:AP50"/>
-    <mergeCell ref="AR49:AY50"/>
-    <mergeCell ref="BA49:BH50"/>
-    <mergeCell ref="BJ39:BQ40"/>
-    <mergeCell ref="H44:O45"/>
-    <mergeCell ref="Q44:X45"/>
-    <mergeCell ref="Z44:AG45"/>
-    <mergeCell ref="AI44:AP45"/>
-    <mergeCell ref="AR44:AY45"/>
-    <mergeCell ref="BA44:BH45"/>
-    <mergeCell ref="BJ44:BQ45"/>
-    <mergeCell ref="H39:O40"/>
-    <mergeCell ref="Q39:X40"/>
-    <mergeCell ref="Z39:AG40"/>
-    <mergeCell ref="AI39:AP40"/>
-    <mergeCell ref="AR39:AY40"/>
-    <mergeCell ref="BA39:BH40"/>
-    <mergeCell ref="BJ29:BQ30"/>
-    <mergeCell ref="AR34:AY35"/>
-    <mergeCell ref="BA34:BH35"/>
-    <mergeCell ref="BJ34:BQ35"/>
-    <mergeCell ref="Z24:AG25"/>
-    <mergeCell ref="AI24:AP25"/>
-    <mergeCell ref="AR24:AY25"/>
-    <mergeCell ref="BA24:BH25"/>
-    <mergeCell ref="H29:O30"/>
-    <mergeCell ref="Q29:X30"/>
-    <mergeCell ref="Z29:AG30"/>
-    <mergeCell ref="AI29:AP30"/>
-    <mergeCell ref="AR29:AY30"/>
-    <mergeCell ref="BJ24:BQ25"/>
-    <mergeCell ref="BA9:BH10"/>
-    <mergeCell ref="AR9:AY10"/>
-    <mergeCell ref="AI9:AP10"/>
-    <mergeCell ref="Z9:AG10"/>
-    <mergeCell ref="Q9:X10"/>
-    <mergeCell ref="Q24:X25"/>
-    <mergeCell ref="CB56:CF56"/>
-    <mergeCell ref="CB9:CG9"/>
-    <mergeCell ref="C14:F15"/>
-    <mergeCell ref="Q14:X15"/>
-    <mergeCell ref="Z14:AG15"/>
-    <mergeCell ref="AI14:AP15"/>
-    <mergeCell ref="AR14:AY15"/>
-    <mergeCell ref="BA14:BH15"/>
-    <mergeCell ref="BJ14:BQ15"/>
-    <mergeCell ref="BA19:BH20"/>
-    <mergeCell ref="BJ9:BQ10"/>
-    <mergeCell ref="H9:O10"/>
-    <mergeCell ref="C9:F10"/>
-    <mergeCell ref="CB14:CG14"/>
-    <mergeCell ref="CB16:CD16"/>
-    <mergeCell ref="CB17:CD17"/>
-    <mergeCell ref="CE16:CG16"/>
-    <mergeCell ref="CE17:CG17"/>
-    <mergeCell ref="CB57:CF57"/>
-    <mergeCell ref="CB58:CF58"/>
-    <mergeCell ref="CB59:CF59"/>
-    <mergeCell ref="CB60:CF60"/>
-    <mergeCell ref="CB61:CF61"/>
-    <mergeCell ref="BA29:BH30"/>
-    <mergeCell ref="H24:O25"/>
-    <mergeCell ref="BJ19:BQ20"/>
-    <mergeCell ref="CE11:CG11"/>
-    <mergeCell ref="CB12:CD12"/>
-    <mergeCell ref="CE12:CG12"/>
-    <mergeCell ref="CB11:CD11"/>
-    <mergeCell ref="H19:O20"/>
-    <mergeCell ref="Q19:X20"/>
-    <mergeCell ref="Z19:AG20"/>
-    <mergeCell ref="AI19:AP20"/>
-    <mergeCell ref="AR19:AY20"/>
-    <mergeCell ref="H14:O15"/>
-    <mergeCell ref="H34:O35"/>
-    <mergeCell ref="Q34:X35"/>
-    <mergeCell ref="Z34:AG35"/>
-    <mergeCell ref="AI34:AP35"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="24" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/plantillas/excel_base.xlsx
+++ b/plantillas/excel_base.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\estudiante\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\estudiante\Downloads\plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B06081CA-CE96-46CA-A714-62E27A8504F1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA18935A-C8CB-476A-AF2F-14857EBB872A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" tabRatio="570" xr2:uid="{73D17D42-2032-4221-9DBF-D2EB2D99B5D8}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" tabRatio="570" activeTab="2" xr2:uid="{73D17D42-2032-4221-9DBF-D2EB2D99B5D8}"/>
   </bookViews>
   <sheets>
     <sheet name="MALLA CURRICULAR" sheetId="8" r:id="rId1"/>
     <sheet name="MODIFICACIONES EN ASIGNATURAS" sheetId="1" r:id="rId2"/>
+    <sheet name="AJUSTE CURRICULAR DAR" sheetId="9" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'MALLA CURRICULAR'!$A$1:$CH$67</definedName>
@@ -67,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="106">
   <si>
     <t>MODIFICACIÓN EN ASIGNATURAS DE LA MALLA CURRICULAR</t>
   </si>
@@ -284,12 +285,114 @@
   <si>
     <t>MALLA CURRICULAR CARRERA</t>
   </si>
+  <si>
+    <t>MATRIZ MAESTRA DE AJUSTES CURRICULARES 2027</t>
+  </si>
+  <si>
+    <t>Descripción Interna</t>
+  </si>
+  <si>
+    <t>Significado</t>
+  </si>
+  <si>
+    <t>Se mantiene</t>
+  </si>
+  <si>
+    <t>No existe cambio entre la malla vigente y la propuesta</t>
+  </si>
+  <si>
+    <t>Nueva materia</t>
+  </si>
+  <si>
+    <t>Se agregó una nueva materia a la malla</t>
+  </si>
+  <si>
+    <t>Eliminación de materia</t>
+  </si>
+  <si>
+    <t>Se eliminó una materia de la malla vigente</t>
+  </si>
+  <si>
+    <t>Cambio de nivel de la materia en la malla</t>
+  </si>
+  <si>
+    <t>Se cambió el nivel de la materia en la malla</t>
+  </si>
+  <si>
+    <t>Cambio de componentes de aprendizaje</t>
+  </si>
+  <si>
+    <t>Se cambió las horas de una materia en uno o más componentes del aprendizaje: horas de aprendizaje en contacto con el docente, aprendizaje práctico-experimental y/o aprendizaje autónomo.</t>
+  </si>
+  <si>
+    <t>Cambio de componente de aprendizaje y de nivel de malla</t>
+  </si>
+  <si>
+    <t>Se cambió las horas de una materia en uno o más componentes del aprendizaje: horas de aprendizaje en contacto con el docente, aprendizaje práctico-experimental y/o aprendizaje autónomo, y además se cambió el nivel de la malla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROPUESTO </t>
+  </si>
+  <si>
+    <t>Cód. Curso</t>
+  </si>
+  <si>
+    <t>Curso</t>
+  </si>
+  <si>
+    <t>Clasificación</t>
+  </si>
+  <si>
+    <t>Nivel de malla</t>
+  </si>
+  <si>
+    <t>ACD (Aprendizaje en Contacto con el Docente)</t>
+  </si>
+  <si>
+    <t>APE (Aprendizaje Práctico-Experimental )</t>
+  </si>
+  <si>
+    <t>AA (Aprendizaje Autónomo)</t>
+  </si>
+  <si>
+    <t>Créditos</t>
+  </si>
+  <si>
+    <t>Contenidos Mínimos</t>
+  </si>
+  <si>
+    <t>Justificación</t>
+  </si>
+  <si>
+    <t>ACD Semestrales (Aprendizaje en Contacto con el Docente)</t>
+  </si>
+  <si>
+    <t>APE Semestrales (Aprendizaje Práctico-Experimental )</t>
+  </si>
+  <si>
+    <t>AA Semestrales (Aprendizaje Autónomo)</t>
+  </si>
+  <si>
+    <t>HT Semestrales</t>
+  </si>
+  <si>
+    <t>Total de Horas ACD</t>
+  </si>
+  <si>
+    <t>Total de Horas APE</t>
+  </si>
+  <si>
+    <t>Total de Horas AA</t>
+  </si>
+  <si>
+    <t>Total de Créditos</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -341,8 +444,42 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -409,8 +546,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="40">
+  <borders count="51">
     <border>
       <left/>
       <right/>
@@ -945,11 +1112,152 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1065,6 +1373,96 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1092,96 +1490,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1202,6 +1510,148 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1632,7 +2082,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="C1:DO68"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="13"/>
     <col min="2" max="2" width="3.7109375" style="13" customWidth="1"/>
@@ -1676,85 +2126,85 @@
     <col min="276" max="16384" width="8.85546875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:85" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="3:85" ht="15" customHeight="1">
       <c r="C1" s="11"/>
       <c r="D1" s="11"/>
       <c r="E1" s="11"/>
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
-      <c r="H1" s="41" t="s">
+      <c r="H1" s="71" t="s">
         <v>71</v>
       </c>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="41"/>
-      <c r="V1" s="41"/>
-      <c r="W1" s="41"/>
-      <c r="X1" s="41"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="41"/>
-      <c r="AA1" s="41"/>
-      <c r="AB1" s="41"/>
-      <c r="AC1" s="41"/>
-      <c r="AD1" s="41"/>
-      <c r="AE1" s="41"/>
-      <c r="AF1" s="41"/>
-      <c r="AG1" s="41"/>
-      <c r="AH1" s="41"/>
-      <c r="AI1" s="41"/>
-      <c r="AJ1" s="41"/>
-      <c r="AK1" s="41"/>
-      <c r="AL1" s="41"/>
-      <c r="AM1" s="41"/>
-      <c r="AN1" s="41"/>
-      <c r="AO1" s="41"/>
-      <c r="AP1" s="41"/>
-      <c r="AQ1" s="41"/>
-      <c r="AR1" s="41"/>
-      <c r="AS1" s="41"/>
-      <c r="AT1" s="41"/>
-      <c r="AU1" s="41"/>
-      <c r="AV1" s="41"/>
-      <c r="AW1" s="41"/>
-      <c r="AX1" s="41"/>
-      <c r="AY1" s="41"/>
-      <c r="AZ1" s="41"/>
-      <c r="BA1" s="41"/>
-      <c r="BB1" s="41"/>
-      <c r="BC1" s="41"/>
-      <c r="BD1" s="41"/>
-      <c r="BE1" s="41"/>
-      <c r="BF1" s="41"/>
-      <c r="BG1" s="41"/>
-      <c r="BH1" s="41"/>
-      <c r="BI1" s="41"/>
-      <c r="BJ1" s="41"/>
-      <c r="BK1" s="41"/>
-      <c r="BL1" s="41"/>
-      <c r="BM1" s="41"/>
-      <c r="BN1" s="41"/>
-      <c r="BO1" s="41"/>
-      <c r="BP1" s="41"/>
-      <c r="BQ1" s="41"/>
-      <c r="BR1" s="41"/>
-      <c r="BS1" s="41"/>
-      <c r="BT1" s="41"/>
-      <c r="BU1" s="41"/>
-      <c r="BV1" s="41"/>
-      <c r="BW1" s="41"/>
-      <c r="BX1" s="41"/>
-      <c r="BY1" s="41"/>
-      <c r="BZ1" s="41"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
+      <c r="O1" s="71"/>
+      <c r="P1" s="71"/>
+      <c r="Q1" s="71"/>
+      <c r="R1" s="71"/>
+      <c r="S1" s="71"/>
+      <c r="T1" s="71"/>
+      <c r="U1" s="71"/>
+      <c r="V1" s="71"/>
+      <c r="W1" s="71"/>
+      <c r="X1" s="71"/>
+      <c r="Y1" s="71"/>
+      <c r="Z1" s="71"/>
+      <c r="AA1" s="71"/>
+      <c r="AB1" s="71"/>
+      <c r="AC1" s="71"/>
+      <c r="AD1" s="71"/>
+      <c r="AE1" s="71"/>
+      <c r="AF1" s="71"/>
+      <c r="AG1" s="71"/>
+      <c r="AH1" s="71"/>
+      <c r="AI1" s="71"/>
+      <c r="AJ1" s="71"/>
+      <c r="AK1" s="71"/>
+      <c r="AL1" s="71"/>
+      <c r="AM1" s="71"/>
+      <c r="AN1" s="71"/>
+      <c r="AO1" s="71"/>
+      <c r="AP1" s="71"/>
+      <c r="AQ1" s="71"/>
+      <c r="AR1" s="71"/>
+      <c r="AS1" s="71"/>
+      <c r="AT1" s="71"/>
+      <c r="AU1" s="71"/>
+      <c r="AV1" s="71"/>
+      <c r="AW1" s="71"/>
+      <c r="AX1" s="71"/>
+      <c r="AY1" s="71"/>
+      <c r="AZ1" s="71"/>
+      <c r="BA1" s="71"/>
+      <c r="BB1" s="71"/>
+      <c r="BC1" s="71"/>
+      <c r="BD1" s="71"/>
+      <c r="BE1" s="71"/>
+      <c r="BF1" s="71"/>
+      <c r="BG1" s="71"/>
+      <c r="BH1" s="71"/>
+      <c r="BI1" s="71"/>
+      <c r="BJ1" s="71"/>
+      <c r="BK1" s="71"/>
+      <c r="BL1" s="71"/>
+      <c r="BM1" s="71"/>
+      <c r="BN1" s="71"/>
+      <c r="BO1" s="71"/>
+      <c r="BP1" s="71"/>
+      <c r="BQ1" s="71"/>
+      <c r="BR1" s="71"/>
+      <c r="BS1" s="71"/>
+      <c r="BT1" s="71"/>
+      <c r="BU1" s="71"/>
+      <c r="BV1" s="71"/>
+      <c r="BW1" s="71"/>
+      <c r="BX1" s="71"/>
+      <c r="BY1" s="71"/>
+      <c r="BZ1" s="71"/>
       <c r="CA1" s="11"/>
       <c r="CB1" s="11"/>
       <c r="CC1" s="11"/>
@@ -1763,83 +2213,83 @@
       <c r="CF1" s="11"/>
       <c r="CG1" s="11"/>
     </row>
-    <row r="2" spans="3:85" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:85" ht="15" customHeight="1">
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="11"/>
       <c r="G2" s="11"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="41"/>
-      <c r="R2" s="41"/>
-      <c r="S2" s="41"/>
-      <c r="T2" s="41"/>
-      <c r="U2" s="41"/>
-      <c r="V2" s="41"/>
-      <c r="W2" s="41"/>
-      <c r="X2" s="41"/>
-      <c r="Y2" s="41"/>
-      <c r="Z2" s="41"/>
-      <c r="AA2" s="41"/>
-      <c r="AB2" s="41"/>
-      <c r="AC2" s="41"/>
-      <c r="AD2" s="41"/>
-      <c r="AE2" s="41"/>
-      <c r="AF2" s="41"/>
-      <c r="AG2" s="41"/>
-      <c r="AH2" s="41"/>
-      <c r="AI2" s="41"/>
-      <c r="AJ2" s="41"/>
-      <c r="AK2" s="41"/>
-      <c r="AL2" s="41"/>
-      <c r="AM2" s="41"/>
-      <c r="AN2" s="41"/>
-      <c r="AO2" s="41"/>
-      <c r="AP2" s="41"/>
-      <c r="AQ2" s="41"/>
-      <c r="AR2" s="41"/>
-      <c r="AS2" s="41"/>
-      <c r="AT2" s="41"/>
-      <c r="AU2" s="41"/>
-      <c r="AV2" s="41"/>
-      <c r="AW2" s="41"/>
-      <c r="AX2" s="41"/>
-      <c r="AY2" s="41"/>
-      <c r="AZ2" s="41"/>
-      <c r="BA2" s="41"/>
-      <c r="BB2" s="41"/>
-      <c r="BC2" s="41"/>
-      <c r="BD2" s="41"/>
-      <c r="BE2" s="41"/>
-      <c r="BF2" s="41"/>
-      <c r="BG2" s="41"/>
-      <c r="BH2" s="41"/>
-      <c r="BI2" s="41"/>
-      <c r="BJ2" s="41"/>
-      <c r="BK2" s="41"/>
-      <c r="BL2" s="41"/>
-      <c r="BM2" s="41"/>
-      <c r="BN2" s="41"/>
-      <c r="BO2" s="41"/>
-      <c r="BP2" s="41"/>
-      <c r="BQ2" s="41"/>
-      <c r="BR2" s="41"/>
-      <c r="BS2" s="41"/>
-      <c r="BT2" s="41"/>
-      <c r="BU2" s="41"/>
-      <c r="BV2" s="41"/>
-      <c r="BW2" s="41"/>
-      <c r="BX2" s="41"/>
-      <c r="BY2" s="41"/>
-      <c r="BZ2" s="41"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
+      <c r="N2" s="71"/>
+      <c r="O2" s="71"/>
+      <c r="P2" s="71"/>
+      <c r="Q2" s="71"/>
+      <c r="R2" s="71"/>
+      <c r="S2" s="71"/>
+      <c r="T2" s="71"/>
+      <c r="U2" s="71"/>
+      <c r="V2" s="71"/>
+      <c r="W2" s="71"/>
+      <c r="X2" s="71"/>
+      <c r="Y2" s="71"/>
+      <c r="Z2" s="71"/>
+      <c r="AA2" s="71"/>
+      <c r="AB2" s="71"/>
+      <c r="AC2" s="71"/>
+      <c r="AD2" s="71"/>
+      <c r="AE2" s="71"/>
+      <c r="AF2" s="71"/>
+      <c r="AG2" s="71"/>
+      <c r="AH2" s="71"/>
+      <c r="AI2" s="71"/>
+      <c r="AJ2" s="71"/>
+      <c r="AK2" s="71"/>
+      <c r="AL2" s="71"/>
+      <c r="AM2" s="71"/>
+      <c r="AN2" s="71"/>
+      <c r="AO2" s="71"/>
+      <c r="AP2" s="71"/>
+      <c r="AQ2" s="71"/>
+      <c r="AR2" s="71"/>
+      <c r="AS2" s="71"/>
+      <c r="AT2" s="71"/>
+      <c r="AU2" s="71"/>
+      <c r="AV2" s="71"/>
+      <c r="AW2" s="71"/>
+      <c r="AX2" s="71"/>
+      <c r="AY2" s="71"/>
+      <c r="AZ2" s="71"/>
+      <c r="BA2" s="71"/>
+      <c r="BB2" s="71"/>
+      <c r="BC2" s="71"/>
+      <c r="BD2" s="71"/>
+      <c r="BE2" s="71"/>
+      <c r="BF2" s="71"/>
+      <c r="BG2" s="71"/>
+      <c r="BH2" s="71"/>
+      <c r="BI2" s="71"/>
+      <c r="BJ2" s="71"/>
+      <c r="BK2" s="71"/>
+      <c r="BL2" s="71"/>
+      <c r="BM2" s="71"/>
+      <c r="BN2" s="71"/>
+      <c r="BO2" s="71"/>
+      <c r="BP2" s="71"/>
+      <c r="BQ2" s="71"/>
+      <c r="BR2" s="71"/>
+      <c r="BS2" s="71"/>
+      <c r="BT2" s="71"/>
+      <c r="BU2" s="71"/>
+      <c r="BV2" s="71"/>
+      <c r="BW2" s="71"/>
+      <c r="BX2" s="71"/>
+      <c r="BY2" s="71"/>
+      <c r="BZ2" s="71"/>
       <c r="CA2" s="11"/>
       <c r="CB2" s="11"/>
       <c r="CC2" s="11"/>
@@ -1848,83 +2298,83 @@
       <c r="CF2" s="11"/>
       <c r="CG2" s="11"/>
     </row>
-    <row r="3" spans="3:85" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:85" ht="15" customHeight="1">
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="41"/>
-      <c r="R3" s="41"/>
-      <c r="S3" s="41"/>
-      <c r="T3" s="41"/>
-      <c r="U3" s="41"/>
-      <c r="V3" s="41"/>
-      <c r="W3" s="41"/>
-      <c r="X3" s="41"/>
-      <c r="Y3" s="41"/>
-      <c r="Z3" s="41"/>
-      <c r="AA3" s="41"/>
-      <c r="AB3" s="41"/>
-      <c r="AC3" s="41"/>
-      <c r="AD3" s="41"/>
-      <c r="AE3" s="41"/>
-      <c r="AF3" s="41"/>
-      <c r="AG3" s="41"/>
-      <c r="AH3" s="41"/>
-      <c r="AI3" s="41"/>
-      <c r="AJ3" s="41"/>
-      <c r="AK3" s="41"/>
-      <c r="AL3" s="41"/>
-      <c r="AM3" s="41"/>
-      <c r="AN3" s="41"/>
-      <c r="AO3" s="41"/>
-      <c r="AP3" s="41"/>
-      <c r="AQ3" s="41"/>
-      <c r="AR3" s="41"/>
-      <c r="AS3" s="41"/>
-      <c r="AT3" s="41"/>
-      <c r="AU3" s="41"/>
-      <c r="AV3" s="41"/>
-      <c r="AW3" s="41"/>
-      <c r="AX3" s="41"/>
-      <c r="AY3" s="41"/>
-      <c r="AZ3" s="41"/>
-      <c r="BA3" s="41"/>
-      <c r="BB3" s="41"/>
-      <c r="BC3" s="41"/>
-      <c r="BD3" s="41"/>
-      <c r="BE3" s="41"/>
-      <c r="BF3" s="41"/>
-      <c r="BG3" s="41"/>
-      <c r="BH3" s="41"/>
-      <c r="BI3" s="41"/>
-      <c r="BJ3" s="41"/>
-      <c r="BK3" s="41"/>
-      <c r="BL3" s="41"/>
-      <c r="BM3" s="41"/>
-      <c r="BN3" s="41"/>
-      <c r="BO3" s="41"/>
-      <c r="BP3" s="41"/>
-      <c r="BQ3" s="41"/>
-      <c r="BR3" s="41"/>
-      <c r="BS3" s="41"/>
-      <c r="BT3" s="41"/>
-      <c r="BU3" s="41"/>
-      <c r="BV3" s="41"/>
-      <c r="BW3" s="41"/>
-      <c r="BX3" s="41"/>
-      <c r="BY3" s="41"/>
-      <c r="BZ3" s="41"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+      <c r="N3" s="71"/>
+      <c r="O3" s="71"/>
+      <c r="P3" s="71"/>
+      <c r="Q3" s="71"/>
+      <c r="R3" s="71"/>
+      <c r="S3" s="71"/>
+      <c r="T3" s="71"/>
+      <c r="U3" s="71"/>
+      <c r="V3" s="71"/>
+      <c r="W3" s="71"/>
+      <c r="X3" s="71"/>
+      <c r="Y3" s="71"/>
+      <c r="Z3" s="71"/>
+      <c r="AA3" s="71"/>
+      <c r="AB3" s="71"/>
+      <c r="AC3" s="71"/>
+      <c r="AD3" s="71"/>
+      <c r="AE3" s="71"/>
+      <c r="AF3" s="71"/>
+      <c r="AG3" s="71"/>
+      <c r="AH3" s="71"/>
+      <c r="AI3" s="71"/>
+      <c r="AJ3" s="71"/>
+      <c r="AK3" s="71"/>
+      <c r="AL3" s="71"/>
+      <c r="AM3" s="71"/>
+      <c r="AN3" s="71"/>
+      <c r="AO3" s="71"/>
+      <c r="AP3" s="71"/>
+      <c r="AQ3" s="71"/>
+      <c r="AR3" s="71"/>
+      <c r="AS3" s="71"/>
+      <c r="AT3" s="71"/>
+      <c r="AU3" s="71"/>
+      <c r="AV3" s="71"/>
+      <c r="AW3" s="71"/>
+      <c r="AX3" s="71"/>
+      <c r="AY3" s="71"/>
+      <c r="AZ3" s="71"/>
+      <c r="BA3" s="71"/>
+      <c r="BB3" s="71"/>
+      <c r="BC3" s="71"/>
+      <c r="BD3" s="71"/>
+      <c r="BE3" s="71"/>
+      <c r="BF3" s="71"/>
+      <c r="BG3" s="71"/>
+      <c r="BH3" s="71"/>
+      <c r="BI3" s="71"/>
+      <c r="BJ3" s="71"/>
+      <c r="BK3" s="71"/>
+      <c r="BL3" s="71"/>
+      <c r="BM3" s="71"/>
+      <c r="BN3" s="71"/>
+      <c r="BO3" s="71"/>
+      <c r="BP3" s="71"/>
+      <c r="BQ3" s="71"/>
+      <c r="BR3" s="71"/>
+      <c r="BS3" s="71"/>
+      <c r="BT3" s="71"/>
+      <c r="BU3" s="71"/>
+      <c r="BV3" s="71"/>
+      <c r="BW3" s="71"/>
+      <c r="BX3" s="71"/>
+      <c r="BY3" s="71"/>
+      <c r="BZ3" s="71"/>
       <c r="CA3" s="11"/>
       <c r="CB3" s="11"/>
       <c r="CC3" s="11"/>
@@ -1933,83 +2383,83 @@
       <c r="CF3" s="11"/>
       <c r="CG3" s="11"/>
     </row>
-    <row r="4" spans="3:85" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:85" ht="15" customHeight="1">
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
       <c r="F4" s="12"/>
       <c r="G4" s="12"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="41"/>
-      <c r="N4" s="41"/>
-      <c r="O4" s="41"/>
-      <c r="P4" s="41"/>
-      <c r="Q4" s="41"/>
-      <c r="R4" s="41"/>
-      <c r="S4" s="41"/>
-      <c r="T4" s="41"/>
-      <c r="U4" s="41"/>
-      <c r="V4" s="41"/>
-      <c r="W4" s="41"/>
-      <c r="X4" s="41"/>
-      <c r="Y4" s="41"/>
-      <c r="Z4" s="41"/>
-      <c r="AA4" s="41"/>
-      <c r="AB4" s="41"/>
-      <c r="AC4" s="41"/>
-      <c r="AD4" s="41"/>
-      <c r="AE4" s="41"/>
-      <c r="AF4" s="41"/>
-      <c r="AG4" s="41"/>
-      <c r="AH4" s="41"/>
-      <c r="AI4" s="41"/>
-      <c r="AJ4" s="41"/>
-      <c r="AK4" s="41"/>
-      <c r="AL4" s="41"/>
-      <c r="AM4" s="41"/>
-      <c r="AN4" s="41"/>
-      <c r="AO4" s="41"/>
-      <c r="AP4" s="41"/>
-      <c r="AQ4" s="41"/>
-      <c r="AR4" s="41"/>
-      <c r="AS4" s="41"/>
-      <c r="AT4" s="41"/>
-      <c r="AU4" s="41"/>
-      <c r="AV4" s="41"/>
-      <c r="AW4" s="41"/>
-      <c r="AX4" s="41"/>
-      <c r="AY4" s="41"/>
-      <c r="AZ4" s="41"/>
-      <c r="BA4" s="41"/>
-      <c r="BB4" s="41"/>
-      <c r="BC4" s="41"/>
-      <c r="BD4" s="41"/>
-      <c r="BE4" s="41"/>
-      <c r="BF4" s="41"/>
-      <c r="BG4" s="41"/>
-      <c r="BH4" s="41"/>
-      <c r="BI4" s="41"/>
-      <c r="BJ4" s="41"/>
-      <c r="BK4" s="41"/>
-      <c r="BL4" s="41"/>
-      <c r="BM4" s="41"/>
-      <c r="BN4" s="41"/>
-      <c r="BO4" s="41"/>
-      <c r="BP4" s="41"/>
-      <c r="BQ4" s="41"/>
-      <c r="BR4" s="41"/>
-      <c r="BS4" s="41"/>
-      <c r="BT4" s="41"/>
-      <c r="BU4" s="41"/>
-      <c r="BV4" s="41"/>
-      <c r="BW4" s="41"/>
-      <c r="BX4" s="41"/>
-      <c r="BY4" s="41"/>
-      <c r="BZ4" s="41"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="71"/>
+      <c r="K4" s="71"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="71"/>
+      <c r="N4" s="71"/>
+      <c r="O4" s="71"/>
+      <c r="P4" s="71"/>
+      <c r="Q4" s="71"/>
+      <c r="R4" s="71"/>
+      <c r="S4" s="71"/>
+      <c r="T4" s="71"/>
+      <c r="U4" s="71"/>
+      <c r="V4" s="71"/>
+      <c r="W4" s="71"/>
+      <c r="X4" s="71"/>
+      <c r="Y4" s="71"/>
+      <c r="Z4" s="71"/>
+      <c r="AA4" s="71"/>
+      <c r="AB4" s="71"/>
+      <c r="AC4" s="71"/>
+      <c r="AD4" s="71"/>
+      <c r="AE4" s="71"/>
+      <c r="AF4" s="71"/>
+      <c r="AG4" s="71"/>
+      <c r="AH4" s="71"/>
+      <c r="AI4" s="71"/>
+      <c r="AJ4" s="71"/>
+      <c r="AK4" s="71"/>
+      <c r="AL4" s="71"/>
+      <c r="AM4" s="71"/>
+      <c r="AN4" s="71"/>
+      <c r="AO4" s="71"/>
+      <c r="AP4" s="71"/>
+      <c r="AQ4" s="71"/>
+      <c r="AR4" s="71"/>
+      <c r="AS4" s="71"/>
+      <c r="AT4" s="71"/>
+      <c r="AU4" s="71"/>
+      <c r="AV4" s="71"/>
+      <c r="AW4" s="71"/>
+      <c r="AX4" s="71"/>
+      <c r="AY4" s="71"/>
+      <c r="AZ4" s="71"/>
+      <c r="BA4" s="71"/>
+      <c r="BB4" s="71"/>
+      <c r="BC4" s="71"/>
+      <c r="BD4" s="71"/>
+      <c r="BE4" s="71"/>
+      <c r="BF4" s="71"/>
+      <c r="BG4" s="71"/>
+      <c r="BH4" s="71"/>
+      <c r="BI4" s="71"/>
+      <c r="BJ4" s="71"/>
+      <c r="BK4" s="71"/>
+      <c r="BL4" s="71"/>
+      <c r="BM4" s="71"/>
+      <c r="BN4" s="71"/>
+      <c r="BO4" s="71"/>
+      <c r="BP4" s="71"/>
+      <c r="BQ4" s="71"/>
+      <c r="BR4" s="71"/>
+      <c r="BS4" s="71"/>
+      <c r="BT4" s="71"/>
+      <c r="BU4" s="71"/>
+      <c r="BV4" s="71"/>
+      <c r="BW4" s="71"/>
+      <c r="BX4" s="71"/>
+      <c r="BY4" s="71"/>
+      <c r="BZ4" s="71"/>
       <c r="CA4" s="12"/>
       <c r="CB4" s="12"/>
       <c r="CC4" s="12"/>
@@ -2018,7 +2468,7 @@
       <c r="CF4" s="12"/>
       <c r="CG4" s="12"/>
     </row>
-    <row r="5" spans="3:85" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:85" ht="15" customHeight="1" thickBot="1">
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
       <c r="E5" s="12"/>
@@ -2103,147 +2553,147 @@
       <c r="CF5" s="12"/>
       <c r="CG5" s="12"/>
     </row>
-    <row r="6" spans="3:85" x14ac:dyDescent="0.25">
-      <c r="I6" s="42" t="s">
+    <row r="6" spans="3:85">
+      <c r="I6" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="J6" s="43"/>
-      <c r="K6" s="43"/>
-      <c r="L6" s="43"/>
-      <c r="M6" s="43"/>
-      <c r="N6" s="44"/>
-      <c r="R6" s="42" t="s">
+      <c r="J6" s="73"/>
+      <c r="K6" s="73"/>
+      <c r="L6" s="73"/>
+      <c r="M6" s="73"/>
+      <c r="N6" s="74"/>
+      <c r="R6" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="S6" s="43"/>
-      <c r="T6" s="43"/>
-      <c r="U6" s="43"/>
-      <c r="V6" s="43"/>
-      <c r="W6" s="44"/>
-      <c r="AA6" s="42" t="s">
+      <c r="S6" s="73"/>
+      <c r="T6" s="73"/>
+      <c r="U6" s="73"/>
+      <c r="V6" s="73"/>
+      <c r="W6" s="74"/>
+      <c r="AA6" s="72" t="s">
         <v>62</v>
       </c>
-      <c r="AB6" s="43"/>
-      <c r="AC6" s="43"/>
-      <c r="AD6" s="43"/>
-      <c r="AE6" s="43"/>
-      <c r="AF6" s="44"/>
-      <c r="AJ6" s="42" t="s">
+      <c r="AB6" s="73"/>
+      <c r="AC6" s="73"/>
+      <c r="AD6" s="73"/>
+      <c r="AE6" s="73"/>
+      <c r="AF6" s="74"/>
+      <c r="AJ6" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="AK6" s="43"/>
-      <c r="AL6" s="43"/>
-      <c r="AM6" s="43"/>
-      <c r="AN6" s="43"/>
-      <c r="AO6" s="44"/>
-      <c r="AS6" s="42" t="s">
+      <c r="AK6" s="73"/>
+      <c r="AL6" s="73"/>
+      <c r="AM6" s="73"/>
+      <c r="AN6" s="73"/>
+      <c r="AO6" s="74"/>
+      <c r="AS6" s="72" t="s">
         <v>64</v>
       </c>
-      <c r="AT6" s="43"/>
-      <c r="AU6" s="43"/>
-      <c r="AV6" s="43"/>
-      <c r="AW6" s="43"/>
-      <c r="AX6" s="44"/>
-      <c r="BB6" s="42" t="s">
+      <c r="AT6" s="73"/>
+      <c r="AU6" s="73"/>
+      <c r="AV6" s="73"/>
+      <c r="AW6" s="73"/>
+      <c r="AX6" s="74"/>
+      <c r="BB6" s="72" t="s">
         <v>65</v>
       </c>
-      <c r="BC6" s="43"/>
-      <c r="BD6" s="43"/>
-      <c r="BE6" s="43"/>
-      <c r="BF6" s="43"/>
-      <c r="BG6" s="44"/>
-      <c r="BK6" s="42" t="s">
+      <c r="BC6" s="73"/>
+      <c r="BD6" s="73"/>
+      <c r="BE6" s="73"/>
+      <c r="BF6" s="73"/>
+      <c r="BG6" s="74"/>
+      <c r="BK6" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="BL6" s="43"/>
-      <c r="BM6" s="43"/>
-      <c r="BN6" s="43"/>
-      <c r="BO6" s="43"/>
-      <c r="BP6" s="44"/>
-      <c r="BT6" s="42" t="s">
+      <c r="BL6" s="73"/>
+      <c r="BM6" s="73"/>
+      <c r="BN6" s="73"/>
+      <c r="BO6" s="73"/>
+      <c r="BP6" s="74"/>
+      <c r="BT6" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="BU6" s="43"/>
-      <c r="BV6" s="43"/>
-      <c r="BW6" s="43"/>
-      <c r="BX6" s="43"/>
-      <c r="BY6" s="44"/>
-    </row>
-    <row r="7" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BU6" s="73"/>
+      <c r="BV6" s="73"/>
+      <c r="BW6" s="73"/>
+      <c r="BX6" s="73"/>
+      <c r="BY6" s="74"/>
+    </row>
+    <row r="7" spans="3:85" ht="15.75" thickBot="1">
       <c r="H7" s="23"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
-      <c r="L7" s="46"/>
-      <c r="M7" s="46"/>
-      <c r="N7" s="47"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="76"/>
+      <c r="K7" s="76"/>
+      <c r="L7" s="76"/>
+      <c r="M7" s="76"/>
+      <c r="N7" s="77"/>
       <c r="O7" s="23"/>
       <c r="P7" s="23"/>
       <c r="Q7" s="23"/>
-      <c r="R7" s="45"/>
-      <c r="S7" s="46"/>
-      <c r="T7" s="46"/>
-      <c r="U7" s="46"/>
-      <c r="V7" s="46"/>
-      <c r="W7" s="47"/>
+      <c r="R7" s="75"/>
+      <c r="S7" s="76"/>
+      <c r="T7" s="76"/>
+      <c r="U7" s="76"/>
+      <c r="V7" s="76"/>
+      <c r="W7" s="77"/>
       <c r="X7" s="23"/>
       <c r="Y7" s="23"/>
       <c r="Z7" s="23"/>
-      <c r="AA7" s="45"/>
-      <c r="AB7" s="46"/>
-      <c r="AC7" s="46"/>
-      <c r="AD7" s="46"/>
-      <c r="AE7" s="46"/>
-      <c r="AF7" s="47"/>
+      <c r="AA7" s="75"/>
+      <c r="AB7" s="76"/>
+      <c r="AC7" s="76"/>
+      <c r="AD7" s="76"/>
+      <c r="AE7" s="76"/>
+      <c r="AF7" s="77"/>
       <c r="AG7" s="23"/>
       <c r="AH7" s="23"/>
       <c r="AI7" s="23"/>
-      <c r="AJ7" s="45"/>
-      <c r="AK7" s="46"/>
-      <c r="AL7" s="46"/>
-      <c r="AM7" s="46"/>
-      <c r="AN7" s="46"/>
-      <c r="AO7" s="47"/>
+      <c r="AJ7" s="75"/>
+      <c r="AK7" s="76"/>
+      <c r="AL7" s="76"/>
+      <c r="AM7" s="76"/>
+      <c r="AN7" s="76"/>
+      <c r="AO7" s="77"/>
       <c r="AP7" s="23"/>
       <c r="AQ7" s="23"/>
       <c r="AR7" s="23"/>
-      <c r="AS7" s="45"/>
-      <c r="AT7" s="46"/>
-      <c r="AU7" s="46"/>
-      <c r="AV7" s="46"/>
-      <c r="AW7" s="46"/>
-      <c r="AX7" s="47"/>
+      <c r="AS7" s="75"/>
+      <c r="AT7" s="76"/>
+      <c r="AU7" s="76"/>
+      <c r="AV7" s="76"/>
+      <c r="AW7" s="76"/>
+      <c r="AX7" s="77"/>
       <c r="AY7" s="23"/>
       <c r="AZ7" s="23"/>
       <c r="BA7" s="23"/>
-      <c r="BB7" s="45"/>
-      <c r="BC7" s="46"/>
-      <c r="BD7" s="46"/>
-      <c r="BE7" s="46"/>
-      <c r="BF7" s="46"/>
-      <c r="BG7" s="47"/>
+      <c r="BB7" s="75"/>
+      <c r="BC7" s="76"/>
+      <c r="BD7" s="76"/>
+      <c r="BE7" s="76"/>
+      <c r="BF7" s="76"/>
+      <c r="BG7" s="77"/>
       <c r="BH7" s="23"/>
       <c r="BI7" s="23"/>
       <c r="BJ7" s="23"/>
-      <c r="BK7" s="45"/>
-      <c r="BL7" s="46"/>
-      <c r="BM7" s="46"/>
-      <c r="BN7" s="46"/>
-      <c r="BO7" s="46"/>
-      <c r="BP7" s="47"/>
+      <c r="BK7" s="75"/>
+      <c r="BL7" s="76"/>
+      <c r="BM7" s="76"/>
+      <c r="BN7" s="76"/>
+      <c r="BO7" s="76"/>
+      <c r="BP7" s="77"/>
       <c r="BQ7" s="23"/>
       <c r="BR7" s="23"/>
       <c r="BS7" s="23"/>
-      <c r="BT7" s="45"/>
-      <c r="BU7" s="46"/>
-      <c r="BV7" s="46"/>
-      <c r="BW7" s="46"/>
-      <c r="BX7" s="46"/>
-      <c r="BY7" s="47"/>
+      <c r="BT7" s="75"/>
+      <c r="BU7" s="76"/>
+      <c r="BV7" s="76"/>
+      <c r="BW7" s="76"/>
+      <c r="BX7" s="76"/>
+      <c r="BY7" s="77"/>
       <c r="BZ7" s="23"/>
       <c r="CA7" s="23"/>
     </row>
-    <row r="8" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:85" ht="15.75" thickBot="1">
       <c r="H8" s="23"/>
       <c r="I8" s="23"/>
       <c r="J8" s="23"/>
@@ -2280,155 +2730,155 @@
       <c r="BQ8" s="23"/>
       <c r="BR8" s="23"/>
     </row>
-    <row r="9" spans="3:85" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="58" t="s">
+    <row r="9" spans="3:85" ht="15" customHeight="1">
+      <c r="C9" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="65"/>
-      <c r="J9" s="65"/>
-      <c r="K9" s="65"/>
-      <c r="L9" s="65"/>
-      <c r="M9" s="65"/>
-      <c r="N9" s="65"/>
-      <c r="O9" s="66"/>
-      <c r="Q9" s="64"/>
-      <c r="R9" s="65"/>
-      <c r="S9" s="65"/>
-      <c r="T9" s="65"/>
-      <c r="U9" s="65"/>
-      <c r="V9" s="65"/>
-      <c r="W9" s="65"/>
-      <c r="X9" s="66"/>
-      <c r="Z9" s="64"/>
-      <c r="AA9" s="65"/>
-      <c r="AB9" s="65"/>
-      <c r="AC9" s="65"/>
-      <c r="AD9" s="65"/>
-      <c r="AE9" s="65"/>
-      <c r="AF9" s="65"/>
-      <c r="AG9" s="66"/>
-      <c r="AI9" s="64"/>
-      <c r="AJ9" s="65"/>
-      <c r="AK9" s="65"/>
-      <c r="AL9" s="65"/>
-      <c r="AM9" s="65"/>
-      <c r="AN9" s="65"/>
-      <c r="AO9" s="65"/>
-      <c r="AP9" s="66"/>
-      <c r="AR9" s="64"/>
-      <c r="AS9" s="65"/>
-      <c r="AT9" s="65"/>
-      <c r="AU9" s="65"/>
-      <c r="AV9" s="65"/>
-      <c r="AW9" s="65"/>
-      <c r="AX9" s="65"/>
-      <c r="AY9" s="66"/>
-      <c r="BA9" s="64"/>
-      <c r="BB9" s="65"/>
-      <c r="BC9" s="65"/>
-      <c r="BD9" s="65"/>
-      <c r="BE9" s="65"/>
-      <c r="BF9" s="65"/>
-      <c r="BG9" s="65"/>
-      <c r="BH9" s="66"/>
-      <c r="BJ9" s="48"/>
-      <c r="BK9" s="49"/>
-      <c r="BL9" s="49"/>
-      <c r="BM9" s="49"/>
-      <c r="BN9" s="49"/>
-      <c r="BO9" s="49"/>
-      <c r="BP9" s="49"/>
-      <c r="BQ9" s="50"/>
-      <c r="BS9" s="48"/>
-      <c r="BT9" s="49"/>
-      <c r="BU9" s="49"/>
-      <c r="BV9" s="49"/>
-      <c r="BW9" s="49"/>
-      <c r="BX9" s="49"/>
-      <c r="BY9" s="49"/>
-      <c r="BZ9" s="50"/>
-      <c r="CB9" s="72" t="s">
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="40"/>
+      <c r="M9" s="40"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="41"/>
+      <c r="Q9" s="39"/>
+      <c r="R9" s="40"/>
+      <c r="S9" s="40"/>
+      <c r="T9" s="40"/>
+      <c r="U9" s="40"/>
+      <c r="V9" s="40"/>
+      <c r="W9" s="40"/>
+      <c r="X9" s="41"/>
+      <c r="Z9" s="39"/>
+      <c r="AA9" s="40"/>
+      <c r="AB9" s="40"/>
+      <c r="AC9" s="40"/>
+      <c r="AD9" s="40"/>
+      <c r="AE9" s="40"/>
+      <c r="AF9" s="40"/>
+      <c r="AG9" s="41"/>
+      <c r="AI9" s="39"/>
+      <c r="AJ9" s="40"/>
+      <c r="AK9" s="40"/>
+      <c r="AL9" s="40"/>
+      <c r="AM9" s="40"/>
+      <c r="AN9" s="40"/>
+      <c r="AO9" s="40"/>
+      <c r="AP9" s="41"/>
+      <c r="AR9" s="39"/>
+      <c r="AS9" s="40"/>
+      <c r="AT9" s="40"/>
+      <c r="AU9" s="40"/>
+      <c r="AV9" s="40"/>
+      <c r="AW9" s="40"/>
+      <c r="AX9" s="40"/>
+      <c r="AY9" s="41"/>
+      <c r="BA9" s="39"/>
+      <c r="BB9" s="40"/>
+      <c r="BC9" s="40"/>
+      <c r="BD9" s="40"/>
+      <c r="BE9" s="40"/>
+      <c r="BF9" s="40"/>
+      <c r="BG9" s="40"/>
+      <c r="BH9" s="41"/>
+      <c r="BJ9" s="45"/>
+      <c r="BK9" s="46"/>
+      <c r="BL9" s="46"/>
+      <c r="BM9" s="46"/>
+      <c r="BN9" s="46"/>
+      <c r="BO9" s="46"/>
+      <c r="BP9" s="46"/>
+      <c r="BQ9" s="47"/>
+      <c r="BS9" s="45"/>
+      <c r="BT9" s="46"/>
+      <c r="BU9" s="46"/>
+      <c r="BV9" s="46"/>
+      <c r="BW9" s="46"/>
+      <c r="BX9" s="46"/>
+      <c r="BY9" s="46"/>
+      <c r="BZ9" s="47"/>
+      <c r="CB9" s="59" t="s">
         <v>49</v>
       </c>
-      <c r="CC9" s="73"/>
-      <c r="CD9" s="73"/>
-      <c r="CE9" s="73"/>
-      <c r="CF9" s="73"/>
-      <c r="CG9" s="74"/>
-    </row>
-    <row r="10" spans="3:85" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
-      <c r="H10" s="67"/>
-      <c r="I10" s="68"/>
-      <c r="J10" s="68"/>
-      <c r="K10" s="68"/>
-      <c r="L10" s="68"/>
-      <c r="M10" s="68"/>
-      <c r="N10" s="68"/>
-      <c r="O10" s="69"/>
-      <c r="Q10" s="67"/>
-      <c r="R10" s="68"/>
-      <c r="S10" s="68"/>
-      <c r="T10" s="68"/>
-      <c r="U10" s="68"/>
-      <c r="V10" s="68"/>
-      <c r="W10" s="68"/>
-      <c r="X10" s="69"/>
-      <c r="Z10" s="67"/>
-      <c r="AA10" s="68"/>
-      <c r="AB10" s="68"/>
-      <c r="AC10" s="68"/>
-      <c r="AD10" s="68"/>
-      <c r="AE10" s="68"/>
-      <c r="AF10" s="68"/>
-      <c r="AG10" s="69"/>
-      <c r="AI10" s="67"/>
-      <c r="AJ10" s="68"/>
-      <c r="AK10" s="68"/>
-      <c r="AL10" s="68"/>
-      <c r="AM10" s="68"/>
-      <c r="AN10" s="68"/>
-      <c r="AO10" s="68"/>
-      <c r="AP10" s="69"/>
-      <c r="AR10" s="67"/>
-      <c r="AS10" s="68"/>
-      <c r="AT10" s="68"/>
-      <c r="AU10" s="68"/>
-      <c r="AV10" s="68"/>
-      <c r="AW10" s="68"/>
-      <c r="AX10" s="68"/>
-      <c r="AY10" s="69"/>
-      <c r="BA10" s="67"/>
-      <c r="BB10" s="68"/>
-      <c r="BC10" s="68"/>
-      <c r="BD10" s="68"/>
-      <c r="BE10" s="68"/>
-      <c r="BF10" s="68"/>
-      <c r="BG10" s="68"/>
-      <c r="BH10" s="69"/>
-      <c r="BJ10" s="51"/>
-      <c r="BK10" s="52"/>
-      <c r="BL10" s="52"/>
-      <c r="BM10" s="52"/>
-      <c r="BN10" s="52"/>
-      <c r="BO10" s="52"/>
-      <c r="BP10" s="52"/>
-      <c r="BQ10" s="53"/>
-      <c r="BS10" s="51"/>
-      <c r="BT10" s="52"/>
-      <c r="BU10" s="52"/>
-      <c r="BV10" s="52"/>
-      <c r="BW10" s="52"/>
-      <c r="BX10" s="52"/>
-      <c r="BY10" s="52"/>
-      <c r="BZ10" s="53"/>
+      <c r="CC9" s="60"/>
+      <c r="CD9" s="60"/>
+      <c r="CE9" s="60"/>
+      <c r="CF9" s="60"/>
+      <c r="CG9" s="61"/>
+    </row>
+    <row r="10" spans="3:85" ht="15" customHeight="1">
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="43"/>
+      <c r="N10" s="43"/>
+      <c r="O10" s="44"/>
+      <c r="Q10" s="42"/>
+      <c r="R10" s="43"/>
+      <c r="S10" s="43"/>
+      <c r="T10" s="43"/>
+      <c r="U10" s="43"/>
+      <c r="V10" s="43"/>
+      <c r="W10" s="43"/>
+      <c r="X10" s="44"/>
+      <c r="Z10" s="42"/>
+      <c r="AA10" s="43"/>
+      <c r="AB10" s="43"/>
+      <c r="AC10" s="43"/>
+      <c r="AD10" s="43"/>
+      <c r="AE10" s="43"/>
+      <c r="AF10" s="43"/>
+      <c r="AG10" s="44"/>
+      <c r="AI10" s="42"/>
+      <c r="AJ10" s="43"/>
+      <c r="AK10" s="43"/>
+      <c r="AL10" s="43"/>
+      <c r="AM10" s="43"/>
+      <c r="AN10" s="43"/>
+      <c r="AO10" s="43"/>
+      <c r="AP10" s="44"/>
+      <c r="AR10" s="42"/>
+      <c r="AS10" s="43"/>
+      <c r="AT10" s="43"/>
+      <c r="AU10" s="43"/>
+      <c r="AV10" s="43"/>
+      <c r="AW10" s="43"/>
+      <c r="AX10" s="43"/>
+      <c r="AY10" s="44"/>
+      <c r="BA10" s="42"/>
+      <c r="BB10" s="43"/>
+      <c r="BC10" s="43"/>
+      <c r="BD10" s="43"/>
+      <c r="BE10" s="43"/>
+      <c r="BF10" s="43"/>
+      <c r="BG10" s="43"/>
+      <c r="BH10" s="44"/>
+      <c r="BJ10" s="48"/>
+      <c r="BK10" s="49"/>
+      <c r="BL10" s="49"/>
+      <c r="BM10" s="49"/>
+      <c r="BN10" s="49"/>
+      <c r="BO10" s="49"/>
+      <c r="BP10" s="49"/>
+      <c r="BQ10" s="50"/>
+      <c r="BS10" s="48"/>
+      <c r="BT10" s="49"/>
+      <c r="BU10" s="49"/>
+      <c r="BV10" s="49"/>
+      <c r="BW10" s="49"/>
+      <c r="BX10" s="49"/>
+      <c r="BY10" s="49"/>
+      <c r="BZ10" s="50"/>
       <c r="CB10" s="16" t="s">
         <v>18</v>
       </c>
@@ -2451,7 +2901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:85" ht="15.75" thickBot="1">
       <c r="H11" s="24" t="s">
         <v>18</v>
       </c>
@@ -2604,19 +3054,19 @@
         <f>SUM(BT11+BV11+BX11)*16</f>
         <v>0</v>
       </c>
-      <c r="CB11" s="77" t="s">
+      <c r="CB11" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="CC11" s="58"/>
-      <c r="CD11" s="58"/>
-      <c r="CE11" s="58">
+      <c r="CC11" s="51"/>
+      <c r="CD11" s="51"/>
+      <c r="CE11" s="51">
         <f ca="1">CE12*3*16</f>
         <v>0</v>
       </c>
-      <c r="CF11" s="58"/>
-      <c r="CG11" s="75"/>
-    </row>
-    <row r="12" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="CF11" s="51"/>
+      <c r="CG11" s="52"/>
+    </row>
+    <row r="12" spans="3:85" ht="15.75" thickBot="1">
       <c r="N12" s="28" t="s">
         <v>51</v>
       </c>
@@ -2673,168 +3123,168 @@
         <f>(BT11+BV11+BX11)/3</f>
         <v>0</v>
       </c>
-      <c r="CB12" s="76" t="s">
+      <c r="CB12" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="CC12" s="56"/>
-      <c r="CD12" s="56"/>
-      <c r="CE12" s="56">
+      <c r="CC12" s="54"/>
+      <c r="CD12" s="54"/>
+      <c r="CE12" s="54">
         <f ca="1">SUM(IF(MOD(COLUMN(O12:OFFSET(CE12,0,-1)) - COLUMN(O12), 9) = 0, O12:OFFSET(CE12,0,-1), 0))</f>
         <v>0</v>
       </c>
-      <c r="CF12" s="56"/>
-      <c r="CG12" s="57"/>
-    </row>
-    <row r="13" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="3:85" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="58" t="s">
+      <c r="CF12" s="54"/>
+      <c r="CG12" s="55"/>
+    </row>
+    <row r="13" spans="3:85" ht="15.75" thickBot="1"/>
+    <row r="14" spans="3:85" ht="15" customHeight="1">
+      <c r="C14" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="65"/>
-      <c r="K14" s="65"/>
-      <c r="L14" s="65"/>
-      <c r="M14" s="65"/>
-      <c r="N14" s="65"/>
-      <c r="O14" s="66"/>
-      <c r="Q14" s="64"/>
-      <c r="R14" s="65"/>
-      <c r="S14" s="65"/>
-      <c r="T14" s="65"/>
-      <c r="U14" s="65"/>
-      <c r="V14" s="65"/>
-      <c r="W14" s="65"/>
-      <c r="X14" s="66"/>
-      <c r="Z14" s="64"/>
-      <c r="AA14" s="65"/>
-      <c r="AB14" s="65"/>
-      <c r="AC14" s="65"/>
-      <c r="AD14" s="65"/>
-      <c r="AE14" s="65"/>
-      <c r="AF14" s="65"/>
-      <c r="AG14" s="66"/>
-      <c r="AI14" s="64"/>
-      <c r="AJ14" s="65"/>
-      <c r="AK14" s="65"/>
-      <c r="AL14" s="65"/>
-      <c r="AM14" s="65"/>
-      <c r="AN14" s="65"/>
-      <c r="AO14" s="65"/>
-      <c r="AP14" s="66"/>
-      <c r="AR14" s="64"/>
-      <c r="AS14" s="65"/>
-      <c r="AT14" s="65"/>
-      <c r="AU14" s="65"/>
-      <c r="AV14" s="65"/>
-      <c r="AW14" s="65"/>
-      <c r="AX14" s="65"/>
-      <c r="AY14" s="66"/>
-      <c r="BA14" s="64"/>
-      <c r="BB14" s="65"/>
-      <c r="BC14" s="65"/>
-      <c r="BD14" s="65"/>
-      <c r="BE14" s="65"/>
-      <c r="BF14" s="65"/>
-      <c r="BG14" s="65"/>
-      <c r="BH14" s="66"/>
-      <c r="BJ14" s="48"/>
-      <c r="BK14" s="49"/>
-      <c r="BL14" s="49"/>
-      <c r="BM14" s="49"/>
-      <c r="BN14" s="49"/>
-      <c r="BO14" s="49"/>
-      <c r="BP14" s="49"/>
-      <c r="BQ14" s="50"/>
-      <c r="BS14" s="48"/>
-      <c r="BT14" s="49"/>
-      <c r="BU14" s="49"/>
-      <c r="BV14" s="49"/>
-      <c r="BW14" s="49"/>
-      <c r="BX14" s="49"/>
-      <c r="BY14" s="49"/>
-      <c r="BZ14" s="50"/>
-      <c r="CB14" s="61" t="s">
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="40"/>
+      <c r="L14" s="40"/>
+      <c r="M14" s="40"/>
+      <c r="N14" s="40"/>
+      <c r="O14" s="41"/>
+      <c r="Q14" s="39"/>
+      <c r="R14" s="40"/>
+      <c r="S14" s="40"/>
+      <c r="T14" s="40"/>
+      <c r="U14" s="40"/>
+      <c r="V14" s="40"/>
+      <c r="W14" s="40"/>
+      <c r="X14" s="41"/>
+      <c r="Z14" s="39"/>
+      <c r="AA14" s="40"/>
+      <c r="AB14" s="40"/>
+      <c r="AC14" s="40"/>
+      <c r="AD14" s="40"/>
+      <c r="AE14" s="40"/>
+      <c r="AF14" s="40"/>
+      <c r="AG14" s="41"/>
+      <c r="AI14" s="39"/>
+      <c r="AJ14" s="40"/>
+      <c r="AK14" s="40"/>
+      <c r="AL14" s="40"/>
+      <c r="AM14" s="40"/>
+      <c r="AN14" s="40"/>
+      <c r="AO14" s="40"/>
+      <c r="AP14" s="41"/>
+      <c r="AR14" s="39"/>
+      <c r="AS14" s="40"/>
+      <c r="AT14" s="40"/>
+      <c r="AU14" s="40"/>
+      <c r="AV14" s="40"/>
+      <c r="AW14" s="40"/>
+      <c r="AX14" s="40"/>
+      <c r="AY14" s="41"/>
+      <c r="BA14" s="39"/>
+      <c r="BB14" s="40"/>
+      <c r="BC14" s="40"/>
+      <c r="BD14" s="40"/>
+      <c r="BE14" s="40"/>
+      <c r="BF14" s="40"/>
+      <c r="BG14" s="40"/>
+      <c r="BH14" s="41"/>
+      <c r="BJ14" s="45"/>
+      <c r="BK14" s="46"/>
+      <c r="BL14" s="46"/>
+      <c r="BM14" s="46"/>
+      <c r="BN14" s="46"/>
+      <c r="BO14" s="46"/>
+      <c r="BP14" s="46"/>
+      <c r="BQ14" s="47"/>
+      <c r="BS14" s="45"/>
+      <c r="BT14" s="46"/>
+      <c r="BU14" s="46"/>
+      <c r="BV14" s="46"/>
+      <c r="BW14" s="46"/>
+      <c r="BX14" s="46"/>
+      <c r="BY14" s="46"/>
+      <c r="BZ14" s="47"/>
+      <c r="CB14" s="62" t="s">
         <v>52</v>
       </c>
-      <c r="CC14" s="62"/>
-      <c r="CD14" s="62"/>
-      <c r="CE14" s="62"/>
-      <c r="CF14" s="62"/>
-      <c r="CG14" s="63"/>
-    </row>
-    <row r="15" spans="3:85" x14ac:dyDescent="0.25">
-      <c r="C15" s="58"/>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="58"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="68"/>
-      <c r="J15" s="68"/>
-      <c r="K15" s="68"/>
-      <c r="L15" s="68"/>
-      <c r="M15" s="68"/>
-      <c r="N15" s="68"/>
-      <c r="O15" s="69"/>
-      <c r="Q15" s="67"/>
-      <c r="R15" s="68"/>
-      <c r="S15" s="68"/>
-      <c r="T15" s="68"/>
-      <c r="U15" s="68"/>
-      <c r="V15" s="68"/>
-      <c r="W15" s="68"/>
-      <c r="X15" s="69"/>
-      <c r="Z15" s="67"/>
-      <c r="AA15" s="68"/>
-      <c r="AB15" s="68"/>
-      <c r="AC15" s="68"/>
-      <c r="AD15" s="68"/>
-      <c r="AE15" s="68"/>
-      <c r="AF15" s="68"/>
-      <c r="AG15" s="69"/>
-      <c r="AI15" s="67"/>
-      <c r="AJ15" s="68"/>
-      <c r="AK15" s="68"/>
-      <c r="AL15" s="68"/>
-      <c r="AM15" s="68"/>
-      <c r="AN15" s="68"/>
-      <c r="AO15" s="68"/>
-      <c r="AP15" s="69"/>
-      <c r="AR15" s="67"/>
-      <c r="AS15" s="68"/>
-      <c r="AT15" s="68"/>
-      <c r="AU15" s="68"/>
-      <c r="AV15" s="68"/>
-      <c r="AW15" s="68"/>
-      <c r="AX15" s="68"/>
-      <c r="AY15" s="69"/>
-      <c r="BA15" s="67"/>
-      <c r="BB15" s="68"/>
-      <c r="BC15" s="68"/>
-      <c r="BD15" s="68"/>
-      <c r="BE15" s="68"/>
-      <c r="BF15" s="68"/>
-      <c r="BG15" s="68"/>
-      <c r="BH15" s="69"/>
-      <c r="BJ15" s="51"/>
-      <c r="BK15" s="52"/>
-      <c r="BL15" s="52"/>
-      <c r="BM15" s="52"/>
-      <c r="BN15" s="52"/>
-      <c r="BO15" s="52"/>
-      <c r="BP15" s="52"/>
-      <c r="BQ15" s="53"/>
-      <c r="BS15" s="51"/>
-      <c r="BT15" s="52"/>
-      <c r="BU15" s="52"/>
-      <c r="BV15" s="52"/>
-      <c r="BW15" s="52"/>
-      <c r="BX15" s="52"/>
-      <c r="BY15" s="52"/>
-      <c r="BZ15" s="53"/>
+      <c r="CC14" s="63"/>
+      <c r="CD14" s="63"/>
+      <c r="CE14" s="63"/>
+      <c r="CF14" s="63"/>
+      <c r="CG14" s="64"/>
+    </row>
+    <row r="15" spans="3:85">
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="43"/>
+      <c r="L15" s="43"/>
+      <c r="M15" s="43"/>
+      <c r="N15" s="43"/>
+      <c r="O15" s="44"/>
+      <c r="Q15" s="42"/>
+      <c r="R15" s="43"/>
+      <c r="S15" s="43"/>
+      <c r="T15" s="43"/>
+      <c r="U15" s="43"/>
+      <c r="V15" s="43"/>
+      <c r="W15" s="43"/>
+      <c r="X15" s="44"/>
+      <c r="Z15" s="42"/>
+      <c r="AA15" s="43"/>
+      <c r="AB15" s="43"/>
+      <c r="AC15" s="43"/>
+      <c r="AD15" s="43"/>
+      <c r="AE15" s="43"/>
+      <c r="AF15" s="43"/>
+      <c r="AG15" s="44"/>
+      <c r="AI15" s="42"/>
+      <c r="AJ15" s="43"/>
+      <c r="AK15" s="43"/>
+      <c r="AL15" s="43"/>
+      <c r="AM15" s="43"/>
+      <c r="AN15" s="43"/>
+      <c r="AO15" s="43"/>
+      <c r="AP15" s="44"/>
+      <c r="AR15" s="42"/>
+      <c r="AS15" s="43"/>
+      <c r="AT15" s="43"/>
+      <c r="AU15" s="43"/>
+      <c r="AV15" s="43"/>
+      <c r="AW15" s="43"/>
+      <c r="AX15" s="43"/>
+      <c r="AY15" s="44"/>
+      <c r="BA15" s="42"/>
+      <c r="BB15" s="43"/>
+      <c r="BC15" s="43"/>
+      <c r="BD15" s="43"/>
+      <c r="BE15" s="43"/>
+      <c r="BF15" s="43"/>
+      <c r="BG15" s="43"/>
+      <c r="BH15" s="44"/>
+      <c r="BJ15" s="48"/>
+      <c r="BK15" s="49"/>
+      <c r="BL15" s="49"/>
+      <c r="BM15" s="49"/>
+      <c r="BN15" s="49"/>
+      <c r="BO15" s="49"/>
+      <c r="BP15" s="49"/>
+      <c r="BQ15" s="50"/>
+      <c r="BS15" s="48"/>
+      <c r="BT15" s="49"/>
+      <c r="BU15" s="49"/>
+      <c r="BV15" s="49"/>
+      <c r="BW15" s="49"/>
+      <c r="BX15" s="49"/>
+      <c r="BY15" s="49"/>
+      <c r="BZ15" s="50"/>
       <c r="CB15" s="16" t="s">
         <v>18</v>
       </c>
@@ -2857,7 +3307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:85" ht="15.75" thickBot="1">
       <c r="H16" s="24" t="s">
         <v>18</v>
       </c>
@@ -3010,19 +3460,19 @@
         <f>SUM(BT16+BV16+BX16)*16</f>
         <v>0</v>
       </c>
-      <c r="CB16" s="60" t="s">
+      <c r="CB16" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="CC16" s="58"/>
-      <c r="CD16" s="58"/>
-      <c r="CE16" s="58">
+      <c r="CC16" s="51"/>
+      <c r="CD16" s="51"/>
+      <c r="CE16" s="51">
         <f ca="1">CE17*3*16</f>
         <v>0</v>
       </c>
-      <c r="CF16" s="58"/>
-      <c r="CG16" s="59"/>
-    </row>
-    <row r="17" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="CF16" s="51"/>
+      <c r="CG16" s="68"/>
+    </row>
+    <row r="17" spans="3:85" ht="15.75" thickBot="1">
       <c r="N17" s="28" t="s">
         <v>51</v>
       </c>
@@ -3079,168 +3529,168 @@
         <f>(BT16+BV16+BX16)/3</f>
         <v>0</v>
       </c>
-      <c r="CB17" s="54" t="s">
+      <c r="CB17" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="CC17" s="55"/>
-      <c r="CD17" s="55"/>
-      <c r="CE17" s="56">
+      <c r="CC17" s="67"/>
+      <c r="CD17" s="67"/>
+      <c r="CE17" s="54">
         <f ca="1">SUM(IF(MOD(COLUMN(O17:OFFSET(CE17,0,-1)) - COLUMN(O17), 9) = 0, O17:OFFSET(CE17,0,-1), 0))</f>
         <v>0</v>
       </c>
-      <c r="CF17" s="56"/>
-      <c r="CG17" s="57"/>
-    </row>
-    <row r="18" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="3:85" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="58" t="s">
+      <c r="CF17" s="54"/>
+      <c r="CG17" s="55"/>
+    </row>
+    <row r="18" spans="3:85" ht="15.75" thickBot="1"/>
+    <row r="19" spans="3:85" ht="15" customHeight="1">
+      <c r="C19" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="58"/>
-      <c r="E19" s="58"/>
-      <c r="F19" s="58"/>
-      <c r="H19" s="64"/>
-      <c r="I19" s="65"/>
-      <c r="J19" s="65"/>
-      <c r="K19" s="65"/>
-      <c r="L19" s="65"/>
-      <c r="M19" s="65"/>
-      <c r="N19" s="65"/>
-      <c r="O19" s="66"/>
-      <c r="Q19" s="64"/>
-      <c r="R19" s="65"/>
-      <c r="S19" s="65"/>
-      <c r="T19" s="65"/>
-      <c r="U19" s="65"/>
-      <c r="V19" s="65"/>
-      <c r="W19" s="65"/>
-      <c r="X19" s="66"/>
-      <c r="Z19" s="64"/>
-      <c r="AA19" s="65"/>
-      <c r="AB19" s="65"/>
-      <c r="AC19" s="65"/>
-      <c r="AD19" s="65"/>
-      <c r="AE19" s="65"/>
-      <c r="AF19" s="65"/>
-      <c r="AG19" s="66"/>
-      <c r="AI19" s="64"/>
-      <c r="AJ19" s="65"/>
-      <c r="AK19" s="65"/>
-      <c r="AL19" s="65"/>
-      <c r="AM19" s="65"/>
-      <c r="AN19" s="65"/>
-      <c r="AO19" s="65"/>
-      <c r="AP19" s="66"/>
-      <c r="AR19" s="64"/>
-      <c r="AS19" s="65"/>
-      <c r="AT19" s="65"/>
-      <c r="AU19" s="65"/>
-      <c r="AV19" s="65"/>
-      <c r="AW19" s="65"/>
-      <c r="AX19" s="65"/>
-      <c r="AY19" s="66"/>
-      <c r="BA19" s="64"/>
-      <c r="BB19" s="65"/>
-      <c r="BC19" s="65"/>
-      <c r="BD19" s="65"/>
-      <c r="BE19" s="65"/>
-      <c r="BF19" s="65"/>
-      <c r="BG19" s="65"/>
-      <c r="BH19" s="66"/>
-      <c r="BJ19" s="48"/>
-      <c r="BK19" s="49"/>
-      <c r="BL19" s="49"/>
-      <c r="BM19" s="49"/>
-      <c r="BN19" s="49"/>
-      <c r="BO19" s="49"/>
-      <c r="BP19" s="49"/>
-      <c r="BQ19" s="50"/>
-      <c r="BS19" s="48"/>
-      <c r="BT19" s="49"/>
-      <c r="BU19" s="49"/>
-      <c r="BV19" s="49"/>
-      <c r="BW19" s="49"/>
-      <c r="BX19" s="49"/>
-      <c r="BY19" s="49"/>
-      <c r="BZ19" s="50"/>
-      <c r="CB19" s="61" t="s">
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="40"/>
+      <c r="K19" s="40"/>
+      <c r="L19" s="40"/>
+      <c r="M19" s="40"/>
+      <c r="N19" s="40"/>
+      <c r="O19" s="41"/>
+      <c r="Q19" s="39"/>
+      <c r="R19" s="40"/>
+      <c r="S19" s="40"/>
+      <c r="T19" s="40"/>
+      <c r="U19" s="40"/>
+      <c r="V19" s="40"/>
+      <c r="W19" s="40"/>
+      <c r="X19" s="41"/>
+      <c r="Z19" s="39"/>
+      <c r="AA19" s="40"/>
+      <c r="AB19" s="40"/>
+      <c r="AC19" s="40"/>
+      <c r="AD19" s="40"/>
+      <c r="AE19" s="40"/>
+      <c r="AF19" s="40"/>
+      <c r="AG19" s="41"/>
+      <c r="AI19" s="39"/>
+      <c r="AJ19" s="40"/>
+      <c r="AK19" s="40"/>
+      <c r="AL19" s="40"/>
+      <c r="AM19" s="40"/>
+      <c r="AN19" s="40"/>
+      <c r="AO19" s="40"/>
+      <c r="AP19" s="41"/>
+      <c r="AR19" s="39"/>
+      <c r="AS19" s="40"/>
+      <c r="AT19" s="40"/>
+      <c r="AU19" s="40"/>
+      <c r="AV19" s="40"/>
+      <c r="AW19" s="40"/>
+      <c r="AX19" s="40"/>
+      <c r="AY19" s="41"/>
+      <c r="BA19" s="39"/>
+      <c r="BB19" s="40"/>
+      <c r="BC19" s="40"/>
+      <c r="BD19" s="40"/>
+      <c r="BE19" s="40"/>
+      <c r="BF19" s="40"/>
+      <c r="BG19" s="40"/>
+      <c r="BH19" s="41"/>
+      <c r="BJ19" s="45"/>
+      <c r="BK19" s="46"/>
+      <c r="BL19" s="46"/>
+      <c r="BM19" s="46"/>
+      <c r="BN19" s="46"/>
+      <c r="BO19" s="46"/>
+      <c r="BP19" s="46"/>
+      <c r="BQ19" s="47"/>
+      <c r="BS19" s="45"/>
+      <c r="BT19" s="46"/>
+      <c r="BU19" s="46"/>
+      <c r="BV19" s="46"/>
+      <c r="BW19" s="46"/>
+      <c r="BX19" s="46"/>
+      <c r="BY19" s="46"/>
+      <c r="BZ19" s="47"/>
+      <c r="CB19" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="CC19" s="62"/>
-      <c r="CD19" s="62"/>
-      <c r="CE19" s="62"/>
-      <c r="CF19" s="62"/>
-      <c r="CG19" s="63"/>
-    </row>
-    <row r="20" spans="3:85" x14ac:dyDescent="0.25">
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="H20" s="67"/>
-      <c r="I20" s="68"/>
-      <c r="J20" s="68"/>
-      <c r="K20" s="68"/>
-      <c r="L20" s="68"/>
-      <c r="M20" s="68"/>
-      <c r="N20" s="68"/>
-      <c r="O20" s="69"/>
-      <c r="Q20" s="67"/>
-      <c r="R20" s="68"/>
-      <c r="S20" s="68"/>
-      <c r="T20" s="68"/>
-      <c r="U20" s="68"/>
-      <c r="V20" s="68"/>
-      <c r="W20" s="68"/>
-      <c r="X20" s="69"/>
-      <c r="Z20" s="67"/>
-      <c r="AA20" s="68"/>
-      <c r="AB20" s="68"/>
-      <c r="AC20" s="68"/>
-      <c r="AD20" s="68"/>
-      <c r="AE20" s="68"/>
-      <c r="AF20" s="68"/>
-      <c r="AG20" s="69"/>
-      <c r="AI20" s="67"/>
-      <c r="AJ20" s="68"/>
-      <c r="AK20" s="68"/>
-      <c r="AL20" s="68"/>
-      <c r="AM20" s="68"/>
-      <c r="AN20" s="68"/>
-      <c r="AO20" s="68"/>
-      <c r="AP20" s="69"/>
-      <c r="AR20" s="67"/>
-      <c r="AS20" s="68"/>
-      <c r="AT20" s="68"/>
-      <c r="AU20" s="68"/>
-      <c r="AV20" s="68"/>
-      <c r="AW20" s="68"/>
-      <c r="AX20" s="68"/>
-      <c r="AY20" s="69"/>
-      <c r="BA20" s="67"/>
-      <c r="BB20" s="68"/>
-      <c r="BC20" s="68"/>
-      <c r="BD20" s="68"/>
-      <c r="BE20" s="68"/>
-      <c r="BF20" s="68"/>
-      <c r="BG20" s="68"/>
-      <c r="BH20" s="69"/>
-      <c r="BJ20" s="51"/>
-      <c r="BK20" s="52"/>
-      <c r="BL20" s="52"/>
-      <c r="BM20" s="52"/>
-      <c r="BN20" s="52"/>
-      <c r="BO20" s="52"/>
-      <c r="BP20" s="52"/>
-      <c r="BQ20" s="53"/>
-      <c r="BS20" s="51"/>
-      <c r="BT20" s="52"/>
-      <c r="BU20" s="52"/>
-      <c r="BV20" s="52"/>
-      <c r="BW20" s="52"/>
-      <c r="BX20" s="52"/>
-      <c r="BY20" s="52"/>
-      <c r="BZ20" s="53"/>
+      <c r="CC19" s="63"/>
+      <c r="CD19" s="63"/>
+      <c r="CE19" s="63"/>
+      <c r="CF19" s="63"/>
+      <c r="CG19" s="64"/>
+    </row>
+    <row r="20" spans="3:85">
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="43"/>
+      <c r="M20" s="43"/>
+      <c r="N20" s="43"/>
+      <c r="O20" s="44"/>
+      <c r="Q20" s="42"/>
+      <c r="R20" s="43"/>
+      <c r="S20" s="43"/>
+      <c r="T20" s="43"/>
+      <c r="U20" s="43"/>
+      <c r="V20" s="43"/>
+      <c r="W20" s="43"/>
+      <c r="X20" s="44"/>
+      <c r="Z20" s="42"/>
+      <c r="AA20" s="43"/>
+      <c r="AB20" s="43"/>
+      <c r="AC20" s="43"/>
+      <c r="AD20" s="43"/>
+      <c r="AE20" s="43"/>
+      <c r="AF20" s="43"/>
+      <c r="AG20" s="44"/>
+      <c r="AI20" s="42"/>
+      <c r="AJ20" s="43"/>
+      <c r="AK20" s="43"/>
+      <c r="AL20" s="43"/>
+      <c r="AM20" s="43"/>
+      <c r="AN20" s="43"/>
+      <c r="AO20" s="43"/>
+      <c r="AP20" s="44"/>
+      <c r="AR20" s="42"/>
+      <c r="AS20" s="43"/>
+      <c r="AT20" s="43"/>
+      <c r="AU20" s="43"/>
+      <c r="AV20" s="43"/>
+      <c r="AW20" s="43"/>
+      <c r="AX20" s="43"/>
+      <c r="AY20" s="44"/>
+      <c r="BA20" s="42"/>
+      <c r="BB20" s="43"/>
+      <c r="BC20" s="43"/>
+      <c r="BD20" s="43"/>
+      <c r="BE20" s="43"/>
+      <c r="BF20" s="43"/>
+      <c r="BG20" s="43"/>
+      <c r="BH20" s="44"/>
+      <c r="BJ20" s="48"/>
+      <c r="BK20" s="49"/>
+      <c r="BL20" s="49"/>
+      <c r="BM20" s="49"/>
+      <c r="BN20" s="49"/>
+      <c r="BO20" s="49"/>
+      <c r="BP20" s="49"/>
+      <c r="BQ20" s="50"/>
+      <c r="BS20" s="48"/>
+      <c r="BT20" s="49"/>
+      <c r="BU20" s="49"/>
+      <c r="BV20" s="49"/>
+      <c r="BW20" s="49"/>
+      <c r="BX20" s="49"/>
+      <c r="BY20" s="49"/>
+      <c r="BZ20" s="50"/>
       <c r="CB20" s="16" t="s">
         <v>18</v>
       </c>
@@ -3263,7 +3713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:85" ht="15.75" thickBot="1">
       <c r="H21" s="24" t="s">
         <v>18</v>
       </c>
@@ -3416,19 +3866,19 @@
         <f>SUM(BT21+BV21+BX21)*16</f>
         <v>0</v>
       </c>
-      <c r="CB21" s="60" t="s">
+      <c r="CB21" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="CC21" s="58"/>
-      <c r="CD21" s="58"/>
-      <c r="CE21" s="58">
+      <c r="CC21" s="51"/>
+      <c r="CD21" s="51"/>
+      <c r="CE21" s="51">
         <f ca="1">CE22*3*16</f>
         <v>0</v>
       </c>
-      <c r="CF21" s="58"/>
-      <c r="CG21" s="59"/>
-    </row>
-    <row r="22" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="CF21" s="51"/>
+      <c r="CG21" s="68"/>
+    </row>
+    <row r="22" spans="3:85" ht="15.75" thickBot="1">
       <c r="N22" s="28" t="s">
         <v>51</v>
       </c>
@@ -3485,168 +3935,168 @@
         <f>(BT21+BV21+BX21)/3</f>
         <v>0</v>
       </c>
-      <c r="CB22" s="54" t="s">
+      <c r="CB22" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="CC22" s="55"/>
-      <c r="CD22" s="55"/>
-      <c r="CE22" s="56">
+      <c r="CC22" s="67"/>
+      <c r="CD22" s="67"/>
+      <c r="CE22" s="54">
         <f ca="1">SUM(IF(MOD(COLUMN(O22:OFFSET(CE22,0,-1)) - COLUMN(O22), 9) = 0, O22:OFFSET(CE22,0,-1), 0))</f>
         <v>0</v>
       </c>
-      <c r="CF22" s="56"/>
-      <c r="CG22" s="57"/>
-    </row>
-    <row r="23" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="3:85" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C24" s="58" t="s">
+      <c r="CF22" s="54"/>
+      <c r="CG22" s="55"/>
+    </row>
+    <row r="23" spans="3:85" ht="15.75" thickBot="1"/>
+    <row r="24" spans="3:85" ht="15" customHeight="1">
+      <c r="C24" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="58"/>
-      <c r="H24" s="64"/>
-      <c r="I24" s="65"/>
-      <c r="J24" s="65"/>
-      <c r="K24" s="65"/>
-      <c r="L24" s="65"/>
-      <c r="M24" s="65"/>
-      <c r="N24" s="65"/>
-      <c r="O24" s="66"/>
-      <c r="Q24" s="64"/>
-      <c r="R24" s="65"/>
-      <c r="S24" s="65"/>
-      <c r="T24" s="65"/>
-      <c r="U24" s="65"/>
-      <c r="V24" s="65"/>
-      <c r="W24" s="65"/>
-      <c r="X24" s="66"/>
-      <c r="Z24" s="64"/>
-      <c r="AA24" s="65"/>
-      <c r="AB24" s="65"/>
-      <c r="AC24" s="65"/>
-      <c r="AD24" s="65"/>
-      <c r="AE24" s="65"/>
-      <c r="AF24" s="65"/>
-      <c r="AG24" s="66"/>
-      <c r="AI24" s="64"/>
-      <c r="AJ24" s="65"/>
-      <c r="AK24" s="65"/>
-      <c r="AL24" s="65"/>
-      <c r="AM24" s="65"/>
-      <c r="AN24" s="65"/>
-      <c r="AO24" s="65"/>
-      <c r="AP24" s="66"/>
-      <c r="AR24" s="64"/>
-      <c r="AS24" s="65"/>
-      <c r="AT24" s="65"/>
-      <c r="AU24" s="65"/>
-      <c r="AV24" s="65"/>
-      <c r="AW24" s="65"/>
-      <c r="AX24" s="65"/>
-      <c r="AY24" s="66"/>
-      <c r="BA24" s="64"/>
-      <c r="BB24" s="65"/>
-      <c r="BC24" s="65"/>
-      <c r="BD24" s="65"/>
-      <c r="BE24" s="65"/>
-      <c r="BF24" s="65"/>
-      <c r="BG24" s="65"/>
-      <c r="BH24" s="66"/>
-      <c r="BJ24" s="48"/>
-      <c r="BK24" s="49"/>
-      <c r="BL24" s="49"/>
-      <c r="BM24" s="49"/>
-      <c r="BN24" s="49"/>
-      <c r="BO24" s="49"/>
-      <c r="BP24" s="49"/>
-      <c r="BQ24" s="50"/>
-      <c r="BS24" s="48"/>
-      <c r="BT24" s="49"/>
-      <c r="BU24" s="49"/>
-      <c r="BV24" s="49"/>
-      <c r="BW24" s="49"/>
-      <c r="BX24" s="49"/>
-      <c r="BY24" s="49"/>
-      <c r="BZ24" s="50"/>
-      <c r="CB24" s="61" t="s">
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="40"/>
+      <c r="K24" s="40"/>
+      <c r="L24" s="40"/>
+      <c r="M24" s="40"/>
+      <c r="N24" s="40"/>
+      <c r="O24" s="41"/>
+      <c r="Q24" s="39"/>
+      <c r="R24" s="40"/>
+      <c r="S24" s="40"/>
+      <c r="T24" s="40"/>
+      <c r="U24" s="40"/>
+      <c r="V24" s="40"/>
+      <c r="W24" s="40"/>
+      <c r="X24" s="41"/>
+      <c r="Z24" s="39"/>
+      <c r="AA24" s="40"/>
+      <c r="AB24" s="40"/>
+      <c r="AC24" s="40"/>
+      <c r="AD24" s="40"/>
+      <c r="AE24" s="40"/>
+      <c r="AF24" s="40"/>
+      <c r="AG24" s="41"/>
+      <c r="AI24" s="39"/>
+      <c r="AJ24" s="40"/>
+      <c r="AK24" s="40"/>
+      <c r="AL24" s="40"/>
+      <c r="AM24" s="40"/>
+      <c r="AN24" s="40"/>
+      <c r="AO24" s="40"/>
+      <c r="AP24" s="41"/>
+      <c r="AR24" s="39"/>
+      <c r="AS24" s="40"/>
+      <c r="AT24" s="40"/>
+      <c r="AU24" s="40"/>
+      <c r="AV24" s="40"/>
+      <c r="AW24" s="40"/>
+      <c r="AX24" s="40"/>
+      <c r="AY24" s="41"/>
+      <c r="BA24" s="39"/>
+      <c r="BB24" s="40"/>
+      <c r="BC24" s="40"/>
+      <c r="BD24" s="40"/>
+      <c r="BE24" s="40"/>
+      <c r="BF24" s="40"/>
+      <c r="BG24" s="40"/>
+      <c r="BH24" s="41"/>
+      <c r="BJ24" s="45"/>
+      <c r="BK24" s="46"/>
+      <c r="BL24" s="46"/>
+      <c r="BM24" s="46"/>
+      <c r="BN24" s="46"/>
+      <c r="BO24" s="46"/>
+      <c r="BP24" s="46"/>
+      <c r="BQ24" s="47"/>
+      <c r="BS24" s="45"/>
+      <c r="BT24" s="46"/>
+      <c r="BU24" s="46"/>
+      <c r="BV24" s="46"/>
+      <c r="BW24" s="46"/>
+      <c r="BX24" s="46"/>
+      <c r="BY24" s="46"/>
+      <c r="BZ24" s="47"/>
+      <c r="CB24" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="CC24" s="62"/>
-      <c r="CD24" s="62"/>
-      <c r="CE24" s="62"/>
-      <c r="CF24" s="62"/>
-      <c r="CG24" s="63"/>
-    </row>
-    <row r="25" spans="3:85" x14ac:dyDescent="0.25">
-      <c r="C25" s="58"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="58"/>
-      <c r="H25" s="67"/>
-      <c r="I25" s="68"/>
-      <c r="J25" s="68"/>
-      <c r="K25" s="68"/>
-      <c r="L25" s="68"/>
-      <c r="M25" s="68"/>
-      <c r="N25" s="68"/>
-      <c r="O25" s="69"/>
-      <c r="Q25" s="67"/>
-      <c r="R25" s="68"/>
-      <c r="S25" s="68"/>
-      <c r="T25" s="68"/>
-      <c r="U25" s="68"/>
-      <c r="V25" s="68"/>
-      <c r="W25" s="68"/>
-      <c r="X25" s="69"/>
-      <c r="Z25" s="67"/>
-      <c r="AA25" s="68"/>
-      <c r="AB25" s="68"/>
-      <c r="AC25" s="68"/>
-      <c r="AD25" s="68"/>
-      <c r="AE25" s="68"/>
-      <c r="AF25" s="68"/>
-      <c r="AG25" s="69"/>
-      <c r="AI25" s="67"/>
-      <c r="AJ25" s="68"/>
-      <c r="AK25" s="68"/>
-      <c r="AL25" s="68"/>
-      <c r="AM25" s="68"/>
-      <c r="AN25" s="68"/>
-      <c r="AO25" s="68"/>
-      <c r="AP25" s="69"/>
-      <c r="AR25" s="67"/>
-      <c r="AS25" s="68"/>
-      <c r="AT25" s="68"/>
-      <c r="AU25" s="68"/>
-      <c r="AV25" s="68"/>
-      <c r="AW25" s="68"/>
-      <c r="AX25" s="68"/>
-      <c r="AY25" s="69"/>
-      <c r="BA25" s="67"/>
-      <c r="BB25" s="68"/>
-      <c r="BC25" s="68"/>
-      <c r="BD25" s="68"/>
-      <c r="BE25" s="68"/>
-      <c r="BF25" s="68"/>
-      <c r="BG25" s="68"/>
-      <c r="BH25" s="69"/>
-      <c r="BJ25" s="51"/>
-      <c r="BK25" s="52"/>
-      <c r="BL25" s="52"/>
-      <c r="BM25" s="52"/>
-      <c r="BN25" s="52"/>
-      <c r="BO25" s="52"/>
-      <c r="BP25" s="52"/>
-      <c r="BQ25" s="53"/>
-      <c r="BS25" s="51"/>
-      <c r="BT25" s="52"/>
-      <c r="BU25" s="52"/>
-      <c r="BV25" s="52"/>
-      <c r="BW25" s="52"/>
-      <c r="BX25" s="52"/>
-      <c r="BY25" s="52"/>
-      <c r="BZ25" s="53"/>
+      <c r="CC24" s="63"/>
+      <c r="CD24" s="63"/>
+      <c r="CE24" s="63"/>
+      <c r="CF24" s="63"/>
+      <c r="CG24" s="64"/>
+    </row>
+    <row r="25" spans="3:85">
+      <c r="C25" s="51"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="51"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+      <c r="L25" s="43"/>
+      <c r="M25" s="43"/>
+      <c r="N25" s="43"/>
+      <c r="O25" s="44"/>
+      <c r="Q25" s="42"/>
+      <c r="R25" s="43"/>
+      <c r="S25" s="43"/>
+      <c r="T25" s="43"/>
+      <c r="U25" s="43"/>
+      <c r="V25" s="43"/>
+      <c r="W25" s="43"/>
+      <c r="X25" s="44"/>
+      <c r="Z25" s="42"/>
+      <c r="AA25" s="43"/>
+      <c r="AB25" s="43"/>
+      <c r="AC25" s="43"/>
+      <c r="AD25" s="43"/>
+      <c r="AE25" s="43"/>
+      <c r="AF25" s="43"/>
+      <c r="AG25" s="44"/>
+      <c r="AI25" s="42"/>
+      <c r="AJ25" s="43"/>
+      <c r="AK25" s="43"/>
+      <c r="AL25" s="43"/>
+      <c r="AM25" s="43"/>
+      <c r="AN25" s="43"/>
+      <c r="AO25" s="43"/>
+      <c r="AP25" s="44"/>
+      <c r="AR25" s="42"/>
+      <c r="AS25" s="43"/>
+      <c r="AT25" s="43"/>
+      <c r="AU25" s="43"/>
+      <c r="AV25" s="43"/>
+      <c r="AW25" s="43"/>
+      <c r="AX25" s="43"/>
+      <c r="AY25" s="44"/>
+      <c r="BA25" s="42"/>
+      <c r="BB25" s="43"/>
+      <c r="BC25" s="43"/>
+      <c r="BD25" s="43"/>
+      <c r="BE25" s="43"/>
+      <c r="BF25" s="43"/>
+      <c r="BG25" s="43"/>
+      <c r="BH25" s="44"/>
+      <c r="BJ25" s="48"/>
+      <c r="BK25" s="49"/>
+      <c r="BL25" s="49"/>
+      <c r="BM25" s="49"/>
+      <c r="BN25" s="49"/>
+      <c r="BO25" s="49"/>
+      <c r="BP25" s="49"/>
+      <c r="BQ25" s="50"/>
+      <c r="BS25" s="48"/>
+      <c r="BT25" s="49"/>
+      <c r="BU25" s="49"/>
+      <c r="BV25" s="49"/>
+      <c r="BW25" s="49"/>
+      <c r="BX25" s="49"/>
+      <c r="BY25" s="49"/>
+      <c r="BZ25" s="50"/>
       <c r="CB25" s="16" t="s">
         <v>18</v>
       </c>
@@ -3669,7 +4119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:85" ht="15.75" thickBot="1">
       <c r="H26" s="24" t="s">
         <v>18</v>
       </c>
@@ -3822,19 +4272,19 @@
         <f>SUM(BT26+BV26+BX26)*16</f>
         <v>0</v>
       </c>
-      <c r="CB26" s="60" t="s">
+      <c r="CB26" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="CC26" s="58"/>
-      <c r="CD26" s="58"/>
-      <c r="CE26" s="58">
+      <c r="CC26" s="51"/>
+      <c r="CD26" s="51"/>
+      <c r="CE26" s="51">
         <f ca="1">CE27*3*16</f>
         <v>0</v>
       </c>
-      <c r="CF26" s="58"/>
-      <c r="CG26" s="59"/>
-    </row>
-    <row r="27" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="CF26" s="51"/>
+      <c r="CG26" s="68"/>
+    </row>
+    <row r="27" spans="3:85" ht="15.75" thickBot="1">
       <c r="N27" s="28" t="s">
         <v>51</v>
       </c>
@@ -3891,168 +4341,168 @@
         <f>(BT26+BV26+BX26)/3</f>
         <v>0</v>
       </c>
-      <c r="CB27" s="54" t="s">
+      <c r="CB27" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="CC27" s="55"/>
-      <c r="CD27" s="55"/>
-      <c r="CE27" s="56">
+      <c r="CC27" s="67"/>
+      <c r="CD27" s="67"/>
+      <c r="CE27" s="54">
         <f ca="1">SUM(IF(MOD(COLUMN(O27:OFFSET(CE27,0,-1)) - COLUMN(O27), 9) = 0, O27:OFFSET(CE27,0,-1), 0))</f>
         <v>0</v>
       </c>
-      <c r="CF27" s="56"/>
-      <c r="CG27" s="57"/>
-    </row>
-    <row r="28" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="3:85" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C29" s="58" t="s">
+      <c r="CF27" s="54"/>
+      <c r="CG27" s="55"/>
+    </row>
+    <row r="28" spans="3:85" ht="15.75" thickBot="1"/>
+    <row r="29" spans="3:85" ht="15" customHeight="1">
+      <c r="C29" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="D29" s="58"/>
-      <c r="E29" s="58"/>
-      <c r="F29" s="58"/>
-      <c r="H29" s="64"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="65"/>
-      <c r="K29" s="65"/>
-      <c r="L29" s="65"/>
-      <c r="M29" s="65"/>
-      <c r="N29" s="65"/>
-      <c r="O29" s="66"/>
-      <c r="Q29" s="64"/>
-      <c r="R29" s="65"/>
-      <c r="S29" s="65"/>
-      <c r="T29" s="65"/>
-      <c r="U29" s="65"/>
-      <c r="V29" s="65"/>
-      <c r="W29" s="65"/>
-      <c r="X29" s="66"/>
-      <c r="Z29" s="64"/>
-      <c r="AA29" s="65"/>
-      <c r="AB29" s="65"/>
-      <c r="AC29" s="65"/>
-      <c r="AD29" s="65"/>
-      <c r="AE29" s="65"/>
-      <c r="AF29" s="65"/>
-      <c r="AG29" s="66"/>
-      <c r="AI29" s="64"/>
-      <c r="AJ29" s="65"/>
-      <c r="AK29" s="65"/>
-      <c r="AL29" s="65"/>
-      <c r="AM29" s="65"/>
-      <c r="AN29" s="65"/>
-      <c r="AO29" s="65"/>
-      <c r="AP29" s="66"/>
-      <c r="AR29" s="64"/>
-      <c r="AS29" s="65"/>
-      <c r="AT29" s="65"/>
-      <c r="AU29" s="65"/>
-      <c r="AV29" s="65"/>
-      <c r="AW29" s="65"/>
-      <c r="AX29" s="65"/>
-      <c r="AY29" s="66"/>
-      <c r="BA29" s="64"/>
-      <c r="BB29" s="65"/>
-      <c r="BC29" s="65"/>
-      <c r="BD29" s="65"/>
-      <c r="BE29" s="65"/>
-      <c r="BF29" s="65"/>
-      <c r="BG29" s="65"/>
-      <c r="BH29" s="66"/>
-      <c r="BJ29" s="48"/>
-      <c r="BK29" s="49"/>
-      <c r="BL29" s="49"/>
-      <c r="BM29" s="49"/>
-      <c r="BN29" s="49"/>
-      <c r="BO29" s="49"/>
-      <c r="BP29" s="49"/>
-      <c r="BQ29" s="50"/>
-      <c r="BS29" s="48"/>
-      <c r="BT29" s="49"/>
-      <c r="BU29" s="49"/>
-      <c r="BV29" s="49"/>
-      <c r="BW29" s="49"/>
-      <c r="BX29" s="49"/>
-      <c r="BY29" s="49"/>
-      <c r="BZ29" s="50"/>
-      <c r="CB29" s="61" t="s">
+      <c r="D29" s="51"/>
+      <c r="E29" s="51"/>
+      <c r="F29" s="51"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="40"/>
+      <c r="K29" s="40"/>
+      <c r="L29" s="40"/>
+      <c r="M29" s="40"/>
+      <c r="N29" s="40"/>
+      <c r="O29" s="41"/>
+      <c r="Q29" s="39"/>
+      <c r="R29" s="40"/>
+      <c r="S29" s="40"/>
+      <c r="T29" s="40"/>
+      <c r="U29" s="40"/>
+      <c r="V29" s="40"/>
+      <c r="W29" s="40"/>
+      <c r="X29" s="41"/>
+      <c r="Z29" s="39"/>
+      <c r="AA29" s="40"/>
+      <c r="AB29" s="40"/>
+      <c r="AC29" s="40"/>
+      <c r="AD29" s="40"/>
+      <c r="AE29" s="40"/>
+      <c r="AF29" s="40"/>
+      <c r="AG29" s="41"/>
+      <c r="AI29" s="39"/>
+      <c r="AJ29" s="40"/>
+      <c r="AK29" s="40"/>
+      <c r="AL29" s="40"/>
+      <c r="AM29" s="40"/>
+      <c r="AN29" s="40"/>
+      <c r="AO29" s="40"/>
+      <c r="AP29" s="41"/>
+      <c r="AR29" s="39"/>
+      <c r="AS29" s="40"/>
+      <c r="AT29" s="40"/>
+      <c r="AU29" s="40"/>
+      <c r="AV29" s="40"/>
+      <c r="AW29" s="40"/>
+      <c r="AX29" s="40"/>
+      <c r="AY29" s="41"/>
+      <c r="BA29" s="39"/>
+      <c r="BB29" s="40"/>
+      <c r="BC29" s="40"/>
+      <c r="BD29" s="40"/>
+      <c r="BE29" s="40"/>
+      <c r="BF29" s="40"/>
+      <c r="BG29" s="40"/>
+      <c r="BH29" s="41"/>
+      <c r="BJ29" s="45"/>
+      <c r="BK29" s="46"/>
+      <c r="BL29" s="46"/>
+      <c r="BM29" s="46"/>
+      <c r="BN29" s="46"/>
+      <c r="BO29" s="46"/>
+      <c r="BP29" s="46"/>
+      <c r="BQ29" s="47"/>
+      <c r="BS29" s="45"/>
+      <c r="BT29" s="46"/>
+      <c r="BU29" s="46"/>
+      <c r="BV29" s="46"/>
+      <c r="BW29" s="46"/>
+      <c r="BX29" s="46"/>
+      <c r="BY29" s="46"/>
+      <c r="BZ29" s="47"/>
+      <c r="CB29" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="CC29" s="62"/>
-      <c r="CD29" s="62"/>
-      <c r="CE29" s="62"/>
-      <c r="CF29" s="62"/>
-      <c r="CG29" s="63"/>
-    </row>
-    <row r="30" spans="3:85" x14ac:dyDescent="0.25">
-      <c r="C30" s="58"/>
-      <c r="D30" s="58"/>
-      <c r="E30" s="58"/>
-      <c r="F30" s="58"/>
-      <c r="H30" s="67"/>
-      <c r="I30" s="68"/>
-      <c r="J30" s="68"/>
-      <c r="K30" s="68"/>
-      <c r="L30" s="68"/>
-      <c r="M30" s="68"/>
-      <c r="N30" s="68"/>
-      <c r="O30" s="69"/>
-      <c r="Q30" s="67"/>
-      <c r="R30" s="68"/>
-      <c r="S30" s="68"/>
-      <c r="T30" s="68"/>
-      <c r="U30" s="68"/>
-      <c r="V30" s="68"/>
-      <c r="W30" s="68"/>
-      <c r="X30" s="69"/>
-      <c r="Z30" s="67"/>
-      <c r="AA30" s="68"/>
-      <c r="AB30" s="68"/>
-      <c r="AC30" s="68"/>
-      <c r="AD30" s="68"/>
-      <c r="AE30" s="68"/>
-      <c r="AF30" s="68"/>
-      <c r="AG30" s="69"/>
-      <c r="AI30" s="67"/>
-      <c r="AJ30" s="68"/>
-      <c r="AK30" s="68"/>
-      <c r="AL30" s="68"/>
-      <c r="AM30" s="68"/>
-      <c r="AN30" s="68"/>
-      <c r="AO30" s="68"/>
-      <c r="AP30" s="69"/>
-      <c r="AR30" s="67"/>
-      <c r="AS30" s="68"/>
-      <c r="AT30" s="68"/>
-      <c r="AU30" s="68"/>
-      <c r="AV30" s="68"/>
-      <c r="AW30" s="68"/>
-      <c r="AX30" s="68"/>
-      <c r="AY30" s="69"/>
-      <c r="BA30" s="67"/>
-      <c r="BB30" s="68"/>
-      <c r="BC30" s="68"/>
-      <c r="BD30" s="68"/>
-      <c r="BE30" s="68"/>
-      <c r="BF30" s="68"/>
-      <c r="BG30" s="68"/>
-      <c r="BH30" s="69"/>
-      <c r="BJ30" s="51"/>
-      <c r="BK30" s="52"/>
-      <c r="BL30" s="52"/>
-      <c r="BM30" s="52"/>
-      <c r="BN30" s="52"/>
-      <c r="BO30" s="52"/>
-      <c r="BP30" s="52"/>
-      <c r="BQ30" s="53"/>
-      <c r="BS30" s="51"/>
-      <c r="BT30" s="52"/>
-      <c r="BU30" s="52"/>
-      <c r="BV30" s="52"/>
-      <c r="BW30" s="52"/>
-      <c r="BX30" s="52"/>
-      <c r="BY30" s="52"/>
-      <c r="BZ30" s="53"/>
+      <c r="CC29" s="63"/>
+      <c r="CD29" s="63"/>
+      <c r="CE29" s="63"/>
+      <c r="CF29" s="63"/>
+      <c r="CG29" s="64"/>
+    </row>
+    <row r="30" spans="3:85">
+      <c r="C30" s="51"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="51"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
+      <c r="L30" s="43"/>
+      <c r="M30" s="43"/>
+      <c r="N30" s="43"/>
+      <c r="O30" s="44"/>
+      <c r="Q30" s="42"/>
+      <c r="R30" s="43"/>
+      <c r="S30" s="43"/>
+      <c r="T30" s="43"/>
+      <c r="U30" s="43"/>
+      <c r="V30" s="43"/>
+      <c r="W30" s="43"/>
+      <c r="X30" s="44"/>
+      <c r="Z30" s="42"/>
+      <c r="AA30" s="43"/>
+      <c r="AB30" s="43"/>
+      <c r="AC30" s="43"/>
+      <c r="AD30" s="43"/>
+      <c r="AE30" s="43"/>
+      <c r="AF30" s="43"/>
+      <c r="AG30" s="44"/>
+      <c r="AI30" s="42"/>
+      <c r="AJ30" s="43"/>
+      <c r="AK30" s="43"/>
+      <c r="AL30" s="43"/>
+      <c r="AM30" s="43"/>
+      <c r="AN30" s="43"/>
+      <c r="AO30" s="43"/>
+      <c r="AP30" s="44"/>
+      <c r="AR30" s="42"/>
+      <c r="AS30" s="43"/>
+      <c r="AT30" s="43"/>
+      <c r="AU30" s="43"/>
+      <c r="AV30" s="43"/>
+      <c r="AW30" s="43"/>
+      <c r="AX30" s="43"/>
+      <c r="AY30" s="44"/>
+      <c r="BA30" s="42"/>
+      <c r="BB30" s="43"/>
+      <c r="BC30" s="43"/>
+      <c r="BD30" s="43"/>
+      <c r="BE30" s="43"/>
+      <c r="BF30" s="43"/>
+      <c r="BG30" s="43"/>
+      <c r="BH30" s="44"/>
+      <c r="BJ30" s="48"/>
+      <c r="BK30" s="49"/>
+      <c r="BL30" s="49"/>
+      <c r="BM30" s="49"/>
+      <c r="BN30" s="49"/>
+      <c r="BO30" s="49"/>
+      <c r="BP30" s="49"/>
+      <c r="BQ30" s="50"/>
+      <c r="BS30" s="48"/>
+      <c r="BT30" s="49"/>
+      <c r="BU30" s="49"/>
+      <c r="BV30" s="49"/>
+      <c r="BW30" s="49"/>
+      <c r="BX30" s="49"/>
+      <c r="BY30" s="49"/>
+      <c r="BZ30" s="50"/>
       <c r="CB30" s="16" t="s">
         <v>18</v>
       </c>
@@ -4075,7 +4525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:85" ht="15.75" thickBot="1">
       <c r="H31" s="24" t="s">
         <v>18</v>
       </c>
@@ -4228,19 +4678,19 @@
         <f>SUM(BT31+BV31+BX31)*16</f>
         <v>0</v>
       </c>
-      <c r="CB31" s="60" t="s">
+      <c r="CB31" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="CC31" s="58"/>
-      <c r="CD31" s="58"/>
-      <c r="CE31" s="58">
+      <c r="CC31" s="51"/>
+      <c r="CD31" s="51"/>
+      <c r="CE31" s="51">
         <f ca="1">CE32*3*16</f>
         <v>0</v>
       </c>
-      <c r="CF31" s="58"/>
-      <c r="CG31" s="59"/>
-    </row>
-    <row r="32" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="CF31" s="51"/>
+      <c r="CG31" s="68"/>
+    </row>
+    <row r="32" spans="3:85" ht="15.75" thickBot="1">
       <c r="N32" s="28" t="s">
         <v>51</v>
       </c>
@@ -4297,168 +4747,168 @@
         <f>(BT31+BV31+BX31)/3</f>
         <v>0</v>
       </c>
-      <c r="CB32" s="54" t="s">
+      <c r="CB32" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="CC32" s="55"/>
-      <c r="CD32" s="55"/>
-      <c r="CE32" s="56">
+      <c r="CC32" s="67"/>
+      <c r="CD32" s="67"/>
+      <c r="CE32" s="54">
         <f ca="1">SUM(IF(MOD(COLUMN(O32:OFFSET(CE32,0,-1)) - COLUMN(O32), 9) = 0, O32:OFFSET(CE32,0,-1), 0))</f>
         <v>0</v>
       </c>
-      <c r="CF32" s="56"/>
-      <c r="CG32" s="57"/>
-    </row>
-    <row r="33" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="34" spans="3:85" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C34" s="58" t="s">
+      <c r="CF32" s="54"/>
+      <c r="CG32" s="55"/>
+    </row>
+    <row r="33" spans="3:85" ht="15.75" thickBot="1"/>
+    <row r="34" spans="3:85" ht="15" customHeight="1">
+      <c r="C34" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="D34" s="58"/>
-      <c r="E34" s="58"/>
-      <c r="F34" s="58"/>
-      <c r="H34" s="64"/>
-      <c r="I34" s="65"/>
-      <c r="J34" s="65"/>
-      <c r="K34" s="65"/>
-      <c r="L34" s="65"/>
-      <c r="M34" s="65"/>
-      <c r="N34" s="65"/>
-      <c r="O34" s="66"/>
-      <c r="Q34" s="64"/>
-      <c r="R34" s="65"/>
-      <c r="S34" s="65"/>
-      <c r="T34" s="65"/>
-      <c r="U34" s="65"/>
-      <c r="V34" s="65"/>
-      <c r="W34" s="65"/>
-      <c r="X34" s="66"/>
-      <c r="Z34" s="64"/>
-      <c r="AA34" s="65"/>
-      <c r="AB34" s="65"/>
-      <c r="AC34" s="65"/>
-      <c r="AD34" s="65"/>
-      <c r="AE34" s="65"/>
-      <c r="AF34" s="65"/>
-      <c r="AG34" s="66"/>
-      <c r="AI34" s="64"/>
-      <c r="AJ34" s="65"/>
-      <c r="AK34" s="65"/>
-      <c r="AL34" s="65"/>
-      <c r="AM34" s="65"/>
-      <c r="AN34" s="65"/>
-      <c r="AO34" s="65"/>
-      <c r="AP34" s="66"/>
-      <c r="AR34" s="64"/>
-      <c r="AS34" s="65"/>
-      <c r="AT34" s="65"/>
-      <c r="AU34" s="65"/>
-      <c r="AV34" s="65"/>
-      <c r="AW34" s="65"/>
-      <c r="AX34" s="65"/>
-      <c r="AY34" s="66"/>
-      <c r="BA34" s="64"/>
-      <c r="BB34" s="65"/>
-      <c r="BC34" s="65"/>
-      <c r="BD34" s="65"/>
-      <c r="BE34" s="65"/>
-      <c r="BF34" s="65"/>
-      <c r="BG34" s="65"/>
-      <c r="BH34" s="66"/>
-      <c r="BJ34" s="48"/>
-      <c r="BK34" s="49"/>
-      <c r="BL34" s="49"/>
-      <c r="BM34" s="49"/>
-      <c r="BN34" s="49"/>
-      <c r="BO34" s="49"/>
-      <c r="BP34" s="49"/>
-      <c r="BQ34" s="50"/>
-      <c r="BS34" s="48"/>
-      <c r="BT34" s="49"/>
-      <c r="BU34" s="49"/>
-      <c r="BV34" s="49"/>
-      <c r="BW34" s="49"/>
-      <c r="BX34" s="49"/>
-      <c r="BY34" s="49"/>
-      <c r="BZ34" s="50"/>
-      <c r="CB34" s="61" t="s">
+      <c r="D34" s="51"/>
+      <c r="E34" s="51"/>
+      <c r="F34" s="51"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="40"/>
+      <c r="J34" s="40"/>
+      <c r="K34" s="40"/>
+      <c r="L34" s="40"/>
+      <c r="M34" s="40"/>
+      <c r="N34" s="40"/>
+      <c r="O34" s="41"/>
+      <c r="Q34" s="39"/>
+      <c r="R34" s="40"/>
+      <c r="S34" s="40"/>
+      <c r="T34" s="40"/>
+      <c r="U34" s="40"/>
+      <c r="V34" s="40"/>
+      <c r="W34" s="40"/>
+      <c r="X34" s="41"/>
+      <c r="Z34" s="39"/>
+      <c r="AA34" s="40"/>
+      <c r="AB34" s="40"/>
+      <c r="AC34" s="40"/>
+      <c r="AD34" s="40"/>
+      <c r="AE34" s="40"/>
+      <c r="AF34" s="40"/>
+      <c r="AG34" s="41"/>
+      <c r="AI34" s="39"/>
+      <c r="AJ34" s="40"/>
+      <c r="AK34" s="40"/>
+      <c r="AL34" s="40"/>
+      <c r="AM34" s="40"/>
+      <c r="AN34" s="40"/>
+      <c r="AO34" s="40"/>
+      <c r="AP34" s="41"/>
+      <c r="AR34" s="39"/>
+      <c r="AS34" s="40"/>
+      <c r="AT34" s="40"/>
+      <c r="AU34" s="40"/>
+      <c r="AV34" s="40"/>
+      <c r="AW34" s="40"/>
+      <c r="AX34" s="40"/>
+      <c r="AY34" s="41"/>
+      <c r="BA34" s="39"/>
+      <c r="BB34" s="40"/>
+      <c r="BC34" s="40"/>
+      <c r="BD34" s="40"/>
+      <c r="BE34" s="40"/>
+      <c r="BF34" s="40"/>
+      <c r="BG34" s="40"/>
+      <c r="BH34" s="41"/>
+      <c r="BJ34" s="45"/>
+      <c r="BK34" s="46"/>
+      <c r="BL34" s="46"/>
+      <c r="BM34" s="46"/>
+      <c r="BN34" s="46"/>
+      <c r="BO34" s="46"/>
+      <c r="BP34" s="46"/>
+      <c r="BQ34" s="47"/>
+      <c r="BS34" s="45"/>
+      <c r="BT34" s="46"/>
+      <c r="BU34" s="46"/>
+      <c r="BV34" s="46"/>
+      <c r="BW34" s="46"/>
+      <c r="BX34" s="46"/>
+      <c r="BY34" s="46"/>
+      <c r="BZ34" s="47"/>
+      <c r="CB34" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="CC34" s="62"/>
-      <c r="CD34" s="62"/>
-      <c r="CE34" s="62"/>
-      <c r="CF34" s="62"/>
-      <c r="CG34" s="63"/>
-    </row>
-    <row r="35" spans="3:85" x14ac:dyDescent="0.25">
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="H35" s="67"/>
-      <c r="I35" s="68"/>
-      <c r="J35" s="68"/>
-      <c r="K35" s="68"/>
-      <c r="L35" s="68"/>
-      <c r="M35" s="68"/>
-      <c r="N35" s="68"/>
-      <c r="O35" s="69"/>
-      <c r="Q35" s="67"/>
-      <c r="R35" s="68"/>
-      <c r="S35" s="68"/>
-      <c r="T35" s="68"/>
-      <c r="U35" s="68"/>
-      <c r="V35" s="68"/>
-      <c r="W35" s="68"/>
-      <c r="X35" s="69"/>
-      <c r="Z35" s="67"/>
-      <c r="AA35" s="68"/>
-      <c r="AB35" s="68"/>
-      <c r="AC35" s="68"/>
-      <c r="AD35" s="68"/>
-      <c r="AE35" s="68"/>
-      <c r="AF35" s="68"/>
-      <c r="AG35" s="69"/>
-      <c r="AI35" s="67"/>
-      <c r="AJ35" s="68"/>
-      <c r="AK35" s="68"/>
-      <c r="AL35" s="68"/>
-      <c r="AM35" s="68"/>
-      <c r="AN35" s="68"/>
-      <c r="AO35" s="68"/>
-      <c r="AP35" s="69"/>
-      <c r="AR35" s="67"/>
-      <c r="AS35" s="68"/>
-      <c r="AT35" s="68"/>
-      <c r="AU35" s="68"/>
-      <c r="AV35" s="68"/>
-      <c r="AW35" s="68"/>
-      <c r="AX35" s="68"/>
-      <c r="AY35" s="69"/>
-      <c r="BA35" s="67"/>
-      <c r="BB35" s="68"/>
-      <c r="BC35" s="68"/>
-      <c r="BD35" s="68"/>
-      <c r="BE35" s="68"/>
-      <c r="BF35" s="68"/>
-      <c r="BG35" s="68"/>
-      <c r="BH35" s="69"/>
-      <c r="BJ35" s="51"/>
-      <c r="BK35" s="52"/>
-      <c r="BL35" s="52"/>
-      <c r="BM35" s="52"/>
-      <c r="BN35" s="52"/>
-      <c r="BO35" s="52"/>
-      <c r="BP35" s="52"/>
-      <c r="BQ35" s="53"/>
-      <c r="BS35" s="51"/>
-      <c r="BT35" s="52"/>
-      <c r="BU35" s="52"/>
-      <c r="BV35" s="52"/>
-      <c r="BW35" s="52"/>
-      <c r="BX35" s="52"/>
-      <c r="BY35" s="52"/>
-      <c r="BZ35" s="53"/>
+      <c r="CC34" s="63"/>
+      <c r="CD34" s="63"/>
+      <c r="CE34" s="63"/>
+      <c r="CF34" s="63"/>
+      <c r="CG34" s="64"/>
+    </row>
+    <row r="35" spans="3:85">
+      <c r="C35" s="51"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="51"/>
+      <c r="H35" s="42"/>
+      <c r="I35" s="43"/>
+      <c r="J35" s="43"/>
+      <c r="K35" s="43"/>
+      <c r="L35" s="43"/>
+      <c r="M35" s="43"/>
+      <c r="N35" s="43"/>
+      <c r="O35" s="44"/>
+      <c r="Q35" s="42"/>
+      <c r="R35" s="43"/>
+      <c r="S35" s="43"/>
+      <c r="T35" s="43"/>
+      <c r="U35" s="43"/>
+      <c r="V35" s="43"/>
+      <c r="W35" s="43"/>
+      <c r="X35" s="44"/>
+      <c r="Z35" s="42"/>
+      <c r="AA35" s="43"/>
+      <c r="AB35" s="43"/>
+      <c r="AC35" s="43"/>
+      <c r="AD35" s="43"/>
+      <c r="AE35" s="43"/>
+      <c r="AF35" s="43"/>
+      <c r="AG35" s="44"/>
+      <c r="AI35" s="42"/>
+      <c r="AJ35" s="43"/>
+      <c r="AK35" s="43"/>
+      <c r="AL35" s="43"/>
+      <c r="AM35" s="43"/>
+      <c r="AN35" s="43"/>
+      <c r="AO35" s="43"/>
+      <c r="AP35" s="44"/>
+      <c r="AR35" s="42"/>
+      <c r="AS35" s="43"/>
+      <c r="AT35" s="43"/>
+      <c r="AU35" s="43"/>
+      <c r="AV35" s="43"/>
+      <c r="AW35" s="43"/>
+      <c r="AX35" s="43"/>
+      <c r="AY35" s="44"/>
+      <c r="BA35" s="42"/>
+      <c r="BB35" s="43"/>
+      <c r="BC35" s="43"/>
+      <c r="BD35" s="43"/>
+      <c r="BE35" s="43"/>
+      <c r="BF35" s="43"/>
+      <c r="BG35" s="43"/>
+      <c r="BH35" s="44"/>
+      <c r="BJ35" s="48"/>
+      <c r="BK35" s="49"/>
+      <c r="BL35" s="49"/>
+      <c r="BM35" s="49"/>
+      <c r="BN35" s="49"/>
+      <c r="BO35" s="49"/>
+      <c r="BP35" s="49"/>
+      <c r="BQ35" s="50"/>
+      <c r="BS35" s="48"/>
+      <c r="BT35" s="49"/>
+      <c r="BU35" s="49"/>
+      <c r="BV35" s="49"/>
+      <c r="BW35" s="49"/>
+      <c r="BX35" s="49"/>
+      <c r="BY35" s="49"/>
+      <c r="BZ35" s="50"/>
       <c r="CB35" s="16" t="s">
         <v>18</v>
       </c>
@@ -4481,7 +4931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:85" ht="15.75" thickBot="1">
       <c r="H36" s="24" t="s">
         <v>18</v>
       </c>
@@ -4634,19 +5084,19 @@
         <f>SUM(BT36+BV36+BX36)*16</f>
         <v>0</v>
       </c>
-      <c r="CB36" s="60" t="s">
+      <c r="CB36" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="CC36" s="58"/>
-      <c r="CD36" s="58"/>
-      <c r="CE36" s="58">
+      <c r="CC36" s="51"/>
+      <c r="CD36" s="51"/>
+      <c r="CE36" s="51">
         <f ca="1">CE37*3*16</f>
         <v>0</v>
       </c>
-      <c r="CF36" s="58"/>
-      <c r="CG36" s="59"/>
-    </row>
-    <row r="37" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="CF36" s="51"/>
+      <c r="CG36" s="68"/>
+    </row>
+    <row r="37" spans="3:85" ht="15.75" thickBot="1">
       <c r="N37" s="28" t="s">
         <v>51</v>
       </c>
@@ -4703,168 +5153,168 @@
         <f>(BT36+BV36+BX36)/3</f>
         <v>0</v>
       </c>
-      <c r="CB37" s="54" t="s">
+      <c r="CB37" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="CC37" s="55"/>
-      <c r="CD37" s="55"/>
-      <c r="CE37" s="56">
+      <c r="CC37" s="67"/>
+      <c r="CD37" s="67"/>
+      <c r="CE37" s="54">
         <f ca="1">SUM(IF(MOD(COLUMN(O37:OFFSET(CE37,0,-1)) - COLUMN(O37), 9) = 0, O37:OFFSET(CE37,0,-1), 0))</f>
         <v>0</v>
       </c>
-      <c r="CF37" s="56"/>
-      <c r="CG37" s="57"/>
-    </row>
-    <row r="38" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="3:85" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="58" t="s">
+      <c r="CF37" s="54"/>
+      <c r="CG37" s="55"/>
+    </row>
+    <row r="38" spans="3:85" ht="15.75" thickBot="1"/>
+    <row r="39" spans="3:85" ht="15" customHeight="1">
+      <c r="C39" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="D39" s="58"/>
-      <c r="E39" s="58"/>
-      <c r="F39" s="58"/>
-      <c r="H39" s="64"/>
-      <c r="I39" s="65"/>
-      <c r="J39" s="65"/>
-      <c r="K39" s="65"/>
-      <c r="L39" s="65"/>
-      <c r="M39" s="65"/>
-      <c r="N39" s="65"/>
-      <c r="O39" s="66"/>
-      <c r="Q39" s="64"/>
-      <c r="R39" s="65"/>
-      <c r="S39" s="65"/>
-      <c r="T39" s="65"/>
-      <c r="U39" s="65"/>
-      <c r="V39" s="65"/>
-      <c r="W39" s="65"/>
-      <c r="X39" s="66"/>
-      <c r="Z39" s="64"/>
-      <c r="AA39" s="65"/>
-      <c r="AB39" s="65"/>
-      <c r="AC39" s="65"/>
-      <c r="AD39" s="65"/>
-      <c r="AE39" s="65"/>
-      <c r="AF39" s="65"/>
-      <c r="AG39" s="66"/>
-      <c r="AI39" s="64"/>
-      <c r="AJ39" s="65"/>
-      <c r="AK39" s="65"/>
-      <c r="AL39" s="65"/>
-      <c r="AM39" s="65"/>
-      <c r="AN39" s="65"/>
-      <c r="AO39" s="65"/>
-      <c r="AP39" s="66"/>
-      <c r="AR39" s="64"/>
-      <c r="AS39" s="65"/>
-      <c r="AT39" s="65"/>
-      <c r="AU39" s="65"/>
-      <c r="AV39" s="65"/>
-      <c r="AW39" s="65"/>
-      <c r="AX39" s="65"/>
-      <c r="AY39" s="66"/>
-      <c r="BA39" s="64"/>
-      <c r="BB39" s="65"/>
-      <c r="BC39" s="65"/>
-      <c r="BD39" s="65"/>
-      <c r="BE39" s="65"/>
-      <c r="BF39" s="65"/>
-      <c r="BG39" s="65"/>
-      <c r="BH39" s="66"/>
-      <c r="BJ39" s="48"/>
-      <c r="BK39" s="49"/>
-      <c r="BL39" s="49"/>
-      <c r="BM39" s="49"/>
-      <c r="BN39" s="49"/>
-      <c r="BO39" s="49"/>
-      <c r="BP39" s="49"/>
-      <c r="BQ39" s="50"/>
-      <c r="BS39" s="48"/>
-      <c r="BT39" s="49"/>
-      <c r="BU39" s="49"/>
-      <c r="BV39" s="49"/>
-      <c r="BW39" s="49"/>
-      <c r="BX39" s="49"/>
-      <c r="BY39" s="49"/>
-      <c r="BZ39" s="50"/>
-      <c r="CB39" s="61" t="s">
+      <c r="D39" s="51"/>
+      <c r="E39" s="51"/>
+      <c r="F39" s="51"/>
+      <c r="H39" s="39"/>
+      <c r="I39" s="40"/>
+      <c r="J39" s="40"/>
+      <c r="K39" s="40"/>
+      <c r="L39" s="40"/>
+      <c r="M39" s="40"/>
+      <c r="N39" s="40"/>
+      <c r="O39" s="41"/>
+      <c r="Q39" s="39"/>
+      <c r="R39" s="40"/>
+      <c r="S39" s="40"/>
+      <c r="T39" s="40"/>
+      <c r="U39" s="40"/>
+      <c r="V39" s="40"/>
+      <c r="W39" s="40"/>
+      <c r="X39" s="41"/>
+      <c r="Z39" s="39"/>
+      <c r="AA39" s="40"/>
+      <c r="AB39" s="40"/>
+      <c r="AC39" s="40"/>
+      <c r="AD39" s="40"/>
+      <c r="AE39" s="40"/>
+      <c r="AF39" s="40"/>
+      <c r="AG39" s="41"/>
+      <c r="AI39" s="39"/>
+      <c r="AJ39" s="40"/>
+      <c r="AK39" s="40"/>
+      <c r="AL39" s="40"/>
+      <c r="AM39" s="40"/>
+      <c r="AN39" s="40"/>
+      <c r="AO39" s="40"/>
+      <c r="AP39" s="41"/>
+      <c r="AR39" s="39"/>
+      <c r="AS39" s="40"/>
+      <c r="AT39" s="40"/>
+      <c r="AU39" s="40"/>
+      <c r="AV39" s="40"/>
+      <c r="AW39" s="40"/>
+      <c r="AX39" s="40"/>
+      <c r="AY39" s="41"/>
+      <c r="BA39" s="39"/>
+      <c r="BB39" s="40"/>
+      <c r="BC39" s="40"/>
+      <c r="BD39" s="40"/>
+      <c r="BE39" s="40"/>
+      <c r="BF39" s="40"/>
+      <c r="BG39" s="40"/>
+      <c r="BH39" s="41"/>
+      <c r="BJ39" s="45"/>
+      <c r="BK39" s="46"/>
+      <c r="BL39" s="46"/>
+      <c r="BM39" s="46"/>
+      <c r="BN39" s="46"/>
+      <c r="BO39" s="46"/>
+      <c r="BP39" s="46"/>
+      <c r="BQ39" s="47"/>
+      <c r="BS39" s="45"/>
+      <c r="BT39" s="46"/>
+      <c r="BU39" s="46"/>
+      <c r="BV39" s="46"/>
+      <c r="BW39" s="46"/>
+      <c r="BX39" s="46"/>
+      <c r="BY39" s="46"/>
+      <c r="BZ39" s="47"/>
+      <c r="CB39" s="62" t="s">
         <v>57</v>
       </c>
-      <c r="CC39" s="62"/>
-      <c r="CD39" s="62"/>
-      <c r="CE39" s="62"/>
-      <c r="CF39" s="62"/>
-      <c r="CG39" s="63"/>
-    </row>
-    <row r="40" spans="3:85" x14ac:dyDescent="0.25">
-      <c r="C40" s="58"/>
-      <c r="D40" s="58"/>
-      <c r="E40" s="58"/>
-      <c r="F40" s="58"/>
-      <c r="H40" s="67"/>
-      <c r="I40" s="68"/>
-      <c r="J40" s="68"/>
-      <c r="K40" s="68"/>
-      <c r="L40" s="68"/>
-      <c r="M40" s="68"/>
-      <c r="N40" s="68"/>
-      <c r="O40" s="69"/>
-      <c r="Q40" s="67"/>
-      <c r="R40" s="68"/>
-      <c r="S40" s="68"/>
-      <c r="T40" s="68"/>
-      <c r="U40" s="68"/>
-      <c r="V40" s="68"/>
-      <c r="W40" s="68"/>
-      <c r="X40" s="69"/>
-      <c r="Z40" s="67"/>
-      <c r="AA40" s="68"/>
-      <c r="AB40" s="68"/>
-      <c r="AC40" s="68"/>
-      <c r="AD40" s="68"/>
-      <c r="AE40" s="68"/>
-      <c r="AF40" s="68"/>
-      <c r="AG40" s="69"/>
-      <c r="AI40" s="67"/>
-      <c r="AJ40" s="68"/>
-      <c r="AK40" s="68"/>
-      <c r="AL40" s="68"/>
-      <c r="AM40" s="68"/>
-      <c r="AN40" s="68"/>
-      <c r="AO40" s="68"/>
-      <c r="AP40" s="69"/>
-      <c r="AR40" s="67"/>
-      <c r="AS40" s="68"/>
-      <c r="AT40" s="68"/>
-      <c r="AU40" s="68"/>
-      <c r="AV40" s="68"/>
-      <c r="AW40" s="68"/>
-      <c r="AX40" s="68"/>
-      <c r="AY40" s="69"/>
-      <c r="BA40" s="67"/>
-      <c r="BB40" s="68"/>
-      <c r="BC40" s="68"/>
-      <c r="BD40" s="68"/>
-      <c r="BE40" s="68"/>
-      <c r="BF40" s="68"/>
-      <c r="BG40" s="68"/>
-      <c r="BH40" s="69"/>
-      <c r="BJ40" s="51"/>
-      <c r="BK40" s="52"/>
-      <c r="BL40" s="52"/>
-      <c r="BM40" s="52"/>
-      <c r="BN40" s="52"/>
-      <c r="BO40" s="52"/>
-      <c r="BP40" s="52"/>
-      <c r="BQ40" s="53"/>
-      <c r="BS40" s="51"/>
-      <c r="BT40" s="52"/>
-      <c r="BU40" s="52"/>
-      <c r="BV40" s="52"/>
-      <c r="BW40" s="52"/>
-      <c r="BX40" s="52"/>
-      <c r="BY40" s="52"/>
-      <c r="BZ40" s="53"/>
+      <c r="CC39" s="63"/>
+      <c r="CD39" s="63"/>
+      <c r="CE39" s="63"/>
+      <c r="CF39" s="63"/>
+      <c r="CG39" s="64"/>
+    </row>
+    <row r="40" spans="3:85">
+      <c r="C40" s="51"/>
+      <c r="D40" s="51"/>
+      <c r="E40" s="51"/>
+      <c r="F40" s="51"/>
+      <c r="H40" s="42"/>
+      <c r="I40" s="43"/>
+      <c r="J40" s="43"/>
+      <c r="K40" s="43"/>
+      <c r="L40" s="43"/>
+      <c r="M40" s="43"/>
+      <c r="N40" s="43"/>
+      <c r="O40" s="44"/>
+      <c r="Q40" s="42"/>
+      <c r="R40" s="43"/>
+      <c r="S40" s="43"/>
+      <c r="T40" s="43"/>
+      <c r="U40" s="43"/>
+      <c r="V40" s="43"/>
+      <c r="W40" s="43"/>
+      <c r="X40" s="44"/>
+      <c r="Z40" s="42"/>
+      <c r="AA40" s="43"/>
+      <c r="AB40" s="43"/>
+      <c r="AC40" s="43"/>
+      <c r="AD40" s="43"/>
+      <c r="AE40" s="43"/>
+      <c r="AF40" s="43"/>
+      <c r="AG40" s="44"/>
+      <c r="AI40" s="42"/>
+      <c r="AJ40" s="43"/>
+      <c r="AK40" s="43"/>
+      <c r="AL40" s="43"/>
+      <c r="AM40" s="43"/>
+      <c r="AN40" s="43"/>
+      <c r="AO40" s="43"/>
+      <c r="AP40" s="44"/>
+      <c r="AR40" s="42"/>
+      <c r="AS40" s="43"/>
+      <c r="AT40" s="43"/>
+      <c r="AU40" s="43"/>
+      <c r="AV40" s="43"/>
+      <c r="AW40" s="43"/>
+      <c r="AX40" s="43"/>
+      <c r="AY40" s="44"/>
+      <c r="BA40" s="42"/>
+      <c r="BB40" s="43"/>
+      <c r="BC40" s="43"/>
+      <c r="BD40" s="43"/>
+      <c r="BE40" s="43"/>
+      <c r="BF40" s="43"/>
+      <c r="BG40" s="43"/>
+      <c r="BH40" s="44"/>
+      <c r="BJ40" s="48"/>
+      <c r="BK40" s="49"/>
+      <c r="BL40" s="49"/>
+      <c r="BM40" s="49"/>
+      <c r="BN40" s="49"/>
+      <c r="BO40" s="49"/>
+      <c r="BP40" s="49"/>
+      <c r="BQ40" s="50"/>
+      <c r="BS40" s="48"/>
+      <c r="BT40" s="49"/>
+      <c r="BU40" s="49"/>
+      <c r="BV40" s="49"/>
+      <c r="BW40" s="49"/>
+      <c r="BX40" s="49"/>
+      <c r="BY40" s="49"/>
+      <c r="BZ40" s="50"/>
       <c r="CB40" s="16" t="s">
         <v>18</v>
       </c>
@@ -4887,7 +5337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:85" ht="15.75" thickBot="1">
       <c r="H41" s="24" t="s">
         <v>18</v>
       </c>
@@ -5040,19 +5490,19 @@
         <f>SUM(BT41+BV41+BX41)*16</f>
         <v>0</v>
       </c>
-      <c r="CB41" s="60" t="s">
+      <c r="CB41" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="CC41" s="58"/>
-      <c r="CD41" s="58"/>
-      <c r="CE41" s="58">
+      <c r="CC41" s="51"/>
+      <c r="CD41" s="51"/>
+      <c r="CE41" s="51">
         <f ca="1">CE42*3*16</f>
         <v>0</v>
       </c>
-      <c r="CF41" s="58"/>
-      <c r="CG41" s="59"/>
-    </row>
-    <row r="42" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="CF41" s="51"/>
+      <c r="CG41" s="68"/>
+    </row>
+    <row r="42" spans="3:85" ht="15.75" thickBot="1">
       <c r="N42" s="28" t="s">
         <v>51</v>
       </c>
@@ -5109,168 +5559,168 @@
         <f>(BT41+BV41+BX41)/3</f>
         <v>0</v>
       </c>
-      <c r="CB42" s="54" t="s">
+      <c r="CB42" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="CC42" s="55"/>
-      <c r="CD42" s="55"/>
-      <c r="CE42" s="56">
+      <c r="CC42" s="67"/>
+      <c r="CD42" s="67"/>
+      <c r="CE42" s="54">
         <f ca="1">SUM(IF(MOD(COLUMN(O42:OFFSET(CE42,0,-1)) - COLUMN(O42), 9) = 0, O42:OFFSET(CE42,0,-1), 0))</f>
         <v>0</v>
       </c>
-      <c r="CF42" s="56"/>
-      <c r="CG42" s="57"/>
-    </row>
-    <row r="43" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="44" spans="3:85" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="58" t="s">
+      <c r="CF42" s="54"/>
+      <c r="CG42" s="55"/>
+    </row>
+    <row r="43" spans="3:85" ht="15.75" thickBot="1"/>
+    <row r="44" spans="3:85" ht="15" customHeight="1">
+      <c r="C44" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="D44" s="58"/>
-      <c r="E44" s="58"/>
-      <c r="F44" s="58"/>
-      <c r="H44" s="64"/>
-      <c r="I44" s="65"/>
-      <c r="J44" s="65"/>
-      <c r="K44" s="65"/>
-      <c r="L44" s="65"/>
-      <c r="M44" s="65"/>
-      <c r="N44" s="65"/>
-      <c r="O44" s="66"/>
-      <c r="Q44" s="64"/>
-      <c r="R44" s="65"/>
-      <c r="S44" s="65"/>
-      <c r="T44" s="65"/>
-      <c r="U44" s="65"/>
-      <c r="V44" s="65"/>
-      <c r="W44" s="65"/>
-      <c r="X44" s="66"/>
-      <c r="Z44" s="64"/>
-      <c r="AA44" s="65"/>
-      <c r="AB44" s="65"/>
-      <c r="AC44" s="65"/>
-      <c r="AD44" s="65"/>
-      <c r="AE44" s="65"/>
-      <c r="AF44" s="65"/>
-      <c r="AG44" s="66"/>
-      <c r="AI44" s="64"/>
-      <c r="AJ44" s="65"/>
-      <c r="AK44" s="65"/>
-      <c r="AL44" s="65"/>
-      <c r="AM44" s="65"/>
-      <c r="AN44" s="65"/>
-      <c r="AO44" s="65"/>
-      <c r="AP44" s="66"/>
-      <c r="AR44" s="64"/>
-      <c r="AS44" s="65"/>
-      <c r="AT44" s="65"/>
-      <c r="AU44" s="65"/>
-      <c r="AV44" s="65"/>
-      <c r="AW44" s="65"/>
-      <c r="AX44" s="65"/>
-      <c r="AY44" s="66"/>
-      <c r="BA44" s="64"/>
-      <c r="BB44" s="65"/>
-      <c r="BC44" s="65"/>
-      <c r="BD44" s="65"/>
-      <c r="BE44" s="65"/>
-      <c r="BF44" s="65"/>
-      <c r="BG44" s="65"/>
-      <c r="BH44" s="66"/>
-      <c r="BJ44" s="48"/>
-      <c r="BK44" s="49"/>
-      <c r="BL44" s="49"/>
-      <c r="BM44" s="49"/>
-      <c r="BN44" s="49"/>
-      <c r="BO44" s="49"/>
-      <c r="BP44" s="49"/>
-      <c r="BQ44" s="50"/>
-      <c r="BS44" s="48"/>
-      <c r="BT44" s="49"/>
-      <c r="BU44" s="49"/>
-      <c r="BV44" s="49"/>
-      <c r="BW44" s="49"/>
-      <c r="BX44" s="49"/>
-      <c r="BY44" s="49"/>
-      <c r="BZ44" s="50"/>
-      <c r="CB44" s="61" t="s">
+      <c r="D44" s="51"/>
+      <c r="E44" s="51"/>
+      <c r="F44" s="51"/>
+      <c r="H44" s="39"/>
+      <c r="I44" s="40"/>
+      <c r="J44" s="40"/>
+      <c r="K44" s="40"/>
+      <c r="L44" s="40"/>
+      <c r="M44" s="40"/>
+      <c r="N44" s="40"/>
+      <c r="O44" s="41"/>
+      <c r="Q44" s="39"/>
+      <c r="R44" s="40"/>
+      <c r="S44" s="40"/>
+      <c r="T44" s="40"/>
+      <c r="U44" s="40"/>
+      <c r="V44" s="40"/>
+      <c r="W44" s="40"/>
+      <c r="X44" s="41"/>
+      <c r="Z44" s="39"/>
+      <c r="AA44" s="40"/>
+      <c r="AB44" s="40"/>
+      <c r="AC44" s="40"/>
+      <c r="AD44" s="40"/>
+      <c r="AE44" s="40"/>
+      <c r="AF44" s="40"/>
+      <c r="AG44" s="41"/>
+      <c r="AI44" s="39"/>
+      <c r="AJ44" s="40"/>
+      <c r="AK44" s="40"/>
+      <c r="AL44" s="40"/>
+      <c r="AM44" s="40"/>
+      <c r="AN44" s="40"/>
+      <c r="AO44" s="40"/>
+      <c r="AP44" s="41"/>
+      <c r="AR44" s="39"/>
+      <c r="AS44" s="40"/>
+      <c r="AT44" s="40"/>
+      <c r="AU44" s="40"/>
+      <c r="AV44" s="40"/>
+      <c r="AW44" s="40"/>
+      <c r="AX44" s="40"/>
+      <c r="AY44" s="41"/>
+      <c r="BA44" s="39"/>
+      <c r="BB44" s="40"/>
+      <c r="BC44" s="40"/>
+      <c r="BD44" s="40"/>
+      <c r="BE44" s="40"/>
+      <c r="BF44" s="40"/>
+      <c r="BG44" s="40"/>
+      <c r="BH44" s="41"/>
+      <c r="BJ44" s="45"/>
+      <c r="BK44" s="46"/>
+      <c r="BL44" s="46"/>
+      <c r="BM44" s="46"/>
+      <c r="BN44" s="46"/>
+      <c r="BO44" s="46"/>
+      <c r="BP44" s="46"/>
+      <c r="BQ44" s="47"/>
+      <c r="BS44" s="45"/>
+      <c r="BT44" s="46"/>
+      <c r="BU44" s="46"/>
+      <c r="BV44" s="46"/>
+      <c r="BW44" s="46"/>
+      <c r="BX44" s="46"/>
+      <c r="BY44" s="46"/>
+      <c r="BZ44" s="47"/>
+      <c r="CB44" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="CC44" s="62"/>
-      <c r="CD44" s="62"/>
-      <c r="CE44" s="62"/>
-      <c r="CF44" s="62"/>
-      <c r="CG44" s="63"/>
-    </row>
-    <row r="45" spans="3:85" x14ac:dyDescent="0.25">
-      <c r="C45" s="58"/>
-      <c r="D45" s="58"/>
-      <c r="E45" s="58"/>
-      <c r="F45" s="58"/>
-      <c r="H45" s="67"/>
-      <c r="I45" s="68"/>
-      <c r="J45" s="68"/>
-      <c r="K45" s="68"/>
-      <c r="L45" s="68"/>
-      <c r="M45" s="68"/>
-      <c r="N45" s="68"/>
-      <c r="O45" s="69"/>
-      <c r="Q45" s="67"/>
-      <c r="R45" s="68"/>
-      <c r="S45" s="68"/>
-      <c r="T45" s="68"/>
-      <c r="U45" s="68"/>
-      <c r="V45" s="68"/>
-      <c r="W45" s="68"/>
-      <c r="X45" s="69"/>
-      <c r="Z45" s="67"/>
-      <c r="AA45" s="68"/>
-      <c r="AB45" s="68"/>
-      <c r="AC45" s="68"/>
-      <c r="AD45" s="68"/>
-      <c r="AE45" s="68"/>
-      <c r="AF45" s="68"/>
-      <c r="AG45" s="69"/>
-      <c r="AI45" s="67"/>
-      <c r="AJ45" s="68"/>
-      <c r="AK45" s="68"/>
-      <c r="AL45" s="68"/>
-      <c r="AM45" s="68"/>
-      <c r="AN45" s="68"/>
-      <c r="AO45" s="68"/>
-      <c r="AP45" s="69"/>
-      <c r="AR45" s="67"/>
-      <c r="AS45" s="68"/>
-      <c r="AT45" s="68"/>
-      <c r="AU45" s="68"/>
-      <c r="AV45" s="68"/>
-      <c r="AW45" s="68"/>
-      <c r="AX45" s="68"/>
-      <c r="AY45" s="69"/>
-      <c r="BA45" s="67"/>
-      <c r="BB45" s="68"/>
-      <c r="BC45" s="68"/>
-      <c r="BD45" s="68"/>
-      <c r="BE45" s="68"/>
-      <c r="BF45" s="68"/>
-      <c r="BG45" s="68"/>
-      <c r="BH45" s="69"/>
-      <c r="BJ45" s="51"/>
-      <c r="BK45" s="52"/>
-      <c r="BL45" s="52"/>
-      <c r="BM45" s="52"/>
-      <c r="BN45" s="52"/>
-      <c r="BO45" s="52"/>
-      <c r="BP45" s="52"/>
-      <c r="BQ45" s="53"/>
-      <c r="BS45" s="51"/>
-      <c r="BT45" s="52"/>
-      <c r="BU45" s="52"/>
-      <c r="BV45" s="52"/>
-      <c r="BW45" s="52"/>
-      <c r="BX45" s="52"/>
-      <c r="BY45" s="52"/>
-      <c r="BZ45" s="53"/>
+      <c r="CC44" s="63"/>
+      <c r="CD44" s="63"/>
+      <c r="CE44" s="63"/>
+      <c r="CF44" s="63"/>
+      <c r="CG44" s="64"/>
+    </row>
+    <row r="45" spans="3:85">
+      <c r="C45" s="51"/>
+      <c r="D45" s="51"/>
+      <c r="E45" s="51"/>
+      <c r="F45" s="51"/>
+      <c r="H45" s="42"/>
+      <c r="I45" s="43"/>
+      <c r="J45" s="43"/>
+      <c r="K45" s="43"/>
+      <c r="L45" s="43"/>
+      <c r="M45" s="43"/>
+      <c r="N45" s="43"/>
+      <c r="O45" s="44"/>
+      <c r="Q45" s="42"/>
+      <c r="R45" s="43"/>
+      <c r="S45" s="43"/>
+      <c r="T45" s="43"/>
+      <c r="U45" s="43"/>
+      <c r="V45" s="43"/>
+      <c r="W45" s="43"/>
+      <c r="X45" s="44"/>
+      <c r="Z45" s="42"/>
+      <c r="AA45" s="43"/>
+      <c r="AB45" s="43"/>
+      <c r="AC45" s="43"/>
+      <c r="AD45" s="43"/>
+      <c r="AE45" s="43"/>
+      <c r="AF45" s="43"/>
+      <c r="AG45" s="44"/>
+      <c r="AI45" s="42"/>
+      <c r="AJ45" s="43"/>
+      <c r="AK45" s="43"/>
+      <c r="AL45" s="43"/>
+      <c r="AM45" s="43"/>
+      <c r="AN45" s="43"/>
+      <c r="AO45" s="43"/>
+      <c r="AP45" s="44"/>
+      <c r="AR45" s="42"/>
+      <c r="AS45" s="43"/>
+      <c r="AT45" s="43"/>
+      <c r="AU45" s="43"/>
+      <c r="AV45" s="43"/>
+      <c r="AW45" s="43"/>
+      <c r="AX45" s="43"/>
+      <c r="AY45" s="44"/>
+      <c r="BA45" s="42"/>
+      <c r="BB45" s="43"/>
+      <c r="BC45" s="43"/>
+      <c r="BD45" s="43"/>
+      <c r="BE45" s="43"/>
+      <c r="BF45" s="43"/>
+      <c r="BG45" s="43"/>
+      <c r="BH45" s="44"/>
+      <c r="BJ45" s="48"/>
+      <c r="BK45" s="49"/>
+      <c r="BL45" s="49"/>
+      <c r="BM45" s="49"/>
+      <c r="BN45" s="49"/>
+      <c r="BO45" s="49"/>
+      <c r="BP45" s="49"/>
+      <c r="BQ45" s="50"/>
+      <c r="BS45" s="48"/>
+      <c r="BT45" s="49"/>
+      <c r="BU45" s="49"/>
+      <c r="BV45" s="49"/>
+      <c r="BW45" s="49"/>
+      <c r="BX45" s="49"/>
+      <c r="BY45" s="49"/>
+      <c r="BZ45" s="50"/>
       <c r="CB45" s="16" t="s">
         <v>18</v>
       </c>
@@ -5293,7 +5743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:85" ht="15.75" thickBot="1">
       <c r="H46" s="24" t="s">
         <v>18</v>
       </c>
@@ -5446,19 +5896,19 @@
         <f>SUM(BT46+BV46+BX46)*16</f>
         <v>0</v>
       </c>
-      <c r="CB46" s="60" t="s">
+      <c r="CB46" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="CC46" s="58"/>
-      <c r="CD46" s="58"/>
-      <c r="CE46" s="58">
+      <c r="CC46" s="51"/>
+      <c r="CD46" s="51"/>
+      <c r="CE46" s="51">
         <f ca="1">CE47*3*16</f>
         <v>0</v>
       </c>
-      <c r="CF46" s="58"/>
-      <c r="CG46" s="59"/>
-    </row>
-    <row r="47" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="CF46" s="51"/>
+      <c r="CG46" s="68"/>
+    </row>
+    <row r="47" spans="3:85" ht="15.75" thickBot="1">
       <c r="N47" s="28" t="s">
         <v>51</v>
       </c>
@@ -5515,19 +5965,19 @@
         <f>(BT46+BV46+BX46)/3</f>
         <v>0</v>
       </c>
-      <c r="CB47" s="54" t="s">
+      <c r="CB47" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="CC47" s="55"/>
-      <c r="CD47" s="55"/>
-      <c r="CE47" s="56">
+      <c r="CC47" s="67"/>
+      <c r="CD47" s="67"/>
+      <c r="CE47" s="54">
         <f ca="1">SUM(IF(MOD(COLUMN(O47:OFFSET(CE47,0,-1)) - COLUMN(O47), 9) = 0, O47:OFFSET(CE47,0,-1), 0))</f>
         <v>0</v>
       </c>
-      <c r="CF47" s="56"/>
-      <c r="CG47" s="57"/>
-    </row>
-    <row r="48" spans="3:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="CF47" s="54"/>
+      <c r="CG47" s="55"/>
+    </row>
+    <row r="48" spans="3:85" ht="15.75" thickBot="1">
       <c r="CB48" s="18"/>
       <c r="CC48" s="18"/>
       <c r="CD48" s="18"/>
@@ -5535,155 +5985,155 @@
       <c r="CF48" s="18"/>
       <c r="CG48" s="18"/>
     </row>
-    <row r="49" spans="3:119" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C49" s="58" t="s">
+    <row r="49" spans="3:119" ht="15" customHeight="1">
+      <c r="C49" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="D49" s="58"/>
-      <c r="E49" s="58"/>
-      <c r="F49" s="58"/>
-      <c r="H49" s="64"/>
-      <c r="I49" s="65"/>
-      <c r="J49" s="65"/>
-      <c r="K49" s="65"/>
-      <c r="L49" s="65"/>
-      <c r="M49" s="65"/>
-      <c r="N49" s="65"/>
-      <c r="O49" s="66"/>
-      <c r="Q49" s="64"/>
-      <c r="R49" s="65"/>
-      <c r="S49" s="65"/>
-      <c r="T49" s="65"/>
-      <c r="U49" s="65"/>
-      <c r="V49" s="65"/>
-      <c r="W49" s="65"/>
-      <c r="X49" s="66"/>
-      <c r="Z49" s="64"/>
-      <c r="AA49" s="65"/>
-      <c r="AB49" s="65"/>
-      <c r="AC49" s="65"/>
-      <c r="AD49" s="65"/>
-      <c r="AE49" s="65"/>
-      <c r="AF49" s="65"/>
-      <c r="AG49" s="66"/>
-      <c r="AI49" s="64"/>
-      <c r="AJ49" s="65"/>
-      <c r="AK49" s="65"/>
-      <c r="AL49" s="65"/>
-      <c r="AM49" s="65"/>
-      <c r="AN49" s="65"/>
-      <c r="AO49" s="65"/>
-      <c r="AP49" s="66"/>
-      <c r="AR49" s="64"/>
-      <c r="AS49" s="65"/>
-      <c r="AT49" s="65"/>
-      <c r="AU49" s="65"/>
-      <c r="AV49" s="65"/>
-      <c r="AW49" s="65"/>
-      <c r="AX49" s="65"/>
-      <c r="AY49" s="66"/>
-      <c r="BA49" s="64"/>
-      <c r="BB49" s="65"/>
-      <c r="BC49" s="65"/>
-      <c r="BD49" s="65"/>
-      <c r="BE49" s="65"/>
-      <c r="BF49" s="65"/>
-      <c r="BG49" s="65"/>
-      <c r="BH49" s="66"/>
-      <c r="BJ49" s="48"/>
-      <c r="BK49" s="49"/>
-      <c r="BL49" s="49"/>
-      <c r="BM49" s="49"/>
-      <c r="BN49" s="49"/>
-      <c r="BO49" s="49"/>
-      <c r="BP49" s="49"/>
-      <c r="BQ49" s="50"/>
-      <c r="BS49" s="48"/>
-      <c r="BT49" s="49"/>
-      <c r="BU49" s="49"/>
-      <c r="BV49" s="49"/>
-      <c r="BW49" s="49"/>
-      <c r="BX49" s="49"/>
-      <c r="BY49" s="49"/>
-      <c r="BZ49" s="50"/>
-      <c r="CB49" s="61" t="s">
+      <c r="D49" s="51"/>
+      <c r="E49" s="51"/>
+      <c r="F49" s="51"/>
+      <c r="H49" s="39"/>
+      <c r="I49" s="40"/>
+      <c r="J49" s="40"/>
+      <c r="K49" s="40"/>
+      <c r="L49" s="40"/>
+      <c r="M49" s="40"/>
+      <c r="N49" s="40"/>
+      <c r="O49" s="41"/>
+      <c r="Q49" s="39"/>
+      <c r="R49" s="40"/>
+      <c r="S49" s="40"/>
+      <c r="T49" s="40"/>
+      <c r="U49" s="40"/>
+      <c r="V49" s="40"/>
+      <c r="W49" s="40"/>
+      <c r="X49" s="41"/>
+      <c r="Z49" s="39"/>
+      <c r="AA49" s="40"/>
+      <c r="AB49" s="40"/>
+      <c r="AC49" s="40"/>
+      <c r="AD49" s="40"/>
+      <c r="AE49" s="40"/>
+      <c r="AF49" s="40"/>
+      <c r="AG49" s="41"/>
+      <c r="AI49" s="39"/>
+      <c r="AJ49" s="40"/>
+      <c r="AK49" s="40"/>
+      <c r="AL49" s="40"/>
+      <c r="AM49" s="40"/>
+      <c r="AN49" s="40"/>
+      <c r="AO49" s="40"/>
+      <c r="AP49" s="41"/>
+      <c r="AR49" s="39"/>
+      <c r="AS49" s="40"/>
+      <c r="AT49" s="40"/>
+      <c r="AU49" s="40"/>
+      <c r="AV49" s="40"/>
+      <c r="AW49" s="40"/>
+      <c r="AX49" s="40"/>
+      <c r="AY49" s="41"/>
+      <c r="BA49" s="39"/>
+      <c r="BB49" s="40"/>
+      <c r="BC49" s="40"/>
+      <c r="BD49" s="40"/>
+      <c r="BE49" s="40"/>
+      <c r="BF49" s="40"/>
+      <c r="BG49" s="40"/>
+      <c r="BH49" s="41"/>
+      <c r="BJ49" s="45"/>
+      <c r="BK49" s="46"/>
+      <c r="BL49" s="46"/>
+      <c r="BM49" s="46"/>
+      <c r="BN49" s="46"/>
+      <c r="BO49" s="46"/>
+      <c r="BP49" s="46"/>
+      <c r="BQ49" s="47"/>
+      <c r="BS49" s="45"/>
+      <c r="BT49" s="46"/>
+      <c r="BU49" s="46"/>
+      <c r="BV49" s="46"/>
+      <c r="BW49" s="46"/>
+      <c r="BX49" s="46"/>
+      <c r="BY49" s="46"/>
+      <c r="BZ49" s="47"/>
+      <c r="CB49" s="62" t="s">
         <v>59</v>
       </c>
-      <c r="CC49" s="62"/>
-      <c r="CD49" s="62"/>
-      <c r="CE49" s="62"/>
-      <c r="CF49" s="62"/>
-      <c r="CG49" s="63"/>
-    </row>
-    <row r="50" spans="3:119" x14ac:dyDescent="0.25">
-      <c r="C50" s="58"/>
-      <c r="D50" s="58"/>
-      <c r="E50" s="58"/>
-      <c r="F50" s="58"/>
-      <c r="H50" s="67"/>
-      <c r="I50" s="68"/>
-      <c r="J50" s="68"/>
-      <c r="K50" s="68"/>
-      <c r="L50" s="68"/>
-      <c r="M50" s="68"/>
-      <c r="N50" s="68"/>
-      <c r="O50" s="69"/>
-      <c r="Q50" s="67"/>
-      <c r="R50" s="68"/>
-      <c r="S50" s="68"/>
-      <c r="T50" s="68"/>
-      <c r="U50" s="68"/>
-      <c r="V50" s="68"/>
-      <c r="W50" s="68"/>
-      <c r="X50" s="69"/>
-      <c r="Z50" s="67"/>
-      <c r="AA50" s="68"/>
-      <c r="AB50" s="68"/>
-      <c r="AC50" s="68"/>
-      <c r="AD50" s="68"/>
-      <c r="AE50" s="68"/>
-      <c r="AF50" s="68"/>
-      <c r="AG50" s="69"/>
-      <c r="AI50" s="67"/>
-      <c r="AJ50" s="68"/>
-      <c r="AK50" s="68"/>
-      <c r="AL50" s="68"/>
-      <c r="AM50" s="68"/>
-      <c r="AN50" s="68"/>
-      <c r="AO50" s="68"/>
-      <c r="AP50" s="69"/>
-      <c r="AR50" s="67"/>
-      <c r="AS50" s="68"/>
-      <c r="AT50" s="68"/>
-      <c r="AU50" s="68"/>
-      <c r="AV50" s="68"/>
-      <c r="AW50" s="68"/>
-      <c r="AX50" s="68"/>
-      <c r="AY50" s="69"/>
-      <c r="BA50" s="67"/>
-      <c r="BB50" s="68"/>
-      <c r="BC50" s="68"/>
-      <c r="BD50" s="68"/>
-      <c r="BE50" s="68"/>
-      <c r="BF50" s="68"/>
-      <c r="BG50" s="68"/>
-      <c r="BH50" s="69"/>
-      <c r="BJ50" s="51"/>
-      <c r="BK50" s="52"/>
-      <c r="BL50" s="52"/>
-      <c r="BM50" s="52"/>
-      <c r="BN50" s="52"/>
-      <c r="BO50" s="52"/>
-      <c r="BP50" s="52"/>
-      <c r="BQ50" s="53"/>
-      <c r="BS50" s="51"/>
-      <c r="BT50" s="52"/>
-      <c r="BU50" s="52"/>
-      <c r="BV50" s="52"/>
-      <c r="BW50" s="52"/>
-      <c r="BX50" s="52"/>
-      <c r="BY50" s="52"/>
-      <c r="BZ50" s="53"/>
+      <c r="CC49" s="63"/>
+      <c r="CD49" s="63"/>
+      <c r="CE49" s="63"/>
+      <c r="CF49" s="63"/>
+      <c r="CG49" s="64"/>
+    </row>
+    <row r="50" spans="3:119">
+      <c r="C50" s="51"/>
+      <c r="D50" s="51"/>
+      <c r="E50" s="51"/>
+      <c r="F50" s="51"/>
+      <c r="H50" s="42"/>
+      <c r="I50" s="43"/>
+      <c r="J50" s="43"/>
+      <c r="K50" s="43"/>
+      <c r="L50" s="43"/>
+      <c r="M50" s="43"/>
+      <c r="N50" s="43"/>
+      <c r="O50" s="44"/>
+      <c r="Q50" s="42"/>
+      <c r="R50" s="43"/>
+      <c r="S50" s="43"/>
+      <c r="T50" s="43"/>
+      <c r="U50" s="43"/>
+      <c r="V50" s="43"/>
+      <c r="W50" s="43"/>
+      <c r="X50" s="44"/>
+      <c r="Z50" s="42"/>
+      <c r="AA50" s="43"/>
+      <c r="AB50" s="43"/>
+      <c r="AC50" s="43"/>
+      <c r="AD50" s="43"/>
+      <c r="AE50" s="43"/>
+      <c r="AF50" s="43"/>
+      <c r="AG50" s="44"/>
+      <c r="AI50" s="42"/>
+      <c r="AJ50" s="43"/>
+      <c r="AK50" s="43"/>
+      <c r="AL50" s="43"/>
+      <c r="AM50" s="43"/>
+      <c r="AN50" s="43"/>
+      <c r="AO50" s="43"/>
+      <c r="AP50" s="44"/>
+      <c r="AR50" s="42"/>
+      <c r="AS50" s="43"/>
+      <c r="AT50" s="43"/>
+      <c r="AU50" s="43"/>
+      <c r="AV50" s="43"/>
+      <c r="AW50" s="43"/>
+      <c r="AX50" s="43"/>
+      <c r="AY50" s="44"/>
+      <c r="BA50" s="42"/>
+      <c r="BB50" s="43"/>
+      <c r="BC50" s="43"/>
+      <c r="BD50" s="43"/>
+      <c r="BE50" s="43"/>
+      <c r="BF50" s="43"/>
+      <c r="BG50" s="43"/>
+      <c r="BH50" s="44"/>
+      <c r="BJ50" s="48"/>
+      <c r="BK50" s="49"/>
+      <c r="BL50" s="49"/>
+      <c r="BM50" s="49"/>
+      <c r="BN50" s="49"/>
+      <c r="BO50" s="49"/>
+      <c r="BP50" s="49"/>
+      <c r="BQ50" s="50"/>
+      <c r="BS50" s="48"/>
+      <c r="BT50" s="49"/>
+      <c r="BU50" s="49"/>
+      <c r="BV50" s="49"/>
+      <c r="BW50" s="49"/>
+      <c r="BX50" s="49"/>
+      <c r="BY50" s="49"/>
+      <c r="BZ50" s="50"/>
       <c r="CB50" s="16" t="s">
         <v>18</v>
       </c>
@@ -5706,7 +6156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="3:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:119" ht="15.75" thickBot="1">
       <c r="H51" s="24" t="s">
         <v>18</v>
       </c>
@@ -5859,23 +6309,23 @@
         <f>SUM(BT51+BV51+BX51)*16</f>
         <v>0</v>
       </c>
-      <c r="CB51" s="60" t="s">
+      <c r="CB51" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="CC51" s="58"/>
-      <c r="CD51" s="58"/>
-      <c r="CE51" s="58">
+      <c r="CC51" s="51"/>
+      <c r="CD51" s="51"/>
+      <c r="CE51" s="51">
         <f ca="1">CE52*3*16</f>
         <v>0</v>
       </c>
-      <c r="CF51" s="58"/>
-      <c r="CG51" s="59"/>
+      <c r="CF51" s="51"/>
+      <c r="CG51" s="68"/>
       <c r="CN51" s="18"/>
       <c r="CW51" s="18"/>
       <c r="DF51" s="18"/>
       <c r="DO51" s="18"/>
     </row>
-    <row r="52" spans="3:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:119" ht="15.75" thickBot="1">
       <c r="N52" s="28" t="s">
         <v>51</v>
       </c>
@@ -5932,26 +6382,26 @@
         <f>(BT51+BV51+BX51)/3</f>
         <v>0</v>
       </c>
-      <c r="CB52" s="54" t="s">
+      <c r="CB52" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="CC52" s="55"/>
-      <c r="CD52" s="55"/>
-      <c r="CE52" s="56">
+      <c r="CC52" s="67"/>
+      <c r="CD52" s="67"/>
+      <c r="CE52" s="54">
         <f ca="1">SUM(IF(MOD(COLUMN(O52:OFFSET(CE52,0,-1)) - COLUMN(O52), 9) = 0, O52:OFFSET(CE52,0,-1), 0))</f>
         <v>0</v>
       </c>
-      <c r="CF52" s="56"/>
-      <c r="CG52" s="57"/>
-    </row>
-    <row r="53" spans="3:119" x14ac:dyDescent="0.25">
+      <c r="CF52" s="54"/>
+      <c r="CG52" s="55"/>
+    </row>
+    <row r="53" spans="3:119">
       <c r="CB53" s="19"/>
       <c r="CC53" s="19"/>
       <c r="CD53" s="19"/>
       <c r="CE53" s="19"/>
       <c r="CF53" s="18"/>
     </row>
-    <row r="54" spans="3:119" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:119">
       <c r="H54" s="18" t="s">
         <v>12</v>
       </c>
@@ -5982,7 +6432,7 @@
       <c r="BQ54" s="29"/>
       <c r="BR54" s="29"/>
     </row>
-    <row r="55" spans="3:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:119" ht="15.75" thickBot="1">
       <c r="H55" s="18" t="s">
         <v>14</v>
       </c>
@@ -6013,7 +6463,7 @@
       <c r="BQ55" s="29"/>
       <c r="BR55" s="29"/>
     </row>
-    <row r="56" spans="3:119" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:119">
       <c r="H56" s="18" t="s">
         <v>16</v>
       </c>
@@ -6043,19 +6493,19 @@
       <c r="BP56" s="29"/>
       <c r="BQ56" s="29"/>
       <c r="BR56" s="29"/>
-      <c r="CB56" s="70" t="s">
+      <c r="CB56" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="CC56" s="71"/>
-      <c r="CD56" s="71"/>
-      <c r="CE56" s="71"/>
-      <c r="CF56" s="71"/>
+      <c r="CC56" s="58"/>
+      <c r="CD56" s="58"/>
+      <c r="CE56" s="58"/>
+      <c r="CF56" s="58"/>
       <c r="CG56" s="20">
         <f ca="1">(CC25+CC30+CC35+CC40+CC45+CC20+CC15+CC10+CC50)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="3:119" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:119">
       <c r="AI57" s="18"/>
       <c r="AR57" s="18"/>
       <c r="BA57" s="18"/>
@@ -6072,7 +6522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="3:119" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:119">
       <c r="I58" s="29" t="s">
         <v>33</v>
       </c>
@@ -6093,7 +6543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="3:119" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:119">
       <c r="H59" s="30"/>
       <c r="I59" s="29" t="s">
         <v>34</v>
@@ -6115,7 +6565,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="60" spans="3:119" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:119">
       <c r="H60" s="31"/>
       <c r="I60" s="29" t="s">
         <v>35</v>
@@ -6137,7 +6587,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="61" spans="3:119" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:119">
       <c r="H61" s="32"/>
       <c r="I61" s="29" t="s">
         <v>37</v>
@@ -6159,7 +6609,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="62" spans="3:119" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:119">
       <c r="H62" s="33"/>
       <c r="I62" s="29" t="s">
         <v>39</v>
@@ -6181,7 +6631,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="63" spans="3:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:119" ht="15.75" thickBot="1">
       <c r="H63" s="34"/>
       <c r="I63" s="29" t="s">
         <v>41</v>
@@ -6197,19 +6647,19 @@
       <c r="BA63" s="18"/>
       <c r="BJ63" s="18"/>
       <c r="BK63" s="29"/>
-      <c r="CB63" s="39" t="s">
+      <c r="CB63" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="CC63" s="40"/>
-      <c r="CD63" s="40"/>
-      <c r="CE63" s="40"/>
-      <c r="CF63" s="40"/>
+      <c r="CC63" s="70"/>
+      <c r="CD63" s="70"/>
+      <c r="CE63" s="70"/>
+      <c r="CF63" s="70"/>
       <c r="CG63" s="22">
         <f ca="1">CG62/(3*16)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="3:119" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:119">
       <c r="H64" s="35"/>
       <c r="I64" s="29" t="s">
         <v>43</v>
@@ -6220,7 +6670,7 @@
       <c r="BJ64" s="18"/>
       <c r="BK64" s="29"/>
     </row>
-    <row r="65" spans="8:63" x14ac:dyDescent="0.25">
+    <row r="65" spans="8:63">
       <c r="H65" s="36"/>
       <c r="I65" s="29" t="s">
         <v>44</v>
@@ -6231,7 +6681,7 @@
       <c r="BJ65" s="18"/>
       <c r="BK65" s="29"/>
     </row>
-    <row r="66" spans="8:63" x14ac:dyDescent="0.25">
+    <row r="66" spans="8:63">
       <c r="H66" s="36"/>
       <c r="I66" s="29" t="s">
         <v>45</v>
@@ -6242,40 +6692,113 @@
       <c r="BJ66" s="18"/>
       <c r="BK66" s="29"/>
     </row>
-    <row r="67" spans="8:63" x14ac:dyDescent="0.25">
+    <row r="67" spans="8:63">
       <c r="AR67" s="18"/>
       <c r="BA67" s="18"/>
       <c r="BJ67" s="18"/>
     </row>
-    <row r="68" spans="8:63" x14ac:dyDescent="0.25">
+    <row r="68" spans="8:63">
       <c r="AI68" s="18"/>
       <c r="AR68" s="18"/>
       <c r="BA68" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="143">
-    <mergeCell ref="CB57:CF57"/>
-    <mergeCell ref="CB58:CF58"/>
-    <mergeCell ref="CB59:CF59"/>
-    <mergeCell ref="CB60:CF60"/>
-    <mergeCell ref="CB61:CF61"/>
-    <mergeCell ref="BA29:BH30"/>
-    <mergeCell ref="H24:O25"/>
-    <mergeCell ref="BJ19:BQ20"/>
-    <mergeCell ref="CE11:CG11"/>
-    <mergeCell ref="CB12:CD12"/>
-    <mergeCell ref="CE12:CG12"/>
-    <mergeCell ref="CB11:CD11"/>
-    <mergeCell ref="H19:O20"/>
-    <mergeCell ref="Q19:X20"/>
-    <mergeCell ref="Z19:AG20"/>
-    <mergeCell ref="AI19:AP20"/>
-    <mergeCell ref="AR19:AY20"/>
-    <mergeCell ref="H14:O15"/>
-    <mergeCell ref="H34:O35"/>
-    <mergeCell ref="Q34:X35"/>
-    <mergeCell ref="Z34:AG35"/>
-    <mergeCell ref="AI34:AP35"/>
+    <mergeCell ref="CB62:CF62"/>
+    <mergeCell ref="CB63:CF63"/>
+    <mergeCell ref="H1:BZ4"/>
+    <mergeCell ref="I6:N7"/>
+    <mergeCell ref="R6:W7"/>
+    <mergeCell ref="AA6:AF7"/>
+    <mergeCell ref="AJ6:AO7"/>
+    <mergeCell ref="AS6:AX7"/>
+    <mergeCell ref="BB6:BG7"/>
+    <mergeCell ref="BS49:BZ50"/>
+    <mergeCell ref="BS9:BZ10"/>
+    <mergeCell ref="BS14:BZ15"/>
+    <mergeCell ref="BS19:BZ20"/>
+    <mergeCell ref="BS24:BZ25"/>
+    <mergeCell ref="BS29:BZ30"/>
+    <mergeCell ref="BK6:BP7"/>
+    <mergeCell ref="BT6:BY7"/>
+    <mergeCell ref="CB52:CD52"/>
+    <mergeCell ref="CE52:CG52"/>
+    <mergeCell ref="CE46:CG46"/>
+    <mergeCell ref="CE47:CG47"/>
+    <mergeCell ref="CB51:CD51"/>
+    <mergeCell ref="CE51:CG51"/>
+    <mergeCell ref="CB39:CG39"/>
+    <mergeCell ref="C19:F20"/>
+    <mergeCell ref="C24:F25"/>
+    <mergeCell ref="C29:F30"/>
+    <mergeCell ref="C34:F35"/>
+    <mergeCell ref="C39:F40"/>
+    <mergeCell ref="C44:F45"/>
+    <mergeCell ref="C49:F50"/>
+    <mergeCell ref="BS34:BZ35"/>
+    <mergeCell ref="CB46:CD46"/>
+    <mergeCell ref="CB47:CD47"/>
+    <mergeCell ref="CB49:CG49"/>
+    <mergeCell ref="CE26:CG26"/>
+    <mergeCell ref="CB27:CD27"/>
+    <mergeCell ref="CE27:CG27"/>
+    <mergeCell ref="CB29:CG29"/>
+    <mergeCell ref="CB31:CD31"/>
+    <mergeCell ref="CE31:CG31"/>
+    <mergeCell ref="BJ49:BQ50"/>
+    <mergeCell ref="BS44:BZ45"/>
+    <mergeCell ref="BS39:BZ40"/>
+    <mergeCell ref="CB19:CG19"/>
+    <mergeCell ref="CB21:CD21"/>
+    <mergeCell ref="CE21:CG21"/>
+    <mergeCell ref="CB22:CD22"/>
+    <mergeCell ref="CB41:CD41"/>
+    <mergeCell ref="CE41:CG41"/>
+    <mergeCell ref="CB42:CD42"/>
+    <mergeCell ref="CE42:CG42"/>
+    <mergeCell ref="CB44:CG44"/>
+    <mergeCell ref="CB32:CD32"/>
+    <mergeCell ref="CE32:CG32"/>
+    <mergeCell ref="CB34:CG34"/>
+    <mergeCell ref="CB36:CD36"/>
+    <mergeCell ref="CE36:CG36"/>
+    <mergeCell ref="CB37:CD37"/>
+    <mergeCell ref="CE37:CG37"/>
+    <mergeCell ref="CE22:CG22"/>
+    <mergeCell ref="CB24:CG24"/>
+    <mergeCell ref="CB26:CD26"/>
+    <mergeCell ref="H49:O50"/>
+    <mergeCell ref="Q49:X50"/>
+    <mergeCell ref="Z49:AG50"/>
+    <mergeCell ref="AI49:AP50"/>
+    <mergeCell ref="AR49:AY50"/>
+    <mergeCell ref="BA49:BH50"/>
+    <mergeCell ref="BJ39:BQ40"/>
+    <mergeCell ref="H44:O45"/>
+    <mergeCell ref="Q44:X45"/>
+    <mergeCell ref="Z44:AG45"/>
+    <mergeCell ref="AI44:AP45"/>
+    <mergeCell ref="AR44:AY45"/>
+    <mergeCell ref="BA44:BH45"/>
+    <mergeCell ref="BJ44:BQ45"/>
+    <mergeCell ref="H39:O40"/>
+    <mergeCell ref="Q39:X40"/>
+    <mergeCell ref="Z39:AG40"/>
+    <mergeCell ref="AI39:AP40"/>
+    <mergeCell ref="AR39:AY40"/>
+    <mergeCell ref="BA39:BH40"/>
+    <mergeCell ref="BJ29:BQ30"/>
+    <mergeCell ref="BJ34:BQ35"/>
+    <mergeCell ref="Z24:AG25"/>
+    <mergeCell ref="AI24:AP25"/>
+    <mergeCell ref="AR24:AY25"/>
+    <mergeCell ref="BA24:BH25"/>
+    <mergeCell ref="H29:O30"/>
+    <mergeCell ref="Q29:X30"/>
+    <mergeCell ref="Z29:AG30"/>
+    <mergeCell ref="AI29:AP30"/>
+    <mergeCell ref="AR29:AY30"/>
+    <mergeCell ref="BJ24:BQ25"/>
     <mergeCell ref="BA9:BH10"/>
     <mergeCell ref="AR9:AY10"/>
     <mergeCell ref="AI9:AP10"/>
@@ -6300,103 +6823,30 @@
     <mergeCell ref="CB17:CD17"/>
     <mergeCell ref="CE16:CG16"/>
     <mergeCell ref="CE17:CG17"/>
+    <mergeCell ref="CB57:CF57"/>
+    <mergeCell ref="CB58:CF58"/>
+    <mergeCell ref="CB59:CF59"/>
+    <mergeCell ref="CB60:CF60"/>
+    <mergeCell ref="CB61:CF61"/>
+    <mergeCell ref="BA29:BH30"/>
+    <mergeCell ref="H24:O25"/>
+    <mergeCell ref="BJ19:BQ20"/>
+    <mergeCell ref="CE11:CG11"/>
+    <mergeCell ref="CB12:CD12"/>
+    <mergeCell ref="CE12:CG12"/>
+    <mergeCell ref="CB11:CD11"/>
+    <mergeCell ref="H19:O20"/>
+    <mergeCell ref="Q19:X20"/>
+    <mergeCell ref="Z19:AG20"/>
+    <mergeCell ref="AI19:AP20"/>
+    <mergeCell ref="AR19:AY20"/>
+    <mergeCell ref="H14:O15"/>
+    <mergeCell ref="H34:O35"/>
+    <mergeCell ref="Q34:X35"/>
+    <mergeCell ref="Z34:AG35"/>
+    <mergeCell ref="AI34:AP35"/>
     <mergeCell ref="AR34:AY35"/>
     <mergeCell ref="BA34:BH35"/>
-    <mergeCell ref="BJ34:BQ35"/>
-    <mergeCell ref="Z24:AG25"/>
-    <mergeCell ref="AI24:AP25"/>
-    <mergeCell ref="AR24:AY25"/>
-    <mergeCell ref="BA24:BH25"/>
-    <mergeCell ref="H29:O30"/>
-    <mergeCell ref="Q29:X30"/>
-    <mergeCell ref="Z29:AG30"/>
-    <mergeCell ref="AI29:AP30"/>
-    <mergeCell ref="AR29:AY30"/>
-    <mergeCell ref="BJ24:BQ25"/>
-    <mergeCell ref="CE22:CG22"/>
-    <mergeCell ref="CB24:CG24"/>
-    <mergeCell ref="CB26:CD26"/>
-    <mergeCell ref="H49:O50"/>
-    <mergeCell ref="Q49:X50"/>
-    <mergeCell ref="Z49:AG50"/>
-    <mergeCell ref="AI49:AP50"/>
-    <mergeCell ref="AR49:AY50"/>
-    <mergeCell ref="BA49:BH50"/>
-    <mergeCell ref="BJ39:BQ40"/>
-    <mergeCell ref="H44:O45"/>
-    <mergeCell ref="Q44:X45"/>
-    <mergeCell ref="Z44:AG45"/>
-    <mergeCell ref="AI44:AP45"/>
-    <mergeCell ref="AR44:AY45"/>
-    <mergeCell ref="BA44:BH45"/>
-    <mergeCell ref="BJ44:BQ45"/>
-    <mergeCell ref="H39:O40"/>
-    <mergeCell ref="Q39:X40"/>
-    <mergeCell ref="Z39:AG40"/>
-    <mergeCell ref="AI39:AP40"/>
-    <mergeCell ref="AR39:AY40"/>
-    <mergeCell ref="BA39:BH40"/>
-    <mergeCell ref="BJ29:BQ30"/>
-    <mergeCell ref="CB41:CD41"/>
-    <mergeCell ref="CE41:CG41"/>
-    <mergeCell ref="CB42:CD42"/>
-    <mergeCell ref="CE42:CG42"/>
-    <mergeCell ref="CB44:CG44"/>
-    <mergeCell ref="CB32:CD32"/>
-    <mergeCell ref="CE32:CG32"/>
-    <mergeCell ref="CB34:CG34"/>
-    <mergeCell ref="CB36:CD36"/>
-    <mergeCell ref="CE36:CG36"/>
-    <mergeCell ref="CB37:CD37"/>
-    <mergeCell ref="CE37:CG37"/>
-    <mergeCell ref="C19:F20"/>
-    <mergeCell ref="C24:F25"/>
-    <mergeCell ref="C29:F30"/>
-    <mergeCell ref="C34:F35"/>
-    <mergeCell ref="C39:F40"/>
-    <mergeCell ref="C44:F45"/>
-    <mergeCell ref="C49:F50"/>
-    <mergeCell ref="BS34:BZ35"/>
-    <mergeCell ref="CB46:CD46"/>
-    <mergeCell ref="CB47:CD47"/>
-    <mergeCell ref="CB49:CG49"/>
-    <mergeCell ref="CE26:CG26"/>
-    <mergeCell ref="CB27:CD27"/>
-    <mergeCell ref="CE27:CG27"/>
-    <mergeCell ref="CB29:CG29"/>
-    <mergeCell ref="CB31:CD31"/>
-    <mergeCell ref="CE31:CG31"/>
-    <mergeCell ref="BJ49:BQ50"/>
-    <mergeCell ref="BS44:BZ45"/>
-    <mergeCell ref="BS39:BZ40"/>
-    <mergeCell ref="CB19:CG19"/>
-    <mergeCell ref="CB21:CD21"/>
-    <mergeCell ref="CE21:CG21"/>
-    <mergeCell ref="CB22:CD22"/>
-    <mergeCell ref="CB62:CF62"/>
-    <mergeCell ref="CB63:CF63"/>
-    <mergeCell ref="H1:BZ4"/>
-    <mergeCell ref="I6:N7"/>
-    <mergeCell ref="R6:W7"/>
-    <mergeCell ref="AA6:AF7"/>
-    <mergeCell ref="AJ6:AO7"/>
-    <mergeCell ref="AS6:AX7"/>
-    <mergeCell ref="BB6:BG7"/>
-    <mergeCell ref="BS49:BZ50"/>
-    <mergeCell ref="BS9:BZ10"/>
-    <mergeCell ref="BS14:BZ15"/>
-    <mergeCell ref="BS19:BZ20"/>
-    <mergeCell ref="BS24:BZ25"/>
-    <mergeCell ref="BS29:BZ30"/>
-    <mergeCell ref="BK6:BP7"/>
-    <mergeCell ref="BT6:BY7"/>
-    <mergeCell ref="CB52:CD52"/>
-    <mergeCell ref="CE52:CG52"/>
-    <mergeCell ref="CE46:CG46"/>
-    <mergeCell ref="CE47:CG47"/>
-    <mergeCell ref="CB51:CD51"/>
-    <mergeCell ref="CE51:CG51"/>
-    <mergeCell ref="CB39:CG39"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="24" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
@@ -6411,7 +6861,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ACDF5BE-B64F-40C3-9167-0581D119B289}">
   <dimension ref="A1:N7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="11.42578125" style="5" customWidth="1"/>
     <col min="3" max="3" width="22.140625" style="5" customWidth="1"/>
@@ -6430,7 +6880,7 @@
     <col min="257" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="37.5" customHeight="1">
       <c r="A1" s="81" t="s">
         <v>0</v>
       </c>
@@ -6448,7 +6898,7 @@
       <c r="M1" s="81"/>
       <c r="N1" s="81"/>
     </row>
-    <row r="2" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="32.25" customHeight="1">
       <c r="A2" s="81"/>
       <c r="B2" s="81"/>
       <c r="C2" s="81"/>
@@ -6464,7 +6914,7 @@
       <c r="M2" s="81"/>
       <c r="N2" s="81"/>
     </row>
-    <row r="3" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="21" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -6488,7 +6938,7 @@
       <c r="M3" s="83"/>
       <c r="N3" s="83"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14">
       <c r="A4" s="78"/>
       <c r="B4" s="78"/>
       <c r="C4" s="82"/>
@@ -6520,7 +6970,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="14.45" customHeight="1">
       <c r="A5" s="78"/>
       <c r="B5" s="78"/>
       <c r="C5" s="82"/>
@@ -6542,7 +6992,7 @@
       <c r="M5" s="79"/>
       <c r="N5" s="84"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14">
       <c r="A6" s="78"/>
       <c r="B6" s="78"/>
       <c r="C6" s="82"/>
@@ -6564,7 +7014,7 @@
       <c r="M6" s="79"/>
       <c r="N6" s="84"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14">
       <c r="A7" s="78"/>
       <c r="B7" s="78"/>
       <c r="C7" s="82"/>
@@ -6608,7 +7058,4203 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807DF769-F469-41FB-B301-1E52A25AE3E3}">
+  <dimension ref="A1:AA84"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="50.140625" style="97" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" style="96" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48" style="97" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" style="98" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" style="97" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="96" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="96" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" style="96" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" style="96" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" style="96" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="96" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" style="96" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="96" customWidth="1"/>
+    <col min="14" max="14" width="12.5703125" style="96" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22" style="86" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22" style="86" customWidth="1"/>
+    <col min="17" max="17" width="4.7109375" style="86" customWidth="1"/>
+    <col min="18" max="20" width="19.5703125" style="87" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="87" customWidth="1"/>
+    <col min="22" max="22" width="8" style="87" customWidth="1"/>
+    <col min="23" max="25" width="19.5703125" style="87" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="87" customWidth="1"/>
+    <col min="27" max="27" width="8" style="87" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="86"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" ht="27.75">
+      <c r="A1" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="85"/>
+    </row>
+    <row r="2" spans="1:27" ht="17.25" customHeight="1">
+      <c r="A2" s="88"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="88"/>
+      <c r="M2" s="88"/>
+      <c r="N2" s="88"/>
+    </row>
+    <row r="3" spans="1:27" ht="27.75">
+      <c r="A3" s="90" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="91" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="91"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="91"/>
+      <c r="K3" s="91"/>
+      <c r="L3" s="91"/>
+      <c r="M3" s="91"/>
+      <c r="N3" s="88"/>
+    </row>
+    <row r="4" spans="1:27" ht="20.25" customHeight="1">
+      <c r="A4" s="92" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="93" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="93"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93"/>
+      <c r="M4" s="93"/>
+      <c r="N4" s="88"/>
+    </row>
+    <row r="5" spans="1:27" ht="20.25" customHeight="1">
+      <c r="A5" s="92" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="94" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" s="94"/>
+      <c r="D5" s="94"/>
+      <c r="E5" s="94"/>
+      <c r="F5" s="94"/>
+      <c r="G5" s="94"/>
+      <c r="H5" s="94"/>
+      <c r="I5" s="94"/>
+      <c r="J5" s="94"/>
+      <c r="K5" s="94"/>
+      <c r="L5" s="94"/>
+      <c r="M5" s="94"/>
+      <c r="N5" s="88"/>
+    </row>
+    <row r="6" spans="1:27" ht="20.25" customHeight="1">
+      <c r="A6" s="92" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" s="94" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" s="94"/>
+      <c r="D6" s="94"/>
+      <c r="E6" s="94"/>
+      <c r="F6" s="94"/>
+      <c r="G6" s="94"/>
+      <c r="H6" s="94"/>
+      <c r="I6" s="94"/>
+      <c r="J6" s="94"/>
+      <c r="K6" s="94"/>
+      <c r="L6" s="94"/>
+      <c r="M6" s="94"/>
+      <c r="N6" s="88"/>
+    </row>
+    <row r="7" spans="1:27" ht="20.25" customHeight="1">
+      <c r="A7" s="95" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="94" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="94"/>
+      <c r="D7" s="94"/>
+      <c r="E7" s="94"/>
+      <c r="F7" s="94"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="94"/>
+      <c r="I7" s="94"/>
+      <c r="J7" s="94"/>
+      <c r="K7" s="94"/>
+      <c r="L7" s="94"/>
+      <c r="M7" s="94"/>
+      <c r="N7" s="88"/>
+    </row>
+    <row r="8" spans="1:27" ht="20.25" customHeight="1">
+      <c r="A8" s="95" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="94" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="94"/>
+      <c r="D8" s="94"/>
+      <c r="E8" s="94"/>
+      <c r="F8" s="94"/>
+      <c r="G8" s="94"/>
+      <c r="H8" s="94"/>
+      <c r="I8" s="94"/>
+      <c r="J8" s="94"/>
+      <c r="K8" s="94"/>
+      <c r="L8" s="94"/>
+      <c r="M8" s="94"/>
+      <c r="N8" s="88"/>
+    </row>
+    <row r="9" spans="1:27" ht="28.5">
+      <c r="A9" s="92" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" s="94" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="94"/>
+      <c r="D9" s="94"/>
+      <c r="E9" s="94"/>
+      <c r="F9" s="94"/>
+      <c r="G9" s="94"/>
+      <c r="H9" s="94"/>
+      <c r="I9" s="94"/>
+      <c r="J9" s="94"/>
+      <c r="K9" s="94"/>
+      <c r="L9" s="94"/>
+      <c r="M9" s="94"/>
+      <c r="N9" s="88"/>
+    </row>
+    <row r="10" spans="1:27" ht="24" customHeight="1">
+      <c r="A10" s="86"/>
+      <c r="B10" s="86"/>
+      <c r="C10" s="86"/>
+      <c r="D10" s="86"/>
+      <c r="E10" s="86"/>
+      <c r="F10" s="86"/>
+      <c r="G10" s="86"/>
+      <c r="H10" s="86"/>
+      <c r="I10" s="86"/>
+      <c r="J10" s="86"/>
+      <c r="K10" s="86"/>
+      <c r="L10" s="86"/>
+      <c r="M10" s="86"/>
+    </row>
+    <row r="11" spans="1:27" ht="19.5">
+      <c r="E11" s="99" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="99"/>
+      <c r="I11" s="99"/>
+      <c r="J11" s="100" t="s">
+        <v>87</v>
+      </c>
+      <c r="K11" s="100"/>
+      <c r="L11" s="100"/>
+      <c r="M11" s="100"/>
+      <c r="N11" s="100"/>
+      <c r="R11" s="101" t="s">
+        <v>6</v>
+      </c>
+      <c r="S11" s="101"/>
+      <c r="T11" s="101"/>
+      <c r="U11" s="101"/>
+      <c r="V11" s="101"/>
+      <c r="W11" s="102" t="s">
+        <v>9</v>
+      </c>
+      <c r="X11" s="103"/>
+      <c r="Y11" s="103"/>
+      <c r="Z11" s="103"/>
+      <c r="AA11" s="103"/>
+    </row>
+    <row r="12" spans="1:27" ht="75">
+      <c r="A12" s="104" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="105" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="105" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" s="106" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" s="107" t="s">
+        <v>91</v>
+      </c>
+      <c r="F12" s="107" t="s">
+        <v>92</v>
+      </c>
+      <c r="G12" s="107" t="s">
+        <v>93</v>
+      </c>
+      <c r="H12" s="107" t="s">
+        <v>94</v>
+      </c>
+      <c r="I12" s="108" t="s">
+        <v>95</v>
+      </c>
+      <c r="J12" s="109" t="s">
+        <v>91</v>
+      </c>
+      <c r="K12" s="109" t="s">
+        <v>92</v>
+      </c>
+      <c r="L12" s="109" t="s">
+        <v>93</v>
+      </c>
+      <c r="M12" s="109" t="s">
+        <v>94</v>
+      </c>
+      <c r="N12" s="110" t="s">
+        <v>95</v>
+      </c>
+      <c r="O12" s="111" t="s">
+        <v>96</v>
+      </c>
+      <c r="P12" s="112" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q12" s="113"/>
+      <c r="R12" s="114" t="s">
+        <v>98</v>
+      </c>
+      <c r="S12" s="114" t="s">
+        <v>99</v>
+      </c>
+      <c r="T12" s="114" t="s">
+        <v>100</v>
+      </c>
+      <c r="U12" s="114" t="s">
+        <v>101</v>
+      </c>
+      <c r="V12" s="114" t="s">
+        <v>95</v>
+      </c>
+      <c r="W12" s="115" t="s">
+        <v>98</v>
+      </c>
+      <c r="X12" s="116" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y12" s="116" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z12" s="116" t="s">
+        <v>101</v>
+      </c>
+      <c r="AA12" s="116" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27">
+      <c r="A13" s="117"/>
+      <c r="B13" s="119"/>
+      <c r="C13" s="118"/>
+      <c r="D13" s="119"/>
+      <c r="E13" s="120"/>
+      <c r="F13" s="120"/>
+      <c r="G13" s="120"/>
+      <c r="H13" s="120"/>
+      <c r="I13" s="120">
+        <f t="shared" ref="I13:I76" si="0">((F13+G13+H13)*16)/48</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="121"/>
+      <c r="K13" s="121"/>
+      <c r="L13" s="121"/>
+      <c r="M13" s="121"/>
+      <c r="N13" s="122">
+        <f t="shared" ref="N13:N76" si="1">((K13+L13+M13)*16)/48</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="123"/>
+      <c r="P13" s="124"/>
+      <c r="Q13" s="125"/>
+      <c r="R13" s="126">
+        <f>F13*16</f>
+        <v>0</v>
+      </c>
+      <c r="S13" s="126">
+        <f t="shared" ref="S13:T28" si="2">G13*16</f>
+        <v>0</v>
+      </c>
+      <c r="T13" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="126">
+        <f t="shared" ref="U13:U56" si="3">R13+S13+T13</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="126">
+        <f>I13</f>
+        <v>0</v>
+      </c>
+      <c r="W13" s="127">
+        <f>K13*16</f>
+        <v>0</v>
+      </c>
+      <c r="X13" s="128">
+        <f t="shared" ref="X13:Y28" si="4">L13*16</f>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="128">
+        <f t="shared" ref="Z13:Z56" si="5">W13+X13+Y13</f>
+        <v>0</v>
+      </c>
+      <c r="AA13" s="128">
+        <f>N13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="18" customHeight="1">
+      <c r="A14" s="117"/>
+      <c r="B14" s="119"/>
+      <c r="C14" s="118"/>
+      <c r="D14" s="119"/>
+      <c r="E14" s="120"/>
+      <c r="F14" s="120"/>
+      <c r="G14" s="120"/>
+      <c r="H14" s="120"/>
+      <c r="I14" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="121"/>
+      <c r="K14" s="121"/>
+      <c r="L14" s="121"/>
+      <c r="M14" s="121"/>
+      <c r="N14" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O14" s="123"/>
+      <c r="P14" s="124"/>
+      <c r="Q14" s="125"/>
+      <c r="R14" s="126">
+        <f t="shared" ref="R14:T56" si="6">F14*16</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="126">
+        <f t="shared" ref="V14:V56" si="7">I14</f>
+        <v>0</v>
+      </c>
+      <c r="W14" s="127">
+        <f t="shared" ref="W14:Y56" si="8">K14*16</f>
+        <v>0</v>
+      </c>
+      <c r="X14" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z14" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA14" s="128">
+        <f t="shared" ref="AA14:AA56" si="9">N14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27">
+      <c r="A15" s="117"/>
+      <c r="B15" s="119"/>
+      <c r="C15" s="118"/>
+      <c r="D15" s="119"/>
+      <c r="E15" s="120"/>
+      <c r="F15" s="120"/>
+      <c r="G15" s="120"/>
+      <c r="H15" s="120"/>
+      <c r="I15" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="121"/>
+      <c r="K15" s="121"/>
+      <c r="L15" s="121"/>
+      <c r="M15" s="121"/>
+      <c r="N15" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O15" s="123"/>
+      <c r="P15" s="124"/>
+      <c r="Q15" s="125"/>
+      <c r="R15" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X15" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z15" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA15" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="18" customHeight="1">
+      <c r="A16" s="117"/>
+      <c r="B16" s="119"/>
+      <c r="C16" s="118"/>
+      <c r="D16" s="119"/>
+      <c r="E16" s="120"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="120"/>
+      <c r="H16" s="120"/>
+      <c r="I16" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="121"/>
+      <c r="K16" s="121"/>
+      <c r="L16" s="121"/>
+      <c r="M16" s="121"/>
+      <c r="N16" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="123"/>
+      <c r="P16" s="124"/>
+      <c r="Q16" s="125"/>
+      <c r="R16" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z16" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA16" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27">
+      <c r="A17" s="117"/>
+      <c r="B17" s="119"/>
+      <c r="C17" s="118"/>
+      <c r="D17" s="119"/>
+      <c r="E17" s="120"/>
+      <c r="F17" s="120"/>
+      <c r="G17" s="120"/>
+      <c r="H17" s="120"/>
+      <c r="I17" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="121"/>
+      <c r="K17" s="121"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O17" s="123"/>
+      <c r="P17" s="124"/>
+      <c r="Q17" s="125"/>
+      <c r="R17" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z17" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA17" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27">
+      <c r="A18" s="117"/>
+      <c r="B18" s="119"/>
+      <c r="C18" s="118"/>
+      <c r="D18" s="119"/>
+      <c r="E18" s="120"/>
+      <c r="F18" s="120"/>
+      <c r="G18" s="120"/>
+      <c r="H18" s="120"/>
+      <c r="I18" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="121"/>
+      <c r="K18" s="121"/>
+      <c r="L18" s="121"/>
+      <c r="M18" s="121"/>
+      <c r="N18" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O18" s="123"/>
+      <c r="P18" s="124"/>
+      <c r="Q18" s="125"/>
+      <c r="R18" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X18" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z18" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA18" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27">
+      <c r="A19" s="117"/>
+      <c r="B19" s="119"/>
+      <c r="C19" s="118"/>
+      <c r="D19" s="119"/>
+      <c r="E19" s="120"/>
+      <c r="F19" s="120"/>
+      <c r="G19" s="120"/>
+      <c r="H19" s="120"/>
+      <c r="I19" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="121"/>
+      <c r="K19" s="121"/>
+      <c r="L19" s="121"/>
+      <c r="M19" s="121"/>
+      <c r="N19" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O19" s="123"/>
+      <c r="P19" s="124"/>
+      <c r="Q19" s="125"/>
+      <c r="R19" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z19" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA19" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27">
+      <c r="A20" s="117"/>
+      <c r="B20" s="119"/>
+      <c r="C20" s="118"/>
+      <c r="D20" s="119"/>
+      <c r="E20" s="120"/>
+      <c r="F20" s="120"/>
+      <c r="G20" s="120"/>
+      <c r="H20" s="120"/>
+      <c r="I20" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="121"/>
+      <c r="K20" s="121"/>
+      <c r="L20" s="121"/>
+      <c r="M20" s="121"/>
+      <c r="N20" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O20" s="123"/>
+      <c r="P20" s="124"/>
+      <c r="Q20" s="125"/>
+      <c r="R20" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X20" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z20" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA20" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27">
+      <c r="A21" s="117"/>
+      <c r="B21" s="119"/>
+      <c r="C21" s="118"/>
+      <c r="D21" s="119"/>
+      <c r="E21" s="120"/>
+      <c r="F21" s="120"/>
+      <c r="G21" s="120"/>
+      <c r="H21" s="120"/>
+      <c r="I21" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="121"/>
+      <c r="K21" s="121"/>
+      <c r="L21" s="121"/>
+      <c r="M21" s="121"/>
+      <c r="N21" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O21" s="123"/>
+      <c r="P21" s="124"/>
+      <c r="Q21" s="125"/>
+      <c r="R21" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X21" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z21" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA21" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27">
+      <c r="A22" s="117"/>
+      <c r="B22" s="119"/>
+      <c r="C22" s="118"/>
+      <c r="D22" s="119"/>
+      <c r="E22" s="120"/>
+      <c r="F22" s="120"/>
+      <c r="G22" s="120"/>
+      <c r="H22" s="120"/>
+      <c r="I22" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="121"/>
+      <c r="K22" s="121"/>
+      <c r="L22" s="121"/>
+      <c r="M22" s="121"/>
+      <c r="N22" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O22" s="123"/>
+      <c r="P22" s="124"/>
+      <c r="Q22" s="125"/>
+      <c r="R22" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X22" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z22" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA22" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27">
+      <c r="A23" s="117"/>
+      <c r="B23" s="119"/>
+      <c r="C23" s="118"/>
+      <c r="D23" s="119"/>
+      <c r="E23" s="120"/>
+      <c r="F23" s="120"/>
+      <c r="G23" s="120"/>
+      <c r="H23" s="120"/>
+      <c r="I23" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="121"/>
+      <c r="K23" s="121"/>
+      <c r="L23" s="121"/>
+      <c r="M23" s="121"/>
+      <c r="N23" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O23" s="123"/>
+      <c r="P23" s="124"/>
+      <c r="Q23" s="125"/>
+      <c r="R23" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X23" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z23" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA23" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27">
+      <c r="A24" s="117"/>
+      <c r="B24" s="119"/>
+      <c r="C24" s="118"/>
+      <c r="D24" s="119"/>
+      <c r="E24" s="120"/>
+      <c r="F24" s="120"/>
+      <c r="G24" s="120"/>
+      <c r="H24" s="120"/>
+      <c r="I24" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="121"/>
+      <c r="K24" s="121"/>
+      <c r="L24" s="121"/>
+      <c r="M24" s="121"/>
+      <c r="N24" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O24" s="123"/>
+      <c r="P24" s="124"/>
+      <c r="Q24" s="125"/>
+      <c r="R24" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X24" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z24" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA24" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27">
+      <c r="A25" s="117"/>
+      <c r="B25" s="119"/>
+      <c r="C25" s="118"/>
+      <c r="D25" s="119"/>
+      <c r="E25" s="120"/>
+      <c r="F25" s="120"/>
+      <c r="G25" s="120"/>
+      <c r="H25" s="120"/>
+      <c r="I25" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="121"/>
+      <c r="K25" s="121"/>
+      <c r="L25" s="121"/>
+      <c r="M25" s="121"/>
+      <c r="N25" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O25" s="123"/>
+      <c r="P25" s="124"/>
+      <c r="Q25" s="125"/>
+      <c r="R25" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X25" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z25" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA25" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27">
+      <c r="A26" s="117"/>
+      <c r="B26" s="119"/>
+      <c r="C26" s="118"/>
+      <c r="D26" s="119"/>
+      <c r="E26" s="120"/>
+      <c r="F26" s="120"/>
+      <c r="G26" s="120"/>
+      <c r="H26" s="120"/>
+      <c r="I26" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="121"/>
+      <c r="K26" s="121"/>
+      <c r="L26" s="121"/>
+      <c r="M26" s="121"/>
+      <c r="N26" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O26" s="123"/>
+      <c r="P26" s="124"/>
+      <c r="Q26" s="125"/>
+      <c r="R26" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X26" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z26" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA26" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27">
+      <c r="A27" s="117"/>
+      <c r="B27" s="119"/>
+      <c r="C27" s="118"/>
+      <c r="D27" s="119"/>
+      <c r="E27" s="120"/>
+      <c r="F27" s="120"/>
+      <c r="G27" s="120"/>
+      <c r="H27" s="120"/>
+      <c r="I27" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="121"/>
+      <c r="K27" s="121"/>
+      <c r="L27" s="121"/>
+      <c r="M27" s="121"/>
+      <c r="N27" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O27" s="123"/>
+      <c r="P27" s="124"/>
+      <c r="Q27" s="125"/>
+      <c r="R27" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z27" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA27" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27">
+      <c r="A28" s="117"/>
+      <c r="B28" s="119"/>
+      <c r="C28" s="118"/>
+      <c r="D28" s="119"/>
+      <c r="E28" s="120"/>
+      <c r="F28" s="120"/>
+      <c r="G28" s="120"/>
+      <c r="H28" s="120"/>
+      <c r="I28" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="121"/>
+      <c r="K28" s="121"/>
+      <c r="L28" s="121"/>
+      <c r="M28" s="121"/>
+      <c r="N28" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O28" s="123"/>
+      <c r="P28" s="124"/>
+      <c r="Q28" s="125"/>
+      <c r="R28" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X28" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="128">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z28" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA28" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27">
+      <c r="A29" s="117"/>
+      <c r="B29" s="119"/>
+      <c r="C29" s="118"/>
+      <c r="D29" s="119"/>
+      <c r="E29" s="120"/>
+      <c r="F29" s="120"/>
+      <c r="G29" s="120"/>
+      <c r="H29" s="120"/>
+      <c r="I29" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="121"/>
+      <c r="K29" s="121"/>
+      <c r="L29" s="121"/>
+      <c r="M29" s="121"/>
+      <c r="N29" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O29" s="123"/>
+      <c r="P29" s="124"/>
+      <c r="Q29" s="125"/>
+      <c r="R29" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S29" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W29" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X29" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z29" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA29" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27">
+      <c r="A30" s="117"/>
+      <c r="B30" s="119"/>
+      <c r="C30" s="118"/>
+      <c r="D30" s="119"/>
+      <c r="E30" s="120"/>
+      <c r="F30" s="120"/>
+      <c r="G30" s="120"/>
+      <c r="H30" s="120"/>
+      <c r="I30" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="121"/>
+      <c r="K30" s="121"/>
+      <c r="L30" s="121"/>
+      <c r="M30" s="121"/>
+      <c r="N30" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O30" s="123"/>
+      <c r="P30" s="124"/>
+      <c r="Q30" s="125"/>
+      <c r="R30" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W30" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X30" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z30" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA30" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27">
+      <c r="A31" s="117"/>
+      <c r="B31" s="119"/>
+      <c r="C31" s="118"/>
+      <c r="D31" s="119"/>
+      <c r="E31" s="120"/>
+      <c r="F31" s="120"/>
+      <c r="G31" s="120"/>
+      <c r="H31" s="120"/>
+      <c r="I31" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="121"/>
+      <c r="K31" s="121"/>
+      <c r="L31" s="121"/>
+      <c r="M31" s="121"/>
+      <c r="N31" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O31" s="123"/>
+      <c r="P31" s="124"/>
+      <c r="Q31" s="125"/>
+      <c r="R31" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W31" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X31" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z31" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA31" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27">
+      <c r="A32" s="117"/>
+      <c r="B32" s="119"/>
+      <c r="C32" s="118"/>
+      <c r="D32" s="119"/>
+      <c r="E32" s="120"/>
+      <c r="F32" s="120"/>
+      <c r="G32" s="120"/>
+      <c r="H32" s="120"/>
+      <c r="I32" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="121"/>
+      <c r="K32" s="121"/>
+      <c r="L32" s="121"/>
+      <c r="M32" s="121"/>
+      <c r="N32" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O32" s="123"/>
+      <c r="P32" s="124"/>
+      <c r="Q32" s="125"/>
+      <c r="R32" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T32" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W32" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z32" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA32" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27">
+      <c r="A33" s="117"/>
+      <c r="B33" s="119"/>
+      <c r="C33" s="118"/>
+      <c r="D33" s="119"/>
+      <c r="E33" s="120"/>
+      <c r="F33" s="120"/>
+      <c r="G33" s="120"/>
+      <c r="H33" s="120"/>
+      <c r="I33" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="121"/>
+      <c r="K33" s="121"/>
+      <c r="L33" s="121"/>
+      <c r="M33" s="121"/>
+      <c r="N33" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O33" s="123"/>
+      <c r="P33" s="124"/>
+      <c r="Q33" s="125"/>
+      <c r="R33" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W33" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X33" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z33" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA33" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27">
+      <c r="A34" s="117"/>
+      <c r="B34" s="119"/>
+      <c r="C34" s="118"/>
+      <c r="D34" s="119"/>
+      <c r="E34" s="120"/>
+      <c r="F34" s="120"/>
+      <c r="G34" s="120"/>
+      <c r="H34" s="120"/>
+      <c r="I34" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="121"/>
+      <c r="K34" s="121"/>
+      <c r="L34" s="121"/>
+      <c r="M34" s="121"/>
+      <c r="N34" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O34" s="123"/>
+      <c r="P34" s="124"/>
+      <c r="Q34" s="125"/>
+      <c r="R34" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U34" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z34" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA34" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27">
+      <c r="A35" s="117"/>
+      <c r="B35" s="119"/>
+      <c r="C35" s="118"/>
+      <c r="D35" s="119"/>
+      <c r="E35" s="120"/>
+      <c r="F35" s="120"/>
+      <c r="G35" s="120"/>
+      <c r="H35" s="120"/>
+      <c r="I35" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="121"/>
+      <c r="K35" s="121"/>
+      <c r="L35" s="121"/>
+      <c r="M35" s="121"/>
+      <c r="N35" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O35" s="123"/>
+      <c r="P35" s="124"/>
+      <c r="Q35" s="125"/>
+      <c r="R35" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S35" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W35" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X35" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z35" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA35" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27">
+      <c r="A36" s="117"/>
+      <c r="B36" s="119"/>
+      <c r="C36" s="118"/>
+      <c r="D36" s="119"/>
+      <c r="E36" s="120"/>
+      <c r="F36" s="120"/>
+      <c r="G36" s="120"/>
+      <c r="H36" s="120"/>
+      <c r="I36" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="121"/>
+      <c r="K36" s="121"/>
+      <c r="L36" s="121"/>
+      <c r="M36" s="121"/>
+      <c r="N36" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O36" s="123"/>
+      <c r="P36" s="124"/>
+      <c r="Q36" s="125"/>
+      <c r="R36" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z36" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA36" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27">
+      <c r="A37" s="117"/>
+      <c r="B37" s="119"/>
+      <c r="C37" s="118"/>
+      <c r="D37" s="119"/>
+      <c r="E37" s="120"/>
+      <c r="F37" s="120"/>
+      <c r="G37" s="120"/>
+      <c r="H37" s="120"/>
+      <c r="I37" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="121"/>
+      <c r="K37" s="121"/>
+      <c r="L37" s="121"/>
+      <c r="M37" s="121"/>
+      <c r="N37" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O37" s="123"/>
+      <c r="P37" s="124"/>
+      <c r="Q37" s="125"/>
+      <c r="R37" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U37" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z37" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA37" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27">
+      <c r="A38" s="117"/>
+      <c r="B38" s="119"/>
+      <c r="C38" s="118"/>
+      <c r="D38" s="119"/>
+      <c r="E38" s="120"/>
+      <c r="F38" s="120"/>
+      <c r="G38" s="120"/>
+      <c r="H38" s="120"/>
+      <c r="I38" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="121"/>
+      <c r="K38" s="121"/>
+      <c r="L38" s="121"/>
+      <c r="M38" s="121"/>
+      <c r="N38" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O38" s="123"/>
+      <c r="P38" s="124"/>
+      <c r="Q38" s="125"/>
+      <c r="R38" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S38" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V38" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W38" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X38" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z38" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA38" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27">
+      <c r="A39" s="117"/>
+      <c r="B39" s="119"/>
+      <c r="C39" s="118"/>
+      <c r="D39" s="119"/>
+      <c r="E39" s="120"/>
+      <c r="F39" s="120"/>
+      <c r="G39" s="120"/>
+      <c r="H39" s="120"/>
+      <c r="I39" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="121"/>
+      <c r="K39" s="121"/>
+      <c r="L39" s="121"/>
+      <c r="M39" s="121"/>
+      <c r="N39" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O39" s="123"/>
+      <c r="P39" s="124"/>
+      <c r="Q39" s="125"/>
+      <c r="R39" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V39" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W39" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X39" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z39" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA39" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:27">
+      <c r="A40" s="117"/>
+      <c r="B40" s="119"/>
+      <c r="C40" s="118"/>
+      <c r="D40" s="119"/>
+      <c r="E40" s="120"/>
+      <c r="F40" s="120"/>
+      <c r="G40" s="120"/>
+      <c r="H40" s="120"/>
+      <c r="I40" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="121"/>
+      <c r="K40" s="121"/>
+      <c r="L40" s="121"/>
+      <c r="M40" s="121"/>
+      <c r="N40" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O40" s="123"/>
+      <c r="P40" s="124"/>
+      <c r="Q40" s="125"/>
+      <c r="R40" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U40" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z40" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA40" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:27">
+      <c r="A41" s="117"/>
+      <c r="B41" s="119"/>
+      <c r="C41" s="118"/>
+      <c r="D41" s="119"/>
+      <c r="E41" s="120"/>
+      <c r="F41" s="120"/>
+      <c r="G41" s="120"/>
+      <c r="H41" s="120"/>
+      <c r="I41" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="121"/>
+      <c r="K41" s="121"/>
+      <c r="L41" s="121"/>
+      <c r="M41" s="121"/>
+      <c r="N41" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O41" s="123"/>
+      <c r="P41" s="124"/>
+      <c r="Q41" s="125"/>
+      <c r="R41" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S41" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V41" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W41" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X41" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y41" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z41" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA41" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27">
+      <c r="A42" s="117"/>
+      <c r="B42" s="119"/>
+      <c r="C42" s="118"/>
+      <c r="D42" s="119"/>
+      <c r="E42" s="120"/>
+      <c r="F42" s="120"/>
+      <c r="G42" s="120"/>
+      <c r="H42" s="120"/>
+      <c r="I42" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="121"/>
+      <c r="K42" s="121"/>
+      <c r="L42" s="121"/>
+      <c r="M42" s="121"/>
+      <c r="N42" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O42" s="123"/>
+      <c r="P42" s="124"/>
+      <c r="Q42" s="125"/>
+      <c r="R42" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S42" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U42" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V42" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W42" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X42" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z42" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA42" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:27">
+      <c r="A43" s="117"/>
+      <c r="B43" s="119"/>
+      <c r="C43" s="118"/>
+      <c r="D43" s="119"/>
+      <c r="E43" s="120"/>
+      <c r="F43" s="120"/>
+      <c r="G43" s="120"/>
+      <c r="H43" s="120"/>
+      <c r="I43" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="121"/>
+      <c r="K43" s="121"/>
+      <c r="L43" s="121"/>
+      <c r="M43" s="121"/>
+      <c r="N43" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O43" s="123"/>
+      <c r="P43" s="124"/>
+      <c r="Q43" s="125"/>
+      <c r="R43" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U43" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V43" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W43" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X43" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z43" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA43" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:27">
+      <c r="A44" s="117"/>
+      <c r="B44" s="119"/>
+      <c r="C44" s="118"/>
+      <c r="D44" s="119"/>
+      <c r="E44" s="120"/>
+      <c r="F44" s="120"/>
+      <c r="G44" s="120"/>
+      <c r="H44" s="120"/>
+      <c r="I44" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J44" s="121"/>
+      <c r="K44" s="121"/>
+      <c r="L44" s="121"/>
+      <c r="M44" s="121"/>
+      <c r="N44" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O44" s="123"/>
+      <c r="P44" s="124"/>
+      <c r="Q44" s="125"/>
+      <c r="R44" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S44" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U44" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V44" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W44" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X44" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z44" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA44" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:27">
+      <c r="A45" s="117"/>
+      <c r="B45" s="119"/>
+      <c r="C45" s="118"/>
+      <c r="D45" s="119"/>
+      <c r="E45" s="120"/>
+      <c r="F45" s="120"/>
+      <c r="G45" s="120"/>
+      <c r="H45" s="120"/>
+      <c r="I45" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="121"/>
+      <c r="K45" s="121"/>
+      <c r="L45" s="121"/>
+      <c r="M45" s="121"/>
+      <c r="N45" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O45" s="123"/>
+      <c r="P45" s="124"/>
+      <c r="Q45" s="125"/>
+      <c r="R45" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U45" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V45" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W45" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X45" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z45" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA45" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:27">
+      <c r="A46" s="117"/>
+      <c r="B46" s="119"/>
+      <c r="C46" s="118"/>
+      <c r="D46" s="119"/>
+      <c r="E46" s="120"/>
+      <c r="F46" s="120"/>
+      <c r="G46" s="120"/>
+      <c r="H46" s="120"/>
+      <c r="I46" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="121"/>
+      <c r="K46" s="121"/>
+      <c r="L46" s="121"/>
+      <c r="M46" s="121"/>
+      <c r="N46" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O46" s="123"/>
+      <c r="P46" s="124"/>
+      <c r="Q46" s="125"/>
+      <c r="R46" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V46" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W46" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X46" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z46" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA46" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:27">
+      <c r="A47" s="117"/>
+      <c r="B47" s="119"/>
+      <c r="C47" s="118"/>
+      <c r="D47" s="119"/>
+      <c r="E47" s="120"/>
+      <c r="F47" s="120"/>
+      <c r="G47" s="120"/>
+      <c r="H47" s="120"/>
+      <c r="I47" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="121"/>
+      <c r="K47" s="121"/>
+      <c r="L47" s="121"/>
+      <c r="M47" s="121"/>
+      <c r="N47" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O47" s="123"/>
+      <c r="P47" s="124"/>
+      <c r="Q47" s="125"/>
+      <c r="R47" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U47" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W47" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X47" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z47" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA47" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:27">
+      <c r="A48" s="117"/>
+      <c r="B48" s="119"/>
+      <c r="C48" s="118"/>
+      <c r="D48" s="119"/>
+      <c r="E48" s="120"/>
+      <c r="F48" s="120"/>
+      <c r="G48" s="120"/>
+      <c r="H48" s="120"/>
+      <c r="I48" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J48" s="121"/>
+      <c r="K48" s="121"/>
+      <c r="L48" s="121"/>
+      <c r="M48" s="121"/>
+      <c r="N48" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O48" s="123"/>
+      <c r="P48" s="124"/>
+      <c r="Q48" s="125"/>
+      <c r="R48" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S48" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U48" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V48" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W48" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X48" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y48" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z48" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA48" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:27">
+      <c r="A49" s="117"/>
+      <c r="B49" s="119"/>
+      <c r="C49" s="118"/>
+      <c r="D49" s="119"/>
+      <c r="E49" s="120"/>
+      <c r="F49" s="120"/>
+      <c r="G49" s="120"/>
+      <c r="H49" s="120"/>
+      <c r="I49" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J49" s="121"/>
+      <c r="K49" s="121"/>
+      <c r="L49" s="121"/>
+      <c r="M49" s="121"/>
+      <c r="N49" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O49" s="123"/>
+      <c r="P49" s="124"/>
+      <c r="Q49" s="125"/>
+      <c r="R49" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T49" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W49" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X49" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z49" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA49" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:27">
+      <c r="A50" s="117"/>
+      <c r="B50" s="119"/>
+      <c r="C50" s="118"/>
+      <c r="D50" s="119"/>
+      <c r="E50" s="120"/>
+      <c r="F50" s="120"/>
+      <c r="G50" s="120"/>
+      <c r="H50" s="120"/>
+      <c r="I50" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="121"/>
+      <c r="K50" s="121"/>
+      <c r="L50" s="121"/>
+      <c r="M50" s="121"/>
+      <c r="N50" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O50" s="123"/>
+      <c r="P50" s="124"/>
+      <c r="Q50" s="125"/>
+      <c r="R50" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z50" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA50" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:27">
+      <c r="A51" s="117"/>
+      <c r="B51" s="119"/>
+      <c r="C51" s="118"/>
+      <c r="D51" s="119"/>
+      <c r="E51" s="120"/>
+      <c r="F51" s="120"/>
+      <c r="G51" s="120"/>
+      <c r="H51" s="120"/>
+      <c r="I51" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="121"/>
+      <c r="K51" s="121"/>
+      <c r="L51" s="121"/>
+      <c r="M51" s="121"/>
+      <c r="N51" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O51" s="123"/>
+      <c r="P51" s="124"/>
+      <c r="Q51" s="125"/>
+      <c r="R51" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z51" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA51" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:27">
+      <c r="A52" s="117"/>
+      <c r="B52" s="119"/>
+      <c r="C52" s="118"/>
+      <c r="D52" s="119"/>
+      <c r="E52" s="120"/>
+      <c r="F52" s="120"/>
+      <c r="G52" s="120"/>
+      <c r="H52" s="120"/>
+      <c r="I52" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J52" s="121"/>
+      <c r="K52" s="121"/>
+      <c r="L52" s="121"/>
+      <c r="M52" s="121"/>
+      <c r="N52" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O52" s="123"/>
+      <c r="P52" s="124"/>
+      <c r="Q52" s="125"/>
+      <c r="R52" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V52" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W52" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X52" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z52" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA52" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:27">
+      <c r="A53" s="117"/>
+      <c r="B53" s="119"/>
+      <c r="C53" s="118"/>
+      <c r="D53" s="119"/>
+      <c r="E53" s="120"/>
+      <c r="F53" s="120"/>
+      <c r="G53" s="120"/>
+      <c r="H53" s="120"/>
+      <c r="I53" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="121"/>
+      <c r="K53" s="121"/>
+      <c r="L53" s="121"/>
+      <c r="M53" s="121"/>
+      <c r="N53" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O53" s="123"/>
+      <c r="P53" s="124"/>
+      <c r="Q53" s="125"/>
+      <c r="R53" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V53" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W53" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X53" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y53" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z53" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA53" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:27">
+      <c r="A54" s="117"/>
+      <c r="B54" s="119"/>
+      <c r="C54" s="118"/>
+      <c r="D54" s="119"/>
+      <c r="E54" s="120"/>
+      <c r="F54" s="120"/>
+      <c r="G54" s="120"/>
+      <c r="H54" s="120"/>
+      <c r="I54" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="121"/>
+      <c r="K54" s="121"/>
+      <c r="L54" s="121"/>
+      <c r="M54" s="121"/>
+      <c r="N54" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O54" s="123"/>
+      <c r="P54" s="124"/>
+      <c r="Q54" s="125"/>
+      <c r="R54" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T54" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X54" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y54" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z54" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA54" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:27">
+      <c r="A55" s="117"/>
+      <c r="B55" s="119"/>
+      <c r="C55" s="118"/>
+      <c r="D55" s="119"/>
+      <c r="E55" s="120"/>
+      <c r="F55" s="120"/>
+      <c r="G55" s="120"/>
+      <c r="H55" s="120"/>
+      <c r="I55" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="121"/>
+      <c r="K55" s="121"/>
+      <c r="L55" s="121"/>
+      <c r="M55" s="121"/>
+      <c r="N55" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O55" s="123"/>
+      <c r="P55" s="124"/>
+      <c r="Q55" s="125"/>
+      <c r="R55" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U55" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V55" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W55" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X55" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y55" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z55" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA55" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:27">
+      <c r="A56" s="117"/>
+      <c r="B56" s="119"/>
+      <c r="C56" s="118"/>
+      <c r="D56" s="119"/>
+      <c r="E56" s="120"/>
+      <c r="F56" s="120"/>
+      <c r="G56" s="120"/>
+      <c r="H56" s="120"/>
+      <c r="I56" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="121"/>
+      <c r="K56" s="121"/>
+      <c r="L56" s="121"/>
+      <c r="M56" s="121"/>
+      <c r="N56" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O56" s="123"/>
+      <c r="P56" s="124"/>
+      <c r="Q56" s="125"/>
+      <c r="R56" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="126">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U56" s="126">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V56" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W56" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X56" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y56" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z56" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA56" s="128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:27">
+      <c r="A57" s="117"/>
+      <c r="B57" s="119"/>
+      <c r="C57" s="118"/>
+      <c r="D57" s="119"/>
+      <c r="E57" s="120"/>
+      <c r="F57" s="120"/>
+      <c r="G57" s="120"/>
+      <c r="H57" s="120"/>
+      <c r="I57" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="121"/>
+      <c r="K57" s="121"/>
+      <c r="L57" s="121"/>
+      <c r="M57" s="121"/>
+      <c r="N57" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O57" s="123"/>
+      <c r="P57" s="124"/>
+      <c r="Q57" s="125"/>
+      <c r="R57" s="126"/>
+      <c r="S57" s="126"/>
+      <c r="T57" s="126"/>
+      <c r="U57" s="126"/>
+      <c r="V57" s="126"/>
+      <c r="W57" s="127"/>
+      <c r="X57" s="128"/>
+      <c r="Y57" s="128"/>
+      <c r="Z57" s="128"/>
+      <c r="AA57" s="128"/>
+    </row>
+    <row r="58" spans="1:27">
+      <c r="A58" s="117"/>
+      <c r="B58" s="119"/>
+      <c r="C58" s="118"/>
+      <c r="D58" s="119"/>
+      <c r="E58" s="120"/>
+      <c r="F58" s="120"/>
+      <c r="G58" s="120"/>
+      <c r="H58" s="120"/>
+      <c r="I58" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="121"/>
+      <c r="K58" s="121"/>
+      <c r="L58" s="121"/>
+      <c r="M58" s="121"/>
+      <c r="N58" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="123"/>
+      <c r="P58" s="124"/>
+      <c r="Q58" s="125"/>
+      <c r="R58" s="126"/>
+      <c r="S58" s="126"/>
+      <c r="T58" s="126"/>
+      <c r="U58" s="126"/>
+      <c r="V58" s="126"/>
+      <c r="W58" s="127"/>
+      <c r="X58" s="128"/>
+      <c r="Y58" s="128"/>
+      <c r="Z58" s="128"/>
+      <c r="AA58" s="128"/>
+    </row>
+    <row r="59" spans="1:27">
+      <c r="A59" s="117"/>
+      <c r="B59" s="119"/>
+      <c r="C59" s="118"/>
+      <c r="D59" s="119"/>
+      <c r="E59" s="120"/>
+      <c r="F59" s="120"/>
+      <c r="G59" s="120"/>
+      <c r="H59" s="120"/>
+      <c r="I59" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="121"/>
+      <c r="K59" s="121"/>
+      <c r="L59" s="121"/>
+      <c r="M59" s="121"/>
+      <c r="N59" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O59" s="123"/>
+      <c r="P59" s="124"/>
+      <c r="Q59" s="125"/>
+      <c r="R59" s="126"/>
+      <c r="S59" s="126"/>
+      <c r="T59" s="126"/>
+      <c r="U59" s="126"/>
+      <c r="V59" s="126"/>
+      <c r="W59" s="127"/>
+      <c r="X59" s="128"/>
+      <c r="Y59" s="128"/>
+      <c r="Z59" s="128"/>
+      <c r="AA59" s="128"/>
+    </row>
+    <row r="60" spans="1:27">
+      <c r="A60" s="117"/>
+      <c r="B60" s="119"/>
+      <c r="C60" s="118"/>
+      <c r="D60" s="119"/>
+      <c r="E60" s="120"/>
+      <c r="F60" s="120"/>
+      <c r="G60" s="120"/>
+      <c r="H60" s="120"/>
+      <c r="I60" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J60" s="121"/>
+      <c r="K60" s="121"/>
+      <c r="L60" s="121"/>
+      <c r="M60" s="121"/>
+      <c r="N60" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O60" s="123"/>
+      <c r="P60" s="124"/>
+      <c r="Q60" s="125"/>
+      <c r="R60" s="126"/>
+      <c r="S60" s="126"/>
+      <c r="T60" s="126"/>
+      <c r="U60" s="126"/>
+      <c r="V60" s="126"/>
+      <c r="W60" s="127"/>
+      <c r="X60" s="128"/>
+      <c r="Y60" s="128"/>
+      <c r="Z60" s="128"/>
+      <c r="AA60" s="128"/>
+    </row>
+    <row r="61" spans="1:27">
+      <c r="A61" s="117"/>
+      <c r="B61" s="119"/>
+      <c r="C61" s="118"/>
+      <c r="D61" s="119"/>
+      <c r="E61" s="120"/>
+      <c r="F61" s="120"/>
+      <c r="G61" s="120"/>
+      <c r="H61" s="120"/>
+      <c r="I61" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J61" s="121"/>
+      <c r="K61" s="121"/>
+      <c r="L61" s="121"/>
+      <c r="M61" s="121"/>
+      <c r="N61" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O61" s="123"/>
+      <c r="P61" s="124"/>
+      <c r="Q61" s="125"/>
+      <c r="R61" s="126"/>
+      <c r="S61" s="126"/>
+      <c r="T61" s="126"/>
+      <c r="U61" s="126"/>
+      <c r="V61" s="126"/>
+      <c r="W61" s="127"/>
+      <c r="X61" s="128"/>
+      <c r="Y61" s="128"/>
+      <c r="Z61" s="128"/>
+      <c r="AA61" s="128"/>
+    </row>
+    <row r="62" spans="1:27">
+      <c r="A62" s="117"/>
+      <c r="B62" s="119"/>
+      <c r="C62" s="118"/>
+      <c r="D62" s="119"/>
+      <c r="E62" s="120"/>
+      <c r="F62" s="120"/>
+      <c r="G62" s="120"/>
+      <c r="H62" s="120"/>
+      <c r="I62" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J62" s="121"/>
+      <c r="K62" s="121"/>
+      <c r="L62" s="121"/>
+      <c r="M62" s="121"/>
+      <c r="N62" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O62" s="123"/>
+      <c r="P62" s="124"/>
+      <c r="Q62" s="125"/>
+      <c r="R62" s="126"/>
+      <c r="S62" s="126"/>
+      <c r="T62" s="126"/>
+      <c r="U62" s="126"/>
+      <c r="V62" s="126"/>
+      <c r="W62" s="127"/>
+      <c r="X62" s="128"/>
+      <c r="Y62" s="128"/>
+      <c r="Z62" s="128"/>
+      <c r="AA62" s="128"/>
+    </row>
+    <row r="63" spans="1:27">
+      <c r="A63" s="117"/>
+      <c r="B63" s="119"/>
+      <c r="C63" s="118"/>
+      <c r="D63" s="119"/>
+      <c r="E63" s="120"/>
+      <c r="F63" s="120"/>
+      <c r="G63" s="120"/>
+      <c r="H63" s="120"/>
+      <c r="I63" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J63" s="121"/>
+      <c r="K63" s="121"/>
+      <c r="L63" s="121"/>
+      <c r="M63" s="121"/>
+      <c r="N63" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O63" s="123"/>
+      <c r="P63" s="124"/>
+      <c r="Q63" s="125"/>
+      <c r="R63" s="126"/>
+      <c r="S63" s="126"/>
+      <c r="T63" s="126"/>
+      <c r="U63" s="126"/>
+      <c r="V63" s="126"/>
+      <c r="W63" s="127"/>
+      <c r="X63" s="128"/>
+      <c r="Y63" s="128"/>
+      <c r="Z63" s="128"/>
+      <c r="AA63" s="128"/>
+    </row>
+    <row r="64" spans="1:27">
+      <c r="A64" s="117"/>
+      <c r="B64" s="119"/>
+      <c r="C64" s="118"/>
+      <c r="D64" s="119"/>
+      <c r="E64" s="120"/>
+      <c r="F64" s="120"/>
+      <c r="G64" s="120"/>
+      <c r="H64" s="120"/>
+      <c r="I64" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J64" s="121"/>
+      <c r="K64" s="121"/>
+      <c r="L64" s="121"/>
+      <c r="M64" s="121"/>
+      <c r="N64" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O64" s="123"/>
+      <c r="P64" s="124"/>
+      <c r="Q64" s="125"/>
+      <c r="R64" s="126"/>
+      <c r="S64" s="126"/>
+      <c r="T64" s="126"/>
+      <c r="U64" s="126"/>
+      <c r="V64" s="126"/>
+      <c r="W64" s="127"/>
+      <c r="X64" s="128"/>
+      <c r="Y64" s="128"/>
+      <c r="Z64" s="128"/>
+      <c r="AA64" s="128"/>
+    </row>
+    <row r="65" spans="1:27">
+      <c r="A65" s="117"/>
+      <c r="B65" s="119"/>
+      <c r="C65" s="118"/>
+      <c r="D65" s="119"/>
+      <c r="E65" s="120"/>
+      <c r="F65" s="120"/>
+      <c r="G65" s="120"/>
+      <c r="H65" s="120"/>
+      <c r="I65" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J65" s="121"/>
+      <c r="K65" s="121"/>
+      <c r="L65" s="121"/>
+      <c r="M65" s="121"/>
+      <c r="N65" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O65" s="123"/>
+      <c r="P65" s="124"/>
+      <c r="Q65" s="125"/>
+      <c r="R65" s="126"/>
+      <c r="S65" s="126"/>
+      <c r="T65" s="126"/>
+      <c r="U65" s="126"/>
+      <c r="V65" s="126"/>
+      <c r="W65" s="127"/>
+      <c r="X65" s="128"/>
+      <c r="Y65" s="128"/>
+      <c r="Z65" s="128"/>
+      <c r="AA65" s="128"/>
+    </row>
+    <row r="66" spans="1:27">
+      <c r="A66" s="117"/>
+      <c r="B66" s="119"/>
+      <c r="C66" s="118"/>
+      <c r="D66" s="119"/>
+      <c r="E66" s="120"/>
+      <c r="F66" s="120"/>
+      <c r="G66" s="120"/>
+      <c r="H66" s="120"/>
+      <c r="I66" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J66" s="121"/>
+      <c r="K66" s="121"/>
+      <c r="L66" s="121"/>
+      <c r="M66" s="121"/>
+      <c r="N66" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O66" s="123"/>
+      <c r="P66" s="124"/>
+      <c r="Q66" s="125"/>
+      <c r="R66" s="126"/>
+      <c r="S66" s="126"/>
+      <c r="T66" s="126"/>
+      <c r="U66" s="126"/>
+      <c r="V66" s="126"/>
+      <c r="W66" s="127"/>
+      <c r="X66" s="128"/>
+      <c r="Y66" s="128"/>
+      <c r="Z66" s="128"/>
+      <c r="AA66" s="128"/>
+    </row>
+    <row r="67" spans="1:27">
+      <c r="A67" s="117"/>
+      <c r="B67" s="119"/>
+      <c r="C67" s="118"/>
+      <c r="D67" s="119"/>
+      <c r="E67" s="120"/>
+      <c r="F67" s="120"/>
+      <c r="G67" s="120"/>
+      <c r="H67" s="120"/>
+      <c r="I67" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J67" s="121"/>
+      <c r="K67" s="121"/>
+      <c r="L67" s="121"/>
+      <c r="M67" s="121"/>
+      <c r="N67" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O67" s="123"/>
+      <c r="P67" s="124"/>
+      <c r="Q67" s="125"/>
+      <c r="R67" s="126"/>
+      <c r="S67" s="126"/>
+      <c r="T67" s="126"/>
+      <c r="U67" s="126"/>
+      <c r="V67" s="126"/>
+      <c r="W67" s="127"/>
+      <c r="X67" s="128"/>
+      <c r="Y67" s="128"/>
+      <c r="Z67" s="128"/>
+      <c r="AA67" s="128"/>
+    </row>
+    <row r="68" spans="1:27">
+      <c r="A68" s="117"/>
+      <c r="B68" s="119"/>
+      <c r="C68" s="118"/>
+      <c r="D68" s="119"/>
+      <c r="E68" s="120"/>
+      <c r="F68" s="120"/>
+      <c r="G68" s="120"/>
+      <c r="H68" s="120"/>
+      <c r="I68" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J68" s="121"/>
+      <c r="K68" s="121"/>
+      <c r="L68" s="121"/>
+      <c r="M68" s="121"/>
+      <c r="N68" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O68" s="123"/>
+      <c r="P68" s="124"/>
+      <c r="Q68" s="125"/>
+      <c r="R68" s="126"/>
+      <c r="S68" s="126"/>
+      <c r="T68" s="126"/>
+      <c r="U68" s="126"/>
+      <c r="V68" s="126"/>
+      <c r="W68" s="127"/>
+      <c r="X68" s="128"/>
+      <c r="Y68" s="128"/>
+      <c r="Z68" s="128"/>
+      <c r="AA68" s="128"/>
+    </row>
+    <row r="69" spans="1:27">
+      <c r="A69" s="117"/>
+      <c r="B69" s="119"/>
+      <c r="C69" s="118"/>
+      <c r="D69" s="119"/>
+      <c r="E69" s="120"/>
+      <c r="F69" s="120"/>
+      <c r="G69" s="120"/>
+      <c r="H69" s="120"/>
+      <c r="I69" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J69" s="121"/>
+      <c r="K69" s="121"/>
+      <c r="L69" s="121"/>
+      <c r="M69" s="121"/>
+      <c r="N69" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O69" s="123"/>
+      <c r="P69" s="124"/>
+      <c r="Q69" s="125"/>
+      <c r="R69" s="126"/>
+      <c r="S69" s="126"/>
+      <c r="T69" s="126"/>
+      <c r="U69" s="126"/>
+      <c r="V69" s="126"/>
+      <c r="W69" s="127"/>
+      <c r="X69" s="128"/>
+      <c r="Y69" s="128"/>
+      <c r="Z69" s="128"/>
+      <c r="AA69" s="128"/>
+    </row>
+    <row r="70" spans="1:27">
+      <c r="A70" s="117"/>
+      <c r="B70" s="119"/>
+      <c r="C70" s="118"/>
+      <c r="D70" s="119"/>
+      <c r="E70" s="120"/>
+      <c r="F70" s="120"/>
+      <c r="G70" s="120"/>
+      <c r="H70" s="120"/>
+      <c r="I70" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J70" s="121"/>
+      <c r="K70" s="121"/>
+      <c r="L70" s="121"/>
+      <c r="M70" s="121"/>
+      <c r="N70" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O70" s="123"/>
+      <c r="P70" s="124"/>
+      <c r="Q70" s="125"/>
+      <c r="R70" s="126"/>
+      <c r="S70" s="126"/>
+      <c r="T70" s="126"/>
+      <c r="U70" s="126"/>
+      <c r="V70" s="126"/>
+      <c r="W70" s="127"/>
+      <c r="X70" s="128"/>
+      <c r="Y70" s="128"/>
+      <c r="Z70" s="128"/>
+      <c r="AA70" s="128"/>
+    </row>
+    <row r="71" spans="1:27">
+      <c r="A71" s="117"/>
+      <c r="B71" s="119"/>
+      <c r="C71" s="118"/>
+      <c r="D71" s="119"/>
+      <c r="E71" s="120"/>
+      <c r="F71" s="120"/>
+      <c r="G71" s="120"/>
+      <c r="H71" s="120"/>
+      <c r="I71" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J71" s="121"/>
+      <c r="K71" s="121"/>
+      <c r="L71" s="121"/>
+      <c r="M71" s="121"/>
+      <c r="N71" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O71" s="123"/>
+      <c r="P71" s="124"/>
+      <c r="Q71" s="125"/>
+      <c r="R71" s="126"/>
+      <c r="S71" s="126"/>
+      <c r="T71" s="126"/>
+      <c r="U71" s="126"/>
+      <c r="V71" s="126"/>
+      <c r="W71" s="127"/>
+      <c r="X71" s="128"/>
+      <c r="Y71" s="128"/>
+      <c r="Z71" s="128"/>
+      <c r="AA71" s="128"/>
+    </row>
+    <row r="72" spans="1:27">
+      <c r="A72" s="117"/>
+      <c r="B72" s="119"/>
+      <c r="C72" s="118"/>
+      <c r="D72" s="119"/>
+      <c r="E72" s="120"/>
+      <c r="F72" s="120"/>
+      <c r="G72" s="120"/>
+      <c r="H72" s="120"/>
+      <c r="I72" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J72" s="121"/>
+      <c r="K72" s="121"/>
+      <c r="L72" s="121"/>
+      <c r="M72" s="121"/>
+      <c r="N72" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O72" s="123"/>
+      <c r="P72" s="124"/>
+      <c r="Q72" s="125"/>
+      <c r="R72" s="126"/>
+      <c r="S72" s="126"/>
+      <c r="T72" s="126"/>
+      <c r="U72" s="126"/>
+      <c r="V72" s="126"/>
+      <c r="W72" s="127"/>
+      <c r="X72" s="128"/>
+      <c r="Y72" s="128"/>
+      <c r="Z72" s="128"/>
+      <c r="AA72" s="128"/>
+    </row>
+    <row r="73" spans="1:27">
+      <c r="A73" s="117"/>
+      <c r="B73" s="119"/>
+      <c r="C73" s="118"/>
+      <c r="D73" s="119"/>
+      <c r="E73" s="120"/>
+      <c r="F73" s="120"/>
+      <c r="G73" s="120"/>
+      <c r="H73" s="120"/>
+      <c r="I73" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J73" s="121"/>
+      <c r="K73" s="121"/>
+      <c r="L73" s="121"/>
+      <c r="M73" s="121"/>
+      <c r="N73" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O73" s="123"/>
+      <c r="P73" s="124"/>
+      <c r="Q73" s="125"/>
+      <c r="R73" s="126"/>
+      <c r="S73" s="126"/>
+      <c r="T73" s="126"/>
+      <c r="U73" s="126"/>
+      <c r="V73" s="126"/>
+      <c r="W73" s="127"/>
+      <c r="X73" s="128"/>
+      <c r="Y73" s="128"/>
+      <c r="Z73" s="128"/>
+      <c r="AA73" s="128"/>
+    </row>
+    <row r="74" spans="1:27">
+      <c r="A74" s="117"/>
+      <c r="B74" s="119"/>
+      <c r="C74" s="118"/>
+      <c r="D74" s="119"/>
+      <c r="E74" s="120"/>
+      <c r="F74" s="120"/>
+      <c r="G74" s="120"/>
+      <c r="H74" s="120"/>
+      <c r="I74" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J74" s="121"/>
+      <c r="K74" s="121"/>
+      <c r="L74" s="121"/>
+      <c r="M74" s="121"/>
+      <c r="N74" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O74" s="123"/>
+      <c r="P74" s="124"/>
+      <c r="Q74" s="125"/>
+      <c r="R74" s="126"/>
+      <c r="S74" s="126"/>
+      <c r="T74" s="126"/>
+      <c r="U74" s="126"/>
+      <c r="V74" s="126"/>
+      <c r="W74" s="127"/>
+      <c r="X74" s="128"/>
+      <c r="Y74" s="128"/>
+      <c r="Z74" s="128"/>
+      <c r="AA74" s="128"/>
+    </row>
+    <row r="75" spans="1:27">
+      <c r="A75" s="117"/>
+      <c r="B75" s="119"/>
+      <c r="C75" s="118"/>
+      <c r="D75" s="119"/>
+      <c r="E75" s="120"/>
+      <c r="F75" s="120"/>
+      <c r="G75" s="120"/>
+      <c r="H75" s="120"/>
+      <c r="I75" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J75" s="121"/>
+      <c r="K75" s="121"/>
+      <c r="L75" s="121"/>
+      <c r="M75" s="121"/>
+      <c r="N75" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O75" s="123"/>
+      <c r="P75" s="124"/>
+      <c r="Q75" s="125"/>
+      <c r="R75" s="126"/>
+      <c r="S75" s="126"/>
+      <c r="T75" s="126"/>
+      <c r="U75" s="126"/>
+      <c r="V75" s="126"/>
+      <c r="W75" s="127"/>
+      <c r="X75" s="128"/>
+      <c r="Y75" s="128"/>
+      <c r="Z75" s="128"/>
+      <c r="AA75" s="128"/>
+    </row>
+    <row r="76" spans="1:27">
+      <c r="A76" s="117"/>
+      <c r="B76" s="119"/>
+      <c r="C76" s="118"/>
+      <c r="D76" s="119"/>
+      <c r="E76" s="120"/>
+      <c r="F76" s="120"/>
+      <c r="G76" s="120"/>
+      <c r="H76" s="120"/>
+      <c r="I76" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J76" s="121"/>
+      <c r="K76" s="121"/>
+      <c r="L76" s="121"/>
+      <c r="M76" s="121"/>
+      <c r="N76" s="121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O76" s="123"/>
+      <c r="P76" s="124"/>
+      <c r="Q76" s="125"/>
+      <c r="R76" s="126"/>
+      <c r="S76" s="126"/>
+      <c r="T76" s="126"/>
+      <c r="U76" s="126"/>
+      <c r="V76" s="126"/>
+      <c r="W76" s="127"/>
+      <c r="X76" s="128"/>
+      <c r="Y76" s="128"/>
+      <c r="Z76" s="128"/>
+      <c r="AA76" s="128"/>
+    </row>
+    <row r="77" spans="1:27">
+      <c r="A77" s="117"/>
+      <c r="B77" s="119"/>
+      <c r="C77" s="118"/>
+      <c r="D77" s="119"/>
+      <c r="E77" s="120"/>
+      <c r="F77" s="120"/>
+      <c r="G77" s="120"/>
+      <c r="H77" s="120"/>
+      <c r="I77" s="120">
+        <f t="shared" ref="I77:I82" si="10">((F77+G77+H77)*16)/48</f>
+        <v>0</v>
+      </c>
+      <c r="J77" s="121"/>
+      <c r="K77" s="121"/>
+      <c r="L77" s="121"/>
+      <c r="M77" s="121"/>
+      <c r="N77" s="121">
+        <f t="shared" ref="N77:N82" si="11">((K77+L77+M77)*16)/48</f>
+        <v>0</v>
+      </c>
+      <c r="O77" s="123"/>
+      <c r="P77" s="124"/>
+      <c r="Q77" s="125"/>
+      <c r="R77" s="126"/>
+      <c r="S77" s="126"/>
+      <c r="T77" s="126"/>
+      <c r="U77" s="126"/>
+      <c r="V77" s="126"/>
+      <c r="W77" s="127"/>
+      <c r="X77" s="128"/>
+      <c r="Y77" s="128"/>
+      <c r="Z77" s="128"/>
+      <c r="AA77" s="128"/>
+    </row>
+    <row r="78" spans="1:27">
+      <c r="A78" s="117"/>
+      <c r="B78" s="119"/>
+      <c r="C78" s="118"/>
+      <c r="D78" s="119"/>
+      <c r="E78" s="120"/>
+      <c r="F78" s="120"/>
+      <c r="G78" s="120"/>
+      <c r="H78" s="120"/>
+      <c r="I78" s="120">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J78" s="121"/>
+      <c r="K78" s="121"/>
+      <c r="L78" s="121"/>
+      <c r="M78" s="121"/>
+      <c r="N78" s="121">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="O78" s="123"/>
+      <c r="P78" s="124"/>
+      <c r="Q78" s="125"/>
+      <c r="R78" s="126"/>
+      <c r="S78" s="126"/>
+      <c r="T78" s="126"/>
+      <c r="U78" s="126"/>
+      <c r="V78" s="126"/>
+      <c r="W78" s="127"/>
+      <c r="X78" s="128"/>
+      <c r="Y78" s="128"/>
+      <c r="Z78" s="128"/>
+      <c r="AA78" s="128"/>
+    </row>
+    <row r="79" spans="1:27">
+      <c r="A79" s="117"/>
+      <c r="B79" s="119"/>
+      <c r="C79" s="118"/>
+      <c r="D79" s="119"/>
+      <c r="E79" s="120"/>
+      <c r="F79" s="120"/>
+      <c r="G79" s="120"/>
+      <c r="H79" s="120"/>
+      <c r="I79" s="120">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J79" s="121"/>
+      <c r="K79" s="121"/>
+      <c r="L79" s="121"/>
+      <c r="M79" s="121"/>
+      <c r="N79" s="121">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="O79" s="123"/>
+      <c r="P79" s="124"/>
+      <c r="Q79" s="125"/>
+      <c r="R79" s="126"/>
+      <c r="S79" s="126"/>
+      <c r="T79" s="126"/>
+      <c r="U79" s="126"/>
+      <c r="V79" s="126"/>
+      <c r="W79" s="127"/>
+      <c r="X79" s="128"/>
+      <c r="Y79" s="128"/>
+      <c r="Z79" s="128"/>
+      <c r="AA79" s="128"/>
+    </row>
+    <row r="80" spans="1:27">
+      <c r="A80" s="117"/>
+      <c r="B80" s="119"/>
+      <c r="C80" s="118"/>
+      <c r="D80" s="119"/>
+      <c r="E80" s="120"/>
+      <c r="F80" s="120"/>
+      <c r="G80" s="120"/>
+      <c r="H80" s="120"/>
+      <c r="I80" s="120">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J80" s="121"/>
+      <c r="K80" s="121"/>
+      <c r="L80" s="121"/>
+      <c r="M80" s="121"/>
+      <c r="N80" s="121">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="O80" s="123"/>
+      <c r="P80" s="124"/>
+      <c r="Q80" s="125"/>
+      <c r="R80" s="126"/>
+      <c r="S80" s="126"/>
+      <c r="T80" s="126"/>
+      <c r="U80" s="126"/>
+      <c r="V80" s="126"/>
+      <c r="W80" s="127"/>
+      <c r="X80" s="128"/>
+      <c r="Y80" s="128"/>
+      <c r="Z80" s="128"/>
+      <c r="AA80" s="128"/>
+    </row>
+    <row r="81" spans="1:27">
+      <c r="A81" s="117"/>
+      <c r="B81" s="119"/>
+      <c r="C81" s="118"/>
+      <c r="D81" s="119"/>
+      <c r="E81" s="120"/>
+      <c r="F81" s="120"/>
+      <c r="G81" s="120"/>
+      <c r="H81" s="120"/>
+      <c r="I81" s="120">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J81" s="121"/>
+      <c r="K81" s="121"/>
+      <c r="L81" s="121"/>
+      <c r="M81" s="121"/>
+      <c r="N81" s="121">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="O81" s="123"/>
+      <c r="P81" s="124"/>
+      <c r="Q81" s="125"/>
+      <c r="R81" s="126"/>
+      <c r="S81" s="126"/>
+      <c r="T81" s="126"/>
+      <c r="U81" s="126"/>
+      <c r="V81" s="126"/>
+      <c r="W81" s="127"/>
+      <c r="X81" s="128"/>
+      <c r="Y81" s="128"/>
+      <c r="Z81" s="128"/>
+      <c r="AA81" s="128"/>
+    </row>
+    <row r="82" spans="1:27">
+      <c r="A82" s="117"/>
+      <c r="B82" s="119"/>
+      <c r="C82" s="118"/>
+      <c r="D82" s="119"/>
+      <c r="E82" s="120"/>
+      <c r="F82" s="120"/>
+      <c r="G82" s="120"/>
+      <c r="H82" s="120"/>
+      <c r="I82" s="120">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J82" s="121"/>
+      <c r="K82" s="121"/>
+      <c r="L82" s="121"/>
+      <c r="M82" s="121"/>
+      <c r="N82" s="121">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="O82" s="129"/>
+      <c r="P82" s="124"/>
+      <c r="Q82" s="125"/>
+      <c r="R82" s="126"/>
+      <c r="S82" s="126"/>
+      <c r="T82" s="126"/>
+      <c r="U82" s="126"/>
+      <c r="V82" s="126"/>
+      <c r="W82" s="127"/>
+      <c r="X82" s="128"/>
+      <c r="Y82" s="128"/>
+      <c r="Z82" s="128"/>
+      <c r="AA82" s="128"/>
+    </row>
+    <row r="83" spans="1:27">
+      <c r="F83" s="130">
+        <f>SUM(F13:F82)</f>
+        <v>0</v>
+      </c>
+      <c r="G83" s="131">
+        <f>SUM(G13:G82)</f>
+        <v>0</v>
+      </c>
+      <c r="H83" s="131">
+        <f>SUM(H13:H82)</f>
+        <v>0</v>
+      </c>
+      <c r="I83" s="131">
+        <f>SUM(I13:I82)</f>
+        <v>0</v>
+      </c>
+      <c r="K83" s="131">
+        <f>SUM(K13:K82)</f>
+        <v>0</v>
+      </c>
+      <c r="L83" s="131">
+        <f>SUM(L13:L82)</f>
+        <v>0</v>
+      </c>
+      <c r="M83" s="131">
+        <f>SUM(M13:M82)</f>
+        <v>0</v>
+      </c>
+      <c r="N83" s="131">
+        <f>SUM(N13:N82)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:27" ht="30">
+      <c r="F84" s="132" t="s">
+        <v>102</v>
+      </c>
+      <c r="G84" s="132" t="s">
+        <v>103</v>
+      </c>
+      <c r="H84" s="132" t="s">
+        <v>104</v>
+      </c>
+      <c r="I84" s="132" t="s">
+        <v>105</v>
+      </c>
+      <c r="K84" s="132" t="s">
+        <v>102</v>
+      </c>
+      <c r="L84" s="132" t="s">
+        <v>103</v>
+      </c>
+      <c r="M84" s="132" t="s">
+        <v>104</v>
+      </c>
+      <c r="N84" s="132" t="s">
+        <v>105</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="B8:M8"/>
+    <mergeCell ref="B9:M9"/>
+    <mergeCell ref="E11:I11"/>
+    <mergeCell ref="J11:N11"/>
+    <mergeCell ref="R11:V11"/>
+    <mergeCell ref="W11:AA11"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B4:M4"/>
+    <mergeCell ref="B5:M5"/>
+    <mergeCell ref="B6:M6"/>
+    <mergeCell ref="B7:M7"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A13:A82" xr:uid="{ECFB1832-D01E-4CFF-93C9-42B237314F37}">
+      <formula1>"Se mantiene, Nueva materia, Eliminación de materia, Cambio de nivel en la malla, Cambio de componentes de aprendizaje, Cambio de componente de aprendizaje y de nivel de malla"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101000D056AFC88326C4799448B54C880494B" ma:contentTypeVersion="0" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="4e1e4b56ebf0b63f67924dd21a513bd2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="26ff3a126252e742cc2543983a566b0e">
     <xsd:element name="properties">
@@ -6722,16 +11368,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C29C807D-6D16-46D1-BB9C-632513C228B6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0D9287C-CE41-4A48-B358-97A71E5FD6DC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6745,12 +11390,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C29C807D-6D16-46D1-BB9C-632513C228B6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>